--- a/output/multi_factor_reports/factor_collinearity_report_P10.xlsx
+++ b/output/multi_factor_reports/factor_collinearity_report_P10.xlsx
@@ -520,8 +520,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5169902208698246"/>
-          <min val="-0.454611801609983"/>
+          <max val="0.5274111771127306"/>
+          <min val="-0.4597078449374216"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -928,8 +928,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6.577557327004162"/>
-          <min val="-7.107069120458897"/>
+          <max val="6.525375276450917"/>
+          <min val="-7.275289174167862"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1355,16 +1355,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.327714</v>
+        <v>0.32826</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-0.000685</v>
+        <v>0.016973</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.36066</v>
+        <v>0.368027</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.389196</v>
+        <v>0.388507</v>
       </c>
     </row>
     <row r="4">
@@ -1374,19 +1374,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.327714</v>
+        <v>0.32826</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.030073</v>
+        <v>-0.009745999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.1174</v>
+        <v>0.117792</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.39782</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="5">
@@ -1396,19 +1396,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-0.000685</v>
+        <v>0.016973</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>-0.030073</v>
+        <v>-0.009745999999999999</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.006225</v>
+        <v>0.017421</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.008283</v>
+        <v>0.034874</v>
       </c>
     </row>
     <row r="6">
@@ -1418,19 +1418,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.36066</v>
+        <v>0.368027</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1174</v>
+        <v>0.117792</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.006225</v>
+        <v>0.017421</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.023811</v>
+        <v>0.02707</v>
       </c>
     </row>
     <row r="7">
@@ -1440,16 +1440,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.389196</v>
+        <v>0.388507</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.39782</v>
+        <v>0.394</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.008283</v>
+        <v>0.034874</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.023811</v>
+        <v>0.02707</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
@@ -1499,16 +1499,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.039405</v>
+        <v>-0.040721</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.005861</v>
+        <v>0.005703</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.08526599999999999</v>
+        <v>0.08611099999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.177805</v>
+        <v>0.178172</v>
       </c>
     </row>
     <row r="13">
@@ -1518,19 +1518,19 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>-0.039405</v>
+        <v>-0.040721</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.05457</v>
+        <v>-0.052286</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.08164299999999999</v>
+        <v>-0.083092</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.074918</v>
+        <v>0.069317</v>
       </c>
     </row>
     <row r="14">
@@ -1540,19 +1540,19 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.005861</v>
+        <v>0.005703</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.05457</v>
+        <v>-0.052286</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.06443400000000001</v>
+        <v>0.062001</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.01329</v>
+        <v>-0.013144</v>
       </c>
     </row>
     <row r="15">
@@ -1562,19 +1562,19 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.08526599999999999</v>
+        <v>0.08611099999999999</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.08164299999999999</v>
+        <v>-0.083092</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.06443400000000001</v>
+        <v>0.062001</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.080568</v>
+        <v>0.080544</v>
       </c>
     </row>
     <row r="16">
@@ -1584,16 +1584,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.177805</v>
+        <v>0.178172</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.074918</v>
+        <v>0.069317</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.01329</v>
+        <v>-0.013144</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.080568</v>
+        <v>0.080544</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>1</v>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.0002018531209727497</v>
+        <v>-0.002368322385558906</v>
       </c>
     </row>
     <row r="4">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.009818087918120399</v>
+        <v>-0.05530389024218322</v>
       </c>
     </row>
     <row r="5">
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.04561504595866447</v>
+        <v>-0.04608735379818363</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09534625892455931</v>
+        <v>-0.09667364890456623</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3439857737374094</v>
+        <v>-0.3449569378157145</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1655714950212809</v>
+        <v>-0.1631058934897514</v>
       </c>
       <c r="I5" t="n">
-        <v>0.336195013872797</v>
+        <v>0.3337119062359572</v>
       </c>
     </row>
     <row r="6">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.0354098577332833</v>
+        <v>-0.03576168592263949</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.09534625892455931</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1849405606491815</v>
+        <v>-0.1857553784545526</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.00459519800394988</v>
+        <v>-0.01080905825351657</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08830054905635452</v>
+        <v>0.08536655898367068</v>
       </c>
     </row>
     <row r="7">
@@ -1860,19 +1860,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.04421235698634565</v>
+        <v>-0.04466732126975047</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09534625892455931</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1652210717517121</v>
+        <v>-0.1613314482298978</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.06134577137082112</v>
+        <v>-0.0603163293782013</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07676616113485611</v>
+        <v>0.07295405746286956</v>
       </c>
     </row>
     <row r="8">
@@ -1882,19 +1882,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09848078939079276</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.09534625892455929</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1334363009608081</v>
+        <v>-0.1400507713852512</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07494906137910234</v>
+        <v>0.06849500995685898</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06430976430976437</v>
+        <v>0.05556508399324763</v>
       </c>
     </row>
     <row r="9">
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.09534625892455932</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09534625892455931</v>
+        <v>-0.09667364890456623</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1496365054086467</v>
+        <v>-0.1522884784804273</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.03447723219435703</v>
+        <v>-0.03708949863663292</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06430976430976441</v>
+        <v>-0.03703703703703694</v>
       </c>
     </row>
     <row r="10">
@@ -1926,19 +1926,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09534625892455929</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.04707526333175405</v>
+        <v>-0.04706890484094069</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.004106283187058506</v>
+        <v>-0.01123848817392102</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1558922558922561</v>
+        <v>-0.1851851851851846</v>
       </c>
     </row>
     <row r="11">
@@ -1948,22 +1948,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.08296391418673557</v>
+        <v>-0.08293945999691466</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.006278039126360486</v>
+        <v>-0.007642946226594015</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.006278039126360515</v>
+        <v>-0.005090921208157421</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1509720401098653</v>
+        <v>0.1298776533433356</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02121753343840899</v>
+        <v>0.01931200068674832</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1909581646423752</v>
+        <v>0.1649768610401621</v>
       </c>
     </row>
     <row r="12">
@@ -1973,19 +1973,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.09534625892455929</v>
+        <v>0.09667364890456623</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09361211200067832</v>
+        <v>-0.09489966977658215</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.21422507869065</v>
+        <v>-0.2148798917762172</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2242156136250874</v>
+        <v>-0.240217530929801</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4499831848367344</v>
+        <v>0.4259989772815654</v>
       </c>
     </row>
     <row r="13">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1077126938390158</v>
+        <v>-0.1079590277276307</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00125433889334079</v>
+        <v>0.00254415042438965</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.02951309486374437</v>
+        <v>-0.03130737810082721</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07048802346969556</v>
+        <v>-0.08057287901822122</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2048319228664506</v>
+        <v>-0.1985300373943934</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1615431036422487</v>
+        <v>0.1751916690801975</v>
       </c>
     </row>
     <row r="14">
@@ -2020,19 +2020,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.09534625892455932</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.08535791995526414</v>
+        <v>-0.08646754023342332</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.02789694328593895</v>
+        <v>-0.03880022126416782</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.04727957130457831</v>
+        <v>-0.04900029675436288</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04510117745262847</v>
+        <v>0.03726779962499646</v>
       </c>
     </row>
     <row r="15">
@@ -2042,19 +2042,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.08858233390878897</v>
+        <v>-0.08975922963071523</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1026164605758665</v>
+        <v>-0.102202248581786</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.232139743711587</v>
+        <v>-0.2273893205229671</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.04531524178253767</v>
+        <v>-0.04926490420108146</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.05924176047330804</v>
+        <v>-0.05166182503249432</v>
       </c>
     </row>
     <row r="16">
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0936121120006783</v>
+        <v>-0.09489966977658215</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04968537647256653</v>
+        <v>-0.0609202233188512</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0347170909857363</v>
+        <v>-0.0529563983135022</v>
       </c>
       <c r="I16" t="n">
-        <v>0.009430785310949525</v>
+        <v>0.05556508399324762</v>
       </c>
     </row>
     <row r="17">
@@ -2086,19 +2086,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.0936121120006783</v>
+        <v>-0.09489966977658215</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09534625892455931</v>
+        <v>-0.09489966977658212</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04761719049830913</v>
+        <v>0.0278309045353752</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1265946947034513</v>
+        <v>-0.135929069581664</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1374200145309787</v>
+        <v>0.1108061749571183</v>
       </c>
     </row>
     <row r="18">
@@ -2108,19 +2108,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.09023171533395161</v>
+        <v>-0.08975922963071523</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1045271540123709</v>
+        <v>-0.1060806267448933</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.06273730222709767</v>
+        <v>-0.05838643189931884</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1051262599392492</v>
+        <v>0.09775474594071547</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.02234260680707617</v>
+        <v>-0.01174237301357899</v>
       </c>
     </row>
     <row r="19">
@@ -2130,19 +2130,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.09891091079316953</v>
+        <v>-0.09848078939079276</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1045271540123709</v>
+        <v>-0.1041207063716297</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1243250675559711</v>
+        <v>-0.1581720394612569</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1650727802050455</v>
+        <v>-0.1628033512757457</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1726942763371998</v>
+        <v>0.2029241489049277</v>
       </c>
     </row>
     <row r="20">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09848078939079276</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2175723479436126</v>
+        <v>-0.2243954529666052</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3622764116750872</v>
+        <v>-0.3605088506655661</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4127946127946139</v>
+        <v>0.4259989772815653</v>
       </c>
     </row>
     <row r="21">
@@ -2174,22 +2174,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.00169067063477572</v>
+        <v>-0.001695785221965964</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001254338893340792</v>
+        <v>0.002544150424389656</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.01132725336428534</v>
+        <v>-0.01020288654985709</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0770899653712328</v>
+        <v>0.07623607932259434</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2316601219136518</v>
+        <v>0.2277258411708745</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3966238850496299</v>
+        <v>0.391402849921708</v>
       </c>
     </row>
     <row r="22">
@@ -2199,22 +2199,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.03521915898529307</v>
+        <v>0.0340653258138684</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1330047129674815</v>
+        <v>-0.1348399724926482</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.01132725336428536</v>
+        <v>-0.01020288654985711</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06689724888354942</v>
+        <v>0.04599669141106139</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1065554243486942</v>
+        <v>-0.104384318977928</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.06218345762435376</v>
+        <v>-0.09148783662493334</v>
       </c>
     </row>
     <row r="23">
@@ -2224,19 +2224,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.09711193038612524</v>
+        <v>0.09667364890456624</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.09190779909650126</v>
+        <v>-0.09315705904653858</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1233143487704574</v>
+        <v>-0.1343938963309065</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.04182334298016998</v>
+        <v>-0.04785783660715914</v>
       </c>
       <c r="I23" t="n">
-        <v>0.008763064809841403</v>
+        <v>5.315062723673765e-18</v>
       </c>
     </row>
     <row r="24">
@@ -2246,22 +2246,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.06847969840341146</v>
+        <v>-0.0688877610192544</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1379772782674857</v>
+        <v>-0.1399282733414276</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02951309486374439</v>
+        <v>0.02858010659525691</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.07404133095017779</v>
+        <v>-0.05818340211593905</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1711368266176627</v>
+        <v>-0.1775584181068761</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2514423574815383</v>
+        <v>-0.2610033533109415</v>
       </c>
     </row>
     <row r="25">
@@ -2271,19 +2271,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0936121120006783</v>
+        <v>0.09315705904653855</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.08695819912499175</v>
+        <v>-0.08646754023342336</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1637536415509665</v>
+        <v>0.1574026445807406</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1127309318942139</v>
+        <v>-0.1106263302521133</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2278292343799171</v>
+        <v>-0.2196166114936574</v>
       </c>
     </row>
     <row r="26">
@@ -2293,22 +2293,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.03820454428388465</v>
+        <v>0.03968690701039092</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.003764284329268346</v>
+        <v>-0.005090921208157397</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.001254338893340793</v>
+        <v>-1.498685596457613e-18</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1481740300933157</v>
+        <v>0.1614061526914258</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.04203200162424961</v>
+        <v>-0.04998103916024009</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1741327144914608</v>
+        <v>0.185312329165275</v>
       </c>
     </row>
     <row r="27">
@@ -2318,28 +2318,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.08535791995526412</v>
+        <v>-0.08646754023342336</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1270892622911756</v>
+        <v>-0.135269350780775</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1884425636510563</v>
+        <v>-0.1897168945832034</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2796871422641454</v>
+        <v>0.2835151618181107</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3245250137004923</v>
+        <v>0.3354101966249679</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.03503399867171513</v>
+        <v>-0.03223028885762776</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1609914478241022</v>
+        <v>0.1533335261719049</v>
       </c>
     </row>
     <row r="28">
@@ -2349,28 +2349,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.0936121120006783</v>
+        <v>-0.09489966977658215</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1084756899431481</v>
+        <v>-0.1080844252917793</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001543174619976302</v>
+        <v>0.004478985761879545</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05176632082585721</v>
+        <v>0.01899839775268079</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2271068778536593</v>
+        <v>0.2387675808816703</v>
       </c>
       <c r="I28" t="n">
-        <v>0.160451453721126</v>
+        <v>0.1698046501453295</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1786592842325821</v>
+        <v>0.1716340502860449</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1466600547431615</v>
+        <v>0.1230415764847932</v>
       </c>
     </row>
     <row r="29">
@@ -2380,34 +2380,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.03497138749716529</v>
+        <v>-0.03547599222264934</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.003764284329268321</v>
+        <v>-0.1399282733414276</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.006278039126360495</v>
+        <v>-0.005090921208157422</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2521337221192557</v>
+        <v>0.2472975825015158</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1524982320900255</v>
+        <v>0.1536815646617752</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.02322345644428986</v>
+        <v>-0.02281118492314448</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2712344309420974</v>
+        <v>0.277738489833152</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1942009881832292</v>
+        <v>-0.1674961608635269</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.112761210163965</v>
+        <v>-0.1221085042602959</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.0217777633495188</v>
+        <v>-0.01602035498090487</v>
       </c>
     </row>
     <row r="30">
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.05577552457104578</v>
+        <v>-0.05584332508745906</v>
       </c>
       <c r="C30" t="n">
-        <v>0.001254338893340785</v>
+        <v>-5.245659880237252e-18</v>
       </c>
       <c r="D30" t="n">
-        <v>0.008798164312670992</v>
+        <v>0.007642946226594014</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02479165437317323</v>
+        <v>0.02404171158721094</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1688928951871659</v>
+        <v>-0.1697409437311151</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.08302593798596304</v>
+        <v>-0.08387621235415542</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3493006207006243</v>
+        <v>0.3525072627331406</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1740894255142761</v>
+        <v>0.1669244652223968</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1095739947676053</v>
+        <v>-0.1176876324681365</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.08212196718639464</v>
+        <v>-0.09019353870762734</v>
       </c>
     </row>
     <row r="31">
@@ -2454,28 +2454,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.09534625892455931</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1372884360513692</v>
+        <v>0.1594296495277263</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.04700134802146168</v>
+        <v>-0.03958286570511839</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2947563219963413</v>
+        <v>0.3030627892641972</v>
       </c>
       <c r="I31" t="n">
-        <v>0.06430976430976441</v>
+        <v>0.07407407407407388</v>
       </c>
       <c r="J31" t="n">
-        <v>0.09529020590720082</v>
+        <v>0.06015928172538267</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.003685327999098076</v>
+        <v>-0.01044746386747225</v>
       </c>
     </row>
     <row r="32">
@@ -2485,34 +2485,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.03554173467869092</v>
+        <v>-0.03621989075802057</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.006278039126360492</v>
+        <v>-0.00509092120815736</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0189950131551108</v>
+        <v>0.02057677418787306</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03073622448363022</v>
+        <v>0.02986814331553922</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1863159436993117</v>
+        <v>-0.1866602934218036</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1523397943843611</v>
+        <v>-0.1429550893478627</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2796122520598125</v>
+        <v>0.2830304327118041</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.09561421120009735</v>
+        <v>-0.1068760195147075</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2135170161456242</v>
+        <v>-0.2110006763579251</v>
       </c>
       <c r="K32" t="n">
-        <v>0.08395187559556269</v>
+        <v>0.08822109163214197</v>
       </c>
     </row>
     <row r="33">
@@ -2522,34 +2522,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01583279722678352</v>
+        <v>-0.0158131122088035</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1354686004808041</v>
+        <v>-0.1373605639486888</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00879816431267103</v>
+        <v>0.01020288654985701</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2686364749593864</v>
+        <v>0.2585901201848593</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09480417253948054</v>
+        <v>0.1049331959759601</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.07364707567376436</v>
+        <v>-0.07955350727956016</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2387072355881997</v>
+        <v>0.24115476130036</v>
       </c>
       <c r="I33" t="n">
-        <v>0.02699060860686458</v>
+        <v>-2.481304330884651e-17</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.04854657013908946</v>
+        <v>-0.02381732022419195</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0325033000095612</v>
+        <v>-0.03341232905287115</v>
       </c>
     </row>
     <row r="34">
@@ -2559,28 +2559,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0936121120006783</v>
+        <v>-0.09489966977658215</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.01899072512099626</v>
+        <v>-0.04266376243066657</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2499657151149681</v>
+        <v>-0.2465131444828575</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1742971377461012</v>
+        <v>0.1761852185353884</v>
       </c>
       <c r="I34" t="n">
-        <v>0.08285618523191365</v>
+        <v>0.05556508399324763</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1072689751461226</v>
+        <v>0.1064232922776278</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.0132227094105949</v>
+        <v>-0.01151116859595155</v>
       </c>
     </row>
     <row r="35">
@@ -2590,28 +2590,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.09891091079316949</v>
+        <v>-0.09848078939079274</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1142261372501029</v>
+        <v>0.1177111439937965</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.09588041792537398</v>
+        <v>-0.08957764983721943</v>
       </c>
       <c r="H35" t="n">
-        <v>0.183533574297793</v>
+        <v>0.1806142723180401</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.04614348527143148</v>
+        <v>-0.05556508399324765</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1518314970891551</v>
+        <v>-0.1513334185259347</v>
       </c>
       <c r="K35" t="n">
-        <v>0.01395680099007497</v>
+        <v>0.01554428124361444</v>
       </c>
     </row>
     <row r="36">
@@ -2621,28 +2621,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-0.1064794274999899</v>
+        <v>-0.1080844252917793</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.09190779909650126</v>
+        <v>-0.09315705904653858</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1169358162620402</v>
+        <v>-0.1169830518935558</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.08446338602912158</v>
+        <v>-0.08599686453946098</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1806926049565673</v>
+        <v>0.1831719374389791</v>
       </c>
       <c r="I36" t="n">
-        <v>0.05081342796647071</v>
+        <v>0.04143709650823726</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.009407517734574194</v>
+        <v>-0.009607423941977299</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03989823054360286</v>
+        <v>0.03978824120338015</v>
       </c>
     </row>
     <row r="37">
@@ -2652,28 +2652,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-0.09190779909650126</v>
+        <v>-0.09315705904653855</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1026164605758665</v>
+        <v>-0.1041207063716297</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1388692426423541</v>
+        <v>-0.1391268176612411</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.04760560310628659</v>
+        <v>-0.06178618051827926</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1803088514343745</v>
+        <v>0.1773091821942435</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.09827765935771127</v>
+        <v>-0.07157620211606368</v>
       </c>
       <c r="J37" t="n">
-        <v>0.05966332368107802</v>
+        <v>0.06419834487543215</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1852694005040261</v>
+        <v>0.1639909270702125</v>
       </c>
     </row>
     <row r="38">
@@ -2683,28 +2683,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-0.09190779909650128</v>
+        <v>-0.09315705904653855</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1147550621098495</v>
+        <v>-0.1143858039685551</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.2054503576335587</v>
+        <v>-0.1845676926114365</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2174511385757497</v>
+        <v>-0.2222138648587878</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1703192226726274</v>
+        <v>0.1667244851200683</v>
       </c>
       <c r="I38" t="n">
-        <v>0.129376815248663</v>
+        <v>0.1378234030339618</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1238106875044361</v>
+        <v>-0.0888815651178437</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.02134858103998969</v>
+        <v>-0.02879493020818703</v>
       </c>
     </row>
     <row r="39">
@@ -2714,28 +2714,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-0.09361211200067829</v>
+        <v>-0.09315705904653858</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.08535791995526414</v>
+        <v>-0.08646754023342335</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1590960284155672</v>
+        <v>0.1642408610599827</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.04463976104621097</v>
+        <v>-0.04629682314930227</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1830729631971755</v>
+        <v>0.1856110088018534</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3202244657774695</v>
+        <v>0.3314967720658977</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1206795023628906</v>
+        <v>0.1111596206009156</v>
       </c>
       <c r="K39" t="n">
-        <v>0.05592494559303856</v>
+        <v>0.06633106098738135</v>
       </c>
     </row>
     <row r="40">
@@ -2745,28 +2745,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-0.09023171533395161</v>
+        <v>-0.08975922963071524</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.09361211200067829</v>
+        <v>-0.09489966977658211</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.1702805175763787</v>
+        <v>-0.1650277876016729</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07697450871417633</v>
+        <v>0.05355492420737962</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2164213642167697</v>
+        <v>0.2155854553268961</v>
       </c>
       <c r="I40" t="n">
-        <v>0.08099910283865573</v>
+        <v>0.1286332740515982</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1425605320662413</v>
+        <v>-0.1231481843694827</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2814945248889395</v>
+        <v>0.2509190237362108</v>
       </c>
     </row>
     <row r="41">
@@ -2776,28 +2776,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.0936121120006783</v>
+        <v>-0.09489966977658215</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.08695819912499175</v>
+        <v>-0.0881008594999961</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.03940349750359756</v>
+        <v>-0.04661211351052923</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1052222829548144</v>
+        <v>-0.0991044982053315</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1196608500779547</v>
+        <v>0.1190038894521346</v>
       </c>
       <c r="I41" t="n">
-        <v>0.006432028905228038</v>
+        <v>-0.001722370898485415</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.05995359443487147</v>
+        <v>-0.05012007329824453</v>
       </c>
       <c r="K41" t="n">
-        <v>0.07237386138824047</v>
+        <v>0.07579306808756597</v>
       </c>
     </row>
     <row r="42">
@@ -2807,28 +2807,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.09711193038612524</v>
+        <v>0.09667364890456624</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.09534625892455931</v>
+        <v>-0.09489966977658212</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.07722508880912847</v>
+        <v>-0.06110202347442362</v>
       </c>
       <c r="G42" t="n">
-        <v>0.130001095044107</v>
+        <v>0.1219607329870361</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04116135567935459</v>
+        <v>0.02906615500942961</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.02760942760942766</v>
+        <v>-0.01852169466441587</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.01945229217444768</v>
+        <v>-0.01499560915064126</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1464503665337391</v>
+        <v>0.1423319870177078</v>
       </c>
     </row>
     <row r="43">
@@ -2838,28 +2838,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.09190779909650124</v>
+        <v>-0.09315705904653858</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1045271540123709</v>
+        <v>-0.1060806267448933</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.04332715482737932</v>
+        <v>-0.04643431825327679</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.142032430386773</v>
+        <v>-0.1447099911303564</v>
       </c>
       <c r="H43" t="n">
-        <v>0.09336408817440499</v>
+        <v>0.08867327931913561</v>
       </c>
       <c r="I43" t="n">
-        <v>0.03145088284892722</v>
+        <v>0.02205770086888883</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0208813959890649</v>
+        <v>0.02334027653113569</v>
       </c>
       <c r="K43" t="n">
-        <v>0.07205351575212925</v>
+        <v>0.07527541261783886</v>
       </c>
     </row>
     <row r="44">
@@ -2869,28 +2869,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.09534625892455932</v>
+        <v>0.09489966977658215</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1007450874711649</v>
+        <v>-0.100322986665503</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2212486149506172</v>
+        <v>0.2236180004809247</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.1436893981544377</v>
+        <v>-0.1257301016249899</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1541407835618741</v>
+        <v>0.1479896106417184</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08223799283081909</v>
+        <v>0.09198559653980573</v>
       </c>
       <c r="J44" t="n">
-        <v>0.08476915776468688</v>
+        <v>0.08548234375602363</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01170189577172026</v>
+        <v>0.01160658679935699</v>
       </c>
     </row>
     <row r="45">
@@ -2900,28 +2900,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.1026164605758665</v>
+        <v>-0.1041207063716297</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.09023171533395162</v>
+        <v>-0.08975922963071521</v>
       </c>
       <c r="F45" t="n">
-        <v>0.03101217355683578</v>
+        <v>0.03198549693065061</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2963123666770854</v>
+        <v>0.2990771748170673</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2041403688902303</v>
+        <v>0.1980145775309414</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2160243407707908</v>
+        <v>0.1917241379310344</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0329964402941096</v>
+        <v>0.018196851657425</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1771870208726956</v>
+        <v>0.1804416549140471</v>
       </c>
     </row>
     <row r="46">
@@ -2931,28 +2931,28 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.09711193038612523</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1723835070364738</v>
+        <v>-0.1500179026481359</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.268679962964728</v>
+        <v>-0.2599223661074114</v>
       </c>
       <c r="H46" t="n">
-        <v>0.127443602139027</v>
+        <v>0.12588308586723</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4494949494949502</v>
+        <v>0.4444444444444431</v>
       </c>
       <c r="J46" t="n">
-        <v>0.002438464962773257</v>
+        <v>0.005091727686591887</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1849531639585648</v>
+        <v>0.1868249792594327</v>
       </c>
     </row>
     <row r="47">
@@ -2962,34 +2962,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.07515757615575361</v>
+        <v>-0.07512170178029713</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0062780391263605</v>
+        <v>0.007642946226593983</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01642294087790961</v>
+        <v>0.01795751586281635</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2593779623990857</v>
+        <v>0.2593157022037975</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1283055421152353</v>
+        <v>-0.1304289233890832</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.1303126739169845</v>
+        <v>-0.1407247860734075</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1152953649292198</v>
+        <v>0.11342745175124</v>
       </c>
       <c r="I47" t="n">
-        <v>0.003733946140845368</v>
+        <v>-0.00727416138944379</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0746649088673968</v>
+        <v>0.07957420963793714</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1111983657603458</v>
+        <v>0.1166739760116336</v>
       </c>
     </row>
     <row r="48">
@@ -2999,34 +2999,34 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.05305772742339804</v>
+        <v>-0.05374223632212462</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1330047129674814</v>
+        <v>0.132363951412094</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.006278039126360464</v>
+        <v>-0.005090921208157415</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2759127967837011</v>
+        <v>0.2772981561457106</v>
       </c>
       <c r="F48" t="n">
-        <v>0.03245631692836533</v>
+        <v>0.02580404217797428</v>
       </c>
       <c r="G48" t="n">
-        <v>0.04501229570306509</v>
+        <v>0.04416528391339533</v>
       </c>
       <c r="H48" t="n">
-        <v>0.07181909552961661</v>
+        <v>0.06357240034113933</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1207013086277709</v>
+        <v>-0.1126373626373624</v>
       </c>
       <c r="J48" t="n">
-        <v>0.07024106066908417</v>
+        <v>0.06549942898869369</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1447248095652106</v>
+        <v>0.1502493227432658</v>
       </c>
     </row>
     <row r="49">
@@ -3036,28 +3036,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.09711193038612523</v>
+        <v>-0.09848078939079276</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.09361211200067829</v>
+        <v>-0.09489966977658215</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.200173266079966</v>
+        <v>-0.2187824136206316</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.2488607278027326</v>
+        <v>-0.2360268741670708</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2063692205607593</v>
+        <v>0.2012110219469513</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2297069850738421</v>
+        <v>0.2226415094339623</v>
       </c>
       <c r="J49" t="n">
-        <v>0.09173166055121793</v>
+        <v>0.0713392309684913</v>
       </c>
       <c r="K49" t="n">
-        <v>0.03483896053735082</v>
+        <v>0.02996380381430788</v>
       </c>
     </row>
     <row r="50">
@@ -3067,28 +3067,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.09711193038612523</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1045271540123709</v>
+        <v>-0.1041207063716297</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.07539817137965713</v>
+        <v>-0.06395843610077333</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.09995527271415108</v>
+        <v>-0.1071800108583475</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05305421476825683</v>
+        <v>0.04961446020611286</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.06520307479947079</v>
+        <v>-0.07427813527082071</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.1550739072578381</v>
+        <v>-0.1372021071021321</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1225347975554304</v>
+        <v>0.1284292031952768</v>
       </c>
     </row>
     <row r="51">
@@ -3098,28 +3098,28 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.1007450874711648</v>
+        <v>0.100322986665503</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.09190779909650125</v>
+        <v>-0.09315705904653858</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2136843736109011</v>
+        <v>-0.2092412723691229</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.04508735170537314</v>
+        <v>-0.04643980451956663</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.07809656511823564</v>
+        <v>-0.08335389285648423</v>
       </c>
       <c r="I51" t="n">
-        <v>0.007085020242914984</v>
+        <v>-0.001373626373626333</v>
       </c>
       <c r="J51" t="n">
-        <v>0.09745483080059754</v>
+        <v>0.09282815462916143</v>
       </c>
       <c r="K51" t="n">
-        <v>0.05377900012425162</v>
+        <v>0.04884179836461346</v>
       </c>
     </row>
     <row r="52">
@@ -3129,34 +3129,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1497046002098503</v>
+        <v>-0.1486462492993756</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1379772782674857</v>
+        <v>-0.1373605639486886</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.01642294087790969</v>
+        <v>-0.01535737792084841</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01490467902229624</v>
+        <v>0.01392472066804773</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.02072657573690481</v>
+        <v>-0.02151178757067089</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.2719425280548633</v>
+        <v>-0.2864774910626983</v>
       </c>
       <c r="H52" t="n">
-        <v>0.04178967119974717</v>
+        <v>0.0370080069022695</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1559890347985647</v>
+        <v>0.1490711984999858</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.09616221277127568</v>
+        <v>-0.0957338031585806</v>
       </c>
       <c r="K52" t="n">
-        <v>0.2045842414464557</v>
+        <v>0.2073606067209885</v>
       </c>
     </row>
     <row r="53">
@@ -3166,28 +3166,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.09891091079316952</v>
+        <v>-0.100322986665503</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.1084756899431481</v>
+        <v>-0.1080844252917793</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2274703161326629</v>
+        <v>0.2267969348896775</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1246131159500369</v>
+        <v>-0.1311056361418802</v>
       </c>
       <c r="H53" t="n">
-        <v>0.05547001194512696</v>
+        <v>0.04906373949193125</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1974265244517871</v>
+        <v>-0.1906106439378912</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0830979105904209</v>
+        <v>0.07931019806686629</v>
       </c>
       <c r="K53" t="n">
-        <v>0.08420922312503763</v>
+        <v>0.08804836699261671</v>
       </c>
     </row>
     <row r="54">
@@ -3197,28 +3197,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.09190779909650126</v>
+        <v>-0.100322986665503</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.09711193038612524</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="F54" t="n">
-        <v>0.05944320015308054</v>
+        <v>0.06721441818338324</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3746809806575998</v>
+        <v>-0.3813662491992049</v>
       </c>
       <c r="H54" t="n">
-        <v>0.00896595588784091</v>
+        <v>0.003923354147105896</v>
       </c>
       <c r="I54" t="n">
-        <v>0.008763064809841381</v>
+        <v>0.037062465833055</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.1716330709711393</v>
+        <v>-0.1748390087966627</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1361437632114844</v>
+        <v>0.1408818955427913</v>
       </c>
     </row>
     <row r="55">
@@ -3228,28 +3228,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.09711193038612523</v>
+        <v>-0.09667364890456624</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.09190779909650124</v>
+        <v>-0.09144411715212425</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1730209940741191</v>
+        <v>-0.1656882337045218</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2876138701878769</v>
+        <v>-0.2802450152817995</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.01420226700577634</v>
+        <v>-0.02470082812035465</v>
       </c>
       <c r="I55" t="n">
-        <v>0.174924255242603</v>
+        <v>0.1669244652223969</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.1254443731202091</v>
+        <v>-0.125501199583858</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1153120082480351</v>
+        <v>0.117452855237211</v>
       </c>
     </row>
     <row r="56">
@@ -3259,31 +3259,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.07899005058596859</v>
+        <v>-0.07929478788303389</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0936121120006783</v>
+        <v>0.09489966977658217</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.09711193038612523</v>
+        <v>-0.09848078939079276</v>
       </c>
       <c r="F56" t="n">
-        <v>0.04107685492628335</v>
+        <v>0.0421205105996744</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.03529671457033034</v>
+        <v>-0.04146379650913672</v>
       </c>
       <c r="H56" t="n">
-        <v>0.06055786871258941</v>
+        <v>0.05274406409459892</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.009430785310949473</v>
+        <v>-0.03739279588336199</v>
       </c>
       <c r="J56" t="n">
-        <v>0.116053339831118</v>
+        <v>0.1288167359562647</v>
       </c>
       <c r="K56" t="n">
-        <v>0.007059255946496317</v>
+        <v>0.006576997016490089</v>
       </c>
     </row>
     <row r="57">
@@ -3293,34 +3293,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.07608055319831823</v>
+        <v>-0.0758711435972285</v>
       </c>
       <c r="C57" t="n">
-        <v>0.09891091079316949</v>
+        <v>0.09848078939079274</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.09711193038612523</v>
+        <v>-0.09667364890456626</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2388908378767793</v>
+        <v>0.2389248193310122</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.324739723540535</v>
+        <v>-0.3043314587613394</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1298394901729829</v>
+        <v>0.1336189417566613</v>
       </c>
       <c r="H57" t="n">
-        <v>0.001763716333030309</v>
+        <v>-0.00497936371579004</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0272819146495326</v>
+        <v>-0.01852169466441588</v>
       </c>
       <c r="J57" t="n">
-        <v>0.04662555305592603</v>
+        <v>0.04381020530099394</v>
       </c>
       <c r="K57" t="n">
-        <v>0.005409691503772185</v>
+        <v>0.006530092036575287</v>
       </c>
     </row>
     <row r="58">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-0.06318021270175025</v>
+        <v>-0.05176470197814495</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2417230493526913</v>
+        <v>0.2347466601901061</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.08063904350847181</v>
+        <v>-0.08694745385789399</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1577008473360546</v>
+        <v>0.2056756627883844</v>
       </c>
       <c r="J58" t="n">
-        <v>0.04828242780174571</v>
+        <v>0.04796322025920589</v>
       </c>
       <c r="K58" t="n">
-        <v>0.043042612041484</v>
+        <v>0.04484015556257551</v>
       </c>
     </row>
     <row r="59">
@@ -3355,22 +3355,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.05576728437228953</v>
+        <v>0.06001469590463403</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.07824342393650198</v>
+        <v>-0.1022826931848897</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1471027166056499</v>
+        <v>0.1349635214726073</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3003052039768532</v>
+        <v>-0.3301150893110446</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.1015282993348551</v>
+        <v>-0.1011602258889614</v>
       </c>
       <c r="K59" t="n">
-        <v>0.08101096470358148</v>
+        <v>0.07471915793087142</v>
       </c>
     </row>
     <row r="60">
@@ -3380,22 +3380,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.228791800484329</v>
+        <v>0.2261944997009043</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2054602061135003</v>
+        <v>0.2148578956640939</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.09053631777107037</v>
+        <v>-0.09775754304005189</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1373960172069489</v>
+        <v>0.1301889109808237</v>
       </c>
       <c r="J60" t="n">
-        <v>0.04426107525889843</v>
+        <v>0.04272810282212482</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1290705564243386</v>
+        <v>0.1281018553770029</v>
       </c>
     </row>
     <row r="61">
@@ -3405,22 +3405,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.06122467168644209</v>
+        <v>0.04985907588314922</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.3876047655768928</v>
+        <v>-0.3888133493182829</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.02504780310828983</v>
+        <v>-0.03754580918900045</v>
       </c>
       <c r="I61" t="n">
-        <v>0.02303542067813336</v>
+        <v>0.03208014974496041</v>
       </c>
       <c r="J61" t="n">
-        <v>0.03443382165301052</v>
+        <v>0.02405216180173983</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1743491980535897</v>
+        <v>0.1863009985665352</v>
       </c>
     </row>
     <row r="62">
@@ -3430,34 +3430,34 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.04492411014617949</v>
+        <v>-0.04560279619550089</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.09711193038612534</v>
+        <v>-0.09667364890456627</v>
       </c>
       <c r="D62" t="n">
-        <v>0.09711193038612538</v>
+        <v>0.0984807893907927</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2267440267622219</v>
+        <v>0.2207933056875792</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.05916963823998114</v>
+        <v>-0.05280914687144304</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.07270660142812702</v>
+        <v>-0.08168482298961623</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.07520020720841915</v>
+        <v>-0.0789728371426722</v>
       </c>
       <c r="I62" t="n">
-        <v>0.06430976430976441</v>
+        <v>0.05556508399324763</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1968468866346242</v>
+        <v>0.1823768658945666</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1207662424098394</v>
+        <v>0.1096458990968842</v>
       </c>
     </row>
     <row r="63">
@@ -3467,22 +3467,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.05113398274763964</v>
+        <v>0.05261597980444675</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.2854384071249143</v>
+        <v>-0.2761620771682435</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.1385221523038725</v>
+        <v>-0.1513777113537805</v>
       </c>
       <c r="I63" t="n">
-        <v>0.06471186321113652</v>
+        <v>0.07523195010384041</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.08201804010939172</v>
+        <v>-0.1209039060079832</v>
       </c>
       <c r="K63" t="n">
-        <v>0.215997759576818</v>
+        <v>0.2031928330036329</v>
       </c>
     </row>
     <row r="64">
@@ -3492,22 +3492,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>-0.1125848328881431</v>
+        <v>-0.09823916361406528</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.2488009434351922</v>
+        <v>-0.2663869061448403</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.07114060395034953</v>
+        <v>-0.09553934877686435</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4472616632860036</v>
+        <v>0.4593340031782372</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.1167641787446801</v>
+        <v>-0.08747694355153619</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1575303295557106</v>
+        <v>0.1394937822225668</v>
       </c>
     </row>
     <row r="65">
@@ -3517,22 +3517,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>-0.07199023259594166</v>
+        <v>-0.06029961288859439</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.007576337823561452</v>
+        <v>7.343289158825754e-05</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.03481122227042219</v>
+        <v>-0.05807240028076543</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2542476613033774</v>
+        <v>0.248510297264644</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.1860120715297183</v>
+        <v>-0.1713665586193234</v>
       </c>
       <c r="K65" t="n">
-        <v>0.08201430832012474</v>
+        <v>0.09771863669288486</v>
       </c>
     </row>
     <row r="66">
@@ -3542,34 +3542,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.009152294402181235</v>
+        <v>-0.009921248040846117</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.09190779909650129</v>
+        <v>-0.09315705904653887</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1045271540123709</v>
+        <v>0.10412070637163</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2509779397625692</v>
+        <v>0.2506445937155518</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1371921634278764</v>
+        <v>-0.1468603426506575</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.2686423490117572</v>
+        <v>-0.2717571403972158</v>
       </c>
       <c r="H66" t="n">
-        <v>0.02478667442282368</v>
+        <v>0.007601236394873842</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1051744576991005</v>
+        <v>-0.07708206381729951</v>
       </c>
       <c r="J66" t="n">
-        <v>0.001545897039151863</v>
+        <v>-0.03778760761718014</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2444306431324782</v>
+        <v>0.2658582894270697</v>
       </c>
     </row>
     <row r="67">
@@ -3579,22 +3579,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>-0.131502116413816</v>
+        <v>-0.1346175940853805</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.1467418985093221</v>
+        <v>-0.1591530343028573</v>
       </c>
       <c r="H67" t="n">
-        <v>0.08562320403682337</v>
+        <v>0.07886330907626518</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.09979773003860372</v>
+        <v>-0.1098901098901099</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.03593723005490988</v>
+        <v>-0.05339588331724737</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.008569218014160327</v>
+        <v>-0.02463433812200702</v>
       </c>
     </row>
     <row r="68">
@@ -3604,22 +3604,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.06824771901961198</v>
+        <v>0.06486701406255696</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.3852285971344422</v>
+        <v>-0.3916306710029284</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2330938353936466</v>
+        <v>0.2133240951913909</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.04579124579124584</v>
+        <v>-0.03703703703703694</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.1001082681235064</v>
+        <v>-0.1124544096629915</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.07515931815477436</v>
+        <v>-0.0648985860379777</v>
       </c>
     </row>
     <row r="69">
@@ -3629,22 +3629,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.01967462059574444</v>
+        <v>0.04119145994677249</v>
       </c>
       <c r="G69" t="n">
-        <v>0.07741661543833829</v>
+        <v>0.08837175995558032</v>
       </c>
       <c r="H69" t="n">
-        <v>0.02816619675007385</v>
+        <v>0.01462358336840148</v>
       </c>
       <c r="I69" t="n">
-        <v>0.190856083147469</v>
+        <v>0.2004704044130356</v>
       </c>
       <c r="J69" t="n">
-        <v>0.02543655911273011</v>
+        <v>0.04685048018322904</v>
       </c>
       <c r="K69" t="n">
-        <v>0.0917518372297602</v>
+        <v>0.1001514151278016</v>
       </c>
     </row>
     <row r="70">
@@ -3654,22 +3654,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>-0.1839018913829775</v>
+        <v>-0.1820083039401273</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.3460330443113883</v>
+        <v>-0.3172192269016708</v>
       </c>
       <c r="H70" t="n">
-        <v>0.05771832050200807</v>
+        <v>0.04484729377544509</v>
       </c>
       <c r="I70" t="n">
-        <v>0.02968960863697705</v>
+        <v>0.03846153846153844</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.03221003517799089</v>
+        <v>-0.02457499987444138</v>
       </c>
       <c r="K70" t="n">
-        <v>0.25685150491408</v>
+        <v>0.2848819861523777</v>
       </c>
     </row>
     <row r="71">
@@ -3679,22 +3679,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>-0.08555185277601872</v>
+        <v>-0.06510884717018928</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.0382758088079673</v>
+        <v>-0.0121006190255681</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2326089683241034</v>
+        <v>0.2300596512015294</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3576962142938716</v>
+        <v>0.3331046312178388</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.04258335144421799</v>
+        <v>-0.03953877360227633</v>
       </c>
       <c r="K71" t="n">
-        <v>0.1248429194223234</v>
+        <v>0.1425691597337548</v>
       </c>
     </row>
     <row r="72">
@@ -3704,34 +3704,34 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.03304410431063796</v>
+        <v>0.02994028183181292</v>
       </c>
       <c r="C72" t="n">
-        <v>0.09361211200067832</v>
+        <v>0.0931570590465389</v>
       </c>
       <c r="D72" t="n">
-        <v>0.09361211200067836</v>
+        <v>0.09489966977658246</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2373678636713567</v>
+        <v>0.2398589101421674</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.01136890660368764</v>
+        <v>-0.02346219662385108</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.04511718449695519</v>
+        <v>-0.02509534632857689</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.06895600983027922</v>
+        <v>-0.06681951859994135</v>
       </c>
       <c r="I72" t="n">
-        <v>0.04514824797843673</v>
+        <v>0.017847951567425</v>
       </c>
       <c r="J72" t="n">
-        <v>0.057950365434079</v>
+        <v>0.06127243022012819</v>
       </c>
       <c r="K72" t="n">
-        <v>0.07039505025220473</v>
+        <v>0.06209889206430068</v>
       </c>
     </row>
     <row r="73">
@@ -3741,22 +3741,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>-0.1583477470117934</v>
+        <v>-0.1604528132175912</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1136399751520614</v>
+        <v>0.1252525573575533</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.1133725586909194</v>
+        <v>-0.1155875543748622</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1613608048246888</v>
+        <v>-0.1553231008958873</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0568034441124388</v>
+        <v>0.01042372716190274</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.1658599834898447</v>
+        <v>-0.1654589174665298</v>
       </c>
     </row>
     <row r="74">
@@ -3766,22 +3766,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>-0.05869081179328328</v>
+        <v>-0.02638731450212668</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.003810145296724547</v>
+        <v>0.01188974179722927</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.04148391119876884</v>
+        <v>-0.0434701307995937</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2654986522911061</v>
+        <v>0.2219554030874786</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.004533400176935646</v>
+        <v>0.01832414238838534</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.08582314459254257</v>
+        <v>-0.07496102488025363</v>
       </c>
     </row>
     <row r="75">
@@ -3791,22 +3791,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>-0.3140826716402098</v>
+        <v>-0.3184474984079286</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.07099971855053673</v>
+        <v>-0.05474759756369497</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2879300870720081</v>
+        <v>0.2829311334203444</v>
       </c>
       <c r="I75" t="n">
-        <v>0.06399461461001464</v>
+        <v>0.05556508399324763</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.04485076428935912</v>
+        <v>-0.04823096381037323</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1205416364915031</v>
+        <v>0.1184244173516226</v>
       </c>
     </row>
     <row r="76">
@@ -3816,34 +3816,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.02801434795427032</v>
+        <v>0.02596314438305249</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.09891091079316962</v>
+        <v>-0.1003229866655029</v>
       </c>
       <c r="D76" t="n">
-        <v>0.09891091079316963</v>
+        <v>0.1003229866655029</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2130511594598328</v>
+        <v>0.2150135705284228</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1259911318131747</v>
+        <v>-0.1255062285779246</v>
       </c>
       <c r="G76" t="n">
-        <v>0.1166267508839812</v>
+        <v>0.0332369907574188</v>
       </c>
       <c r="H76" t="n">
-        <v>0.08794013154900027</v>
+        <v>0.07870557521484214</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.08187331536388166</v>
+        <v>-0.07280219780219775</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.1583249731765582</v>
+        <v>-0.1642129794411089</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1014675415809631</v>
+        <v>0.1048593419206735</v>
       </c>
     </row>
     <row r="77">
@@ -3853,22 +3853,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.02593150155941474</v>
+        <v>0.01705000898101512</v>
       </c>
       <c r="G77" t="n">
-        <v>0.09687147072614785</v>
+        <v>0.09698036470714878</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.2461756517312782</v>
+        <v>-0.2540326884112678</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09688426932273747</v>
+        <v>0.06933451719072091</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.1218295949329442</v>
+        <v>-0.11291343102924</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.05624708986616056</v>
+        <v>-0.06174188249406932</v>
       </c>
     </row>
     <row r="78">
@@ -3878,34 +3878,34 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.07814441931222392</v>
+        <v>-0.08393265364224575</v>
       </c>
       <c r="C78" t="n">
-        <v>0.09891091079316963</v>
+        <v>0.09848078939079268</v>
       </c>
       <c r="D78" t="n">
-        <v>0.09891091079316962</v>
+        <v>0.1003229866655029</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2015344310094305</v>
+        <v>0.2235192619473854</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.0731615071972495</v>
+        <v>-0.1228845479966302</v>
       </c>
       <c r="G78" t="n">
-        <v>0.03107719161091315</v>
+        <v>0.007340123382606749</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.07618349396409242</v>
+        <v>-0.09227961001639091</v>
       </c>
       <c r="I78" t="n">
-        <v>0.192048517520216</v>
+        <v>0.1661232415121866</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.0255560942538995</v>
+        <v>-0.01540253091873067</v>
       </c>
       <c r="K78" t="n">
-        <v>0.08326547912342674</v>
+        <v>0.09458878569740352</v>
       </c>
     </row>
     <row r="79">
@@ -3915,34 +3915,34 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.03000032801781637</v>
+        <v>0.02870445891412488</v>
       </c>
       <c r="C79" t="n">
-        <v>0.09361211200067832</v>
+        <v>0.09489966977658215</v>
       </c>
       <c r="D79" t="n">
-        <v>0.09190779909650125</v>
+        <v>0.09144411715212425</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2220267830350803</v>
+        <v>0.2244594320182665</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.1732074288429781</v>
+        <v>-0.1613304105805765</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.0958864097011341</v>
+        <v>-0.07677700046090881</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.09195276070428217</v>
+        <v>-0.09577663359425904</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2100472493717912</v>
+        <v>0.2215735516756941</v>
       </c>
       <c r="J79" t="n">
-        <v>0.06286680486916958</v>
+        <v>0.0702778234210847</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.1672582559801355</v>
+        <v>-0.1765336451663772</v>
       </c>
     </row>
     <row r="80">
@@ -3952,34 +3952,34 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.05379264979149858</v>
+        <v>-0.05922977476448836</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.09891091079316955</v>
+        <v>-0.09848078939079276</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1007450874711649</v>
+        <v>0.100322986665503</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.05000782580413909</v>
+        <v>-0.05096611659405038</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.1801775294524413</v>
+        <v>-0.1605658804657158</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.1576691038357169</v>
+        <v>-0.1740327113767012</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.04225147592059485</v>
+        <v>-0.05827311887417461</v>
       </c>
       <c r="I80" t="n">
-        <v>0.04720162907231269</v>
+        <v>0.05628969340495582</v>
       </c>
       <c r="J80" t="n">
-        <v>0.07882994063172356</v>
+        <v>0.08580004285106207</v>
       </c>
       <c r="K80" t="n">
-        <v>0.05135935123758722</v>
+        <v>0.04473699886494856</v>
       </c>
     </row>
     <row r="81">
@@ -3989,22 +3989,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>-0.3113116792189</v>
+        <v>-0.336117482774826</v>
       </c>
       <c r="G81" t="n">
-        <v>0.008159129049223595</v>
+        <v>-0.009534043170362898</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.1694597337776092</v>
+        <v>-0.177908981679077</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.01776049510106851</v>
+        <v>-0.04248748499842665</v>
       </c>
       <c r="J81" t="n">
-        <v>0.06063828926154717</v>
+        <v>0.09625411500247075</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1669735043689233</v>
+        <v>0.1641103755531702</v>
       </c>
     </row>
     <row r="82">
@@ -4014,22 +4014,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.006033217327454318</v>
+        <v>0.01527016939870706</v>
       </c>
       <c r="G82" t="n">
-        <v>0.03956066620651066</v>
+        <v>0.0697092457156592</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.1155837387898553</v>
+        <v>-0.1249708666340306</v>
       </c>
       <c r="I82" t="n">
-        <v>0.005070993914807313</v>
+        <v>-0.02273120301429753</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.06761639599275591</v>
+        <v>-0.06164257780582476</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2770769936118571</v>
+        <v>0.2883212374834873</v>
       </c>
     </row>
   </sheetData>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.0002018531209727497</v>
+        <v>-0.002368322385558906</v>
       </c>
     </row>
     <row r="4">
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.01001994103909315</v>
+        <v>-0.05767221262774212</v>
       </c>
     </row>
     <row r="5">
@@ -4130,19 +4130,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.04561504595866447</v>
+        <v>-0.04608735379818363</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.09534625892455931</v>
+        <v>-0.09667364890456623</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3339658326983162</v>
+        <v>-0.4026291504434566</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1655714950212809</v>
+        <v>-0.1631058934897514</v>
       </c>
       <c r="I5" t="n">
-        <v>0.336195013872797</v>
+        <v>0.3337119062359572</v>
       </c>
     </row>
     <row r="6">
@@ -4152,19 +4152,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.08102490369194776</v>
+        <v>-0.08184903972082314</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1906925178491186</v>
+        <v>-0.1933472978091325</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5189063933474978</v>
+        <v>-0.5883845288980092</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1701666930252308</v>
+        <v>-0.1739149517432679</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4244955629291516</v>
+        <v>0.4190784652196279</v>
       </c>
     </row>
     <row r="7">
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.1252372606782934</v>
+        <v>-0.1265163609905736</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2860387767736779</v>
+        <v>-0.2900209467136987</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.68412746509921</v>
+        <v>-0.7497159771279069</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2315124643960519</v>
+        <v>-0.2342312811214692</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5012617240640077</v>
+        <v>0.4920325226824974</v>
       </c>
     </row>
     <row r="8">
@@ -4196,19 +4196,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.2223491910644186</v>
+        <v>-0.2249971503813664</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3813850356982372</v>
+        <v>-0.386694595618265</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.817563766060018</v>
+        <v>-0.8897667485131581</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1565634030169496</v>
+        <v>-0.1657362711646103</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5655714883737721</v>
+        <v>0.5475976066757451</v>
       </c>
     </row>
     <row r="9">
@@ -4218,19 +4218,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.317695449988978</v>
+        <v>-0.3216707992859326</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4767312946227965</v>
+        <v>-0.4833682445228312</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9672002714686647</v>
+        <v>-1.042055226993585</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1910406352113066</v>
+        <v>-0.2028257698012432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5012617240640077</v>
+        <v>0.5105605696387081</v>
       </c>
     </row>
     <row r="10">
@@ -4240,19 +4240,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.4148073803751032</v>
+        <v>-0.4183444481904989</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5720775535473558</v>
+        <v>-0.5800418934273974</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.014275534800419</v>
+        <v>-1.089124131834526</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1951469183983651</v>
+        <v>-0.2140642579751642</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3453694681717516</v>
+        <v>0.3253753844535234</v>
       </c>
     </row>
     <row r="11">
@@ -4262,22 +4262,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.08296391418673557</v>
+        <v>-0.08293945999691466</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4210854195014637</v>
+        <v>-0.4259873944170929</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5783555926737163</v>
+        <v>-0.5851328146355549</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8633034946905533</v>
+        <v>-0.9592464784911906</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1739293849599561</v>
+        <v>-0.1947522572884159</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5363276328141269</v>
+        <v>0.4903522454936856</v>
       </c>
     </row>
     <row r="12">
@@ -4287,19 +4287,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.3257391605769044</v>
+        <v>-0.3293137455125267</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6719677046743946</v>
+        <v>-0.680032484412137</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.077528573381203</v>
+        <v>-1.174126370267408</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3981449985850435</v>
+        <v>-0.4349697882182169</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9863108176508613</v>
+        <v>0.9163512227752509</v>
       </c>
     </row>
     <row r="13">
@@ -4309,22 +4309,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1906766080257514</v>
+        <v>-0.1908984877245453</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3244848216835636</v>
+        <v>-0.326769595088137</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.701480799538139</v>
+        <v>-0.7113398625129642</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.148016596850899</v>
+        <v>-1.254699249285629</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6029769214514941</v>
+        <v>-0.6334998256126102</v>
       </c>
       <c r="I13" t="n">
-        <v>1.14785392129311</v>
+        <v>1.091542891855448</v>
       </c>
     </row>
     <row r="14">
@@ -4334,19 +4334,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.419831080608123</v>
+        <v>-0.4234432439927033</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7868387194934031</v>
+        <v>-0.7978074027463875</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.175913540136838</v>
+        <v>-1.293499470549797</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6502564927560723</v>
+        <v>-0.6825001223669731</v>
       </c>
       <c r="I14" t="n">
-        <v>1.192955098745738</v>
+        <v>1.128810691480445</v>
       </c>
     </row>
     <row r="15">
@@ -4356,19 +4356,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.5084134145169119</v>
+        <v>-0.5132024736234185</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8894551800692696</v>
+        <v>-0.9000096513281735</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.408053283848425</v>
+        <v>-1.520888791072764</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.69557173453861</v>
+        <v>-0.7317650265680545</v>
       </c>
       <c r="I15" t="n">
-        <v>1.13371333827243</v>
+        <v>1.07714886644795</v>
       </c>
     </row>
     <row r="16">
@@ -4378,19 +4378,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.6055253449030371</v>
+        <v>-0.6098761225279847</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9830672920699479</v>
+        <v>-0.9949093211047556</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.457738660320992</v>
+        <v>-1.581809014391615</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7302888255243463</v>
+        <v>-0.7847214248815567</v>
       </c>
       <c r="I16" t="n">
-        <v>1.14314412358338</v>
+        <v>1.132713950441198</v>
       </c>
     </row>
     <row r="17">
@@ -4400,19 +4400,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.6991374569037154</v>
+        <v>-0.7047757923045669</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.078413550994507</v>
+        <v>-1.089808990881338</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.410121469822682</v>
+        <v>-1.55397810985624</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8568835202277976</v>
+        <v>-0.9206504944632208</v>
       </c>
       <c r="I17" t="n">
-        <v>1.280564138114358</v>
+        <v>1.243520125398316</v>
       </c>
     </row>
     <row r="18">
@@ -4422,19 +4422,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.789369172237667</v>
+        <v>-0.7945350219352821</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.182940705006878</v>
+        <v>-1.195889617626231</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.47285877204978</v>
+        <v>-1.612364541755559</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7517572602885484</v>
+        <v>-0.8228957485225054</v>
       </c>
       <c r="I18" t="n">
-        <v>1.258221531307282</v>
+        <v>1.231777752384737</v>
       </c>
     </row>
     <row r="19">
@@ -4444,19 +4444,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.8882800830308365</v>
+        <v>-0.8930158113260749</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.287467859019249</v>
+        <v>-1.300010323997861</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.597183839605751</v>
+        <v>-1.770536581216816</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9168300404935938</v>
+        <v>-0.9856990997982511</v>
       </c>
       <c r="I19" t="n">
-        <v>1.430915807644482</v>
+        <v>1.434701901289665</v>
       </c>
     </row>
     <row r="20">
@@ -4466,19 +4466,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.9853920134169617</v>
+        <v>-0.9914966007168676</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.384579789405374</v>
+        <v>-1.396683972902427</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.814756187549364</v>
+        <v>-1.994932034183421</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.279106452168681</v>
+        <v>-1.346207950463817</v>
       </c>
       <c r="I20" t="n">
-        <v>1.843710420439096</v>
+        <v>1.86070087857123</v>
       </c>
     </row>
     <row r="21">
@@ -4488,22 +4488,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1923672786605271</v>
+        <v>-0.1925942729465113</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.9841376745236209</v>
+        <v>-0.988952450292478</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.39590704276966</v>
+        <v>-1.406886859452284</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.737666222178131</v>
+        <v>-1.918695954860827</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.047446330255029</v>
+        <v>-1.118482109292943</v>
       </c>
       <c r="I21" t="n">
-        <v>2.240334305488726</v>
+        <v>2.252103728492938</v>
       </c>
     </row>
     <row r="22">
@@ -4513,22 +4513,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1571481196752341</v>
+        <v>-0.1585289471326429</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.117142387491102</v>
+        <v>-1.123792422785126</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.407234296133945</v>
+        <v>-1.417089746002141</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.670768973294582</v>
+        <v>-1.872699263449765</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.154001754603723</v>
+        <v>-1.222866428270871</v>
       </c>
       <c r="I22" t="n">
-        <v>2.178150847864372</v>
+        <v>2.160615891868005</v>
       </c>
     </row>
     <row r="23">
@@ -4538,19 +4538,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-1.020030457104977</v>
+        <v>-1.02711877388056</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.499142095230446</v>
+        <v>-1.51024680504868</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.794083322065039</v>
+        <v>-2.007093159780672</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.195825097583893</v>
+        <v>-1.27072426487803</v>
       </c>
       <c r="I23" t="n">
-        <v>2.186913912674214</v>
+        <v>2.160615891868005</v>
       </c>
     </row>
     <row r="24">
@@ -4560,22 +4560,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2256278180786455</v>
+        <v>-0.2274167081518973</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.158007735372463</v>
+        <v>-1.167047047221987</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.469629000366702</v>
+        <v>-1.481666698453423</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.868124653015217</v>
+        <v>-2.06527656189661</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.366961924201556</v>
+        <v>-1.448282682984906</v>
       </c>
       <c r="I24" t="n">
-        <v>1.935471555192675</v>
+        <v>1.899612538557064</v>
       </c>
     </row>
     <row r="25">
@@ -4585,19 +4585,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1.064395623371785</v>
+        <v>-1.073889988175449</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.556587199491694</v>
+        <v>-1.568134238686846</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.70437101146425</v>
+        <v>-1.90787391731587</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.47969285609577</v>
+        <v>-1.558909013237019</v>
       </c>
       <c r="I25" t="n">
-        <v>1.707642320812758</v>
+        <v>1.679995927063406</v>
       </c>
     </row>
     <row r="26">
@@ -4607,22 +4607,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1874232737947609</v>
+        <v>-0.1877298011415063</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.068159907701053</v>
+        <v>-1.078980909383606</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.557841538385034</v>
+        <v>-1.568134238686846</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.556196981370934</v>
+        <v>-1.746467764624444</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.52172485772002</v>
+        <v>-1.608890052397259</v>
       </c>
       <c r="I26" t="n">
-        <v>1.881775035304219</v>
+        <v>1.865308256228681</v>
       </c>
     </row>
     <row r="27">
@@ -4632,28 +4632,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-1.165271838087178</v>
+        <v>-1.175654558288173</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.643199458340298</v>
+        <v>-1.65460177892027</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.68328624366211</v>
+        <v>-1.881737115405219</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.710167421371076</v>
+        <v>-1.798606946980462</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2796871422641454</v>
+        <v>0.2835151618181107</v>
       </c>
       <c r="I27" t="n">
-        <v>2.206300049004712</v>
+        <v>2.200718452853649</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.03503399867171513</v>
+        <v>-0.03223028885762776</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1609914478241022</v>
+        <v>0.1533335261719049</v>
       </c>
     </row>
     <row r="28">
@@ -4663,28 +4663,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-1.258883950087857</v>
+        <v>-1.270554228064755</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.751675148283447</v>
+        <v>-1.762686204212049</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.681743069042134</v>
+        <v>-1.877258129643339</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.658401100545219</v>
+        <v>-1.779608549227782</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5067940201178047</v>
+        <v>0.5222827426997809</v>
       </c>
       <c r="I28" t="n">
-        <v>2.366751502725838</v>
+        <v>2.370523102998979</v>
       </c>
       <c r="J28" t="n">
-        <v>0.143625285560867</v>
+        <v>0.1394037614284172</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3076515025672637</v>
+        <v>0.2763751026566981</v>
       </c>
     </row>
     <row r="29">
@@ -4694,34 +4694,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2223946612919261</v>
+        <v>-0.2232057933641557</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.262648234417125</v>
+        <v>-1.410482501406182</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.757953187409807</v>
+        <v>-1.767777125420206</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2521337221192557</v>
+        <v>0.2472975825015158</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.529244836952108</v>
+        <v>-1.723576564981564</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.681624556989509</v>
+        <v>-1.802419734150926</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7780284510599021</v>
+        <v>0.800021232532933</v>
       </c>
       <c r="I29" t="n">
-        <v>2.172550514542609</v>
+        <v>2.203026942135452</v>
       </c>
       <c r="J29" t="n">
-        <v>0.030864075396902</v>
+        <v>0.01729525716812123</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2858737392177449</v>
+        <v>0.2603547476757932</v>
       </c>
     </row>
     <row r="30">
@@ -4731,34 +4731,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2781701858629719</v>
+        <v>-0.2790491184516147</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.261393895523784</v>
+        <v>-1.410482501406182</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.749155023097136</v>
+        <v>-1.760134179193612</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2769253764924289</v>
+        <v>0.2713392940887268</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.698137732139274</v>
+        <v>-1.89331750871268</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.764650494975472</v>
+        <v>-1.886295946505081</v>
       </c>
       <c r="H30" t="n">
-        <v>1.127329071760526</v>
+        <v>1.152528495266074</v>
       </c>
       <c r="I30" t="n">
-        <v>2.346639940056885</v>
+        <v>2.369951407357849</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.07870991937070332</v>
+        <v>-0.1003923753000152</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2037517720313503</v>
+        <v>0.1701612089681659</v>
       </c>
     </row>
     <row r="31">
@@ -4768,28 +4768,28 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-1.358505825909909</v>
+        <v>-1.507156150310749</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.844501282021695</v>
+        <v>-1.856807828098178</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.560849296087905</v>
+        <v>-1.733887859184953</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.811651842996933</v>
+        <v>-1.9258788122102</v>
       </c>
       <c r="H31" t="n">
-        <v>1.422085393756868</v>
+        <v>1.455591284530271</v>
       </c>
       <c r="I31" t="n">
-        <v>2.410949704366649</v>
+        <v>2.444025481431923</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0165802865364975</v>
+        <v>-0.04023309357463257</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2000664440322522</v>
+        <v>0.1597137451006936</v>
       </c>
     </row>
     <row r="32">
@@ -4799,34 +4799,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3137119205416629</v>
+        <v>-0.3152690092096353</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.36478386503627</v>
+        <v>-1.512247071518906</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.825506268866585</v>
+        <v>-1.836231053910305</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3076616009760591</v>
+        <v>0.301207437404266</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.747165239787217</v>
+        <v>-1.920548152606757</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.963991637381295</v>
+        <v>-2.068833901558063</v>
       </c>
       <c r="H32" t="n">
-        <v>1.70169764581668</v>
+        <v>1.738621717242075</v>
       </c>
       <c r="I32" t="n">
-        <v>2.315335493166552</v>
+        <v>2.337149461917215</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.1969367296091267</v>
+        <v>-0.2512337699325577</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2840183196278149</v>
+        <v>0.2479348367328356</v>
       </c>
     </row>
     <row r="33">
@@ -4836,34 +4836,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3295447177684464</v>
+        <v>-0.3310821214184388</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.500252465517074</v>
+        <v>-1.649607635467595</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.816708104553914</v>
+        <v>-1.826028167360448</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5762980759354455</v>
+        <v>0.5597975575891253</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.652361067247736</v>
+        <v>-1.815614956630797</v>
       </c>
       <c r="G33" t="n">
-        <v>-2.037638713055059</v>
+        <v>-2.148387408837623</v>
       </c>
       <c r="H33" t="n">
-        <v>1.94040488140488</v>
+        <v>1.979776478542435</v>
       </c>
       <c r="I33" t="n">
-        <v>2.342326101773417</v>
+        <v>2.337149461917215</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2454832997482161</v>
+        <v>-0.2750510901567497</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2515150196182537</v>
+        <v>0.2145225076799644</v>
       </c>
     </row>
     <row r="34">
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-1.597364395903199</v>
+        <v>-1.746281284372161</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.910320216554592</v>
+        <v>-1.920927837137031</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.671351792368732</v>
+        <v>-1.858278719061463</v>
       </c>
       <c r="G34" t="n">
-        <v>-2.287604428170027</v>
+        <v>-2.39490055332048</v>
       </c>
       <c r="H34" t="n">
-        <v>2.114702019150981</v>
+        <v>2.155961697077823</v>
       </c>
       <c r="I34" t="n">
-        <v>2.425182287005331</v>
+        <v>2.392714545910463</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.1382143246020935</v>
+        <v>-0.1686277978791219</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2382923102076588</v>
+        <v>0.2030113390840129</v>
       </c>
     </row>
     <row r="35">
@@ -4904,28 +4904,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1.694476326289324</v>
+        <v>-1.842954933276727</v>
       </c>
       <c r="D35" t="n">
-        <v>-2.009231127347761</v>
+        <v>-2.019408626527823</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.557125655118629</v>
+        <v>-1.740567575067667</v>
       </c>
       <c r="G35" t="n">
-        <v>-2.383484846095401</v>
+        <v>-2.4844782031577</v>
       </c>
       <c r="H35" t="n">
-        <v>2.298235593448774</v>
+        <v>2.336575969395863</v>
       </c>
       <c r="I35" t="n">
-        <v>2.379038801733899</v>
+        <v>2.337149461917215</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2900458216912486</v>
+        <v>-0.3199612164050566</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2522491111977337</v>
+        <v>0.2185556203276273</v>
       </c>
     </row>
     <row r="36">
@@ -4935,28 +4935,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-1.800955753789314</v>
+        <v>-1.951039358568507</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.101138926444263</v>
+        <v>-2.112565685574362</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.674061471380669</v>
+        <v>-1.857550626961223</v>
       </c>
       <c r="G36" t="n">
-        <v>-2.467948232124523</v>
+        <v>-2.570475067697161</v>
       </c>
       <c r="H36" t="n">
-        <v>2.478928198405341</v>
+        <v>2.519747906834843</v>
       </c>
       <c r="I36" t="n">
-        <v>2.42985222970037</v>
+        <v>2.378586558425452</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2994533394258228</v>
+        <v>-0.3295686403470339</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2921473417413366</v>
+        <v>0.2583438615310075</v>
       </c>
     </row>
     <row r="37">
@@ -4966,28 +4966,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-1.892863552885816</v>
+        <v>-2.044196417615045</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.203755387020129</v>
+        <v>-2.216686391945991</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.812930714023024</v>
+        <v>-1.996677444622464</v>
       </c>
       <c r="G37" t="n">
-        <v>-2.515553835230809</v>
+        <v>-2.63226124821544</v>
       </c>
       <c r="H37" t="n">
-        <v>2.659237049839716</v>
+        <v>2.697057089029086</v>
       </c>
       <c r="I37" t="n">
-        <v>2.331574570342659</v>
+        <v>2.307010356309389</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2397900157447448</v>
+        <v>-0.2653702954716017</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4774167422453627</v>
+        <v>0.4223347886012199</v>
       </c>
     </row>
     <row r="38">
@@ -4997,28 +4997,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-1.984771351982317</v>
+        <v>-2.137353476661584</v>
       </c>
       <c r="D38" t="n">
-        <v>-2.318510449129979</v>
+        <v>-2.331072195914547</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.018381071656582</v>
+        <v>-2.1812451372339</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.733004973806559</v>
+        <v>-2.854475113074228</v>
       </c>
       <c r="H38" t="n">
-        <v>2.829556272512343</v>
+        <v>2.863781574149154</v>
       </c>
       <c r="I38" t="n">
-        <v>2.460951385591322</v>
+        <v>2.44483375934335</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.3636007032491809</v>
+        <v>-0.3542518605894455</v>
       </c>
       <c r="K38" t="n">
-        <v>0.456068161205373</v>
+        <v>0.3935398583930329</v>
       </c>
     </row>
     <row r="39">
@@ -5028,28 +5028,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-2.078383463982995</v>
+        <v>-2.230510535708122</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.403868369085243</v>
+        <v>-2.41753973614797</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.859285043241015</v>
+        <v>-2.017004276173918</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.77764473485277</v>
+        <v>-2.90077193622353</v>
       </c>
       <c r="H39" t="n">
-        <v>3.012629235709519</v>
+        <v>3.049392582951008</v>
       </c>
       <c r="I39" t="n">
-        <v>2.781175851368792</v>
+        <v>2.776330531409248</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.2429212008862903</v>
+        <v>-0.2430922399885299</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5119931067984115</v>
+        <v>0.4598709193804142</v>
       </c>
     </row>
     <row r="40">
@@ -5059,28 +5059,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-2.168615179316947</v>
+        <v>-2.320269765338837</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.497480481085921</v>
+        <v>-2.512439405924552</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.029565560817394</v>
+        <v>-2.182032063775591</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.700670226138593</v>
+        <v>-2.84721701201615</v>
       </c>
       <c r="H40" t="n">
-        <v>3.229050599926288</v>
+        <v>3.264978038277904</v>
       </c>
       <c r="I40" t="n">
-        <v>2.862174954207447</v>
+        <v>2.904963805460846</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3854817329525316</v>
+        <v>-0.3662404243580126</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7934876316873509</v>
+        <v>0.7107899431166251</v>
       </c>
     </row>
     <row r="41">
@@ -5090,28 +5090,28 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-2.262227291317625</v>
+        <v>-2.415169435115419</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.584438680210913</v>
+        <v>-2.600540265424548</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.068969058320991</v>
+        <v>-2.22864417728612</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.805892509093408</v>
+        <v>-2.946321510221482</v>
       </c>
       <c r="H41" t="n">
-        <v>3.348711450004243</v>
+        <v>3.383981927730038</v>
       </c>
       <c r="I41" t="n">
-        <v>2.868606983112675</v>
+        <v>2.903241434562361</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4454353273874031</v>
+        <v>-0.4163604976562572</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8658614930755913</v>
+        <v>0.7865830112041912</v>
       </c>
     </row>
     <row r="42">
@@ -5121,28 +5121,28 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-2.1651153609315</v>
+        <v>-2.318495786210853</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.679784939135472</v>
+        <v>-2.69543993520113</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.14619414713012</v>
+        <v>-2.289746200760543</v>
       </c>
       <c r="G42" t="n">
-        <v>-2.675891414049301</v>
+        <v>-2.824360777234446</v>
       </c>
       <c r="H42" t="n">
-        <v>3.389872805683598</v>
+        <v>3.413048082739468</v>
       </c>
       <c r="I42" t="n">
-        <v>2.840997555503248</v>
+        <v>2.884719739897945</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4648876195618508</v>
+        <v>-0.4313561068068984</v>
       </c>
       <c r="K42" t="n">
-        <v>1.01231185960933</v>
+        <v>0.9289149982218989</v>
       </c>
     </row>
     <row r="43">
@@ -5152,28 +5152,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-2.257023160028001</v>
+        <v>-2.411652845257392</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.784312093147843</v>
+        <v>-2.801520561946023</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.189521301957499</v>
+        <v>-2.33618051901382</v>
       </c>
       <c r="G43" t="n">
-        <v>-2.817923844436074</v>
+        <v>-2.969070768364802</v>
       </c>
       <c r="H43" t="n">
-        <v>3.483236893858003</v>
+        <v>3.501721362058604</v>
       </c>
       <c r="I43" t="n">
-        <v>2.872448438352175</v>
+        <v>2.906777440766834</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4440062235727859</v>
+        <v>-0.4080158302757627</v>
       </c>
       <c r="K43" t="n">
-        <v>1.084365375361459</v>
+        <v>1.004190410839738</v>
       </c>
     </row>
     <row r="44">
@@ -5183,28 +5183,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-2.161676901103442</v>
+        <v>-2.31675317548081</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.885057180619008</v>
+        <v>-2.901843548611526</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.968272687006882</v>
+        <v>-2.112562518532895</v>
       </c>
       <c r="G44" t="n">
-        <v>-2.961613242590512</v>
+        <v>-3.094800869989792</v>
       </c>
       <c r="H44" t="n">
-        <v>3.637377677419876</v>
+        <v>3.649710972700322</v>
       </c>
       <c r="I44" t="n">
-        <v>2.954686431182994</v>
+        <v>2.99876303730664</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.359237065808099</v>
+        <v>-0.3225334865197391</v>
       </c>
       <c r="K44" t="n">
-        <v>1.09606727113318</v>
+        <v>1.015796997639095</v>
       </c>
     </row>
     <row r="45">
@@ -5214,28 +5214,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2.264293361679309</v>
+        <v>-2.420873881852439</v>
       </c>
       <c r="D45" t="n">
-        <v>-2.97528889595296</v>
+        <v>-2.991602778242241</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.937260513450046</v>
+        <v>-2.080577021602245</v>
       </c>
       <c r="G45" t="n">
-        <v>-2.665300875913426</v>
+        <v>-2.795723695172725</v>
       </c>
       <c r="H45" t="n">
-        <v>3.841518046310107</v>
+        <v>3.847725550231264</v>
       </c>
       <c r="I45" t="n">
-        <v>3.170710771953785</v>
+        <v>3.190487175237674</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.3262406255139894</v>
+        <v>-0.304336634862314</v>
       </c>
       <c r="K45" t="n">
-        <v>1.273254292005875</v>
+        <v>1.196238652553142</v>
       </c>
     </row>
     <row r="46">
@@ -5245,28 +5245,28 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-2.361405292065434</v>
+        <v>-2.517547530757005</v>
       </c>
       <c r="D46" t="n">
-        <v>-3.072400826339085</v>
+        <v>-3.088276427146807</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.10964402048652</v>
+        <v>-2.230594924250381</v>
       </c>
       <c r="G46" t="n">
-        <v>-2.933980838878154</v>
+        <v>-3.055646061280137</v>
       </c>
       <c r="H46" t="n">
-        <v>3.968961648449134</v>
+        <v>3.973608636098493</v>
       </c>
       <c r="I46" t="n">
-        <v>3.620205721448735</v>
+        <v>3.634931619682118</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.3238021605512161</v>
+        <v>-0.2992449071757222</v>
       </c>
       <c r="K46" t="n">
-        <v>1.45820745596444</v>
+        <v>1.383063631812574</v>
       </c>
     </row>
     <row r="47">
@@ -5276,34 +5276,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.4047022939242</v>
+        <v>-0.4062038231987359</v>
       </c>
       <c r="C47" t="n">
-        <v>-2.355127252939074</v>
+        <v>-2.509904584530411</v>
       </c>
       <c r="D47" t="n">
-        <v>-3.055977885461175</v>
+        <v>-3.070318911283991</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8356760383345312</v>
+        <v>0.8191132597929227</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.237949562601755</v>
+        <v>-2.361023847639464</v>
       </c>
       <c r="G47" t="n">
-        <v>-3.064293512795139</v>
+        <v>-3.196370847353544</v>
       </c>
       <c r="H47" t="n">
-        <v>4.084257013378354</v>
+        <v>4.087036087849733</v>
       </c>
       <c r="I47" t="n">
-        <v>3.62393966758958</v>
+        <v>3.627657458292674</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.2491372516838193</v>
+        <v>-0.219670697537785</v>
       </c>
       <c r="K47" t="n">
-        <v>1.569405821724786</v>
+        <v>1.499737607824208</v>
       </c>
     </row>
     <row r="48">
@@ -5313,34 +5313,34 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.457760021347598</v>
+        <v>-0.4599460595208605</v>
       </c>
       <c r="C48" t="n">
-        <v>-2.222122539971592</v>
+        <v>-2.377540633118318</v>
       </c>
       <c r="D48" t="n">
-        <v>-3.062255924587536</v>
+        <v>-3.075409832492148</v>
       </c>
       <c r="E48" t="n">
-        <v>1.111588835118232</v>
+        <v>1.096411415938633</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.20549324567339</v>
+        <v>-2.335219805461489</v>
       </c>
       <c r="G48" t="n">
-        <v>-3.019281217092074</v>
+        <v>-3.152205563440149</v>
       </c>
       <c r="H48" t="n">
-        <v>4.15607610890797</v>
+        <v>4.150608488190873</v>
       </c>
       <c r="I48" t="n">
-        <v>3.503238358961809</v>
+        <v>3.515020095655311</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.1788961910147352</v>
+        <v>-0.1541712685490913</v>
       </c>
       <c r="K48" t="n">
-        <v>1.714130631289997</v>
+        <v>1.649986930567474</v>
       </c>
     </row>
     <row r="49">
@@ -5350,28 +5350,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-2.319234470357717</v>
+        <v>-2.47602142250911</v>
       </c>
       <c r="D49" t="n">
-        <v>-3.155868036588214</v>
+        <v>-3.17030950226873</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.405666511753356</v>
+        <v>-2.554002219082121</v>
       </c>
       <c r="G49" t="n">
-        <v>-3.268141944894806</v>
+        <v>-3.388232437607219</v>
       </c>
       <c r="H49" t="n">
-        <v>4.36244532946873</v>
+        <v>4.351819510137824</v>
       </c>
       <c r="I49" t="n">
-        <v>3.732945344035651</v>
+        <v>3.737661605089274</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.08716453046351724</v>
+        <v>-0.0828320375806</v>
       </c>
       <c r="K49" t="n">
-        <v>1.748969591827348</v>
+        <v>1.679950734381782</v>
       </c>
     </row>
     <row r="50">
@@ -5381,28 +5381,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-2.416346400743843</v>
+        <v>-2.572695071413676</v>
       </c>
       <c r="D50" t="n">
-        <v>-3.260395190600585</v>
+        <v>-3.27443020864036</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.481064683133013</v>
+        <v>-2.617960655182894</v>
       </c>
       <c r="G50" t="n">
-        <v>-3.368097217608958</v>
+        <v>-3.495412448465567</v>
       </c>
       <c r="H50" t="n">
-        <v>4.415499544236987</v>
+        <v>4.401433970343938</v>
       </c>
       <c r="I50" t="n">
-        <v>3.667742269236181</v>
+        <v>3.663383469818453</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.2422384377213554</v>
+        <v>-0.2200341446827321</v>
       </c>
       <c r="K50" t="n">
-        <v>1.871504389382778</v>
+        <v>1.808379937577058</v>
       </c>
     </row>
     <row r="51">
@@ -5412,28 +5412,28 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-2.315601313272678</v>
+        <v>-2.472372084748173</v>
       </c>
       <c r="D51" t="n">
-        <v>-3.352302989697086</v>
+        <v>-3.367587267686898</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.694749056743914</v>
+        <v>-2.827201927552017</v>
       </c>
       <c r="G51" t="n">
-        <v>-3.413184569314331</v>
+        <v>-3.541852252985133</v>
       </c>
       <c r="H51" t="n">
-        <v>4.337402979118751</v>
+        <v>4.318080077487453</v>
       </c>
       <c r="I51" t="n">
-        <v>3.674827289479095</v>
+        <v>3.662009843444827</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.1447836069207578</v>
+        <v>-0.1272059900535706</v>
       </c>
       <c r="K51" t="n">
-        <v>1.925283389507029</v>
+        <v>1.857221735941672</v>
       </c>
     </row>
     <row r="52">
@@ -5443,34 +5443,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.6074646215574483</v>
+        <v>-0.6085923088202361</v>
       </c>
       <c r="C52" t="n">
-        <v>-2.453578591540164</v>
+        <v>-2.609732648696862</v>
       </c>
       <c r="D52" t="n">
-        <v>-3.368725930574996</v>
+        <v>-3.382944645607747</v>
       </c>
       <c r="E52" t="n">
-        <v>1.126493514140529</v>
+        <v>1.110336136606681</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.715475632480819</v>
+        <v>-2.848713715122688</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.685127097369194</v>
+        <v>-3.828329744047831</v>
       </c>
       <c r="H52" t="n">
-        <v>4.379192650318498</v>
+        <v>4.355088084389722</v>
       </c>
       <c r="I52" t="n">
-        <v>3.83081632427766</v>
+        <v>3.811081041944813</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.2409458196920335</v>
+        <v>-0.2229397932121512</v>
       </c>
       <c r="K52" t="n">
-        <v>2.129867630953485</v>
+        <v>2.06458234266266</v>
       </c>
     </row>
     <row r="53">
@@ -5480,28 +5480,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-2.552489502333333</v>
+        <v>-2.710055635362365</v>
       </c>
       <c r="D53" t="n">
-        <v>-3.477201620518144</v>
+        <v>-3.491029070899526</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.488005316348156</v>
+        <v>-2.62191678023301</v>
       </c>
       <c r="G53" t="n">
-        <v>-3.809740213319231</v>
+        <v>-3.959435380189712</v>
       </c>
       <c r="H53" t="n">
-        <v>4.434662662263626</v>
+        <v>4.404151823881653</v>
       </c>
       <c r="I53" t="n">
-        <v>3.633389799825873</v>
+        <v>3.620470398006921</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.1578479091016126</v>
+        <v>-0.1436295951452849</v>
       </c>
       <c r="K53" t="n">
-        <v>2.214076854078523</v>
+        <v>2.152630709655277</v>
       </c>
     </row>
     <row r="54">
@@ -5511,28 +5511,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-2.460581703236832</v>
+        <v>-2.810378622027868</v>
       </c>
       <c r="D54" t="n">
-        <v>-3.57431355090427</v>
+        <v>-3.587702719804092</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.428562116195075</v>
+        <v>-2.554702362049627</v>
       </c>
       <c r="G54" t="n">
-        <v>-4.184421193976831</v>
+        <v>-4.340801629388917</v>
       </c>
       <c r="H54" t="n">
-        <v>4.443628618151466</v>
+        <v>4.408075178028759</v>
       </c>
       <c r="I54" t="n">
-        <v>3.642152864635715</v>
+        <v>3.657532863839976</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.3294809800727519</v>
+        <v>-0.3184686039419476</v>
       </c>
       <c r="K54" t="n">
-        <v>2.350220617290007</v>
+        <v>2.293512605198068</v>
       </c>
     </row>
     <row r="55">
@@ -5542,28 +5542,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-2.557693633622957</v>
+        <v>-2.907052270932434</v>
       </c>
       <c r="D55" t="n">
-        <v>-3.666221350000771</v>
+        <v>-3.679146836956216</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.601583110269194</v>
+        <v>-2.720390595754149</v>
       </c>
       <c r="G55" t="n">
-        <v>-4.472035064164707</v>
+        <v>-4.621046644670717</v>
       </c>
       <c r="H55" t="n">
-        <v>4.42942635114569</v>
+        <v>4.383374349908404</v>
       </c>
       <c r="I55" t="n">
-        <v>3.817077119878318</v>
+        <v>3.824457329062373</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.454925353192961</v>
+        <v>-0.4439698035258056</v>
       </c>
       <c r="K55" t="n">
-        <v>2.465532625538042</v>
+        <v>2.410965460435279</v>
       </c>
     </row>
     <row r="56">
@@ -5573,31 +5573,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.6864546721434168</v>
+        <v>-0.68788709670327</v>
       </c>
       <c r="C56" t="n">
-        <v>-2.464081521622279</v>
+        <v>-2.812152601155852</v>
       </c>
       <c r="D56" t="n">
-        <v>-3.763333280386897</v>
+        <v>-3.777627626347009</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.560506255342911</v>
+        <v>-2.678270085154475</v>
       </c>
       <c r="G56" t="n">
-        <v>-4.507331778735038</v>
+        <v>-4.662510441179854</v>
       </c>
       <c r="H56" t="n">
-        <v>4.489984219858279</v>
+        <v>4.436118414003003</v>
       </c>
       <c r="I56" t="n">
-        <v>3.807646334567368</v>
+        <v>3.787064533179011</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.3388720133618429</v>
+        <v>-0.3151530675695409</v>
       </c>
       <c r="K56" t="n">
-        <v>2.472591881484538</v>
+        <v>2.417542457451769</v>
       </c>
     </row>
     <row r="57">
@@ -5607,34 +5607,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.762535225341735</v>
+        <v>-0.7637582403004984</v>
       </c>
       <c r="C57" t="n">
-        <v>-2.36517061082911</v>
+        <v>-2.713671811765059</v>
       </c>
       <c r="D57" t="n">
-        <v>-3.860445210773022</v>
+        <v>-3.874301275251575</v>
       </c>
       <c r="E57" t="n">
-        <v>1.365384352017308</v>
+        <v>1.349260955937693</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.885245978883446</v>
+        <v>-2.982601543915814</v>
       </c>
       <c r="G57" t="n">
-        <v>-4.377492288562055</v>
+        <v>-4.528891499423192</v>
       </c>
       <c r="H57" t="n">
-        <v>4.49174793619131</v>
+        <v>4.431139050287213</v>
       </c>
       <c r="I57" t="n">
-        <v>3.780364419917836</v>
+        <v>3.768542838514595</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.2922464603059169</v>
+        <v>-0.2713428622685469</v>
       </c>
       <c r="K57" t="n">
-        <v>2.47800157298831</v>
+        <v>2.424072549488345</v>
       </c>
     </row>
     <row r="58">
@@ -5644,22 +5644,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>-2.948426191585197</v>
+        <v>-3.034366245893959</v>
       </c>
       <c r="G58" t="n">
-        <v>-4.135769239209364</v>
+        <v>-4.294144839233086</v>
       </c>
       <c r="H58" t="n">
-        <v>4.411108892682837</v>
+        <v>4.344191596429319</v>
       </c>
       <c r="I58" t="n">
-        <v>3.93806526725389</v>
+        <v>3.97421850130298</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.2439640325041712</v>
+        <v>-0.223379642009341</v>
       </c>
       <c r="K58" t="n">
-        <v>2.521044185029794</v>
+        <v>2.46891270505092</v>
       </c>
     </row>
     <row r="59">
@@ -5669,22 +5669,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>-2.892658907212907</v>
+        <v>-2.974351549989325</v>
       </c>
       <c r="G59" t="n">
-        <v>-4.214012663145867</v>
+        <v>-4.396427532417976</v>
       </c>
       <c r="H59" t="n">
-        <v>4.558211609288487</v>
+        <v>4.479155117901926</v>
       </c>
       <c r="I59" t="n">
-        <v>3.637760063277037</v>
+        <v>3.644103411991935</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.3454923318390263</v>
+        <v>-0.3245398678983025</v>
       </c>
       <c r="K59" t="n">
-        <v>2.602055149733376</v>
+        <v>2.543631862981792</v>
       </c>
     </row>
     <row r="60">
@@ -5694,22 +5694,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-2.663867106728578</v>
+        <v>-2.74815705028842</v>
       </c>
       <c r="G60" t="n">
-        <v>-4.008552457032367</v>
+        <v>-4.181569636753881</v>
       </c>
       <c r="H60" t="n">
-        <v>4.467675291517417</v>
+        <v>4.381397574861874</v>
       </c>
       <c r="I60" t="n">
-        <v>3.775156080483986</v>
+        <v>3.774292322972759</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.3012312565801278</v>
+        <v>-0.2818117650761777</v>
       </c>
       <c r="K60" t="n">
-        <v>2.731125706157715</v>
+        <v>2.671733718358795</v>
       </c>
     </row>
     <row r="61">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>-2.602642435042136</v>
+        <v>-2.698297974405271</v>
       </c>
       <c r="G61" t="n">
-        <v>-4.39615722260926</v>
+        <v>-4.570382986072164</v>
       </c>
       <c r="H61" t="n">
-        <v>4.442627488409127</v>
+        <v>4.343851765672873</v>
       </c>
       <c r="I61" t="n">
-        <v>3.798191501162119</v>
+        <v>3.806372472717719</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.2667974349271173</v>
+        <v>-0.2577596032744379</v>
       </c>
       <c r="K61" t="n">
-        <v>2.905474904211304</v>
+        <v>2.85803471692533</v>
       </c>
     </row>
     <row r="62">
@@ -5744,34 +5744,34 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.8074593354879145</v>
+        <v>-0.8093610364959993</v>
       </c>
       <c r="C62" t="n">
-        <v>-2.462282541215235</v>
+        <v>-2.810345460669625</v>
       </c>
       <c r="D62" t="n">
-        <v>-3.763333280386897</v>
+        <v>-3.775820485860782</v>
       </c>
       <c r="E62" t="n">
-        <v>1.59212837877953</v>
+        <v>1.570054261625272</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.661812073282117</v>
+        <v>-2.751107121276714</v>
       </c>
       <c r="G62" t="n">
-        <v>-4.468863824037387</v>
+        <v>-4.65206780906178</v>
       </c>
       <c r="H62" t="n">
-        <v>4.367427281200708</v>
+        <v>4.264878928530202</v>
       </c>
       <c r="I62" t="n">
-        <v>3.862501265471884</v>
+        <v>3.861937556710967</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.06995054829249309</v>
+        <v>-0.07538273737987128</v>
       </c>
       <c r="K62" t="n">
-        <v>3.026241146621144</v>
+        <v>2.967680616022214</v>
       </c>
     </row>
     <row r="63">
@@ -5781,22 +5781,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>-2.610678090534477</v>
+        <v>-2.698491141472267</v>
       </c>
       <c r="G63" t="n">
-        <v>-4.754302231162301</v>
+        <v>-4.928229886230024</v>
       </c>
       <c r="H63" t="n">
-        <v>4.228905128896836</v>
+        <v>4.113501217176421</v>
       </c>
       <c r="I63" t="n">
-        <v>3.92721312868302</v>
+        <v>3.937169506814807</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.1519685884018848</v>
+        <v>-0.1962866433878545</v>
       </c>
       <c r="K63" t="n">
-        <v>3.242238906197962</v>
+        <v>3.170873449025847</v>
       </c>
     </row>
     <row r="64">
@@ -5806,22 +5806,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>-2.72326292342262</v>
+        <v>-2.796730305086333</v>
       </c>
       <c r="G64" t="n">
-        <v>-5.003103174597493</v>
+        <v>-5.194616792374864</v>
       </c>
       <c r="H64" t="n">
-        <v>4.157764524946486</v>
+        <v>4.017961868399556</v>
       </c>
       <c r="I64" t="n">
-        <v>4.374474791969024</v>
+        <v>4.396503509993044</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.2687327671465649</v>
+        <v>-0.2837635869393907</v>
       </c>
       <c r="K64" t="n">
-        <v>3.399769235753673</v>
+        <v>3.310367231248414</v>
       </c>
     </row>
     <row r="65">
@@ -5831,22 +5831,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>-2.795253156018561</v>
+        <v>-2.857029917974927</v>
       </c>
       <c r="G65" t="n">
-        <v>-5.010679512421055</v>
+        <v>-5.194543359483276</v>
       </c>
       <c r="H65" t="n">
-        <v>4.122953302676064</v>
+        <v>3.959889468118791</v>
       </c>
       <c r="I65" t="n">
-        <v>4.628722453272402</v>
+        <v>4.645013807257688</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.4547448386762832</v>
+        <v>-0.4551301455587141</v>
       </c>
       <c r="K65" t="n">
-        <v>3.481783544073797</v>
+        <v>3.408085867941299</v>
       </c>
     </row>
     <row r="66">
@@ -5856,34 +5856,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8166116298900957</v>
+        <v>-0.8192822845368455</v>
       </c>
       <c r="C66" t="n">
-        <v>-2.554190340311736</v>
+        <v>-2.903502519716164</v>
       </c>
       <c r="D66" t="n">
-        <v>-3.658806126374526</v>
+        <v>-3.671699779489152</v>
       </c>
       <c r="E66" t="n">
-        <v>1.843106318542099</v>
+        <v>1.820698855340824</v>
       </c>
       <c r="F66" t="n">
-        <v>-2.932445319446438</v>
+        <v>-3.003890260625584</v>
       </c>
       <c r="G66" t="n">
-        <v>-5.279321861432812</v>
+        <v>-5.466300499880492</v>
       </c>
       <c r="H66" t="n">
-        <v>4.147739977098888</v>
+        <v>3.967490704513664</v>
       </c>
       <c r="I66" t="n">
-        <v>4.523547995573301</v>
+        <v>4.567931743440388</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.4531989416371314</v>
+        <v>-0.4929177531758942</v>
       </c>
       <c r="K66" t="n">
-        <v>3.726214187206276</v>
+        <v>3.673944157368368</v>
       </c>
     </row>
     <row r="67">
@@ -5893,22 +5893,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>-3.063947435860254</v>
+        <v>-3.138507854710965</v>
       </c>
       <c r="G67" t="n">
-        <v>-5.426063759942134</v>
+        <v>-5.625453534183349</v>
       </c>
       <c r="H67" t="n">
-        <v>4.233363181135711</v>
+        <v>4.04635401358993</v>
       </c>
       <c r="I67" t="n">
-        <v>4.423750265534697</v>
+        <v>4.458041633550279</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.4891361716920413</v>
+        <v>-0.5463136364931416</v>
       </c>
       <c r="K67" t="n">
-        <v>3.717644969192115</v>
+        <v>3.649309819246361</v>
       </c>
     </row>
     <row r="68">
@@ -5918,22 +5918,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>-2.995699716840642</v>
+        <v>-3.073640840648408</v>
       </c>
       <c r="G68" t="n">
-        <v>-5.811292357076576</v>
+        <v>-6.017084205186277</v>
       </c>
       <c r="H68" t="n">
-        <v>4.466457016529358</v>
+        <v>4.259678108781321</v>
       </c>
       <c r="I68" t="n">
-        <v>4.377959019743452</v>
+        <v>4.421004596513241</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.5892444398155477</v>
+        <v>-0.658768046156133</v>
       </c>
       <c r="K68" t="n">
-        <v>3.642485651037341</v>
+        <v>3.584411233208384</v>
       </c>
     </row>
     <row r="69">
@@ -5943,22 +5943,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>-2.976025096244898</v>
+        <v>-3.032449380701635</v>
       </c>
       <c r="G69" t="n">
-        <v>-5.733875741638238</v>
+        <v>-5.928712445230697</v>
       </c>
       <c r="H69" t="n">
-        <v>4.494623213279431</v>
+        <v>4.274301692149723</v>
       </c>
       <c r="I69" t="n">
-        <v>4.568815102890921</v>
+        <v>4.621475000926277</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.5638078807028176</v>
+        <v>-0.611917565972904</v>
       </c>
       <c r="K69" t="n">
-        <v>3.734237488267101</v>
+        <v>3.684562648336185</v>
       </c>
     </row>
     <row r="70">
@@ -5968,22 +5968,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>-3.159926987627875</v>
+        <v>-3.214457684641763</v>
       </c>
       <c r="G70" t="n">
-        <v>-6.079908785949627</v>
+        <v>-6.245931672132367</v>
       </c>
       <c r="H70" t="n">
-        <v>4.55234153378144</v>
+        <v>4.319148985925167</v>
       </c>
       <c r="I70" t="n">
-        <v>4.598504711527897</v>
+        <v>4.659936539387815</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.5960179158808085</v>
+        <v>-0.6364925658473454</v>
       </c>
       <c r="K70" t="n">
-        <v>3.991088993181181</v>
+        <v>3.969444634488563</v>
       </c>
     </row>
     <row r="71">
@@ -5993,22 +5993,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>-3.245478840403894</v>
+        <v>-3.279566531811952</v>
       </c>
       <c r="G71" t="n">
-        <v>-6.118184594757594</v>
+        <v>-6.258032291157935</v>
       </c>
       <c r="H71" t="n">
-        <v>4.784950502105543</v>
+        <v>4.549208637126697</v>
       </c>
       <c r="I71" t="n">
-        <v>4.956200925821769</v>
+        <v>4.993041170605654</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.6386012673250265</v>
+        <v>-0.6760313394496217</v>
       </c>
       <c r="K71" t="n">
-        <v>4.115931912603505</v>
+        <v>4.112013794222318</v>
       </c>
     </row>
     <row r="72">
@@ -6018,34 +6018,34 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.7835675255794577</v>
+        <v>-0.7893420027050325</v>
       </c>
       <c r="C72" t="n">
-        <v>-2.460578228311058</v>
+        <v>-2.810345460669625</v>
       </c>
       <c r="D72" t="n">
-        <v>-3.565194014373847</v>
+        <v>-3.57680010971257</v>
       </c>
       <c r="E72" t="n">
-        <v>2.080474182213456</v>
+        <v>2.060557765482991</v>
       </c>
       <c r="F72" t="n">
-        <v>-3.256847747007582</v>
+        <v>-3.303028728435803</v>
       </c>
       <c r="G72" t="n">
-        <v>-6.163301779254549</v>
+        <v>-6.283127637486512</v>
       </c>
       <c r="H72" t="n">
-        <v>4.715994492275264</v>
+        <v>4.482389118526756</v>
       </c>
       <c r="I72" t="n">
-        <v>5.001349173800206</v>
+        <v>5.010889122173078</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.5806509018909476</v>
+        <v>-0.6147589092294935</v>
       </c>
       <c r="K72" t="n">
-        <v>4.186326962855709</v>
+        <v>4.174112686286619</v>
       </c>
     </row>
     <row r="73">
@@ -6055,22 +6055,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>-3.415195494019375</v>
+        <v>-3.463481541653394</v>
       </c>
       <c r="G73" t="n">
-        <v>-6.049661804102487</v>
+        <v>-6.157875080128958</v>
       </c>
       <c r="H73" t="n">
-        <v>4.602621933584345</v>
+        <v>4.366801564151894</v>
       </c>
       <c r="I73" t="n">
-        <v>4.839988368975517</v>
+        <v>4.855566021277191</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.5238474577785088</v>
+        <v>-0.6043351820675907</v>
       </c>
       <c r="K73" t="n">
-        <v>4.020466979365865</v>
+        <v>4.008653768820089</v>
       </c>
     </row>
     <row r="74">
@@ -6080,22 +6080,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>-3.473886305812658</v>
+        <v>-3.489868856155521</v>
       </c>
       <c r="G74" t="n">
-        <v>-6.053471949399212</v>
+        <v>-6.145985338331729</v>
       </c>
       <c r="H74" t="n">
-        <v>4.561138022385576</v>
+        <v>4.3233314333523</v>
       </c>
       <c r="I74" t="n">
-        <v>5.105487021266623</v>
+        <v>5.07752142436467</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.5283808579554444</v>
+        <v>-0.5860110396792054</v>
       </c>
       <c r="K74" t="n">
-        <v>3.934643834773322</v>
+        <v>3.933692743939836</v>
       </c>
     </row>
     <row r="75">
@@ -6105,22 +6105,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>-3.787968977452868</v>
+        <v>-3.80831635456345</v>
       </c>
       <c r="G75" t="n">
-        <v>-6.124471667949749</v>
+        <v>-6.200732935895425</v>
       </c>
       <c r="H75" t="n">
-        <v>4.849068109457583</v>
+        <v>4.606262566772645</v>
       </c>
       <c r="I75" t="n">
-        <v>5.169481635876638</v>
+        <v>5.133086508357917</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.5732316222448035</v>
+        <v>-0.6342420034895786</v>
       </c>
       <c r="K75" t="n">
-        <v>4.055185471264825</v>
+        <v>4.052117161291458</v>
       </c>
     </row>
     <row r="76">
@@ -6130,34 +6130,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.7555531776251875</v>
+        <v>-0.76337885832198</v>
       </c>
       <c r="C76" t="n">
-        <v>-2.559489139104228</v>
+        <v>-2.910668447335128</v>
       </c>
       <c r="D76" t="n">
-        <v>-3.466283103580678</v>
+        <v>-3.476477123047067</v>
       </c>
       <c r="E76" t="n">
-        <v>2.293525341673289</v>
+        <v>2.275571336011414</v>
       </c>
       <c r="F76" t="n">
-        <v>-3.913960109266042</v>
+        <v>-3.933822583141374</v>
       </c>
       <c r="G76" t="n">
-        <v>-6.007844917065768</v>
+        <v>-6.167495945138006</v>
       </c>
       <c r="H76" t="n">
-        <v>4.937008241006584</v>
+        <v>4.684968141987487</v>
       </c>
       <c r="I76" t="n">
-        <v>5.087608320512756</v>
+        <v>5.060284310555719</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.7315565954213616</v>
+        <v>-0.7984549829306875</v>
       </c>
       <c r="K76" t="n">
-        <v>4.156653012845788</v>
+        <v>4.156976503212132</v>
       </c>
     </row>
     <row r="77">
@@ -6167,22 +6167,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>-3.888028607706628</v>
+        <v>-3.916772574160359</v>
       </c>
       <c r="G77" t="n">
-        <v>-5.91097344633962</v>
+        <v>-6.070515580430857</v>
       </c>
       <c r="H77" t="n">
-        <v>4.690832589275306</v>
+        <v>4.430935453576219</v>
       </c>
       <c r="I77" t="n">
-        <v>5.184492589835494</v>
+        <v>5.12961882774644</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.8533861903543059</v>
+        <v>-0.9113684139599274</v>
       </c>
       <c r="K77" t="n">
-        <v>4.100405922979627</v>
+        <v>4.095234620718062</v>
       </c>
     </row>
     <row r="78">
@@ -6192,34 +6192,34 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.8336975969374114</v>
+        <v>-0.8473115119642258</v>
       </c>
       <c r="C78" t="n">
-        <v>-2.460578228311058</v>
+        <v>-2.812187657944336</v>
       </c>
       <c r="D78" t="n">
-        <v>-3.367372192787508</v>
+        <v>-3.376154136381564</v>
       </c>
       <c r="E78" t="n">
-        <v>2.495059772682719</v>
+        <v>2.4990905979588</v>
       </c>
       <c r="F78" t="n">
-        <v>-3.961190114903877</v>
+        <v>-4.039657122156989</v>
       </c>
       <c r="G78" t="n">
-        <v>-5.879896254728707</v>
+        <v>-6.06317545704825</v>
       </c>
       <c r="H78" t="n">
-        <v>4.614649095311214</v>
+        <v>4.338655843559828</v>
       </c>
       <c r="I78" t="n">
-        <v>5.37654110735571</v>
+        <v>5.295742069258627</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.8789422846082053</v>
+        <v>-0.9267709448786581</v>
       </c>
       <c r="K78" t="n">
-        <v>4.183671402103054</v>
+        <v>4.189823406415466</v>
       </c>
     </row>
     <row r="79">
@@ -6229,34 +6229,34 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.803697268919595</v>
+        <v>-0.818607053050101</v>
       </c>
       <c r="C79" t="n">
-        <v>-2.36696611631038</v>
+        <v>-2.717287988167754</v>
       </c>
       <c r="D79" t="n">
-        <v>-3.275464393691006</v>
+        <v>-3.28471001922944</v>
       </c>
       <c r="E79" t="n">
-        <v>2.717086555717799</v>
+        <v>2.723550029977066</v>
       </c>
       <c r="F79" t="n">
-        <v>-4.134397543746855</v>
+        <v>-4.200987532737566</v>
       </c>
       <c r="G79" t="n">
-        <v>-5.975782664429842</v>
+        <v>-6.139952457509159</v>
       </c>
       <c r="H79" t="n">
-        <v>4.522696334606932</v>
+        <v>4.24287920996557</v>
       </c>
       <c r="I79" t="n">
-        <v>5.586588356727501</v>
+        <v>5.517315620934321</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.8160754797390357</v>
+        <v>-0.8564931214575734</v>
       </c>
       <c r="K79" t="n">
-        <v>4.016413146122919</v>
+        <v>4.013289761249089</v>
       </c>
     </row>
     <row r="80">
@@ -6266,34 +6266,34 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.8574899187110936</v>
+        <v>-0.8778368278145893</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.465877027103549</v>
+        <v>-2.815768777558546</v>
       </c>
       <c r="D80" t="n">
-        <v>-3.174719306219842</v>
+        <v>-3.184387032563937</v>
       </c>
       <c r="E80" t="n">
-        <v>2.66707872991366</v>
+        <v>2.672583913383016</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.314575073199296</v>
+        <v>-4.361553413203281</v>
       </c>
       <c r="G80" t="n">
-        <v>-6.133451768265559</v>
+        <v>-6.31398516888586</v>
       </c>
       <c r="H80" t="n">
-        <v>4.480444858686337</v>
+        <v>4.184606091091395</v>
       </c>
       <c r="I80" t="n">
-        <v>5.633789985799813</v>
+        <v>5.573605314339277</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.7372455391073122</v>
+        <v>-0.7706930786065114</v>
       </c>
       <c r="K80" t="n">
-        <v>4.067772497360506</v>
+        <v>4.058026760114037</v>
       </c>
     </row>
     <row r="81">
@@ -6303,22 +6303,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>-4.625886752418196</v>
+        <v>-4.697670895978107</v>
       </c>
       <c r="G81" t="n">
-        <v>-6.125292639216335</v>
+        <v>-6.323519212056222</v>
       </c>
       <c r="H81" t="n">
-        <v>4.310985124908728</v>
+        <v>4.006697109412318</v>
       </c>
       <c r="I81" t="n">
-        <v>5.616029490698745</v>
+        <v>5.53111782934085</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.676607249845765</v>
+        <v>-0.6744389636040407</v>
       </c>
       <c r="K81" t="n">
-        <v>4.234746001729429</v>
+        <v>4.222137135667207</v>
       </c>
     </row>
     <row r="82">
@@ -6328,22 +6328,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>-4.619853535090741</v>
+        <v>-4.682400726579401</v>
       </c>
       <c r="G82" t="n">
-        <v>-6.085731973009825</v>
+        <v>-6.253809966340564</v>
       </c>
       <c r="H82" t="n">
-        <v>4.195401386118873</v>
+        <v>3.881726242778288</v>
       </c>
       <c r="I82" t="n">
-        <v>5.621100484613552</v>
+        <v>5.508386626326553</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.744223645838521</v>
+        <v>-0.7360815414098654</v>
       </c>
       <c r="K82" t="n">
-        <v>4.511822995341286</v>
+        <v>4.510458373150694</v>
       </c>
     </row>
   </sheetData>

--- a/output/multi_factor_reports/factor_collinearity_report_P10.xlsx
+++ b/output/multi_factor_reports/factor_collinearity_report_P10.xlsx
@@ -190,12 +190,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$B$2:$B$81</f>
+              <f>'corr_series'!$B$2:$B$83</f>
             </numRef>
           </val>
         </ser>
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$C$2:$C$81</f>
+              <f>'corr_series'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -254,12 +254,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$D$2:$D$81</f>
+              <f>'corr_series'!$D$2:$D$83</f>
             </numRef>
           </val>
         </ser>
@@ -286,12 +286,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$E$2:$E$81</f>
+              <f>'corr_series'!$E$2:$E$83</f>
             </numRef>
           </val>
         </ser>
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$F$2:$F$81</f>
+              <f>'corr_series'!$F$2:$F$83</f>
             </numRef>
           </val>
         </ser>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$G$2:$G$81</f>
+              <f>'corr_series'!$G$2:$G$83</f>
             </numRef>
           </val>
         </ser>
@@ -382,12 +382,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$H$2:$H$81</f>
+              <f>'corr_series'!$H$2:$H$83</f>
             </numRef>
           </val>
         </ser>
@@ -414,12 +414,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$I$2:$I$81</f>
+              <f>'corr_series'!$I$2:$I$83</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$J$2:$J$81</f>
+              <f>'corr_series'!$J$2:$J$83</f>
             </numRef>
           </val>
         </ser>
@@ -478,12 +478,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$81</f>
+              <f>'corr_series'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$K$2:$K$81</f>
+              <f>'corr_series'!$K$2:$K$83</f>
             </numRef>
           </val>
         </ser>
@@ -520,8 +520,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5274111771127306"/>
-          <min val="-0.4597078449374216"/>
+          <max val="0.9619405675805962"/>
+          <min val="-1.054615979580843"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -598,12 +598,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$B$2:$B$81</f>
+              <f>'cum_corr'!$B$2:$B$83</f>
             </numRef>
           </val>
         </ser>
@@ -630,12 +630,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$C$2:$C$81</f>
+              <f>'cum_corr'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -662,12 +662,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$D$2:$D$81</f>
+              <f>'cum_corr'!$D$2:$D$83</f>
             </numRef>
           </val>
         </ser>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$E$2:$E$81</f>
+              <f>'cum_corr'!$E$2:$E$83</f>
             </numRef>
           </val>
         </ser>
@@ -726,12 +726,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$F$2:$F$81</f>
+              <f>'cum_corr'!$F$2:$F$83</f>
             </numRef>
           </val>
         </ser>
@@ -758,12 +758,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$G$2:$G$81</f>
+              <f>'cum_corr'!$G$2:$G$83</f>
             </numRef>
           </val>
         </ser>
@@ -790,12 +790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$H$2:$H$81</f>
+              <f>'cum_corr'!$H$2:$H$83</f>
             </numRef>
           </val>
         </ser>
@@ -822,12 +822,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$I$2:$I$81</f>
+              <f>'cum_corr'!$I$2:$I$83</f>
             </numRef>
           </val>
         </ser>
@@ -854,12 +854,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$J$2:$J$81</f>
+              <f>'cum_corr'!$J$2:$J$83</f>
             </numRef>
           </val>
         </ser>
@@ -886,12 +886,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$81</f>
+              <f>'cum_corr'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$K$2:$K$81</f>
+              <f>'cum_corr'!$K$2:$K$83</f>
             </numRef>
           </val>
         </ser>
@@ -928,8 +928,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6.525375276450917"/>
-          <min val="-7.275289174167862"/>
+          <max val="14.28354528810306"/>
+          <min val="-2.478646381354944"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1321,135 +1321,135 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>alpha095</t>
+          <t>alpha023</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>alpha101</t>
+          <t>alpha043</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>alpha062</t>
+          <t>alpha066</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>alpha065</t>
+          <t>alpha045</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>alpha032</t>
+          <t>alpha031</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>alpha095</t>
+          <t>alpha023</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.32826</v>
+        <v>-0.15263</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.016973</v>
+        <v>0.196253</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.368027</v>
+        <v>0.073838</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.388507</v>
+        <v>0.071147</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>alpha101</t>
+          <t>alpha043</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.32826</v>
+        <v>-0.15263</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.009745999999999999</v>
+        <v>0.278187</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.117792</v>
+        <v>0.095137</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.394</v>
+        <v>-0.128815</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>alpha062</t>
+          <t>alpha066</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.016973</v>
+        <v>0.196253</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>-0.009745999999999999</v>
+        <v>0.278187</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.017421</v>
+        <v>0.248127</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.034874</v>
+        <v>0.08637300000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>alpha065</t>
+          <t>alpha045</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.368027</v>
+        <v>0.073838</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.117792</v>
+        <v>0.095137</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.017421</v>
+        <v>0.248127</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.02707</v>
+        <v>0.1981</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>alpha032</t>
+          <t>alpha031</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.388507</v>
+        <v>0.071147</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.394</v>
+        <v>-0.128815</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.034874</v>
+        <v>0.08637300000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.02707</v>
+        <v>0.1981</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
@@ -1465,135 +1465,135 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>alpha095</t>
+          <t>alpha023</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>alpha101</t>
+          <t>alpha043</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>alpha062</t>
+          <t>alpha066</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>alpha065</t>
+          <t>alpha045</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>alpha032</t>
+          <t>alpha031</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>alpha095</t>
+          <t>alpha023</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.040721</v>
+        <v>0.09035799999999999</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.005703</v>
+        <v>0.181282</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.08611099999999999</v>
+        <v>0.174416</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.178172</v>
+        <v>0.162333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>alpha101</t>
+          <t>alpha043</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>-0.040721</v>
+        <v>0.09035799999999999</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.052286</v>
+        <v>0.061887</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.083092</v>
+        <v>0.065001</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.069317</v>
+        <v>0.062409</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>alpha062</t>
+          <t>alpha066</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.005703</v>
+        <v>0.181282</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.052286</v>
+        <v>0.061887</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.062001</v>
+        <v>0.08514099999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.013144</v>
+        <v>0.050776</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>alpha065</t>
+          <t>alpha045</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.08611099999999999</v>
+        <v>0.174416</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.083092</v>
+        <v>0.065001</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.062001</v>
+        <v>0.08514099999999999</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.080544</v>
+        <v>0.061092</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>alpha032</t>
+          <t>alpha031</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.178172</v>
+        <v>0.162333</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.069317</v>
+        <v>0.062409</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.013144</v>
+        <v>0.050776</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.080544</v>
+        <v>0.061092</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>1</v>
@@ -1730,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1739,52 +1739,52 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha101</t>
+          <t>alpha023 vs alpha043</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha062</t>
+          <t>alpha023 vs alpha066</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha065</t>
+          <t>alpha023 vs alpha045</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha032</t>
+          <t>alpha023 vs alpha031</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>alpha101 vs alpha062</t>
+          <t>alpha043 vs alpha066</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>alpha101 vs alpha065</t>
+          <t>alpha043 vs alpha045</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>alpha101 vs alpha032</t>
+          <t>alpha043 vs alpha031</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alpha062 vs alpha065</t>
+          <t>alpha066 vs alpha045</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>alpha062 vs alpha032</t>
+          <t>alpha066 vs alpha031</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>alpha065 vs alpha032</t>
+          <t>alpha045 vs alpha031</t>
         </is>
       </c>
     </row>
@@ -1795,9 +1795,6 @@
           <t>2023-01-03</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>-0.002368322385558906</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1805,9 +1802,6 @@
           <t>2023-01-18</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>-0.05530389024218322</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1816,19 +1810,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.04608735379818363</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.09667364890456623</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.3449569378157145</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.1631058934897514</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.3337119062359572</v>
+        <v>-0.5714561291862538</v>
       </c>
     </row>
     <row r="6">
@@ -1838,19 +1820,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.03576168592263949</v>
+        <v>-0.5076236681290642</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.09667364890456626</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.1857553784545526</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.01080905825351657</v>
+        <v>0.4723304542800635</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1055822156319885</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08536655898367068</v>
+        <v>-0.7946969570461895</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3531290376127579</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.4917108237894436</v>
       </c>
     </row>
     <row r="7">
@@ -1859,20 +1844,35 @@
           <t>2023-03-02</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>0.02331650761758647</v>
+      </c>
       <c r="C7" t="n">
-        <v>-0.04466732126975047</v>
+        <v>0.5335690650707239</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09667364890456626</v>
+        <v>0.1257495335816386</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2694582529415446</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1613314482298978</v>
+        <v>0.1807598435971681</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0603163293782013</v>
+        <v>0.2879676387076954</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.3551465542354422</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07295405746286956</v>
+        <v>-0.2801585786199461</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.1376718427804929</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.2204983061618615</v>
       </c>
     </row>
     <row r="8">
@@ -1881,20 +1881,35 @@
           <t>2023-03-16</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>0.3755041465650356</v>
+      </c>
       <c r="C8" t="n">
-        <v>-0.09848078939079276</v>
+        <v>0.2173273435777417</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.09667364890456624</v>
+        <v>0.1526119101157161</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.08311332715380326</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1400507713852512</v>
+        <v>-0.3866045880189689</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06849500995685898</v>
+        <v>0.1607166515202826</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6158023695891039</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05556508399324763</v>
+        <v>0.08454270294372647</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.1880441569550211</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.3834120539115112</v>
       </c>
     </row>
     <row r="9">
@@ -1903,20 +1918,35 @@
           <t>2023-03-30</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>-0.5081570780855267</v>
+      </c>
       <c r="C9" t="n">
-        <v>-0.09667364890456626</v>
+        <v>-0.01572865484671397</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09667364890456623</v>
+        <v>0.3357985504099618</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.205683688949095</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1522884784804273</v>
+        <v>0.1284951005688817</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.03708949863663292</v>
+        <v>-0.08860776609952457</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2761835757155897</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03703703703703694</v>
+        <v>0.07605301994566976</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.198923797497668</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.008408121376151802</v>
       </c>
     </row>
     <row r="10">
@@ -1925,20 +1955,35 @@
           <t>2023-04-14</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>-0.02270374985768004</v>
+      </c>
       <c r="C10" t="n">
-        <v>-0.09667364890456624</v>
+        <v>-0.2534478651725899</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09667364890456624</v>
+        <v>-0.1074708077737951</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.220539774709887</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.04706890484094069</v>
+        <v>0.2105532404791535</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.01123848817392102</v>
+        <v>0.3070220840568865</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3187364352908575</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1851851851851846</v>
+        <v>0.3180155131745002</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2074544030932307</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1136030083402935</v>
       </c>
     </row>
     <row r="11">
@@ -1948,22 +1993,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.08293945999691466</v>
+        <v>0.2994242782973215</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.007642946226594015</v>
+        <v>0.006474897568108421</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.005090921208157421</v>
+        <v>0.5864837341161391</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.01485298554840908</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1298776533433356</v>
+        <v>-0.01039277881451907</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01931200068674832</v>
+        <v>0.3726557710094966</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1835385097581022</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1649768610401621</v>
+        <v>0.2312375965316762</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1190729993052261</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.07447818022156477</v>
       </c>
     </row>
     <row r="12">
@@ -1972,20 +2029,35 @@
           <t>2023-05-12</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>-0.2196250199621442</v>
+      </c>
       <c r="C12" t="n">
-        <v>0.09667364890456623</v>
+        <v>0.6337317569226034</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09489966977658215</v>
+        <v>-0.4062901709391147</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.1927484129352749</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2148798917762172</v>
+        <v>-0.02118076974794246</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.240217530929801</v>
+        <v>-0.001274689116891428</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.3753942711619879</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4259989772815654</v>
+        <v>-0.09929826799999644</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.02312498450731028</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.231858579486549</v>
       </c>
     </row>
     <row r="13">
@@ -1995,22 +2067,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1079590277276307</v>
+        <v>0.1791567758782872</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00254415042438965</v>
+        <v>0.03038929455737472</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.03130737810082721</v>
+        <v>0.1481823847776924</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.593409839651545</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08057287901822122</v>
+        <v>-0.4694977729007012</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1985300373943934</v>
+        <v>-0.1505825709875905</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4736652718136874</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1751916690801975</v>
+        <v>-0.1628306854487797</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.4295415131809259</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.2963376099524123</v>
       </c>
     </row>
     <row r="14">
@@ -2019,20 +2103,35 @@
           <t>2023-06-12</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>-0.1774210889313259</v>
+      </c>
       <c r="C14" t="n">
-        <v>-0.09667364890456624</v>
+        <v>0.3022835940702479</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.08646754023342332</v>
+        <v>-0.1277403063134306</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2257932007857303</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.03880022126416782</v>
+        <v>-0.3335240682861295</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.04900029675436288</v>
+        <v>0.05813007131138757</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2118668334674707</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03726779962499646</v>
+        <v>-0.03433706670461992</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.0354135911735393</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2261267844293652</v>
       </c>
     </row>
     <row r="15">
@@ -2041,20 +2140,35 @@
           <t>2023-06-27</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>0.3634249763347204</v>
+      </c>
       <c r="C15" t="n">
-        <v>-0.08975922963071523</v>
+        <v>0.2293151238899865</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.102202248581786</v>
+        <v>-0.1867032161542862</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.007554472914762629</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2273893205229671</v>
+        <v>0.1782409612143658</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.04926490420108146</v>
+        <v>-0.08285254526939115</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.03554239716987519</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.05166182503249432</v>
+        <v>-0.2438423595995553</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.1117589459235472</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.1699939528465765</v>
       </c>
     </row>
     <row r="16">
@@ -2063,20 +2177,35 @@
           <t>2023-07-12</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>0.3984913340433024</v>
+      </c>
       <c r="C16" t="n">
-        <v>-0.09667364890456624</v>
+        <v>0.4177432758472135</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.09489966977658215</v>
+        <v>0.4104083977678428</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2577441718860158</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0609202233188512</v>
+        <v>-0.1783314719105165</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0529563983135022</v>
+        <v>0.2794206346569852</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.1629546968645498</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05556508399324762</v>
+        <v>0.4921946761752153</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.06218830701762434</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.2506778074565742</v>
       </c>
     </row>
     <row r="17">
@@ -2085,20 +2214,35 @@
           <t>2023-07-26</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>-0.3657552295972655</v>
+      </c>
       <c r="C17" t="n">
-        <v>-0.09489966977658215</v>
+        <v>-0.183891830219176</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09489966977658212</v>
+        <v>0.2182200837282874</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7362719433487581</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0278309045353752</v>
+        <v>-0.4424404326395066</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.135929069581664</v>
+        <v>0.2981328461736161</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.6036723789698967</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1108061749571183</v>
+        <v>-0.8273819858660931</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3647750590241346</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.3167431937554989</v>
       </c>
     </row>
     <row r="18">
@@ -2107,20 +2251,35 @@
           <t>2023-08-09</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>0.1703494026044174</v>
+      </c>
       <c r="C18" t="n">
-        <v>-0.08975922963071523</v>
+        <v>0.2542008541163047</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1060806267448933</v>
+        <v>-0.07878920262209495</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3236534470307527</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.05838643189931884</v>
+        <v>0.628312634756267</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09775474594071547</v>
+        <v>0.1495407448841971</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4399751363164169</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.01174237301357899</v>
+        <v>0.3903507354044549</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.3085807416925136</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.00188467715847404</v>
       </c>
     </row>
     <row r="19">
@@ -2129,20 +2288,35 @@
           <t>2023-08-23</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>0.0668008751838742</v>
+      </c>
       <c r="C19" t="n">
-        <v>-0.09848078939079276</v>
+        <v>0.6198459698128178</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1041207063716297</v>
+        <v>-0.339165618956633</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7436751320982875</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1581720394612569</v>
+        <v>0.008805686652236194</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1628033512757457</v>
+        <v>-0.6608992973939092</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.09797312309947234</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2029241489049277</v>
+        <v>-0.03832981081587696</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4940164303527401</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.08060551473976399</v>
       </c>
     </row>
     <row r="20">
@@ -2151,20 +2325,35 @@
           <t>2023-09-07</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>0.2407843767186604</v>
+      </c>
       <c r="C20" t="n">
-        <v>-0.09848078939079276</v>
+        <v>-0.1687115411760073</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.09667364890456624</v>
+        <v>0.2403702364828141</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.5549424338558649</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2243954529666052</v>
+        <v>0.3477530594383491</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3605088506655661</v>
+        <v>0.2730176011399764</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.02155696247212088</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4259989772815653</v>
+        <v>0.1934924091451687</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5038256777676822</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.05322395695719732</v>
       </c>
     </row>
     <row r="21">
@@ -2174,22 +2363,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.001695785221965964</v>
+        <v>-0.1921242482059148</v>
       </c>
       <c r="C21" t="n">
-        <v>0.002544150424389656</v>
+        <v>0.2000968697007138</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.01020288654985709</v>
+        <v>0.2396579035131056</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4347141336013311</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07623607932259434</v>
+        <v>0.5571286611194294</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2277258411708745</v>
+        <v>0.06975954757832768</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1709698141210559</v>
       </c>
       <c r="I21" t="n">
-        <v>0.391402849921708</v>
+        <v>0.1019719157173363</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4329426251941345</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5074424882265752</v>
       </c>
     </row>
     <row r="22">
@@ -2199,22 +2400,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0340653258138684</v>
+        <v>0.2659627744599118</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1348399724926482</v>
+        <v>0.61951356126007</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.01020288654985711</v>
+        <v>0.3783903620767765</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.1708422094259205</v>
       </c>
       <c r="F22" t="n">
-        <v>0.04599669141106139</v>
+        <v>0.3987900191233488</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.104384318977928</v>
+        <v>0.105970865067208</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5963427719203009</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.09148783662493334</v>
+        <v>0.4155017762432292</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1432116387180509</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.4330896771487082</v>
       </c>
     </row>
     <row r="23">
@@ -2223,20 +2436,35 @@
           <t>2023-10-19</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>-0.2267641756965417</v>
+      </c>
       <c r="C23" t="n">
-        <v>0.09667364890456624</v>
+        <v>-0.1874120567434944</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.09315705904653858</v>
+        <v>-0.2159428756420185</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.195258586089304</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1343938963309065</v>
+        <v>0.003210367521503695</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.04785783660715914</v>
+        <v>0.3689869369062125</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.310035832304149</v>
       </c>
       <c r="I23" t="n">
-        <v>5.315062723673765e-18</v>
+        <v>0.004459836438908744</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.5313504571220375</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.3525255503156972</v>
       </c>
     </row>
     <row r="24">
@@ -2246,22 +2474,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0688877610192544</v>
+        <v>-0.1746166517445758</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1399282733414276</v>
+        <v>-0.1689551321831703</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02858010659525691</v>
+        <v>0.165440079492151</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1227138122887018</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.05818340211593905</v>
+        <v>0.5361854390884924</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1775584181068761</v>
+        <v>0.2559995387089058</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3434386239183783</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2610033533109415</v>
+        <v>0.05558348288473275</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.240152479470594</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1615308774518783</v>
       </c>
     </row>
     <row r="25">
@@ -2270,20 +2510,35 @@
           <t>2023-11-16</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>0.2174599528413227</v>
+      </c>
       <c r="C25" t="n">
-        <v>0.09315705904653855</v>
+        <v>0.4895484490648185</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.08646754023342336</v>
+        <v>0.3349159101398287</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.07615044837519268</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1574026445807406</v>
+        <v>0.4043187166919326</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1106263302521133</v>
+        <v>0.23401713252289</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2219650888433038</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2196166114936574</v>
+        <v>-0.2491176188055556</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.3302468887160628</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1929701103897334</v>
       </c>
     </row>
     <row r="26">
@@ -2293,22 +2548,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.03968690701039092</v>
+        <v>0.6080786973999197</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.005090921208157397</v>
+        <v>0.1050299501114109</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.498685596457613e-18</v>
+        <v>-0.1166048222542742</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.1166717484564057</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1614061526914258</v>
+        <v>0.7039687064738611</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.04998103916024009</v>
+        <v>-0.143100395213017</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.3129978227697603</v>
       </c>
       <c r="I26" t="n">
-        <v>0.185312329165275</v>
+        <v>-0.3582343016149987</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.2294558721156396</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.151189038215048</v>
       </c>
     </row>
     <row r="27">
@@ -2317,29 +2584,35 @@
           <t>2023-12-15</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>0.4423259336571464</v>
+      </c>
       <c r="C27" t="n">
-        <v>-0.09667364890456624</v>
+        <v>0.4353248586485512</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.08646754023342336</v>
+        <v>-0.2685249731333189</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.2148413419415073</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.135269350780775</v>
+        <v>0.3436430435232949</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1897168945832034</v>
+        <v>-0.1449070354205094</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2835151618181107</v>
+        <v>-0.1773986681669004</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3354101966249679</v>
+        <v>-0.03329259528680126</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.03223028885762776</v>
+        <v>0.358096069274778</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1533335261719049</v>
+        <v>0.5471844811204095</v>
       </c>
     </row>
     <row r="28">
@@ -2348,29 +2621,35 @@
           <t>2024-01-02</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>0.5056816195629766</v>
+      </c>
       <c r="C28" t="n">
-        <v>-0.09489966977658215</v>
+        <v>0.7024743390539998</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1080844252917793</v>
+        <v>0.6732581973981921</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6697218710813165</v>
       </c>
       <c r="F28" t="n">
-        <v>0.004478985761879545</v>
+        <v>0.3937036371678808</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01899839775268079</v>
+        <v>0.4227938098890435</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2387675808816703</v>
+        <v>0.2942839405048707</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1698046501453295</v>
+        <v>0.7875894711436018</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1716340502860449</v>
+        <v>0.4579938448989604</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1230415764847932</v>
+        <v>0.1773942156492643</v>
       </c>
     </row>
     <row r="29">
@@ -2380,34 +2659,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.03547599222264934</v>
+        <v>0.244550225860293</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1399282733414276</v>
+        <v>-0.2147173674963968</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.005090921208157422</v>
+        <v>0.307730205088866</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2472975825015158</v>
+        <v>0.458481816928321</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1536815646617752</v>
+        <v>-0.02024210104770281</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.02281118492314448</v>
+        <v>-0.1192956860035995</v>
       </c>
       <c r="H29" t="n">
-        <v>0.277738489833152</v>
+        <v>-0.08282815251184344</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1674961608635269</v>
+        <v>0.0230980249598083</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1221085042602959</v>
+        <v>0.04990538467783304</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.01602035498090487</v>
+        <v>0.01345622925019509</v>
       </c>
     </row>
     <row r="30">
@@ -2417,34 +2696,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.05584332508745906</v>
+        <v>0.2724354944031757</v>
       </c>
       <c r="C30" t="n">
-        <v>-5.245659880237252e-18</v>
+        <v>-0.09182505279689868</v>
       </c>
       <c r="D30" t="n">
-        <v>0.007642946226594014</v>
+        <v>0.3627237458667481</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02404171158721094</v>
+        <v>-0.2826049493047948</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1697409437311151</v>
+        <v>-0.07188089677407331</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.08387621235415542</v>
+        <v>0.1602153723259242</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3525072627331406</v>
+        <v>0.3249671037091335</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1669244652223968</v>
+        <v>0.3563155753702956</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1176876324681365</v>
+        <v>0.2754494721044271</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.09019353870762734</v>
+        <v>-0.1321982437386661</v>
       </c>
     </row>
     <row r="31">
@@ -2453,29 +2732,35 @@
           <t>2024-02-14</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>-0.02343479609368231</v>
+      </c>
       <c r="C31" t="n">
-        <v>-0.09667364890456624</v>
+        <v>0.1653293088310243</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.09667364890456626</v>
+        <v>0.291328361694137</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3008111587214843</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1594296495277263</v>
+        <v>0.5940364822879934</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.03958286570511839</v>
+        <v>0.3028476193275611</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3030627892641972</v>
+        <v>0.1549605943048965</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07407407407407388</v>
+        <v>0.3216312486506444</v>
       </c>
       <c r="J31" t="n">
-        <v>0.06015928172538267</v>
+        <v>0.2031493888418711</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.01044746386747225</v>
+        <v>0.3612543130023611</v>
       </c>
     </row>
     <row r="32">
@@ -2485,34 +2770,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.03621989075802057</v>
+        <v>0.1062048991005758</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.00509092120815736</v>
+        <v>0.2839184864366087</v>
       </c>
       <c r="D32" t="n">
-        <v>0.02057677418787306</v>
+        <v>0.173945682885153</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02986814331553922</v>
+        <v>0.08695246136443346</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1866602934218036</v>
+        <v>0.2914613088569625</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1429550893478627</v>
+        <v>0.0006116063059528944</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2830304327118041</v>
+        <v>0.04003375726234217</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1068760195147075</v>
+        <v>0.5978386581941435</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2110006763579251</v>
+        <v>-0.1273800667784356</v>
       </c>
       <c r="K32" t="n">
-        <v>0.08822109163214197</v>
+        <v>0.09366547588075338</v>
       </c>
     </row>
     <row r="33">
@@ -2522,34 +2807,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0158131122088035</v>
+        <v>-0.03694513690146339</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1373605639486888</v>
+        <v>0.2580168072056581</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01020288654985701</v>
+        <v>-0.273977079087146</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2585901201848593</v>
+        <v>0.1823049448573328</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1049331959759601</v>
+        <v>0.1218638621998941</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.07955350727956016</v>
+        <v>0.2344843807059921</v>
       </c>
       <c r="H33" t="n">
-        <v>0.24115476130036</v>
+        <v>0.1639808878139933</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.481304330884651e-17</v>
+        <v>0.2716836654999222</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.02381732022419195</v>
+        <v>0.0707028395120384</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.03341232905287115</v>
+        <v>0.1656314065048431</v>
       </c>
     </row>
     <row r="34">
@@ -2558,29 +2843,35 @@
           <t>2024-03-28</t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>-0.06752310124598576</v>
+      </c>
       <c r="C34" t="n">
-        <v>-0.09667364890456626</v>
+        <v>-0.3062950530275269</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.09489966977658215</v>
+        <v>-0.2459735633298625</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.3198935828226905</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.04266376243066657</v>
+        <v>0.2113517104241359</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2465131444828575</v>
+        <v>0.1128186940697274</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1761852185353884</v>
+        <v>-0.08718284049823379</v>
       </c>
       <c r="I34" t="n">
-        <v>0.05556508399324763</v>
+        <v>0.017504082279605</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1064232922776278</v>
+        <v>0.06228186043982176</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.01151116859595155</v>
+        <v>0.2103323776576123</v>
       </c>
     </row>
     <row r="35">
@@ -2589,29 +2880,35 @@
           <t>2024-04-12</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>0.4114052458273766</v>
+      </c>
       <c r="C35" t="n">
-        <v>-0.09667364890456624</v>
+        <v>0.3300495591307788</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.09848078939079274</v>
+        <v>-0.2516371363483164</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.1643623265217111</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1177111439937965</v>
+        <v>0.09444012082417555</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.08957764983721943</v>
+        <v>0.4577669923074066</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1806142723180401</v>
+        <v>0.4719944886619823</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.05556508399324765</v>
+        <v>-0.3973480417428889</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1513334185259347</v>
+        <v>-0.00163936182835946</v>
       </c>
       <c r="K35" t="n">
-        <v>0.01554428124361444</v>
+        <v>-0.03348985826784274</v>
       </c>
     </row>
     <row r="36">
@@ -2620,29 +2917,35 @@
           <t>2024-04-26</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>-0.2246492681065307</v>
+      </c>
       <c r="C36" t="n">
-        <v>-0.1080844252917793</v>
+        <v>-0.390568261218791</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.09315705904653858</v>
+        <v>0.4623074122188183</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.1087932622419168</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1169830518935558</v>
+        <v>-0.2801678949902626</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.08599686453946098</v>
+        <v>-0.4790951314144136</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1831719374389791</v>
+        <v>0.05488050976921902</v>
       </c>
       <c r="I36" t="n">
-        <v>0.04143709650823726</v>
+        <v>-0.2268310586795189</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.009607423941977299</v>
+        <v>0.1532281334347085</v>
       </c>
       <c r="K36" t="n">
-        <v>0.03978824120338015</v>
+        <v>0.002793027452335775</v>
       </c>
     </row>
     <row r="37">
@@ -2651,29 +2954,35 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>0.1207781284636244</v>
+      </c>
       <c r="C37" t="n">
-        <v>-0.09315705904653855</v>
+        <v>0.04978456906691039</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1041207063716297</v>
+        <v>0.4003331108211568</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.4195894626311329</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1391268176612411</v>
+        <v>0.4434929654459966</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.06178618051827926</v>
+        <v>-0.08827169115985527</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1773091821942435</v>
+        <v>0.2457570159361747</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.07157620211606368</v>
+        <v>-0.605545316819212</v>
       </c>
       <c r="J37" t="n">
-        <v>0.06419834487543215</v>
+        <v>0.3086714142571746</v>
       </c>
       <c r="K37" t="n">
-        <v>0.1639909270702125</v>
+        <v>0.07540840122652499</v>
       </c>
     </row>
     <row r="38">
@@ -2682,29 +2991,35 @@
           <t>2024-05-24</t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>0.1406054049484531</v>
+      </c>
       <c r="C38" t="n">
-        <v>-0.09315705904653855</v>
+        <v>0.342538350566911</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1143858039685551</v>
+        <v>-0.6912046174184495</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6934699185591796</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1845676926114365</v>
+        <v>-0.5497281605142216</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2222138648587878</v>
+        <v>0.02977516063404131</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1667244851200683</v>
+        <v>-0.07069037237540868</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1378234030339618</v>
+        <v>-0.09451014858089733</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.0888815651178437</v>
+        <v>0.3158433536464469</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.02879493020818703</v>
+        <v>-0.7935229577181043</v>
       </c>
     </row>
     <row r="39">
@@ -2713,29 +3028,35 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>-0.01277762683021809</v>
+      </c>
       <c r="C39" t="n">
-        <v>-0.09315705904653858</v>
+        <v>0.08449290496211166</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.08646754023342335</v>
+        <v>0.8228677022591177</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.08955573482362575</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1642408610599827</v>
+        <v>-0.2886440982209637</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.04629682314930227</v>
+        <v>0.06684300564254983</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1856110088018534</v>
+        <v>0.2605861103911369</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3314967720658977</v>
+        <v>0.04198903145508651</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1111596206009156</v>
+        <v>0.4489098707055079</v>
       </c>
       <c r="K39" t="n">
-        <v>0.06633106098738135</v>
+        <v>0.2846562327352387</v>
       </c>
     </row>
     <row r="40">
@@ -2744,29 +3065,35 @@
           <t>2024-06-25</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>0.5446753681733605</v>
+      </c>
       <c r="C40" t="n">
-        <v>-0.08975922963071524</v>
+        <v>-0.2896953690250594</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.09489966977658211</v>
+        <v>0.1368267253038068</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.101572285385617</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.1650277876016729</v>
+        <v>-0.2420652195203972</v>
       </c>
       <c r="G40" t="n">
-        <v>0.05355492420737962</v>
+        <v>-0.08769292374934191</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2155854553268961</v>
+        <v>-0.4319819409330257</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1286332740515982</v>
+        <v>0.2932896525491303</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1231481843694827</v>
+        <v>0.2187083642588392</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2509190237362108</v>
+        <v>0.1667009405339025</v>
       </c>
     </row>
     <row r="41">
@@ -2775,29 +3102,35 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>0.3622077851698211</v>
+      </c>
       <c r="C41" t="n">
-        <v>-0.09489966977658215</v>
+        <v>0.1295340694675309</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0881008594999961</v>
+        <v>-0.131150579377894</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.4104799727892759</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.04661211351052923</v>
+        <v>0.1375950981608243</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0991044982053315</v>
+        <v>-0.1453052104792792</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1190038894521346</v>
+        <v>0.06481460880732808</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.001722370898485415</v>
+        <v>0.5346395453076335</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.05012007329824453</v>
+        <v>0.3444567368833556</v>
       </c>
       <c r="K41" t="n">
-        <v>0.07579306808756597</v>
+        <v>-0.3044982615356005</v>
       </c>
     </row>
     <row r="42">
@@ -2806,29 +3139,35 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>0.08365053618220504</v>
+      </c>
       <c r="C42" t="n">
-        <v>0.09667364890456624</v>
+        <v>0.4017077199138588</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.09489966977658212</v>
+        <v>-0.05832472355690407</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.1571309401772211</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.06110202347442362</v>
+        <v>0.1426407710673374</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1219607329870361</v>
+        <v>0.4333009236558562</v>
       </c>
       <c r="H42" t="n">
-        <v>0.02906615500942961</v>
+        <v>0.5977950725655065</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.01852169466441587</v>
+        <v>0.2914558785705189</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.01499560915064126</v>
+        <v>0.4696351870780855</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1423319870177078</v>
+        <v>0.7277982411950313</v>
       </c>
     </row>
     <row r="43">
@@ -2837,29 +3176,35 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>0.0895356744233735</v>
+      </c>
       <c r="C43" t="n">
-        <v>-0.09315705904653858</v>
+        <v>0.3535533905932738</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1060806267448933</v>
+        <v>0.02865867797911589</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.3765148822530835</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.04643431825327679</v>
+        <v>0.4130897261428311</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.1447099911303564</v>
+        <v>0.2516032548133206</v>
       </c>
       <c r="H43" t="n">
-        <v>0.08867327931913561</v>
+        <v>0.2373368137949158</v>
       </c>
       <c r="I43" t="n">
-        <v>0.02205770086888883</v>
+        <v>0.2923780366438845</v>
       </c>
       <c r="J43" t="n">
-        <v>0.02334027653113569</v>
+        <v>0.1096323542489478</v>
       </c>
       <c r="K43" t="n">
-        <v>0.07527541261783886</v>
+        <v>0.5057225095720171</v>
       </c>
     </row>
     <row r="44">
@@ -2868,29 +3213,35 @@
           <t>2024-08-21</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>0.05525076065621567</v>
+      </c>
       <c r="C44" t="n">
-        <v>0.09489966977658215</v>
+        <v>0.3902985826986551</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.100322986665503</v>
+        <v>-0.1034339776237052</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.04216396796223459</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2236180004809247</v>
+        <v>-0.009712706569709779</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.1257301016249899</v>
+        <v>0.008137689034491621</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1479896106417184</v>
+        <v>0.4477579696380408</v>
       </c>
       <c r="I44" t="n">
-        <v>0.09198559653980573</v>
+        <v>-0.3452884238395965</v>
       </c>
       <c r="J44" t="n">
-        <v>0.08548234375602363</v>
+        <v>0.1245917585760705</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01160658679935699</v>
+        <v>0.3722189421726209</v>
       </c>
     </row>
     <row r="45">
@@ -2899,29 +3250,35 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>-0.3390685152296488</v>
+      </c>
       <c r="C45" t="n">
-        <v>-0.1041207063716297</v>
+        <v>0.3110520961974577</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.08975922963071521</v>
+        <v>-0.01005869953094736</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.308215983419325</v>
       </c>
       <c r="F45" t="n">
-        <v>0.03198549693065061</v>
+        <v>-0.3004115305650787</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2990771748170673</v>
+        <v>0.05196539513677037</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1980145775309414</v>
+        <v>-0.06627601390319819</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1917241379310344</v>
+        <v>0.3864522138070876</v>
       </c>
       <c r="J45" t="n">
-        <v>0.018196851657425</v>
+        <v>0.14390464057563</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1804416549140471</v>
+        <v>0.2728613373064874</v>
       </c>
     </row>
     <row r="46">
@@ -2930,29 +3287,35 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>0.4064349435067104</v>
+      </c>
       <c r="C46" t="n">
-        <v>-0.09667364890456626</v>
+        <v>0.3838745910619778</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.09667364890456626</v>
+        <v>0.2630010023761389</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.5317517939018086</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1500179026481359</v>
+        <v>-0.01740781261337389</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.2599223661074114</v>
+        <v>0.02498577308327999</v>
       </c>
       <c r="H46" t="n">
-        <v>0.12588308586723</v>
+        <v>0.3492415458921299</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4444444444444431</v>
+        <v>-0.204999087837749</v>
       </c>
       <c r="J46" t="n">
-        <v>0.005091727686591887</v>
+        <v>0.5050171788827243</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1868249792594327</v>
+        <v>-0.03827213461353984</v>
       </c>
     </row>
     <row r="47">
@@ -2962,34 +3325,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.07512170178029713</v>
+        <v>-0.3290853356191158</v>
       </c>
       <c r="C47" t="n">
-        <v>0.007642946226593983</v>
+        <v>-0.2710236126024882</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01795751586281635</v>
+        <v>0.7377752684451543</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2593157022037975</v>
+        <v>0.3318593253961844</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1304289233890832</v>
+        <v>0.09756270543538333</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.1407247860734075</v>
+        <v>-0.4874208388861863</v>
       </c>
       <c r="H47" t="n">
-        <v>0.11342745175124</v>
+        <v>-0.9155431142593642</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.00727416138944379</v>
+        <v>-0.2815185932360685</v>
       </c>
       <c r="J47" t="n">
-        <v>0.07957420963793714</v>
+        <v>-0.2069576892241895</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1166739760116336</v>
+        <v>0.4251473023874682</v>
       </c>
     </row>
     <row r="48">
@@ -2999,34 +3362,34 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.05374223632212462</v>
+        <v>0.01895118583148413</v>
       </c>
       <c r="C48" t="n">
-        <v>0.132363951412094</v>
+        <v>0.2047592774491713</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.005090921208157415</v>
+        <v>0.4341550551742728</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2772981561457106</v>
+        <v>0.5599658381644137</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02580404217797428</v>
+        <v>0.3004002393390721</v>
       </c>
       <c r="G48" t="n">
-        <v>0.04416528391339533</v>
+        <v>-0.2860232946540188</v>
       </c>
       <c r="H48" t="n">
-        <v>0.06357240034113933</v>
+        <v>-0.2444558308656127</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1126373626373624</v>
+        <v>-0.1094111165292119</v>
       </c>
       <c r="J48" t="n">
-        <v>0.06549942898869369</v>
+        <v>0.1773207961505762</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1502493227432658</v>
+        <v>0.2888069611218965</v>
       </c>
     </row>
     <row r="49">
@@ -3035,29 +3398,35 @@
           <t>2024-10-31</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>0.4739080620568228</v>
+      </c>
       <c r="C49" t="n">
-        <v>-0.09848078939079276</v>
+        <v>0.2365358311211139</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.09489966977658215</v>
+        <v>0.05149334312608513</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.3402906741994698</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.2187824136206316</v>
+        <v>0.1527144279290228</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.2360268741670708</v>
+        <v>0.3485429621304406</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2012110219469513</v>
+        <v>0.1167823013376089</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2226415094339623</v>
+        <v>0.07855243035441058</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0713392309684913</v>
+        <v>-0.1948403221262212</v>
       </c>
       <c r="K49" t="n">
-        <v>0.02996380381430788</v>
+        <v>0.256096358680902</v>
       </c>
     </row>
     <row r="50">
@@ -3066,29 +3435,35 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>-0.1925083307245224</v>
+      </c>
       <c r="C50" t="n">
-        <v>-0.09667364890456626</v>
+        <v>0.4261485685378508</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1041207063716297</v>
+        <v>-0.1887837083499434</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.324294354842353</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.06395843610077333</v>
+        <v>-0.1601894015772173</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.1071800108583475</v>
+        <v>0.7585577615795716</v>
       </c>
       <c r="H50" t="n">
-        <v>0.04961446020611286</v>
+        <v>-0.4085394238643176</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.07427813527082071</v>
+        <v>0.05818931278264989</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.1372021071021321</v>
+        <v>0.3779007120729178</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1284292031952768</v>
+        <v>-0.05491443548658605</v>
       </c>
     </row>
     <row r="51">
@@ -3097,29 +3472,35 @@
           <t>2024-11-29</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>-0.2122609673109542</v>
+      </c>
       <c r="C51" t="n">
-        <v>0.100322986665503</v>
+        <v>0.1182454050265079</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.09315705904653858</v>
+        <v>0.5169079202415419</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.002473742739269535</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2092412723691229</v>
+        <v>-0.05833078847409793</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.04643980451956663</v>
+        <v>-0.5070803409543623</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.08335389285648423</v>
+        <v>0.3472208324021553</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.001373626373626333</v>
+        <v>-0.1228715109818904</v>
       </c>
       <c r="J51" t="n">
-        <v>0.09282815462916143</v>
+        <v>0.6658476397900855</v>
       </c>
       <c r="K51" t="n">
-        <v>0.04884179836461346</v>
+        <v>-0.3275897692773882</v>
       </c>
     </row>
     <row r="52">
@@ -3129,34 +3510,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1486462492993756</v>
+        <v>-0.07654624599733313</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1373605639486886</v>
+        <v>0.2311518750873345</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.01535737792084841</v>
+        <v>0.2487938224847509</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01392472066804773</v>
+        <v>0.3659629338069359</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.02151178757067089</v>
+        <v>-0.07284355988327423</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.2864774910626983</v>
+        <v>0.09024814423567476</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0370080069022695</v>
+        <v>-0.2688963297612906</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1490711984999858</v>
+        <v>-0.1031461067497801</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.0957338031585806</v>
+        <v>0.2939118690504518</v>
       </c>
       <c r="K52" t="n">
-        <v>0.2073606067209885</v>
+        <v>-0.332217201523172</v>
       </c>
     </row>
     <row r="53">
@@ -3165,29 +3546,35 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>-0.3138405302349203</v>
+      </c>
       <c r="C53" t="n">
-        <v>-0.100322986665503</v>
+        <v>0.4255778691820071</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.1080844252917793</v>
+        <v>0.229647317712392</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.1836218512120097</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2267969348896775</v>
+        <v>-0.07529953893815881</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1311056361418802</v>
+        <v>0.3490790761471312</v>
       </c>
       <c r="H53" t="n">
-        <v>0.04906373949193125</v>
+        <v>0.1640048442301508</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1906106439378912</v>
+        <v>0.3977072214742471</v>
       </c>
       <c r="J53" t="n">
-        <v>0.07931019806686629</v>
+        <v>-0.2318327785241652</v>
       </c>
       <c r="K53" t="n">
-        <v>0.08804836699261671</v>
+        <v>0.2787641162068089</v>
       </c>
     </row>
     <row r="54">
@@ -3196,29 +3583,35 @@
           <t>2025-01-15</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>-0.2666457395746782</v>
+      </c>
       <c r="C54" t="n">
-        <v>-0.100322986665503</v>
+        <v>-0.3632414523290475</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.09667364890456626</v>
+        <v>0.5713658708163926</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.3627809080826135</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06721441818338324</v>
+        <v>0.6533028764822782</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3813662491992049</v>
+        <v>-0.1774256216738872</v>
       </c>
       <c r="H54" t="n">
-        <v>0.003923354147105896</v>
+        <v>-0.4392447883112519</v>
       </c>
       <c r="I54" t="n">
-        <v>0.037062465833055</v>
+        <v>-0.07814087382485423</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.1748390087966627</v>
+        <v>-0.5225993647522537</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1408818955427913</v>
+        <v>-0.08007209525805002</v>
       </c>
     </row>
     <row r="55">
@@ -3227,29 +3620,35 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="B55" t="n">
+        <v>0.1873586843847983</v>
+      </c>
       <c r="C55" t="n">
-        <v>-0.09667364890456624</v>
+        <v>0.1091512050408167</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.09144411715212425</v>
+        <v>0.4245702858498834</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.3330096228617831</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1656882337045218</v>
+        <v>-0.4149394520839548</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.2802450152817995</v>
+        <v>0.1050394181629349</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.02470082812035465</v>
+        <v>-0.266596954843554</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1669244652223969</v>
+        <v>0.2878320951175537</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.125501199583858</v>
+        <v>-0.01752017377587671</v>
       </c>
       <c r="K55" t="n">
-        <v>0.117452855237211</v>
+        <v>0.04013757755573681</v>
       </c>
     </row>
     <row r="56">
@@ -3259,31 +3658,34 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.07929478788303389</v>
+        <v>-0.04068146301303018</v>
       </c>
       <c r="C56" t="n">
-        <v>0.09489966977658217</v>
+        <v>0.2078005411647113</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.09848078939079276</v>
+        <v>0.3110647963006511</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.01183667863483522</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0421205105996744</v>
+        <v>0.2470348514085701</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.04146379650913672</v>
+        <v>0.1713350728242826</v>
       </c>
       <c r="H56" t="n">
-        <v>0.05274406409459892</v>
+        <v>-0.2312551342766662</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.03739279588336199</v>
+        <v>0.4839077196299407</v>
       </c>
       <c r="J56" t="n">
-        <v>0.1288167359562647</v>
+        <v>-0.1511927559385499</v>
       </c>
       <c r="K56" t="n">
-        <v>0.006576997016490089</v>
+        <v>-0.169792709283932</v>
       </c>
     </row>
     <row r="57">
@@ -3293,34 +3695,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.0758711435972285</v>
+        <v>0.3735873790511273</v>
       </c>
       <c r="C57" t="n">
-        <v>0.09848078939079274</v>
+        <v>-0.01502914723656337</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.09667364890456626</v>
+        <v>-0.2989012700481803</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2389248193310122</v>
+        <v>-0.4334260888928091</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3043314587613394</v>
+        <v>-0.1686942542138273</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1336189417566613</v>
+        <v>-0.08004721873085753</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.00497936371579004</v>
+        <v>0.3545536755278364</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.01852169466441588</v>
+        <v>0.1234363005347566</v>
       </c>
       <c r="J57" t="n">
-        <v>0.04381020530099394</v>
+        <v>-0.3089896505322169</v>
       </c>
       <c r="K57" t="n">
-        <v>0.006530092036575287</v>
+        <v>0.1957428286628974</v>
       </c>
     </row>
     <row r="58">
@@ -3329,23 +3731,35 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>-0.01775024247289007</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.3275880101295097</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.6758319772972309</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.01116840680670634</v>
+      </c>
       <c r="F58" t="n">
-        <v>-0.05176470197814495</v>
+        <v>0.3612810325872179</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2347466601901061</v>
+        <v>0.4399680164264769</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.08694745385789399</v>
+        <v>0.4891156720486208</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2056756627883844</v>
+        <v>0.3498794773686733</v>
       </c>
       <c r="J58" t="n">
-        <v>0.04796322025920589</v>
+        <v>-0.07806901460993662</v>
       </c>
       <c r="K58" t="n">
-        <v>0.04484015556257551</v>
+        <v>0.2891686151665048</v>
       </c>
     </row>
     <row r="59">
@@ -3354,23 +3768,35 @@
           <t>2025-03-28</t>
         </is>
       </c>
+      <c r="B59" t="n">
+        <v>-0.001329833253294141</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.2002549770323199</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.01217973297009986</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.3961088536014947</v>
+      </c>
       <c r="F59" t="n">
-        <v>0.06001469590463403</v>
+        <v>0.1641096494511076</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.1022826931848897</v>
+        <v>0.6020757471679291</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1349635214726073</v>
+        <v>-0.2130131301024825</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3301150893110446</v>
+        <v>-0.1501358928463456</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.1011602258889614</v>
+        <v>0.06732235019413628</v>
       </c>
       <c r="K59" t="n">
-        <v>0.07471915793087142</v>
+        <v>-0.3299200849433792</v>
       </c>
     </row>
     <row r="60">
@@ -3380,22 +3806,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.2261944997009043</v>
+        <v>0.09231757446583171</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2148578956640939</v>
+        <v>-0.0792703755833403</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.09775754304005189</v>
+        <v>0.06986592893503589</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1301889109808237</v>
+        <v>0.3095173673185369</v>
       </c>
       <c r="J60" t="n">
-        <v>0.04272810282212482</v>
+        <v>0.2113323093181039</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1281018553770029</v>
+        <v>-0.2513154470193898</v>
       </c>
     </row>
     <row r="61">
@@ -3404,23 +3830,35 @@
           <t>2025-04-28</t>
         </is>
       </c>
+      <c r="B61" t="n">
+        <v>0.5455432967861679</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.1750353635194763</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.1727174671708138</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.2522287334020101</v>
+      </c>
       <c r="F61" t="n">
-        <v>0.04985907588314922</v>
+        <v>0.2339507189139954</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.3888133493182829</v>
+        <v>-0.01079042913192608</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.03754580918900045</v>
+        <v>0.347670499338211</v>
       </c>
       <c r="I61" t="n">
-        <v>0.03208014974496041</v>
+        <v>0.02141490212813946</v>
       </c>
       <c r="J61" t="n">
-        <v>0.02405216180173983</v>
+        <v>0.1542630774261792</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1863009985665352</v>
+        <v>0.169117468475187</v>
       </c>
     </row>
     <row r="62">
@@ -3430,34 +3868,34 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.04560279619550089</v>
+        <v>0.4630336560884317</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.09667364890456627</v>
+        <v>0.1241636547805274</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0984807893907927</v>
+        <v>0.5132164579195314</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2207933056875792</v>
+        <v>0.7446042670574503</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.05280914687144304</v>
+        <v>-0.03550639450137515</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.08168482298961623</v>
+        <v>0.6049385247648027</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.0789728371426722</v>
+        <v>0.5329162795120779</v>
       </c>
       <c r="I62" t="n">
-        <v>0.05556508399324763</v>
+        <v>-0.02975888053337666</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1823768658945666</v>
+        <v>-0.2865412993819823</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1096458990968842</v>
+        <v>0.7295824703405061</v>
       </c>
     </row>
     <row r="63">
@@ -3466,23 +3904,35 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="B63" t="n">
+        <v>0.03229718273426623</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.03713089791552409</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.4215376161576915</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.1595555696026312</v>
+      </c>
       <c r="F63" t="n">
-        <v>0.05261597980444675</v>
+        <v>-0.3054520579437195</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.2761620771682435</v>
+        <v>-0.05885833434225379</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.1513777113537805</v>
+        <v>-0.5948099048877711</v>
       </c>
       <c r="I63" t="n">
-        <v>0.07523195010384041</v>
+        <v>-0.1414606046318683</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.1209039060079832</v>
+        <v>0.5377060541023133</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2031928330036329</v>
+        <v>0.01331145208674765</v>
       </c>
     </row>
     <row r="64">
@@ -3491,23 +3941,35 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="B64" t="n">
+        <v>0.1176622373013586</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.1805673997866258</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.284821256495602</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.4089869924441235</v>
+      </c>
       <c r="F64" t="n">
-        <v>-0.09823916361406528</v>
+        <v>-0.299265043431989</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.2663869061448403</v>
+        <v>-0.3003101303689066</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.09553934877686435</v>
+        <v>0.5885864734460529</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4593340031782372</v>
+        <v>0.083179525009256</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.08747694355153619</v>
+        <v>-0.1261733916855509</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1394937822225668</v>
+        <v>-0.4874927231326549</v>
       </c>
     </row>
     <row r="65">
@@ -3516,23 +3978,35 @@
           <t>2025-06-25</t>
         </is>
       </c>
+      <c r="B65" t="n">
+        <v>0.2362382068481566</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.1580206859824446</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.4204186470545902</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.0344117014391628</v>
+      </c>
       <c r="F65" t="n">
-        <v>-0.06029961288859439</v>
+        <v>0.4832013029323111</v>
       </c>
       <c r="G65" t="n">
-        <v>7.343289158825754e-05</v>
+        <v>0.3235437814339232</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.05807240028076543</v>
+        <v>0.3100794758868072</v>
       </c>
       <c r="I65" t="n">
-        <v>0.248510297264644</v>
+        <v>0.2010376570546362</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.1713665586193234</v>
+        <v>-0.04359036189357887</v>
       </c>
       <c r="K65" t="n">
-        <v>0.09771863669288486</v>
+        <v>0.4992043342892382</v>
       </c>
     </row>
     <row r="66">
@@ -3542,34 +4016,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.009921248040846117</v>
+        <v>-0.05914491789698873</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.09315705904653887</v>
+        <v>-0.141587767278958</v>
       </c>
       <c r="D66" t="n">
-        <v>0.10412070637163</v>
+        <v>0.4682608145231487</v>
       </c>
       <c r="E66" t="n">
-        <v>0.2506445937155518</v>
+        <v>0.3031024096711738</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1468603426506575</v>
+        <v>0.3776987117477166</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.2717571403972158</v>
+        <v>0.08844174607021038</v>
       </c>
       <c r="H66" t="n">
-        <v>0.007601236394873842</v>
+        <v>-0.05045931948179256</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.07708206381729951</v>
+        <v>0.06972679912360116</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.03778760761718014</v>
+        <v>-0.376959921144647</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2658582894270697</v>
+        <v>-0.1120022476437436</v>
       </c>
     </row>
     <row r="67">
@@ -3578,23 +4052,35 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="B67" t="n">
+        <v>-0.005637675858660764</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.6015404564515187</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.0954856198665696</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.2999763598009739</v>
+      </c>
       <c r="F67" t="n">
-        <v>-0.1346175940853805</v>
+        <v>0.2819070469012428</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.1591530343028573</v>
+        <v>-0.006416789038238754</v>
       </c>
       <c r="H67" t="n">
-        <v>0.07886330907626518</v>
+        <v>0.1907463810614773</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1098901098901099</v>
+        <v>0.02596983354195163</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.05339588331724737</v>
+        <v>0.2619931138049026</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.02463433812200702</v>
+        <v>-0.2768520478756172</v>
       </c>
     </row>
     <row r="68">
@@ -3603,23 +4089,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="B68" t="n">
+        <v>-0.2053426543996386</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.2106560080171187</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.5435529971861168</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.276489461798409</v>
+      </c>
       <c r="F68" t="n">
-        <v>0.06486701406255696</v>
+        <v>-0.326445050932887</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.3916306710029284</v>
+        <v>-0.2955465561649014</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2133240951913909</v>
+        <v>-0.3776240893549867</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.03703703703703694</v>
+        <v>0.3195664024817995</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.1124544096629915</v>
+        <v>0.0187747567885813</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.0648985860379777</v>
+        <v>0.3064307591067054</v>
       </c>
     </row>
     <row r="69">
@@ -3628,23 +4126,35 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="B69" t="n">
+        <v>0.3740724777271033</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.1113596846169161</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.3184506805795048</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.2122456927017567</v>
+      </c>
       <c r="F69" t="n">
-        <v>0.04119145994677249</v>
+        <v>-0.5630889408382901</v>
       </c>
       <c r="G69" t="n">
-        <v>0.08837175995558032</v>
+        <v>-0.6173290661749115</v>
       </c>
       <c r="H69" t="n">
-        <v>0.01462358336840148</v>
+        <v>0.1424795329820853</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2004704044130356</v>
+        <v>0.3826087424335661</v>
       </c>
       <c r="J69" t="n">
-        <v>0.04685048018322904</v>
+        <v>-0.162438859232946</v>
       </c>
       <c r="K69" t="n">
-        <v>0.1001514151278016</v>
+        <v>-0.1362698205613969</v>
       </c>
     </row>
     <row r="70">
@@ -3653,23 +4163,35 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="B70" t="n">
+        <v>0.197645251742685</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.5220784666078347</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.2241822978084657</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.7528551477471989</v>
+      </c>
       <c r="F70" t="n">
-        <v>-0.1820083039401273</v>
+        <v>0.3409900640538172</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.3172192269016708</v>
+        <v>0.02095519892063923</v>
       </c>
       <c r="H70" t="n">
-        <v>0.04484729377544509</v>
+        <v>-0.1479776217432114</v>
       </c>
       <c r="I70" t="n">
-        <v>0.03846153846153844</v>
+        <v>0.09037111700338815</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.02457499987444138</v>
+        <v>0.5541865397044689</v>
       </c>
       <c r="K70" t="n">
-        <v>0.2848819861523777</v>
+        <v>0.2637778965735981</v>
       </c>
     </row>
     <row r="71">
@@ -3678,23 +4200,35 @@
           <t>2025-09-19</t>
         </is>
       </c>
+      <c r="B71" t="n">
+        <v>0.007533909518559358</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.315678963459565</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-0.2512812985484426</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.194675498522456</v>
+      </c>
       <c r="F71" t="n">
-        <v>-0.06510884717018928</v>
+        <v>-0.1682062837638209</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.0121006190255681</v>
+        <v>0.2451404938759839</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2300596512015294</v>
+        <v>-0.112990171008442</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3331046312178388</v>
+        <v>-0.2521280117240508</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.03953877360227633</v>
+        <v>0.07997933833603184</v>
       </c>
       <c r="K71" t="n">
-        <v>0.1425691597337548</v>
+        <v>-0.2596086165554797</v>
       </c>
     </row>
     <row r="72">
@@ -3704,34 +4238,34 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.02994028183181292</v>
+        <v>0.2022537574904776</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0931570590465389</v>
+        <v>-0.2280622410671326</v>
       </c>
       <c r="D72" t="n">
-        <v>0.09489966977658246</v>
+        <v>0.3090597015686999</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2398589101421674</v>
+        <v>0.1559500542778379</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.02346219662385108</v>
+        <v>-0.3014770852315651</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.02509534632857689</v>
+        <v>0.09022219753297255</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.06681951859994135</v>
+        <v>0.204761273402275</v>
       </c>
       <c r="I72" t="n">
-        <v>0.017847951567425</v>
+        <v>-0.1493097653478746</v>
       </c>
       <c r="J72" t="n">
-        <v>0.06127243022012819</v>
+        <v>-0.2349926039462911</v>
       </c>
       <c r="K72" t="n">
-        <v>0.06209889206430068</v>
+        <v>-0.1280124872906915</v>
       </c>
     </row>
     <row r="73">
@@ -3740,23 +4274,35 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="B73" t="n">
+        <v>0.1726577445719092</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.6382588324662438</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.0316751743300577</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-0.03574019243912507</v>
+      </c>
       <c r="F73" t="n">
-        <v>-0.1604528132175912</v>
+        <v>0.3619651433146613</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1252525573575533</v>
+        <v>0.09448720615482513</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.1155875543748622</v>
+        <v>-0.1354498570934317</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1553231008958873</v>
+        <v>0.2335810902199691</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01042372716190274</v>
+        <v>0.2462822458474995</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.1654589174665298</v>
+        <v>0.1141500460071368</v>
       </c>
     </row>
     <row r="74">
@@ -3765,23 +4311,35 @@
           <t>2025-10-31</t>
         </is>
       </c>
+      <c r="B74" t="n">
+        <v>0.4528253495386964</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.3360143085805596</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.7944940746973576</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.4492780967615606</v>
+      </c>
       <c r="F74" t="n">
-        <v>-0.02638731450212668</v>
+        <v>0.1352093171798163</v>
       </c>
       <c r="G74" t="n">
-        <v>0.01188974179722927</v>
+        <v>0.3589084095756348</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.0434701307995937</v>
+        <v>0.5191846619934327</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2219554030874786</v>
+        <v>0.3868927740666876</v>
       </c>
       <c r="J74" t="n">
-        <v>0.01832414238838534</v>
+        <v>-0.07482964746078041</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.07496102488025363</v>
+        <v>0.2507548345239687</v>
       </c>
     </row>
     <row r="75">
@@ -3790,23 +4348,35 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="B75" t="n">
+        <v>-0.04446944156973466</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.4346800556633272</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.3950157759680226</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.001868631661384786</v>
+      </c>
       <c r="F75" t="n">
-        <v>-0.3184474984079286</v>
+        <v>-0.2594248903010605</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.05474759756369497</v>
+        <v>-0.5889074924064673</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2829311334203444</v>
+        <v>-0.4222408638958541</v>
       </c>
       <c r="I75" t="n">
-        <v>0.05556508399324763</v>
+        <v>0.5241176526462956</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.04823096381037323</v>
+        <v>-0.1325819525903545</v>
       </c>
       <c r="K75" t="n">
-        <v>0.1184244173516226</v>
+        <v>-0.01234068108174933</v>
       </c>
     </row>
     <row r="76">
@@ -3816,34 +4386,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.02596314438305249</v>
+        <v>-0.1549682002464392</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.1003229866655029</v>
+        <v>0.299077004912542</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1003229866655029</v>
+        <v>0.3004612879714781</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2150135705284228</v>
+        <v>-0.0356511523399099</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1255062285779246</v>
+        <v>-0.04933885783346558</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0332369907574188</v>
+        <v>0.120938107133027</v>
       </c>
       <c r="H76" t="n">
-        <v>0.07870557521484214</v>
+        <v>-0.3132291201869397</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.07280219780219775</v>
+        <v>0.4562997975078554</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.1642129794411089</v>
+        <v>0.1016088997197716</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1048593419206735</v>
+        <v>0.2103739224912718</v>
       </c>
     </row>
     <row r="77">
@@ -3852,23 +4422,35 @@
           <t>2025-12-15</t>
         </is>
       </c>
+      <c r="B77" t="n">
+        <v>0.3132009932395022</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.1096115082473384</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-0.01683842960768596</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-0.5759591642956644</v>
+      </c>
       <c r="F77" t="n">
-        <v>0.01705000898101512</v>
+        <v>0.1556404822493064</v>
       </c>
       <c r="G77" t="n">
-        <v>0.09698036470714878</v>
+        <v>-0.02522981064013339</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.2540326884112678</v>
+        <v>-0.04977191454475792</v>
       </c>
       <c r="I77" t="n">
-        <v>0.06933451719072091</v>
+        <v>0.5278901674734442</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.11291343102924</v>
+        <v>-0.1805633102268057</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.06174188249406932</v>
+        <v>-0.06157301977907179</v>
       </c>
     </row>
     <row r="78">
@@ -3878,34 +4460,34 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.08393265364224575</v>
+        <v>-0.02915505750245069</v>
       </c>
       <c r="C78" t="n">
-        <v>0.09848078939079268</v>
+        <v>0.3761383924712342</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1003229866655029</v>
+        <v>-0.1478831300292048</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2235192619473854</v>
+        <v>-0.2909285601997129</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.1228845479966302</v>
+        <v>0.2830292092291452</v>
       </c>
       <c r="G78" t="n">
-        <v>0.007340123382606749</v>
+        <v>0.2003566178831032</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.09227961001639091</v>
+        <v>0.2960584569046261</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1661232415121866</v>
+        <v>0.2364714956095406</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.01540253091873067</v>
+        <v>-0.1958576354140294</v>
       </c>
       <c r="K78" t="n">
-        <v>0.09458878569740352</v>
+        <v>0.2058165455190323</v>
       </c>
     </row>
     <row r="79">
@@ -3915,34 +4497,34 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.02870445891412488</v>
+        <v>0.2968408546141086</v>
       </c>
       <c r="C79" t="n">
-        <v>0.09489966977658215</v>
+        <v>0.2178809024518155</v>
       </c>
       <c r="D79" t="n">
-        <v>0.09144411715212425</v>
+        <v>0.2279996338075116</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2244594320182665</v>
+        <v>0.4642417637802715</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.1613304105805765</v>
+        <v>0.2613090634325655</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.07677700046090881</v>
+        <v>0.3977435886689815</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.09577663359425904</v>
+        <v>0.6839165509661014</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2215735516756941</v>
+        <v>0.09094231573016649</v>
       </c>
       <c r="J79" t="n">
-        <v>0.0702778234210847</v>
+        <v>0.325596872288909</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.1765336451663772</v>
+        <v>0.5495679681198558</v>
       </c>
     </row>
     <row r="80">
@@ -3952,34 +4534,34 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.05922977476448836</v>
+        <v>-0.05132651036150812</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.09848078939079276</v>
+        <v>0.2137412426528469</v>
       </c>
       <c r="D80" t="n">
-        <v>0.100322986665503</v>
+        <v>-0.1301381069526711</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.05096611659405038</v>
+        <v>-0.1200345901878029</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.1605658804657158</v>
+        <v>-0.1186162298268817</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.1740327113767012</v>
+        <v>0.09574659909864768</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.05827311887417461</v>
+        <v>-0.05350996497117667</v>
       </c>
       <c r="I80" t="n">
-        <v>0.05628969340495582</v>
+        <v>-0.273147014186866</v>
       </c>
       <c r="J80" t="n">
-        <v>0.08580004285106207</v>
+        <v>-0.1694122900830539</v>
       </c>
       <c r="K80" t="n">
-        <v>0.04473699886494856</v>
+        <v>-0.3281491193150257</v>
       </c>
     </row>
     <row r="81">
@@ -3988,23 +4570,35 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="B81" t="n">
+        <v>0.3321219540221289</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.2129789285865736</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-0.01324970808700121</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.3033389168699863</v>
+      </c>
       <c r="F81" t="n">
-        <v>-0.336117482774826</v>
+        <v>0.01525234719696055</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.009534043170362898</v>
+        <v>0.01738736313871471</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.177908981679077</v>
+        <v>0.04095955772841704</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.04248748499842665</v>
+        <v>0.09814375816586467</v>
       </c>
       <c r="J81" t="n">
-        <v>0.09625411500247075</v>
+        <v>-0.4155261154355751</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1641103755531702</v>
+        <v>-0.2140070805020489</v>
       </c>
     </row>
     <row r="82">
@@ -4013,23 +4607,109 @@
           <t>2026-02-27</t>
         </is>
       </c>
+      <c r="B82" t="n">
+        <v>0.2020401782835508</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.02470080462267759</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.1483602663137072</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.07962560755747655</v>
+      </c>
       <c r="F82" t="n">
-        <v>0.01527016939870706</v>
+        <v>-0.07080368635968975</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0697092457156592</v>
+        <v>0.02607727390402682</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.1249708666340306</v>
+        <v>-0.00544283032002753</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.02273120301429753</v>
+        <v>-0.04904759250972644</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.06164257780582476</v>
+        <v>-0.4268074865241485</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2883212374834873</v>
+        <v>0.1925574383276958</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>-0.2674343641524937</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.4226365998484868</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.3759120526906599</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.131612698892763</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-0.4462822877226162</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-0.125622548711887</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.02745191285128214</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.06250740119110003</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.1276520355800037</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.657132927174866</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>-0.151706427270369</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.2379065151110886</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-0.01061519401829271</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.3024393201878091</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-0.1290861478242187</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.3524579096228487</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.04520205991488789</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.1373390301246171</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-0.516733349902659</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.1980980157743456</v>
       </c>
     </row>
   </sheetData>
@@ -4044,7 +4724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4053,52 +4733,52 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha101</t>
+          <t>alpha023 vs alpha043</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha062</t>
+          <t>alpha023 vs alpha066</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha065</t>
+          <t>alpha023 vs alpha045</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha032</t>
+          <t>alpha023 vs alpha031</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>alpha101 vs alpha062</t>
+          <t>alpha043 vs alpha066</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>alpha101 vs alpha065</t>
+          <t>alpha043 vs alpha045</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>alpha101 vs alpha032</t>
+          <t>alpha043 vs alpha031</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alpha062 vs alpha065</t>
+          <t>alpha066 vs alpha045</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>alpha062 vs alpha032</t>
+          <t>alpha066 vs alpha031</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>alpha065 vs alpha032</t>
+          <t>alpha045 vs alpha031</t>
         </is>
       </c>
     </row>
@@ -4109,9 +4789,6 @@
           <t>2023-01-03</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>-0.002368322385558906</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4119,9 +4796,6 @@
           <t>2023-01-18</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>-0.05767221262774212</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4130,19 +4804,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.04608735379818363</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.09667364890456623</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.4026291504434566</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.1631058934897514</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.3337119062359572</v>
+        <v>-0.5714561291862538</v>
       </c>
     </row>
     <row r="6">
@@ -4152,19 +4814,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.08184903972082314</v>
+        <v>-1.079079797315318</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1933472978091325</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.5883845288980092</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.1739149517432679</v>
+        <v>0.4723304542800635</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1055822156319885</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4190784652196279</v>
+        <v>-0.7946969570461895</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3531290376127579</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.4917108237894436</v>
       </c>
     </row>
     <row r="7">
@@ -4173,20 +4838,35 @@
           <t>2023-03-02</t>
         </is>
       </c>
+      <c r="B7" t="n">
+        <v>0.02331650761758647</v>
+      </c>
       <c r="C7" t="n">
-        <v>-0.1265163609905736</v>
+        <v>-0.545510732244594</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2900209467136987</v>
+        <v>0.5980799878617021</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.375040468573533</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7497159771279069</v>
+        <v>0.1807598435971681</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2342312811214692</v>
+        <v>0.2879676387076954</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.3551465542354422</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4920325226824974</v>
+        <v>-1.074855535666136</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.215457194832265</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.7122091299513051</v>
       </c>
     </row>
     <row r="8">
@@ -4195,20 +4875,35 @@
           <t>2023-03-16</t>
         </is>
       </c>
+      <c r="B8" t="n">
+        <v>0.398820654182622</v>
+      </c>
       <c r="C8" t="n">
-        <v>-0.2249971503813664</v>
+        <v>-0.3281833886668523</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.386694595618265</v>
+        <v>0.7506918979774182</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.4581537957273363</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8897667485131581</v>
+        <v>-0.2058447444218008</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1657362711646103</v>
+        <v>0.4486842902279781</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2606558153536617</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5475976066757451</v>
+        <v>-0.9903128327224091</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.02741303787724386</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.3287970760397939</v>
       </c>
     </row>
     <row r="9">
@@ -4217,20 +4912,35 @@
           <t>2023-03-30</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>-0.1093364239029047</v>
+      </c>
       <c r="C9" t="n">
-        <v>-0.3216707992859326</v>
+        <v>-0.3439120435135662</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4833682445228312</v>
+        <v>1.08649044838738</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6638374846764312</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.042055226993585</v>
+        <v>-0.07734964385291912</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2028257698012432</v>
+        <v>0.3600765241284535</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5368393910692514</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5105605696387081</v>
+        <v>-0.9142598127767394</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.1715107596204242</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.3203889546636421</v>
       </c>
     </row>
     <row r="10">
@@ -4239,20 +4949,35 @@
           <t>2023-04-14</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>-0.1320401737605847</v>
+      </c>
       <c r="C10" t="n">
-        <v>-0.4183444481904989</v>
+        <v>-0.5973599086861561</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5800418934273974</v>
+        <v>0.9790196406135849</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8843772593863183</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.089124131834526</v>
+        <v>0.1332035966262344</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2140642579751642</v>
+        <v>0.6670986081853401</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.855575826360109</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3253753844535234</v>
+        <v>-0.5962442996022392</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.03594364347280657</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.2067859463233486</v>
       </c>
     </row>
     <row r="11">
@@ -4262,22 +4987,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.08293945999691466</v>
+        <v>0.1673841045367369</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4259873944170929</v>
+        <v>-0.5908850111180477</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5851328146355549</v>
+        <v>1.565503374729724</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.8695242738379092</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9592464784911906</v>
+        <v>0.1228108178117153</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1947522572884159</v>
+        <v>1.039754379194837</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.039114336118211</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4903522454936856</v>
+        <v>-0.365006703070563</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1550166427780326</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.2812641265449134</v>
       </c>
     </row>
     <row r="12">
@@ -4286,20 +5023,35 @@
           <t>2023-05-12</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>-0.05224091542540735</v>
+      </c>
       <c r="C12" t="n">
-        <v>-0.3293137455125267</v>
+        <v>0.04284674580455572</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.680032484412137</v>
+        <v>1.159213203790609</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6767758609026343</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.174126370267408</v>
+        <v>0.1016300480637728</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4349697882182169</v>
+        <v>1.038479690077945</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6637200649562233</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9163512227752509</v>
+        <v>-0.4643049710705595</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1781416272853429</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.5131227060314625</v>
       </c>
     </row>
     <row r="13">
@@ -4309,22 +5061,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1908984877245453</v>
+        <v>0.1269158604528799</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.326769595088137</v>
+        <v>0.07323604036193045</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7113398625129642</v>
+        <v>1.307395588568302</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.08336602125108927</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.254699249285629</v>
+        <v>-0.3678677248369284</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6334998256126102</v>
+        <v>0.8878971190903548</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.137385336769911</v>
       </c>
       <c r="I13" t="n">
-        <v>1.091542891855448</v>
+        <v>-0.6271356565193391</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.251399885895583</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.8094603159838747</v>
       </c>
     </row>
     <row r="14">
@@ -4333,20 +5097,35 @@
           <t>2023-06-12</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>-0.05050522847844599</v>
+      </c>
       <c r="C14" t="n">
-        <v>-0.4234432439927033</v>
+        <v>0.3755196344321783</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7978074027463875</v>
+        <v>1.179655282254871</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.3091592220368196</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.293499470549797</v>
+        <v>-0.7013917931230578</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6825001223669731</v>
+        <v>0.9460271904017424</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.349252170237381</v>
       </c>
       <c r="I14" t="n">
-        <v>1.128810691480445</v>
+        <v>-0.661472723223959</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.2159862947220437</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.5833335315545094</v>
       </c>
     </row>
     <row r="15">
@@ -4355,20 +5134,35 @@
           <t>2023-06-27</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>0.3129197478562744</v>
+      </c>
       <c r="C15" t="n">
-        <v>-0.5132024736234185</v>
+        <v>0.6048347583221648</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9000096513281735</v>
+        <v>0.992952066100585</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3167136949515822</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.520888791072764</v>
+        <v>-0.5231508319086919</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7317650265680545</v>
+        <v>0.8631746451323513</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.384794567407257</v>
       </c>
       <c r="I15" t="n">
-        <v>1.07714886644795</v>
+        <v>-0.9053150828235144</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.3277452406455909</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.7533274844010859</v>
       </c>
     </row>
     <row r="16">
@@ -4377,20 +5171,35 @@
           <t>2023-07-12</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>0.7114110818995768</v>
+      </c>
       <c r="C16" t="n">
-        <v>-0.6098761225279847</v>
+        <v>1.022578034169378</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9949093211047556</v>
+        <v>1.403360463868428</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.574457866837598</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.581809014391615</v>
+        <v>-0.7014823038192084</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7847214248815567</v>
+        <v>1.142595279789337</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.221839870542707</v>
       </c>
       <c r="I16" t="n">
-        <v>1.132713950441198</v>
+        <v>-0.413120406648299</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.2655569336279666</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-1.00400529185766</v>
       </c>
     </row>
     <row r="17">
@@ -4399,20 +5208,35 @@
           <t>2023-07-26</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>0.3456558523023113</v>
+      </c>
       <c r="C17" t="n">
-        <v>-0.7047757923045669</v>
+        <v>0.8386862039502024</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.089808990881338</v>
+        <v>1.621580547596715</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.310729810186356</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.55397810985624</v>
+        <v>-1.143922736458715</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9206504944632208</v>
+        <v>1.440728125962953</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6181674915728103</v>
       </c>
       <c r="I17" t="n">
-        <v>1.243520125398316</v>
+        <v>-1.240502392514392</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.09921812539616803</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.320748485613159</v>
       </c>
     </row>
     <row r="18">
@@ -4421,20 +5245,35 @@
           <t>2023-08-09</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>0.5160052549067287</v>
+      </c>
       <c r="C18" t="n">
-        <v>-0.7945350219352821</v>
+        <v>1.092887058066507</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.195889617626231</v>
+        <v>1.54279134497462</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.634383257217109</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.612364541755559</v>
+        <v>-0.515610101702448</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8228957485225054</v>
+        <v>1.59026887084715</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.058142627889227</v>
       </c>
       <c r="I18" t="n">
-        <v>1.231777752384737</v>
+        <v>-0.8501516571099372</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4077988670886817</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.322633162771633</v>
       </c>
     </row>
     <row r="19">
@@ -4443,20 +5282,35 @@
           <t>2023-08-23</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>0.5828061300906029</v>
+      </c>
       <c r="C19" t="n">
-        <v>-0.8930158113260749</v>
+        <v>1.712733027879325</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.300010323997861</v>
+        <v>1.203625726017987</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.378058389315396</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.770536581216816</v>
+        <v>-0.5068044150502118</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9856990997982511</v>
+        <v>0.9293695734532406</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9601695047897548</v>
       </c>
       <c r="I19" t="n">
-        <v>1.434701901289665</v>
+        <v>-0.8884814679258142</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9018152974414217</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1.242027648031869</v>
       </c>
     </row>
     <row r="20">
@@ -4465,20 +5319,35 @@
           <t>2023-09-07</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>0.8235905068092633</v>
+      </c>
       <c r="C20" t="n">
-        <v>-0.9914966007168676</v>
+        <v>1.544021486703318</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.396683972902427</v>
+        <v>1.443995962500801</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.823115955459531</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.994932034183421</v>
+        <v>-0.1590513556118627</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.346207950463817</v>
+        <v>1.202387174593217</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9817264672618757</v>
       </c>
       <c r="I20" t="n">
-        <v>1.86070087857123</v>
+        <v>-0.6949890587806454</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.405640975209104</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-1.188803691074672</v>
       </c>
     </row>
     <row r="21">
@@ -4488,22 +5357,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1925942729465113</v>
+        <v>0.6314662586033484</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.988952450292478</v>
+        <v>1.744118356404031</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.406886859452284</v>
+        <v>1.683653866013907</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.257830089060862</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.918695954860827</v>
+        <v>0.3980773055075666</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.118482109292943</v>
+        <v>1.272146722171545</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.152696281382932</v>
       </c>
       <c r="I21" t="n">
-        <v>2.252103728492938</v>
+        <v>-0.5930171430633091</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.838583600403239</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.6813612028480965</v>
       </c>
     </row>
     <row r="22">
@@ -4513,22 +5394,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1585289471326429</v>
+        <v>0.8974290330632602</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.123792422785126</v>
+        <v>2.363631917664101</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.417089746002141</v>
+        <v>2.062044228090683</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.086987879634941</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.872699263449765</v>
+        <v>0.7968673246309155</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.222866428270871</v>
+        <v>1.378117587238753</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.749039053303233</v>
       </c>
       <c r="I22" t="n">
-        <v>2.160615891868005</v>
+        <v>-0.1775153668200799</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.981795239121289</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1.114450879996805</v>
       </c>
     </row>
     <row r="23">
@@ -4537,20 +5430,35 @@
           <t>2023-10-19</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>0.6706648573667184</v>
+      </c>
       <c r="C23" t="n">
-        <v>-1.02711877388056</v>
+        <v>2.176219860920606</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.51024680504868</v>
+        <v>1.846101352448665</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.891729293545638</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.007093159780672</v>
+        <v>0.8000776921524192</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.27072426487803</v>
+        <v>1.747104524144965</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.059074885607381</v>
       </c>
       <c r="I23" t="n">
-        <v>2.160615891868005</v>
+        <v>-0.1730555303811712</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.450444781999252</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.7619253296811075</v>
       </c>
     </row>
     <row r="24">
@@ -4560,22 +5468,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2274167081518973</v>
+        <v>0.4960482056221426</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.167047047221987</v>
+        <v>2.007264728737436</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.481666698453423</v>
+        <v>2.011541431940816</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.014443105834339</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.06527656189661</v>
+        <v>1.336263131240912</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.448282682984906</v>
+        <v>2.003104062853871</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.40251350952576</v>
       </c>
       <c r="I24" t="n">
-        <v>1.899612538557064</v>
+        <v>-0.1174720474964384</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.210292302528658</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.6003944522292292</v>
       </c>
     </row>
     <row r="25">
@@ -4584,20 +5504,35 @@
           <t>2023-11-16</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>0.7135081584634653</v>
+      </c>
       <c r="C25" t="n">
-        <v>-1.073889988175449</v>
+        <v>2.496813177802255</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.568134238686846</v>
+        <v>2.346457342080645</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.090593554209532</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.90787391731587</v>
+        <v>1.740581847932844</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.558909013237019</v>
+        <v>2.237121195376761</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.624478598369063</v>
       </c>
       <c r="I25" t="n">
-        <v>1.679995927063406</v>
+        <v>-0.366589666301994</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.880045413812595</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.4074243418394958</v>
       </c>
     </row>
     <row r="26">
@@ -4607,22 +5542,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1877298011415063</v>
+        <v>1.321586855863385</v>
       </c>
       <c r="C26" t="n">
-        <v>-1.078980909383606</v>
+        <v>2.601843127913666</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.568134238686846</v>
+        <v>2.229852519826371</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.973921805753126</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.746467764624444</v>
+        <v>2.444550554406705</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.608890052397259</v>
+        <v>2.094020800163744</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.311480775599303</v>
       </c>
       <c r="I26" t="n">
-        <v>1.865308256228681</v>
+        <v>-0.7248239679169928</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6505895416969555</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.5586133800545439</v>
       </c>
     </row>
     <row r="27">
@@ -4631,29 +5578,35 @@
           <t>2023-12-15</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>1.763912789520531</v>
+      </c>
       <c r="C27" t="n">
-        <v>-1.175654558288173</v>
+        <v>3.037167986562217</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.65460177892027</v>
+        <v>1.961327546693052</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.188763147694634</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.881737115405219</v>
+        <v>2.78819359793</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.798606946980462</v>
+        <v>1.949113764743235</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2835151618181107</v>
+        <v>2.134082107432403</v>
       </c>
       <c r="I27" t="n">
-        <v>2.200718452853649</v>
+        <v>-0.7581165632037941</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.03223028885762776</v>
+        <v>1.008685610971733</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1533335261719049</v>
+        <v>-0.01142889893413435</v>
       </c>
     </row>
     <row r="28">
@@ -4662,29 +5615,35 @@
           <t>2024-01-02</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>2.269594409083508</v>
+      </c>
       <c r="C28" t="n">
-        <v>-1.270554228064755</v>
+        <v>3.739642325616217</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.762686204212049</v>
+        <v>2.634585744091244</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.85848501877595</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.877258129643339</v>
+        <v>3.181897235097881</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.779608549227782</v>
+        <v>2.371907574632278</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5222827426997809</v>
+        <v>2.428366047937273</v>
       </c>
       <c r="I28" t="n">
-        <v>2.370523102998979</v>
+        <v>0.02947290793980772</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1394037614284172</v>
+        <v>1.466679455870694</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2763751026566981</v>
+        <v>0.16596531671513</v>
       </c>
     </row>
     <row r="29">
@@ -4694,34 +5653,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2232057933641557</v>
+        <v>2.514144634943801</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.410482501406182</v>
+        <v>3.52492495811982</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.767777125420206</v>
+        <v>2.94231594918011</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2472975825015158</v>
+        <v>3.316966835704271</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.723576564981564</v>
+        <v>3.161655134050178</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.802419734150926</v>
+        <v>2.252611888628679</v>
       </c>
       <c r="H29" t="n">
-        <v>0.800021232532933</v>
+        <v>2.34553789542543</v>
       </c>
       <c r="I29" t="n">
-        <v>2.203026942135452</v>
+        <v>0.05257093289961603</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01729525716812123</v>
+        <v>1.516584840548527</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2603547476757932</v>
+        <v>0.1794215459653251</v>
       </c>
     </row>
     <row r="30">
@@ -4731,34 +5690,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2790491184516147</v>
+        <v>2.786580129346977</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.410482501406182</v>
+        <v>3.433099905322921</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.760134179193612</v>
+        <v>3.305039695046859</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2713392940887268</v>
+        <v>3.034361886399476</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.89331750871268</v>
+        <v>3.089774237276105</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.886295946505081</v>
+        <v>2.412827260954603</v>
       </c>
       <c r="H30" t="n">
-        <v>1.152528495266074</v>
+        <v>2.670504999134564</v>
       </c>
       <c r="I30" t="n">
-        <v>2.369951407357849</v>
+        <v>0.4088865082699116</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1003923753000152</v>
+        <v>1.792034312652954</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1701612089681659</v>
+        <v>0.04722330222665896</v>
       </c>
     </row>
     <row r="31">
@@ -4767,29 +5726,35 @@
           <t>2024-02-14</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>2.763145333253294</v>
+      </c>
       <c r="C31" t="n">
-        <v>-1.507156150310749</v>
+        <v>3.598429214153945</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.856807828098178</v>
+        <v>3.596368056740995</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.33517304512096</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.733887859184953</v>
+        <v>3.683810719564098</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.9258788122102</v>
+        <v>2.715674880282164</v>
       </c>
       <c r="H31" t="n">
-        <v>1.455591284530271</v>
+        <v>2.82546559343946</v>
       </c>
       <c r="I31" t="n">
-        <v>2.444025481431923</v>
+        <v>0.730517756920556</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.04023309357463257</v>
+        <v>1.995183701494825</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1597137451006936</v>
+        <v>0.40847761522902</v>
       </c>
     </row>
     <row r="32">
@@ -4799,34 +5764,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3152690092096353</v>
+        <v>2.86935023235387</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.512247071518906</v>
+        <v>3.882347700590554</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.836231053910305</v>
+        <v>3.770313739626149</v>
       </c>
       <c r="E32" t="n">
-        <v>0.301207437404266</v>
+        <v>3.422125506485394</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.920548152606757</v>
+        <v>3.975272028421061</v>
       </c>
       <c r="G32" t="n">
-        <v>-2.068833901558063</v>
+        <v>2.716286486588117</v>
       </c>
       <c r="H32" t="n">
-        <v>1.738621717242075</v>
+        <v>2.865499350701803</v>
       </c>
       <c r="I32" t="n">
-        <v>2.337149461917215</v>
+        <v>1.328356415114699</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2512337699325577</v>
+        <v>1.86780363471639</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2479348367328356</v>
+        <v>0.5021430911097734</v>
       </c>
     </row>
     <row r="33">
@@ -4836,34 +5801,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3310821214184388</v>
+        <v>2.832405095452406</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.649607635467595</v>
+        <v>4.140364507796212</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.826028167360448</v>
+        <v>3.496336660539002</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5597975575891253</v>
+        <v>3.604430451342727</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.815614956630797</v>
+        <v>4.097135890620955</v>
       </c>
       <c r="G33" t="n">
-        <v>-2.148387408837623</v>
+        <v>2.950770867294109</v>
       </c>
       <c r="H33" t="n">
-        <v>1.979776478542435</v>
+        <v>3.029480238515796</v>
       </c>
       <c r="I33" t="n">
-        <v>2.337149461917215</v>
+        <v>1.600040080614622</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.2750510901567497</v>
+        <v>1.938506474228428</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2145225076799644</v>
+        <v>0.6677744976146165</v>
       </c>
     </row>
     <row r="34">
@@ -4872,29 +5837,35 @@
           <t>2024-03-28</t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>2.764881994206421</v>
+      </c>
       <c r="C34" t="n">
-        <v>-1.746281284372161</v>
+        <v>3.834069454768685</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.920927837137031</v>
+        <v>3.25036309720914</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.924324034165417</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.858278719061463</v>
+        <v>4.308487601045091</v>
       </c>
       <c r="G34" t="n">
-        <v>-2.39490055332048</v>
+        <v>3.063589561363836</v>
       </c>
       <c r="H34" t="n">
-        <v>2.155961697077823</v>
+        <v>2.942297398017562</v>
       </c>
       <c r="I34" t="n">
-        <v>2.392714545910463</v>
+        <v>1.617544162894227</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.1686277978791219</v>
+        <v>2.00078833466825</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2030113390840129</v>
+        <v>0.8781068752722287</v>
       </c>
     </row>
     <row r="35">
@@ -4903,29 +5874,35 @@
           <t>2024-04-12</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>3.176287240033797</v>
+      </c>
       <c r="C35" t="n">
-        <v>-1.842954933276727</v>
+        <v>4.164119013899464</v>
       </c>
       <c r="D35" t="n">
-        <v>-2.019408626527823</v>
+        <v>2.998725960860824</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.088686360687128</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.740567575067667</v>
+        <v>4.402927721869267</v>
       </c>
       <c r="G35" t="n">
-        <v>-2.4844782031577</v>
+        <v>3.521356553671243</v>
       </c>
       <c r="H35" t="n">
-        <v>2.336575969395863</v>
+        <v>3.414291886679544</v>
       </c>
       <c r="I35" t="n">
-        <v>2.337149461917215</v>
+        <v>1.220196121151338</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3199612164050566</v>
+        <v>1.99914897283989</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2185556203276273</v>
+        <v>0.844617017004386</v>
       </c>
     </row>
     <row r="36">
@@ -4934,29 +5911,35 @@
           <t>2024-04-26</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>2.951637971927267</v>
+      </c>
       <c r="C36" t="n">
-        <v>-1.951039358568507</v>
+        <v>3.773550752680673</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.112565685574362</v>
+        <v>3.461033373079642</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.197479622929045</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.857550626961223</v>
+        <v>4.122759826879004</v>
       </c>
       <c r="G36" t="n">
-        <v>-2.570475067697161</v>
+        <v>3.042261422256829</v>
       </c>
       <c r="H36" t="n">
-        <v>2.519747906834843</v>
+        <v>3.469172396448764</v>
       </c>
       <c r="I36" t="n">
-        <v>2.378586558425452</v>
+        <v>0.9933650624718188</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3295686403470339</v>
+        <v>2.152377106274598</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2583438615310075</v>
+        <v>0.8474100444567217</v>
       </c>
     </row>
     <row r="37">
@@ -4965,29 +5948,35 @@
           <t>2024-05-10</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>3.072416100390891</v>
+      </c>
       <c r="C37" t="n">
-        <v>-2.044196417615045</v>
+        <v>3.823335321747583</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.216686391945991</v>
+        <v>3.861366483900799</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4.617069085560177</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.996677444622464</v>
+        <v>4.566252792325001</v>
       </c>
       <c r="G37" t="n">
-        <v>-2.63226124821544</v>
+        <v>2.953989731096974</v>
       </c>
       <c r="H37" t="n">
-        <v>2.697057089029086</v>
+        <v>3.714929412384938</v>
       </c>
       <c r="I37" t="n">
-        <v>2.307010356309389</v>
+        <v>0.3878197456526068</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2653702954716017</v>
+        <v>2.461048520531773</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4223347886012199</v>
+        <v>0.9228184456832468</v>
       </c>
     </row>
     <row r="38">
@@ -4996,29 +5985,35 @@
           <t>2024-05-24</t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>3.213021505339344</v>
+      </c>
       <c r="C38" t="n">
-        <v>-2.137353476661584</v>
+        <v>4.165873672314494</v>
       </c>
       <c r="D38" t="n">
-        <v>-2.331072195914547</v>
+        <v>3.170161866482349</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5.310539004119357</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.1812451372339</v>
+        <v>4.016524631810779</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.854475113074228</v>
+        <v>2.983764891731016</v>
       </c>
       <c r="H38" t="n">
-        <v>2.863781574149154</v>
+        <v>3.64423904000953</v>
       </c>
       <c r="I38" t="n">
-        <v>2.44483375934335</v>
+        <v>0.2933095970717094</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.3542518605894455</v>
+        <v>2.77689187417822</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3935398583930329</v>
+        <v>0.1292954879651425</v>
       </c>
     </row>
     <row r="39">
@@ -5027,29 +6022,35 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="B39" t="n">
+        <v>3.200243878509126</v>
+      </c>
       <c r="C39" t="n">
-        <v>-2.230510535708122</v>
+        <v>4.250366577276606</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.41753973614797</v>
+        <v>3.993029568741467</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5.400094738942983</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.017004276173918</v>
+        <v>3.727880533589816</v>
       </c>
       <c r="G39" t="n">
-        <v>-2.90077193622353</v>
+        <v>3.050607897373566</v>
       </c>
       <c r="H39" t="n">
-        <v>3.049392582951008</v>
+        <v>3.904825150400667</v>
       </c>
       <c r="I39" t="n">
-        <v>2.776330531409248</v>
+        <v>0.335298628526796</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.2430922399885299</v>
+        <v>3.225801744883728</v>
       </c>
       <c r="K39" t="n">
-        <v>0.4598709193804142</v>
+        <v>0.4139517207003812</v>
       </c>
     </row>
     <row r="40">
@@ -5058,29 +6059,35 @@
           <t>2024-06-25</t>
         </is>
       </c>
+      <c r="B40" t="n">
+        <v>3.744919246682486</v>
+      </c>
       <c r="C40" t="n">
-        <v>-2.320269765338837</v>
+        <v>3.960671208251546</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.512439405924552</v>
+        <v>4.129856294045274</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5.5016670243286</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.182032063775591</v>
+        <v>3.485815314069419</v>
       </c>
       <c r="G40" t="n">
-        <v>-2.84721701201615</v>
+        <v>2.962914973624224</v>
       </c>
       <c r="H40" t="n">
-        <v>3.264978038277904</v>
+        <v>3.472843209467641</v>
       </c>
       <c r="I40" t="n">
-        <v>2.904963805460846</v>
+        <v>0.6285882810759262</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3662404243580126</v>
+        <v>3.444510109142567</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7107899431166251</v>
+        <v>0.5806526612342837</v>
       </c>
     </row>
     <row r="41">
@@ -5089,29 +6096,35 @@
           <t>2024-07-10</t>
         </is>
       </c>
+      <c r="B41" t="n">
+        <v>4.107127031852308</v>
+      </c>
       <c r="C41" t="n">
-        <v>-2.415169435115419</v>
+        <v>4.090205277719077</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.600540265424548</v>
+        <v>3.99870571466738</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5.912146997117876</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.22864417728612</v>
+        <v>3.623410412230243</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.946321510221482</v>
+        <v>2.817609763144944</v>
       </c>
       <c r="H41" t="n">
-        <v>3.383981927730038</v>
+        <v>3.537657818274969</v>
       </c>
       <c r="I41" t="n">
-        <v>2.903241434562361</v>
+        <v>1.16322782638356</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4163604976562572</v>
+        <v>3.788966846025923</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7865830112041912</v>
+        <v>0.2761543996986832</v>
       </c>
     </row>
     <row r="42">
@@ -5120,29 +6133,35 @@
           <t>2024-07-24</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>4.190777568034513</v>
+      </c>
       <c r="C42" t="n">
-        <v>-2.318495786210853</v>
+        <v>4.491912997632936</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.69543993520113</v>
+        <v>3.940380991110476</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6.069277937295097</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.289746200760543</v>
+        <v>3.76605118329758</v>
       </c>
       <c r="G42" t="n">
-        <v>-2.824360777234446</v>
+        <v>3.2509106868008</v>
       </c>
       <c r="H42" t="n">
-        <v>3.413048082739468</v>
+        <v>4.135452890840476</v>
       </c>
       <c r="I42" t="n">
-        <v>2.884719739897945</v>
+        <v>1.454683704954079</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.4313561068068984</v>
+        <v>4.258602033104008</v>
       </c>
       <c r="K42" t="n">
-        <v>0.9289149982218989</v>
+        <v>1.003952640893714</v>
       </c>
     </row>
     <row r="43">
@@ -5151,29 +6170,35 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>4.280313242457886</v>
+      </c>
       <c r="C43" t="n">
-        <v>-2.411652845257392</v>
+        <v>4.84546638822621</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.801520561946023</v>
+        <v>3.969039669089592</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.44579281954818</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.33618051901382</v>
+        <v>4.179140909440411</v>
       </c>
       <c r="G43" t="n">
-        <v>-2.969070768364802</v>
+        <v>3.502513941614121</v>
       </c>
       <c r="H43" t="n">
-        <v>3.501721362058604</v>
+        <v>4.372789704635392</v>
       </c>
       <c r="I43" t="n">
-        <v>2.906777440766834</v>
+        <v>1.747061741597963</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4080158302757627</v>
+        <v>4.368234387352956</v>
       </c>
       <c r="K43" t="n">
-        <v>1.004190410839738</v>
+        <v>1.509675150465732</v>
       </c>
     </row>
     <row r="44">
@@ -5182,29 +6207,35 @@
           <t>2024-08-21</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>4.335564003114102</v>
+      </c>
       <c r="C44" t="n">
-        <v>-2.31675317548081</v>
+        <v>5.235764970924865</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.901843548611526</v>
+        <v>3.865605691465886</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6.487956787510415</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.112562518532895</v>
+        <v>4.169428202870701</v>
       </c>
       <c r="G44" t="n">
-        <v>-3.094800869989792</v>
+        <v>3.510651630648613</v>
       </c>
       <c r="H44" t="n">
-        <v>3.649710972700322</v>
+        <v>4.820547674273433</v>
       </c>
       <c r="I44" t="n">
-        <v>2.99876303730664</v>
+        <v>1.401773317758367</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.3225334865197391</v>
+        <v>4.492826145929026</v>
       </c>
       <c r="K44" t="n">
-        <v>1.015796997639095</v>
+        <v>1.881894092638353</v>
       </c>
     </row>
     <row r="45">
@@ -5213,29 +6244,35 @@
           <t>2024-09-05</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>3.996495487884453</v>
+      </c>
       <c r="C45" t="n">
-        <v>-2.420873881852439</v>
+        <v>5.546817067122324</v>
       </c>
       <c r="D45" t="n">
-        <v>-2.991602778242241</v>
+        <v>3.855546991934939</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6.79617277092974</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.080577021602245</v>
+        <v>3.869016672305623</v>
       </c>
       <c r="G45" t="n">
-        <v>-2.795723695172725</v>
+        <v>3.562617025785383</v>
       </c>
       <c r="H45" t="n">
-        <v>3.847725550231264</v>
+        <v>4.754271660370235</v>
       </c>
       <c r="I45" t="n">
-        <v>3.190487175237674</v>
+        <v>1.788225531565454</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.304336634862314</v>
+        <v>4.636730786504656</v>
       </c>
       <c r="K45" t="n">
-        <v>1.196238652553142</v>
+        <v>2.15475542994484</v>
       </c>
     </row>
     <row r="46">
@@ -5244,29 +6281,35 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>4.402930431391163</v>
+      </c>
       <c r="C46" t="n">
-        <v>-2.517547530757005</v>
+        <v>5.930691658184301</v>
       </c>
       <c r="D46" t="n">
-        <v>-3.088276427146807</v>
+        <v>4.118547994311077</v>
+      </c>
+      <c r="E46" t="n">
+        <v>7.327924564831548</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.230594924250381</v>
+        <v>3.851608859692249</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.055646061280137</v>
+        <v>3.587602798868663</v>
       </c>
       <c r="H46" t="n">
-        <v>3.973608636098493</v>
+        <v>5.103513206262365</v>
       </c>
       <c r="I46" t="n">
-        <v>3.634931619682118</v>
+        <v>1.583226443727705</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.2992449071757222</v>
+        <v>5.14174796538738</v>
       </c>
       <c r="K46" t="n">
-        <v>1.383063631812574</v>
+        <v>2.1164832953313</v>
       </c>
     </row>
     <row r="47">
@@ -5276,34 +6319,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.4062038231987359</v>
+        <v>4.073845095772048</v>
       </c>
       <c r="C47" t="n">
-        <v>-2.509904584530411</v>
+        <v>5.659668045581813</v>
       </c>
       <c r="D47" t="n">
-        <v>-3.070318911283991</v>
+        <v>4.856323262756232</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8191132597929227</v>
+        <v>7.659783890227732</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.361023847639464</v>
+        <v>3.949171565127632</v>
       </c>
       <c r="G47" t="n">
-        <v>-3.196370847353544</v>
+        <v>3.100181959982477</v>
       </c>
       <c r="H47" t="n">
-        <v>4.087036087849733</v>
+        <v>4.187970092003001</v>
       </c>
       <c r="I47" t="n">
-        <v>3.627657458292674</v>
+        <v>1.301707850491637</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.219670697537785</v>
+        <v>4.934790276163191</v>
       </c>
       <c r="K47" t="n">
-        <v>1.499737607824208</v>
+        <v>2.541630597718768</v>
       </c>
     </row>
     <row r="48">
@@ -5313,34 +6356,34 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.4599460595208605</v>
+        <v>4.092796281603531</v>
       </c>
       <c r="C48" t="n">
-        <v>-2.377540633118318</v>
+        <v>5.864427323030984</v>
       </c>
       <c r="D48" t="n">
-        <v>-3.075409832492148</v>
+        <v>5.290478317930504</v>
       </c>
       <c r="E48" t="n">
-        <v>1.096411415938633</v>
+        <v>8.219749728392147</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.335219805461489</v>
+        <v>4.249571804466704</v>
       </c>
       <c r="G48" t="n">
-        <v>-3.152205563440149</v>
+        <v>2.814158665328458</v>
       </c>
       <c r="H48" t="n">
-        <v>4.150608488190873</v>
+        <v>3.943514261137388</v>
       </c>
       <c r="I48" t="n">
-        <v>3.515020095655311</v>
+        <v>1.192296733962425</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.1541712685490913</v>
+        <v>5.112111072313767</v>
       </c>
       <c r="K48" t="n">
-        <v>1.649986930567474</v>
+        <v>2.830437558840665</v>
       </c>
     </row>
     <row r="49">
@@ -5349,29 +6392,35 @@
           <t>2024-10-31</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>4.566704343660354</v>
+      </c>
       <c r="C49" t="n">
-        <v>-2.47602142250911</v>
+        <v>6.100963154152098</v>
       </c>
       <c r="D49" t="n">
-        <v>-3.17030950226873</v>
+        <v>5.34197166105659</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7.879459054192677</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.554002219082121</v>
+        <v>4.402286232395727</v>
       </c>
       <c r="G49" t="n">
-        <v>-3.388232437607219</v>
+        <v>3.162701627458898</v>
       </c>
       <c r="H49" t="n">
-        <v>4.351819510137824</v>
+        <v>4.060296562474997</v>
       </c>
       <c r="I49" t="n">
-        <v>3.737661605089274</v>
+        <v>1.270849164316835</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.0828320375806</v>
+        <v>4.917270750187546</v>
       </c>
       <c r="K49" t="n">
-        <v>1.679950734381782</v>
+        <v>3.086533917521566</v>
       </c>
     </row>
     <row r="50">
@@ -5380,29 +6429,35 @@
           <t>2024-11-14</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>4.374196012935831</v>
+      </c>
       <c r="C50" t="n">
-        <v>-2.572695071413676</v>
+        <v>6.527111722689949</v>
       </c>
       <c r="D50" t="n">
-        <v>-3.27443020864036</v>
+        <v>5.153187952706647</v>
+      </c>
+      <c r="E50" t="n">
+        <v>8.203753409035031</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.617960655182894</v>
+        <v>4.242096830818509</v>
       </c>
       <c r="G50" t="n">
-        <v>-3.495412448465567</v>
+        <v>3.92125938903847</v>
       </c>
       <c r="H50" t="n">
-        <v>4.401433970343938</v>
+        <v>3.65175713861068</v>
       </c>
       <c r="I50" t="n">
-        <v>3.663383469818453</v>
+        <v>1.329038477099485</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.2200341446827321</v>
+        <v>5.295171462260464</v>
       </c>
       <c r="K50" t="n">
-        <v>1.808379937577058</v>
+        <v>3.03161948203498</v>
       </c>
     </row>
     <row r="51">
@@ -5411,29 +6466,35 @@
           <t>2024-11-29</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>4.161935045624877</v>
+      </c>
       <c r="C51" t="n">
-        <v>-2.472372084748173</v>
+        <v>6.645357127716458</v>
       </c>
       <c r="D51" t="n">
-        <v>-3.367587267686898</v>
+        <v>5.670095872948188</v>
+      </c>
+      <c r="E51" t="n">
+        <v>8.2062271517743</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.827201927552017</v>
+        <v>4.183766042344411</v>
       </c>
       <c r="G51" t="n">
-        <v>-3.541852252985133</v>
+        <v>3.414179048084108</v>
       </c>
       <c r="H51" t="n">
-        <v>4.318080077487453</v>
+        <v>3.998977971012835</v>
       </c>
       <c r="I51" t="n">
-        <v>3.662009843444827</v>
+        <v>1.206166966117594</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.1272059900535706</v>
+        <v>5.961019102050549</v>
       </c>
       <c r="K51" t="n">
-        <v>1.857221735941672</v>
+        <v>2.704029712757592</v>
       </c>
     </row>
     <row r="52">
@@ -5443,34 +6504,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.6085923088202361</v>
+        <v>4.085388799627544</v>
       </c>
       <c r="C52" t="n">
-        <v>-2.609732648696862</v>
+        <v>6.876509002803792</v>
       </c>
       <c r="D52" t="n">
-        <v>-3.382944645607747</v>
+        <v>5.918889695432939</v>
       </c>
       <c r="E52" t="n">
-        <v>1.110336136606681</v>
+        <v>8.572190085581235</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.848713715122688</v>
+        <v>4.110922482461136</v>
       </c>
       <c r="G52" t="n">
-        <v>-3.828329744047831</v>
+        <v>3.504427192319783</v>
       </c>
       <c r="H52" t="n">
-        <v>4.355088084389722</v>
+        <v>3.730081641251545</v>
       </c>
       <c r="I52" t="n">
-        <v>3.811081041944813</v>
+        <v>1.103020859367814</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.2229397932121512</v>
+        <v>6.254930971101</v>
       </c>
       <c r="K52" t="n">
-        <v>2.06458234266266</v>
+        <v>2.37181251123442</v>
       </c>
     </row>
     <row r="53">
@@ -5479,29 +6540,35 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>3.771548269392623</v>
+      </c>
       <c r="C53" t="n">
-        <v>-2.710055635362365</v>
+        <v>7.302086871985799</v>
       </c>
       <c r="D53" t="n">
-        <v>-3.491029070899526</v>
+        <v>6.148537013145331</v>
+      </c>
+      <c r="E53" t="n">
+        <v>8.388568234369226</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.62191678023301</v>
+        <v>4.035622943522977</v>
       </c>
       <c r="G53" t="n">
-        <v>-3.959435380189712</v>
+        <v>3.853506268466914</v>
       </c>
       <c r="H53" t="n">
-        <v>4.404151823881653</v>
+        <v>3.894086485481695</v>
       </c>
       <c r="I53" t="n">
-        <v>3.620470398006921</v>
+        <v>1.500728080842062</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.1436295951452849</v>
+        <v>6.023098192576835</v>
       </c>
       <c r="K53" t="n">
-        <v>2.152630709655277</v>
+        <v>2.650576627441229</v>
       </c>
     </row>
     <row r="54">
@@ -5510,29 +6577,35 @@
           <t>2025-01-15</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>3.504902529817945</v>
+      </c>
       <c r="C54" t="n">
-        <v>-2.810378622027868</v>
+        <v>6.938845419656752</v>
       </c>
       <c r="D54" t="n">
-        <v>-3.587702719804092</v>
+        <v>6.719902883961724</v>
+      </c>
+      <c r="E54" t="n">
+        <v>8.75134914245184</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.554702362049627</v>
+        <v>4.688925820005255</v>
       </c>
       <c r="G54" t="n">
-        <v>-4.340801629388917</v>
+        <v>3.676080646793027</v>
       </c>
       <c r="H54" t="n">
-        <v>4.408075178028759</v>
+        <v>3.454841697170444</v>
       </c>
       <c r="I54" t="n">
-        <v>3.657532863839976</v>
+        <v>1.422587207017207</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.3184686039419476</v>
+        <v>5.500498827824582</v>
       </c>
       <c r="K54" t="n">
-        <v>2.293512605198068</v>
+        <v>2.570504532183179</v>
       </c>
     </row>
     <row r="55">
@@ -5541,29 +6614,35 @@
           <t>2025-01-30</t>
         </is>
       </c>
+      <c r="B55" t="n">
+        <v>3.692261214202744</v>
+      </c>
       <c r="C55" t="n">
-        <v>-2.907052270932434</v>
+        <v>7.047996624697569</v>
       </c>
       <c r="D55" t="n">
-        <v>-3.679146836956216</v>
+        <v>7.144473169811607</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9.084358765313622</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.720390595754149</v>
+        <v>4.2739863679213</v>
       </c>
       <c r="G55" t="n">
-        <v>-4.621046644670717</v>
+        <v>3.781120064955962</v>
       </c>
       <c r="H55" t="n">
-        <v>4.383374349908404</v>
+        <v>3.18824474232689</v>
       </c>
       <c r="I55" t="n">
-        <v>3.824457329062373</v>
+        <v>1.710419302134761</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.4439698035258056</v>
+        <v>5.482978654048705</v>
       </c>
       <c r="K55" t="n">
-        <v>2.410965460435279</v>
+        <v>2.610642109738916</v>
       </c>
     </row>
     <row r="56">
@@ -5573,31 +6652,34 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.68788709670327</v>
+        <v>3.651579751189713</v>
       </c>
       <c r="C56" t="n">
-        <v>-2.812152601155852</v>
+        <v>7.25579716586228</v>
       </c>
       <c r="D56" t="n">
-        <v>-3.777627626347009</v>
+        <v>7.455537966112258</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9.096195443948458</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.678270085154475</v>
+        <v>4.521021219329871</v>
       </c>
       <c r="G56" t="n">
-        <v>-4.662510441179854</v>
+        <v>3.952455137780245</v>
       </c>
       <c r="H56" t="n">
-        <v>4.436118414003003</v>
+        <v>2.956989608050224</v>
       </c>
       <c r="I56" t="n">
-        <v>3.787064533179011</v>
+        <v>2.194327021764702</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.3151530675695409</v>
+        <v>5.331785898110155</v>
       </c>
       <c r="K56" t="n">
-        <v>2.417542457451769</v>
+        <v>2.440849400454984</v>
       </c>
     </row>
     <row r="57">
@@ -5607,34 +6689,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.7637582403004984</v>
+        <v>4.025167130240841</v>
       </c>
       <c r="C57" t="n">
-        <v>-2.713671811765059</v>
+        <v>7.240768018625716</v>
       </c>
       <c r="D57" t="n">
-        <v>-3.874301275251575</v>
+        <v>7.156636696064078</v>
       </c>
       <c r="E57" t="n">
-        <v>1.349260955937693</v>
+        <v>8.66276935505565</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.982601543915814</v>
+        <v>4.352326965116044</v>
       </c>
       <c r="G57" t="n">
-        <v>-4.528891499423192</v>
+        <v>3.872407919049387</v>
       </c>
       <c r="H57" t="n">
-        <v>4.431139050287213</v>
+        <v>3.31154328357806</v>
       </c>
       <c r="I57" t="n">
-        <v>3.768542838514595</v>
+        <v>2.317763322299458</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.2713428622685469</v>
+        <v>5.022796247577938</v>
       </c>
       <c r="K57" t="n">
-        <v>2.424072549488345</v>
+        <v>2.636592229117881</v>
       </c>
     </row>
     <row r="58">
@@ -5643,23 +6725,35 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>4.007416887767951</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7.568356028755225</v>
+      </c>
+      <c r="D58" t="n">
+        <v>7.832468673361309</v>
+      </c>
+      <c r="E58" t="n">
+        <v>8.651600948248943</v>
+      </c>
       <c r="F58" t="n">
-        <v>-3.034366245893959</v>
+        <v>4.713607997703262</v>
       </c>
       <c r="G58" t="n">
-        <v>-4.294144839233086</v>
+        <v>4.312375935475864</v>
       </c>
       <c r="H58" t="n">
-        <v>4.344191596429319</v>
+        <v>3.800658955626681</v>
       </c>
       <c r="I58" t="n">
-        <v>3.97421850130298</v>
+        <v>2.667642799668132</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.223379642009341</v>
+        <v>4.944727232968002</v>
       </c>
       <c r="K58" t="n">
-        <v>2.46891270505092</v>
+        <v>2.925760844284386</v>
       </c>
     </row>
     <row r="59">
@@ -5668,23 +6762,35 @@
           <t>2025-03-28</t>
         </is>
       </c>
+      <c r="B59" t="n">
+        <v>4.006087054514657</v>
+      </c>
+      <c r="C59" t="n">
+        <v>7.768611005787545</v>
+      </c>
+      <c r="D59" t="n">
+        <v>7.844648406331409</v>
+      </c>
+      <c r="E59" t="n">
+        <v>9.047709801850438</v>
+      </c>
       <c r="F59" t="n">
-        <v>-2.974351549989325</v>
+        <v>4.87771764715437</v>
       </c>
       <c r="G59" t="n">
-        <v>-4.396427532417976</v>
+        <v>4.914451682643794</v>
       </c>
       <c r="H59" t="n">
-        <v>4.479155117901926</v>
+        <v>3.587645825524199</v>
       </c>
       <c r="I59" t="n">
-        <v>3.644103411991935</v>
+        <v>2.517506906821786</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.3245398678983025</v>
+        <v>5.012049583162138</v>
       </c>
       <c r="K59" t="n">
-        <v>2.543631862981792</v>
+        <v>2.595840759341007</v>
       </c>
     </row>
     <row r="60">
@@ -5694,22 +6800,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>-2.74815705028842</v>
+        <v>4.970035221620202</v>
       </c>
       <c r="G60" t="n">
-        <v>-4.181569636753881</v>
+        <v>4.835181307060453</v>
       </c>
       <c r="H60" t="n">
-        <v>4.381397574861874</v>
+        <v>3.657511754459235</v>
       </c>
       <c r="I60" t="n">
-        <v>3.774292322972759</v>
+        <v>2.827024274140323</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.2818117650761777</v>
+        <v>5.223381892480242</v>
       </c>
       <c r="K60" t="n">
-        <v>2.671733718358795</v>
+        <v>2.344525312321617</v>
       </c>
     </row>
     <row r="61">
@@ -5718,23 +6824,35 @@
           <t>2025-04-28</t>
         </is>
       </c>
+      <c r="B61" t="n">
+        <v>4.551630351300824</v>
+      </c>
+      <c r="C61" t="n">
+        <v>7.943646369307022</v>
+      </c>
+      <c r="D61" t="n">
+        <v>8.017365873502223</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9.299938535252448</v>
+      </c>
       <c r="F61" t="n">
-        <v>-2.698297974405271</v>
+        <v>5.203985940534197</v>
       </c>
       <c r="G61" t="n">
-        <v>-4.570382986072164</v>
+        <v>4.824390877928526</v>
       </c>
       <c r="H61" t="n">
-        <v>4.343851765672873</v>
+        <v>4.005182253797446</v>
       </c>
       <c r="I61" t="n">
-        <v>3.806372472717719</v>
+        <v>2.848439176268462</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.2577596032744379</v>
+        <v>5.377644969906422</v>
       </c>
       <c r="K61" t="n">
-        <v>2.85803471692533</v>
+        <v>2.513642780796804</v>
       </c>
     </row>
     <row r="62">
@@ -5744,34 +6862,34 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.8093610364959993</v>
+        <v>5.014664007389256</v>
       </c>
       <c r="C62" t="n">
-        <v>-2.810345460669625</v>
+        <v>8.067810024087549</v>
       </c>
       <c r="D62" t="n">
-        <v>-3.775820485860782</v>
+        <v>8.530582331421755</v>
       </c>
       <c r="E62" t="n">
-        <v>1.570054261625272</v>
+        <v>10.0445428023099</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.751107121276714</v>
+        <v>5.168479546032821</v>
       </c>
       <c r="G62" t="n">
-        <v>-4.65206780906178</v>
+        <v>5.429329402693329</v>
       </c>
       <c r="H62" t="n">
-        <v>4.264878928530202</v>
+        <v>4.538098533309523</v>
       </c>
       <c r="I62" t="n">
-        <v>3.861937556710967</v>
+        <v>2.818680295735086</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.07538273737987128</v>
+        <v>5.09110367052444</v>
       </c>
       <c r="K62" t="n">
-        <v>2.967680616022214</v>
+        <v>3.243225251137311</v>
       </c>
     </row>
     <row r="63">
@@ -5780,23 +6898,35 @@
           <t>2025-05-27</t>
         </is>
       </c>
+      <c r="B63" t="n">
+        <v>5.046961190123523</v>
+      </c>
+      <c r="C63" t="n">
+        <v>8.104940922003074</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8.952119947579446</v>
+      </c>
+      <c r="E63" t="n">
+        <v>10.20409837191253</v>
+      </c>
       <c r="F63" t="n">
-        <v>-2.698491141472267</v>
+        <v>4.863027488089101</v>
       </c>
       <c r="G63" t="n">
-        <v>-4.928229886230024</v>
+        <v>5.370471068351075</v>
       </c>
       <c r="H63" t="n">
-        <v>4.113501217176421</v>
+        <v>3.943288628421752</v>
       </c>
       <c r="I63" t="n">
-        <v>3.937169506814807</v>
+        <v>2.677219691103217</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.1962866433878545</v>
+        <v>5.628809724626754</v>
       </c>
       <c r="K63" t="n">
-        <v>3.170873449025847</v>
+        <v>3.256536703224058</v>
       </c>
     </row>
     <row r="64">
@@ -5805,23 +6935,35 @@
           <t>2025-06-10</t>
         </is>
       </c>
+      <c r="B64" t="n">
+        <v>5.164623427424881</v>
+      </c>
+      <c r="C64" t="n">
+        <v>8.285508321789699</v>
+      </c>
+      <c r="D64" t="n">
+        <v>9.236941204075048</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10.61308536435665</v>
+      </c>
       <c r="F64" t="n">
-        <v>-2.796730305086333</v>
+        <v>4.563762444657113</v>
       </c>
       <c r="G64" t="n">
-        <v>-5.194616792374864</v>
+        <v>5.070160937982169</v>
       </c>
       <c r="H64" t="n">
-        <v>4.017961868399556</v>
+        <v>4.531875101867805</v>
       </c>
       <c r="I64" t="n">
-        <v>4.396503509993044</v>
+        <v>2.760399216112473</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.2837635869393907</v>
+        <v>5.502636332941202</v>
       </c>
       <c r="K64" t="n">
-        <v>3.310367231248414</v>
+        <v>2.769043980091404</v>
       </c>
     </row>
     <row r="65">
@@ -5830,23 +6972,35 @@
           <t>2025-06-25</t>
         </is>
       </c>
+      <c r="B65" t="n">
+        <v>5.400861634273038</v>
+      </c>
+      <c r="C65" t="n">
+        <v>8.443529007772144</v>
+      </c>
+      <c r="D65" t="n">
+        <v>9.657359851129639</v>
+      </c>
+      <c r="E65" t="n">
+        <v>10.64749706579582</v>
+      </c>
       <c r="F65" t="n">
-        <v>-2.857029917974927</v>
+        <v>5.046963747589424</v>
       </c>
       <c r="G65" t="n">
-        <v>-5.194543359483276</v>
+        <v>5.393704719416092</v>
       </c>
       <c r="H65" t="n">
-        <v>3.959889468118791</v>
+        <v>4.841954577754612</v>
       </c>
       <c r="I65" t="n">
-        <v>4.645013807257688</v>
+        <v>2.96143687316711</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.4551301455587141</v>
+        <v>5.459045971047623</v>
       </c>
       <c r="K65" t="n">
-        <v>3.408085867941299</v>
+        <v>3.268248314380642</v>
       </c>
     </row>
     <row r="66">
@@ -5856,34 +7010,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8192822845368455</v>
+        <v>5.341716716376049</v>
       </c>
       <c r="C66" t="n">
-        <v>-2.903502519716164</v>
+        <v>8.301941240493186</v>
       </c>
       <c r="D66" t="n">
-        <v>-3.671699779489152</v>
+        <v>10.12562066565279</v>
       </c>
       <c r="E66" t="n">
-        <v>1.820698855340824</v>
+        <v>10.95059947546699</v>
       </c>
       <c r="F66" t="n">
-        <v>-3.003890260625584</v>
+        <v>5.42466245933714</v>
       </c>
       <c r="G66" t="n">
-        <v>-5.466300499880492</v>
+        <v>5.482146465486302</v>
       </c>
       <c r="H66" t="n">
-        <v>3.967490704513664</v>
+        <v>4.79149525827282</v>
       </c>
       <c r="I66" t="n">
-        <v>4.567931743440388</v>
+        <v>3.031163672290711</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.4929177531758942</v>
+        <v>5.082086049902976</v>
       </c>
       <c r="K66" t="n">
-        <v>3.673944157368368</v>
+        <v>3.156246066736898</v>
       </c>
     </row>
     <row r="67">
@@ -5892,23 +7046,35 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="B67" t="n">
+        <v>5.336079040517388</v>
+      </c>
+      <c r="C67" t="n">
+        <v>8.903481696944704</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10.22110628551936</v>
+      </c>
+      <c r="E67" t="n">
+        <v>11.25057583526796</v>
+      </c>
       <c r="F67" t="n">
-        <v>-3.138507854710965</v>
+        <v>5.706569506238383</v>
       </c>
       <c r="G67" t="n">
-        <v>-5.625453534183349</v>
+        <v>5.475729676448063</v>
       </c>
       <c r="H67" t="n">
-        <v>4.04635401358993</v>
+        <v>4.982241639334298</v>
       </c>
       <c r="I67" t="n">
-        <v>4.458041633550279</v>
+        <v>3.057133505832663</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.5463136364931416</v>
+        <v>5.344079163707879</v>
       </c>
       <c r="K67" t="n">
-        <v>3.649309819246361</v>
+        <v>2.879394018861281</v>
       </c>
     </row>
     <row r="68">
@@ -5917,23 +7083,35 @@
           <t>2025-08-07</t>
         </is>
       </c>
+      <c r="B68" t="n">
+        <v>5.13073638611775</v>
+      </c>
+      <c r="C68" t="n">
+        <v>9.114137704961824</v>
+      </c>
+      <c r="D68" t="n">
+        <v>10.76465928270547</v>
+      </c>
+      <c r="E68" t="n">
+        <v>11.52706529706637</v>
+      </c>
       <c r="F68" t="n">
-        <v>-3.073640840648408</v>
+        <v>5.380124455305496</v>
       </c>
       <c r="G68" t="n">
-        <v>-6.017084205186277</v>
+        <v>5.180183120283162</v>
       </c>
       <c r="H68" t="n">
-        <v>4.259678108781321</v>
+        <v>4.604617549979311</v>
       </c>
       <c r="I68" t="n">
-        <v>4.421004596513241</v>
+        <v>3.376699908314462</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.658768046156133</v>
+        <v>5.362853920496461</v>
       </c>
       <c r="K68" t="n">
-        <v>3.584411233208384</v>
+        <v>3.185824777967986</v>
       </c>
     </row>
     <row r="69">
@@ -5942,23 +7120,35 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="B69" t="n">
+        <v>5.504808863844853</v>
+      </c>
+      <c r="C69" t="n">
+        <v>9.002778020344907</v>
+      </c>
+      <c r="D69" t="n">
+        <v>10.44620860212597</v>
+      </c>
+      <c r="E69" t="n">
+        <v>11.73931098976813</v>
+      </c>
       <c r="F69" t="n">
-        <v>-3.032449380701635</v>
+        <v>4.817035514467205</v>
       </c>
       <c r="G69" t="n">
-        <v>-5.928712445230697</v>
+        <v>4.56285405410825</v>
       </c>
       <c r="H69" t="n">
-        <v>4.274301692149723</v>
+        <v>4.747097082961396</v>
       </c>
       <c r="I69" t="n">
-        <v>4.621475000926277</v>
+        <v>3.759308650748028</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.611917565972904</v>
+        <v>5.200415061263515</v>
       </c>
       <c r="K69" t="n">
-        <v>3.684562648336185</v>
+        <v>3.049554957406589</v>
       </c>
     </row>
     <row r="70">
@@ -5967,23 +7157,35 @@
           <t>2025-09-05</t>
         </is>
       </c>
+      <c r="B70" t="n">
+        <v>5.702454115587538</v>
+      </c>
+      <c r="C70" t="n">
+        <v>9.524856486952743</v>
+      </c>
+      <c r="D70" t="n">
+        <v>10.67039089993443</v>
+      </c>
+      <c r="E70" t="n">
+        <v>12.49216613751533</v>
+      </c>
       <c r="F70" t="n">
-        <v>-3.214457684641763</v>
+        <v>5.158025578521023</v>
       </c>
       <c r="G70" t="n">
-        <v>-6.245931672132367</v>
+        <v>4.583809253028889</v>
       </c>
       <c r="H70" t="n">
-        <v>4.319148985925167</v>
+        <v>4.599119461218184</v>
       </c>
       <c r="I70" t="n">
-        <v>4.659936539387815</v>
+        <v>3.849679767751416</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.6364925658473454</v>
+        <v>5.754601600967984</v>
       </c>
       <c r="K70" t="n">
-        <v>3.969444634488563</v>
+        <v>3.313332853980187</v>
       </c>
     </row>
     <row r="71">
@@ -5992,23 +7194,35 @@
           <t>2025-09-19</t>
         </is>
       </c>
+      <c r="B71" t="n">
+        <v>5.709988025106098</v>
+      </c>
+      <c r="C71" t="n">
+        <v>9.840535450412307</v>
+      </c>
+      <c r="D71" t="n">
+        <v>10.41910960138599</v>
+      </c>
+      <c r="E71" t="n">
+        <v>12.29749063899287</v>
+      </c>
       <c r="F71" t="n">
-        <v>-3.279566531811952</v>
+        <v>4.989819294757202</v>
       </c>
       <c r="G71" t="n">
-        <v>-6.258032291157935</v>
+        <v>4.828949746904873</v>
       </c>
       <c r="H71" t="n">
-        <v>4.549208637126697</v>
+        <v>4.486129290209742</v>
       </c>
       <c r="I71" t="n">
-        <v>4.993041170605654</v>
+        <v>3.597551756027365</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.6760313394496217</v>
+        <v>5.834580939304016</v>
       </c>
       <c r="K71" t="n">
-        <v>4.112013794222318</v>
+        <v>3.053724237424708</v>
       </c>
     </row>
     <row r="72">
@@ -6018,34 +7232,34 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.7893420027050325</v>
+        <v>5.912241782596575</v>
       </c>
       <c r="C72" t="n">
-        <v>-2.810345460669625</v>
+        <v>9.612473209345175</v>
       </c>
       <c r="D72" t="n">
-        <v>-3.57680010971257</v>
+        <v>10.72816930295469</v>
       </c>
       <c r="E72" t="n">
-        <v>2.060557765482991</v>
+        <v>12.45344069327071</v>
       </c>
       <c r="F72" t="n">
-        <v>-3.303028728435803</v>
+        <v>4.688342209525636</v>
       </c>
       <c r="G72" t="n">
-        <v>-6.283127637486512</v>
+        <v>4.919171944437846</v>
       </c>
       <c r="H72" t="n">
-        <v>4.482389118526756</v>
+        <v>4.690890563612017</v>
       </c>
       <c r="I72" t="n">
-        <v>5.010889122173078</v>
+        <v>3.448241990679491</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.6147589092294935</v>
+        <v>5.599588335357724</v>
       </c>
       <c r="K72" t="n">
-        <v>4.174112686286619</v>
+        <v>2.925711750134016</v>
       </c>
     </row>
     <row r="73">
@@ -6054,23 +7268,35 @@
           <t>2025-10-17</t>
         </is>
       </c>
+      <c r="B73" t="n">
+        <v>6.084899527168484</v>
+      </c>
+      <c r="C73" t="n">
+        <v>10.25073204181142</v>
+      </c>
+      <c r="D73" t="n">
+        <v>10.75984447728475</v>
+      </c>
+      <c r="E73" t="n">
+        <v>12.41770050083159</v>
+      </c>
       <c r="F73" t="n">
-        <v>-3.463481541653394</v>
+        <v>5.050307352840298</v>
       </c>
       <c r="G73" t="n">
-        <v>-6.157875080128958</v>
+        <v>5.01365915059267</v>
       </c>
       <c r="H73" t="n">
-        <v>4.366801564151894</v>
+        <v>4.555440706518586</v>
       </c>
       <c r="I73" t="n">
-        <v>4.855566021277191</v>
+        <v>3.68182308089946</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.6043351820675907</v>
+        <v>5.845870581205224</v>
       </c>
       <c r="K73" t="n">
-        <v>4.008653768820089</v>
+        <v>3.039861796141153</v>
       </c>
     </row>
     <row r="74">
@@ -6079,23 +7305,35 @@
           <t>2025-10-31</t>
         </is>
       </c>
+      <c r="B74" t="n">
+        <v>6.53772487670718</v>
+      </c>
+      <c r="C74" t="n">
+        <v>10.58674635039198</v>
+      </c>
+      <c r="D74" t="n">
+        <v>11.55433855198211</v>
+      </c>
+      <c r="E74" t="n">
+        <v>12.86697859759315</v>
+      </c>
       <c r="F74" t="n">
-        <v>-3.489868856155521</v>
+        <v>5.185516670020114</v>
       </c>
       <c r="G74" t="n">
-        <v>-6.145985338331729</v>
+        <v>5.372567560168306</v>
       </c>
       <c r="H74" t="n">
-        <v>4.3233314333523</v>
+        <v>5.074625368512018</v>
       </c>
       <c r="I74" t="n">
-        <v>5.07752142436467</v>
+        <v>4.068715854966147</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.5860110396792054</v>
+        <v>5.771040933744444</v>
       </c>
       <c r="K74" t="n">
-        <v>3.933692743939836</v>
+        <v>3.290616630665122</v>
       </c>
     </row>
     <row r="75">
@@ -6104,23 +7342,35 @@
           <t>2025-11-14</t>
         </is>
       </c>
+      <c r="B75" t="n">
+        <v>6.493255435137446</v>
+      </c>
+      <c r="C75" t="n">
+        <v>11.0214264060553</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11.94935432795013</v>
+      </c>
+      <c r="E75" t="n">
+        <v>12.86884722925453</v>
+      </c>
       <c r="F75" t="n">
-        <v>-3.80831635456345</v>
+        <v>4.926091779719053</v>
       </c>
       <c r="G75" t="n">
-        <v>-6.200732935895425</v>
+        <v>4.783660067761838</v>
       </c>
       <c r="H75" t="n">
-        <v>4.606262566772645</v>
+        <v>4.652384504616164</v>
       </c>
       <c r="I75" t="n">
-        <v>5.133086508357917</v>
+        <v>4.592833507612442</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.6342420034895786</v>
+        <v>5.638458981154089</v>
       </c>
       <c r="K75" t="n">
-        <v>4.052117161291458</v>
+        <v>3.278275949583373</v>
       </c>
     </row>
     <row r="76">
@@ -6130,34 +7380,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.76337885832198</v>
+        <v>6.338287234891006</v>
       </c>
       <c r="C76" t="n">
-        <v>-2.910668447335128</v>
+        <v>11.32050341096785</v>
       </c>
       <c r="D76" t="n">
-        <v>-3.476477123047067</v>
+        <v>12.24981561592161</v>
       </c>
       <c r="E76" t="n">
-        <v>2.275571336011414</v>
+        <v>12.83319607691462</v>
       </c>
       <c r="F76" t="n">
-        <v>-3.933822583141374</v>
+        <v>4.876752921885588</v>
       </c>
       <c r="G76" t="n">
-        <v>-6.167495945138006</v>
+        <v>4.904598174894865</v>
       </c>
       <c r="H76" t="n">
-        <v>4.684968141987487</v>
+        <v>4.339155384429225</v>
       </c>
       <c r="I76" t="n">
-        <v>5.060284310555719</v>
+        <v>5.049133305120298</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.7984549829306875</v>
+        <v>5.740067880873861</v>
       </c>
       <c r="K76" t="n">
-        <v>4.156976503212132</v>
+        <v>3.488649872074645</v>
       </c>
     </row>
     <row r="77">
@@ -6166,23 +7416,35 @@
           <t>2025-12-15</t>
         </is>
       </c>
+      <c r="B77" t="n">
+        <v>6.651488228130509</v>
+      </c>
+      <c r="C77" t="n">
+        <v>11.43011491921519</v>
+      </c>
+      <c r="D77" t="n">
+        <v>12.23297718631392</v>
+      </c>
+      <c r="E77" t="n">
+        <v>12.25723691261896</v>
+      </c>
       <c r="F77" t="n">
-        <v>-3.916772574160359</v>
+        <v>5.032393404134894</v>
       </c>
       <c r="G77" t="n">
-        <v>-6.070515580430857</v>
+        <v>4.879368364254732</v>
       </c>
       <c r="H77" t="n">
-        <v>4.430935453576219</v>
+        <v>4.289383469884467</v>
       </c>
       <c r="I77" t="n">
-        <v>5.12961882774644</v>
+        <v>5.577023472593742</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.9113684139599274</v>
+        <v>5.559504570647055</v>
       </c>
       <c r="K77" t="n">
-        <v>4.095234620718062</v>
+        <v>3.427076852295573</v>
       </c>
     </row>
     <row r="78">
@@ -6192,34 +7454,34 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.8473115119642258</v>
+        <v>6.622333170628058</v>
       </c>
       <c r="C78" t="n">
-        <v>-2.812187657944336</v>
+        <v>11.80625331168642</v>
       </c>
       <c r="D78" t="n">
-        <v>-3.376154136381564</v>
+        <v>12.08509405628472</v>
       </c>
       <c r="E78" t="n">
-        <v>2.4990905979588</v>
+        <v>11.96630835241925</v>
       </c>
       <c r="F78" t="n">
-        <v>-4.039657122156989</v>
+        <v>5.315422613364039</v>
       </c>
       <c r="G78" t="n">
-        <v>-6.06317545704825</v>
+        <v>5.079724982137835</v>
       </c>
       <c r="H78" t="n">
-        <v>4.338655843559828</v>
+        <v>4.585441926789093</v>
       </c>
       <c r="I78" t="n">
-        <v>5.295742069258627</v>
+        <v>5.813494968203283</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.9267709448786581</v>
+        <v>5.363646935233026</v>
       </c>
       <c r="K78" t="n">
-        <v>4.189823406415466</v>
+        <v>3.632893397814605</v>
       </c>
     </row>
     <row r="79">
@@ -6229,34 +7491,34 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.818607053050101</v>
+        <v>6.919174025242167</v>
       </c>
       <c r="C79" t="n">
-        <v>-2.717287988167754</v>
+        <v>12.02413421413823</v>
       </c>
       <c r="D79" t="n">
-        <v>-3.28471001922944</v>
+        <v>12.31309369009223</v>
       </c>
       <c r="E79" t="n">
-        <v>2.723550029977066</v>
+        <v>12.43055011619952</v>
       </c>
       <c r="F79" t="n">
-        <v>-4.200987532737566</v>
+        <v>5.576731676796605</v>
       </c>
       <c r="G79" t="n">
-        <v>-6.139952457509159</v>
+        <v>5.477468570806816</v>
       </c>
       <c r="H79" t="n">
-        <v>4.24287920996557</v>
+        <v>5.269358477755194</v>
       </c>
       <c r="I79" t="n">
-        <v>5.517315620934321</v>
+        <v>5.90443728393345</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.8564931214575734</v>
+        <v>5.689243807521935</v>
       </c>
       <c r="K79" t="n">
-        <v>4.013289761249089</v>
+        <v>4.18246136593446</v>
       </c>
     </row>
     <row r="80">
@@ -6266,34 +7528,34 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.8778368278145893</v>
+        <v>6.867847514880658</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.815768777558546</v>
+        <v>12.23787545679108</v>
       </c>
       <c r="D80" t="n">
-        <v>-3.184387032563937</v>
+        <v>12.18295558313956</v>
       </c>
       <c r="E80" t="n">
-        <v>2.672583913383016</v>
+        <v>12.31051552601171</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.361553413203281</v>
+        <v>5.458115446969724</v>
       </c>
       <c r="G80" t="n">
-        <v>-6.31398516888586</v>
+        <v>5.573215169905463</v>
       </c>
       <c r="H80" t="n">
-        <v>4.184606091091395</v>
+        <v>5.215848512784017</v>
       </c>
       <c r="I80" t="n">
-        <v>5.573605314339277</v>
+        <v>5.631290269746584</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.7706930786065114</v>
+        <v>5.519831517438881</v>
       </c>
       <c r="K80" t="n">
-        <v>4.058026760114037</v>
+        <v>3.854312246619435</v>
       </c>
     </row>
     <row r="81">
@@ -6302,23 +7564,35 @@
           <t>2026-02-12</t>
         </is>
       </c>
+      <c r="B81" t="n">
+        <v>7.199969468902787</v>
+      </c>
+      <c r="C81" t="n">
+        <v>12.45085438537766</v>
+      </c>
+      <c r="D81" t="n">
+        <v>12.16970587505256</v>
+      </c>
+      <c r="E81" t="n">
+        <v>12.6138544428817</v>
+      </c>
       <c r="F81" t="n">
-        <v>-4.697670895978107</v>
+        <v>5.473367794166684</v>
       </c>
       <c r="G81" t="n">
-        <v>-6.323519212056222</v>
+        <v>5.590602533044178</v>
       </c>
       <c r="H81" t="n">
-        <v>4.006697109412318</v>
+        <v>5.256808070512434</v>
       </c>
       <c r="I81" t="n">
-        <v>5.53111782934085</v>
+        <v>5.729434027912449</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.6744389636040407</v>
+        <v>5.104305402003306</v>
       </c>
       <c r="K81" t="n">
-        <v>4.222137135667207</v>
+        <v>3.640305166117386</v>
       </c>
     </row>
     <row r="82">
@@ -6327,23 +7601,109 @@
           <t>2026-02-27</t>
         </is>
       </c>
+      <c r="B82" t="n">
+        <v>7.402009647186338</v>
+      </c>
+      <c r="C82" t="n">
+        <v>12.42615358075498</v>
+      </c>
+      <c r="D82" t="n">
+        <v>12.31806614136626</v>
+      </c>
+      <c r="E82" t="n">
+        <v>12.69348005043918</v>
+      </c>
       <c r="F82" t="n">
-        <v>-4.682400726579401</v>
+        <v>5.402564107806994</v>
       </c>
       <c r="G82" t="n">
-        <v>-6.253809966340564</v>
+        <v>5.616679806948205</v>
       </c>
       <c r="H82" t="n">
-        <v>3.881726242778288</v>
+        <v>5.251365240192407</v>
       </c>
       <c r="I82" t="n">
-        <v>5.508386626326553</v>
+        <v>5.680386435402722</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.7360815414098654</v>
+        <v>4.677497915479158</v>
       </c>
       <c r="K82" t="n">
-        <v>4.510458373150694</v>
+        <v>3.832862604445082</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>7.134575283033844</v>
+      </c>
+      <c r="C83" t="n">
+        <v>12.84879018060347</v>
+      </c>
+      <c r="D83" t="n">
+        <v>12.69397819405692</v>
+      </c>
+      <c r="E83" t="n">
+        <v>12.82509274933194</v>
+      </c>
+      <c r="F83" t="n">
+        <v>4.956281820084378</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5.491057258236317</v>
+      </c>
+      <c r="H83" t="n">
+        <v>5.223913327341125</v>
+      </c>
+      <c r="I83" t="n">
+        <v>5.742893836593822</v>
+      </c>
+      <c r="J83" t="n">
+        <v>4.805149951059162</v>
+      </c>
+      <c r="K83" t="n">
+        <v>4.489995531619948</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>6.982868855763475</v>
+      </c>
+      <c r="C84" t="n">
+        <v>12.61088366549238</v>
+      </c>
+      <c r="D84" t="n">
+        <v>12.68336300003863</v>
+      </c>
+      <c r="E84" t="n">
+        <v>13.12753206951975</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4.827195672260159</v>
+      </c>
+      <c r="G84" t="n">
+        <v>5.843515167859166</v>
+      </c>
+      <c r="H84" t="n">
+        <v>5.269115387256013</v>
+      </c>
+      <c r="I84" t="n">
+        <v>5.88023286671844</v>
+      </c>
+      <c r="J84" t="n">
+        <v>4.288416601156503</v>
+      </c>
+      <c r="K84" t="n">
+        <v>4.688093547394293</v>
       </c>
     </row>
   </sheetData>

--- a/output/multi_factor_reports/factor_collinearity_report_P10.xlsx
+++ b/output/multi_factor_reports/factor_collinearity_report_P10.xlsx
@@ -190,12 +190,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$B$2:$B$83</f>
+              <f>'corr_series'!$B$2:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$C$2:$C$83</f>
+              <f>'corr_series'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -254,12 +254,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$D$2:$D$83</f>
+              <f>'corr_series'!$D$2:$D$86</f>
             </numRef>
           </val>
         </ser>
@@ -286,12 +286,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$E$2:$E$83</f>
+              <f>'corr_series'!$E$2:$E$86</f>
             </numRef>
           </val>
         </ser>
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$F$2:$F$83</f>
+              <f>'corr_series'!$F$2:$F$86</f>
             </numRef>
           </val>
         </ser>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$G$2:$G$83</f>
+              <f>'corr_series'!$G$2:$G$86</f>
             </numRef>
           </val>
         </ser>
@@ -382,12 +382,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$H$2:$H$83</f>
+              <f>'corr_series'!$H$2:$H$86</f>
             </numRef>
           </val>
         </ser>
@@ -414,12 +414,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$I$2:$I$83</f>
+              <f>'corr_series'!$I$2:$I$86</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$J$2:$J$83</f>
+              <f>'corr_series'!$J$2:$J$86</f>
             </numRef>
           </val>
         </ser>
@@ -478,12 +478,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$83</f>
+              <f>'corr_series'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$K$2:$K$83</f>
+              <f>'corr_series'!$K$2:$K$86</f>
             </numRef>
           </val>
         </ser>
@@ -520,8 +520,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.9619405675805962"/>
-          <min val="-1.054615979580843"/>
+          <max val="0.523671765789401"/>
+          <min val="-0.4280002107059264"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -598,12 +598,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$B$2:$B$83</f>
+              <f>'cum_corr'!$B$2:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -630,12 +630,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$C$2:$C$83</f>
+              <f>'cum_corr'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -662,12 +662,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$D$2:$D$83</f>
+              <f>'cum_corr'!$D$2:$D$86</f>
             </numRef>
           </val>
         </ser>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$E$2:$E$83</f>
+              <f>'cum_corr'!$E$2:$E$86</f>
             </numRef>
           </val>
         </ser>
@@ -726,12 +726,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$F$2:$F$83</f>
+              <f>'cum_corr'!$F$2:$F$86</f>
             </numRef>
           </val>
         </ser>
@@ -758,12 +758,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$G$2:$G$83</f>
+              <f>'cum_corr'!$G$2:$G$86</f>
             </numRef>
           </val>
         </ser>
@@ -790,12 +790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$H$2:$H$83</f>
+              <f>'cum_corr'!$H$2:$H$86</f>
             </numRef>
           </val>
         </ser>
@@ -822,12 +822,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$I$2:$I$83</f>
+              <f>'cum_corr'!$I$2:$I$86</f>
             </numRef>
           </val>
         </ser>
@@ -854,12 +854,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$J$2:$J$83</f>
+              <f>'cum_corr'!$J$2:$J$86</f>
             </numRef>
           </val>
         </ser>
@@ -886,12 +886,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$83</f>
+              <f>'cum_corr'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$K$2:$K$83</f>
+              <f>'cum_corr'!$K$2:$K$86</f>
             </numRef>
           </val>
         </ser>
@@ -928,8 +928,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="14.28354528810306"/>
-          <min val="-2.478646381354944"/>
+          <max val="20.67093435281098"/>
+          <min val="-9.468907141888863"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1321,135 +1321,135 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>alpha023</t>
+          <t>alpha095</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>alpha043</t>
+          <t>alpha099</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>alpha066</t>
+          <t>alpha027</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>alpha045</t>
+          <t>alpha075</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>alpha031</t>
+          <t>alpha019</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>alpha023</t>
+          <t>alpha095</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>-0.15263</v>
+        <v>0.038951</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.196253</v>
+        <v>0.075352</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.073838</v>
+        <v>-0.001175</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.071147</v>
+        <v>0.335272</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>alpha043</t>
+          <t>alpha099</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-0.15263</v>
+        <v>0.038951</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.278187</v>
+        <v>0.211093</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.095137</v>
+        <v>0.291451</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.128815</v>
+        <v>0.264458</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>alpha066</t>
+          <t>alpha027</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.196253</v>
+        <v>0.075352</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.278187</v>
+        <v>0.211093</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.248127</v>
+        <v>0.182269</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.08637300000000001</v>
+        <v>0.260248</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>alpha045</t>
+          <t>alpha075</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.073838</v>
+        <v>-0.001175</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.095137</v>
+        <v>0.291451</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.248127</v>
+        <v>0.182269</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1981</v>
+        <v>0.118276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>alpha031</t>
+          <t>alpha019</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.071147</v>
+        <v>0.335272</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.128815</v>
+        <v>0.264458</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.08637300000000001</v>
+        <v>0.260248</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1981</v>
+        <v>0.118276</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
@@ -1465,135 +1465,135 @@
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>alpha023</t>
+          <t>alpha095</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>alpha043</t>
+          <t>alpha099</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>alpha066</t>
+          <t>alpha027</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>alpha045</t>
+          <t>alpha075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>alpha031</t>
+          <t>alpha019</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>alpha023</t>
+          <t>alpha095</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.09035799999999999</v>
+        <v>0.005978</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.181282</v>
+        <v>0.019739</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.174416</v>
+        <v>-0.030635</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.162333</v>
+        <v>0.081347</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>alpha043</t>
+          <t>alpha099</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0.09035799999999999</v>
+        <v>0.005978</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.061887</v>
+        <v>0.172416</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.065001</v>
+        <v>0.206298</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.062409</v>
+        <v>0.134888</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>alpha066</t>
+          <t>alpha027</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.181282</v>
+        <v>0.019739</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.061887</v>
+        <v>0.172416</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.08514099999999999</v>
+        <v>0.075514</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.050776</v>
+        <v>0.120542</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>alpha045</t>
+          <t>alpha075</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.174416</v>
+        <v>-0.030635</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.065001</v>
+        <v>0.206298</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.08514099999999999</v>
+        <v>0.075514</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.061092</v>
+        <v>0.090701</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>alpha031</t>
+          <t>alpha019</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.162333</v>
+        <v>0.081347</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.062409</v>
+        <v>0.134888</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.050776</v>
+        <v>0.120542</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.061092</v>
+        <v>0.090701</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>1</v>
@@ -1730,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1739,52 +1739,52 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>alpha023 vs alpha043</t>
+          <t>alpha095 vs alpha099</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>alpha023 vs alpha066</t>
+          <t>alpha095 vs alpha027</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>alpha023 vs alpha045</t>
+          <t>alpha095 vs alpha075</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>alpha023 vs alpha031</t>
+          <t>alpha095 vs alpha019</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>alpha043 vs alpha066</t>
+          <t>alpha099 vs alpha027</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>alpha043 vs alpha045</t>
+          <t>alpha099 vs alpha075</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>alpha043 vs alpha031</t>
+          <t>alpha099 vs alpha019</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alpha066 vs alpha045</t>
+          <t>alpha027 vs alpha075</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>alpha066 vs alpha031</t>
+          <t>alpha027 vs alpha019</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>alpha045 vs alpha031</t>
+          <t>alpha075 vs alpha019</t>
         </is>
       </c>
     </row>
@@ -1802,6 +1802,15 @@
           <t>2023-01-18</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>0.2798584181713235</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4283196239717975</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0516305063644384</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1809,8 +1818,23 @@
           <t>2023-02-01</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>-0.207815658533888</v>
+      </c>
       <c r="C5" t="n">
-        <v>-0.5714561291862538</v>
+        <v>-0.1558140140741855</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.210742639639999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2241960288922624</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4266431924882633</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.06778969179620321</v>
       </c>
     </row>
     <row r="6">
@@ -1819,23 +1843,23 @@
           <t>2023-02-15</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>0.210742639639999</v>
+      </c>
       <c r="C6" t="n">
-        <v>-0.5076236681290642</v>
+        <v>-0.1534471651531071</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4723304542800635</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1055822156319885</v>
+        <v>0.207815658533888</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2397687682138353</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3986697965571209</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7946969570461895</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.3531290376127579</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.4917108237894436</v>
+        <v>0.1708531941164454</v>
       </c>
     </row>
     <row r="7">
@@ -1845,34 +1869,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02331650761758647</v>
+        <v>0.210742639639999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5335690650707239</v>
+        <v>-0.1464295251628444</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1257495335816386</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.2694582529415446</v>
+        <v>0.2049287691368834</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1807598435971681</v>
+        <v>0.1984325587557798</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2879676387076954</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.3551465542354422</v>
+        <v>0.2729407213268054</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2801585786199461</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-0.1376718427804929</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.2204983061618615</v>
+        <v>0.2086761069616935</v>
       </c>
     </row>
     <row r="8">
@@ -1882,34 +1894,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3755041465650356</v>
+        <v>0.210742639639999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2173273435777417</v>
+        <v>-0.1654456490020896</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1526119101157161</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.08311332715380326</v>
+        <v>0.207815658533888</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3866045880189689</v>
+        <v>0.2786410685279945</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1607166515202826</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6158023695891039</v>
+        <v>0.3427230046948359</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08454270294372647</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-0.1880441569550211</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.3834120539115112</v>
+        <v>0.09509179322780759</v>
       </c>
     </row>
     <row r="9">
@@ -1919,34 +1919,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.5081570780855267</v>
+        <v>0.2107426396399991</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.01572865484671397</v>
+        <v>-0.1534471651531071</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3357985504099618</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.205683688949095</v>
+        <v>-0.2137114306713208</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1284951005688817</v>
+        <v>0.06378792721514344</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.08860776609952457</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.2761835757155897</v>
+        <v>0.1610252427612625</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07605301994566976</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.198923797497668</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.008408121376151802</v>
+        <v>0.0139499286459505</v>
       </c>
     </row>
     <row r="10">
@@ -1956,34 +1944,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.02270374985768004</v>
+        <v>0.2284634020970603</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2534478651725899</v>
+        <v>-0.1562329432776296</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1074708077737951</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.220539774709887</v>
+        <v>0.1542126632954505</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2105532404791535</v>
+        <v>0.1545240763314812</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3070220840568865</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3187364352908575</v>
+        <v>0.3990996969126015</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3180155131745002</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.2074544030932307</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.1136030083402935</v>
+        <v>0.03582538961237814</v>
       </c>
     </row>
     <row r="11">
@@ -1993,34 +1969,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2994242782973215</v>
+        <v>0.2107426396399991</v>
       </c>
       <c r="C11" t="n">
-        <v>0.006474897568108421</v>
+        <v>-0.1464295251628444</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5864837341161391</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-0.01485298554840908</v>
+        <v>0.213711430671321</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01039277881451907</v>
+        <v>0.1984325587557798</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3726557710094966</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.1835385097581022</v>
+        <v>0.230678932218139</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2312375965316762</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.1190729993052261</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.07447818022156477</v>
+        <v>0.02957286146562942</v>
       </c>
     </row>
     <row r="12">
@@ -2030,34 +1994,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2196250199621442</v>
+        <v>0.2167238245368195</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6337317569226034</v>
+        <v>-0.1487558855455509</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4062901709391147</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.1927484129352749</v>
+        <v>-0.1992687361255656</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.02118076974794246</v>
+        <v>0.1434112654129383</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.001274689116891428</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.3753942711619879</v>
+        <v>0.1173819524811741</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09929826799999644</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.02312498450731028</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.231858579486549</v>
+        <v>0.1534490522196439</v>
       </c>
     </row>
     <row r="13">
@@ -2067,34 +2019,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1791567758782872</v>
+        <v>-0.19649248577246</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03038929455737472</v>
+        <v>-0.1654456490020896</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1481823847776924</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.593409839651545</v>
+        <v>-0.2107426396399989</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4694977729007012</v>
+        <v>0.265893091108908</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1505825709875905</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.4736652718136874</v>
+        <v>0.3437874106520606</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1628306854487797</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-0.4295415131809259</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.2963376099524123</v>
+        <v>-0.04865161513980852</v>
       </c>
     </row>
     <row r="14">
@@ -2104,34 +2044,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1774210889313259</v>
+        <v>0.1857122804094833</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3022835940702479</v>
+        <v>-0.1630111150704538</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1277403063134306</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.2257932007857303</v>
+        <v>0.1992687361255656</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3335240682861295</v>
+        <v>0.1972931825275606</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05813007131138757</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.2118668334674707</v>
+        <v>0.1704171845992144</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.03433706670461992</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.0354135911735393</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2261267844293652</v>
+        <v>-0.03817550870178144</v>
       </c>
     </row>
     <row r="15">
@@ -2141,34 +2069,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3634249763347204</v>
+        <v>0.210742639639999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2293151238899865</v>
+        <v>-0.1487558855455509</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1867032161542862</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.007554472914762629</v>
+        <v>0.2020803228789259</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1782409612143658</v>
+        <v>0.0938253856366657</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.08285254526939115</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.03554239716987519</v>
+        <v>0.09121160311979995</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2438423595995553</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-0.1117589459235472</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.1699939528465765</v>
+        <v>0.09367325428706379</v>
       </c>
     </row>
     <row r="16">
@@ -2178,34 +2094,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3984913340433024</v>
+        <v>-0.1992687361255656</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4177432758472135</v>
+        <v>-0.1418105562875052</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4104083977678428</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.2577441718860158</v>
+        <v>-0.19649248577246</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1783314719105165</v>
+        <v>0.1387463320679484</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2794206346569852</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.1629546968645498</v>
+        <v>0.3125982124676416</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4921946761752153</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.06218830701762434</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.2506778074565742</v>
+        <v>0.1181747071595148</v>
       </c>
     </row>
     <row r="17">
@@ -2215,34 +2119,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.3657552295972655</v>
+        <v>0.2167238245368195</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.183891830219176</v>
+        <v>-0.1654456490020896</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2182200837282874</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.7362719433487581</v>
+        <v>0.1937501051161881</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4424404326395066</v>
+        <v>0.2434009585752097</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2981328461736161</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.6036723789698967</v>
+        <v>0.1360427803040479</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8273819858660931</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.3647750590241346</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.3167431937554989</v>
+        <v>0.01108977355623327</v>
       </c>
     </row>
     <row r="18">
@@ -2252,34 +2144,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1703494026044174</v>
+        <v>0.2020803228789259</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2542008541163047</v>
+        <v>-0.1678996260264862</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.07878920262209495</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.3236534470307527</v>
+        <v>0.19649248577246</v>
       </c>
       <c r="F18" t="n">
-        <v>0.628312634756267</v>
+        <v>0.0866143203260797</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1495407448841971</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.4399751363164169</v>
+        <v>0.3834088727649029</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3903507354044549</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.3085807416925136</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.00188467715847404</v>
+        <v>0.0642468946455559</v>
       </c>
     </row>
     <row r="19">
@@ -2289,34 +2169,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0668008751838742</v>
+        <v>0.2137114306713208</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6198459698128178</v>
+        <v>-0.1728700969412806</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.339165618956633</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.7436751320982875</v>
+        <v>-0.2049287691368834</v>
       </c>
       <c r="F19" t="n">
-        <v>0.008805686652236194</v>
+        <v>0.102805367978397</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6608992973939092</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.09797312309947234</v>
+        <v>0.2164383561643832</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.03832981081587696</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.4940164303527401</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.08060551473976399</v>
+        <v>0.07431473305415143</v>
       </c>
     </row>
     <row r="20">
@@ -2326,34 +2194,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2407843767186604</v>
+        <v>0.1450290087029011</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1687115411760073</v>
+        <v>-0.1714985851425089</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2403702364828141</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-0.5549424338558649</v>
+        <v>0.1390201755279001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3477530594383491</v>
+        <v>0.2041241452319315</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2730176011399764</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.02155696247212088</v>
+        <v>0.3515497850322746</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1934924091451687</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5038256777676822</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.05322395695719732</v>
+        <v>0.03720878486172419</v>
       </c>
     </row>
     <row r="21">
@@ -2363,34 +2219,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1921242482059148</v>
+        <v>-0.1511265162864019</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2000968697007138</v>
+        <v>-0.1127390084824832</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2396579035131056</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.4347141336013311</v>
+        <v>0.2349475281971863</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5571286611194294</v>
+        <v>0.139484344472565</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06975954757832768</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1709698141210559</v>
+        <v>0.08935921591221256</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1019719157173363</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.4329426251941345</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.5074424882265752</v>
+        <v>0.07080755158551552</v>
       </c>
     </row>
     <row r="22">
@@ -2400,34 +2244,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2659627744599118</v>
+        <v>0.1964924857724599</v>
       </c>
       <c r="C22" t="n">
-        <v>0.61951356126007</v>
+        <v>-0.0883777519713818</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3783903620767765</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-0.1708422094259205</v>
+        <v>-0.1409829232776846</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3987900191233488</v>
+        <v>0.1402086024269046</v>
       </c>
       <c r="G22" t="n">
-        <v>0.105970865067208</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.5963427719203009</v>
+        <v>0.2167781506164077</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4155017762432292</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.1432116387180509</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-0.4330896771487082</v>
+        <v>0.06703064241990256</v>
       </c>
     </row>
     <row r="23">
@@ -2437,34 +2269,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.2267641756965417</v>
+        <v>0.1737620117142288</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1874120567434944</v>
+        <v>-0.1482679679745704</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2159428756420185</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-0.195258586089304</v>
+        <v>0.1890202725795696</v>
       </c>
       <c r="F23" t="n">
-        <v>0.003210367521503695</v>
+        <v>0.1896181852559908</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3689869369062125</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.310035832304149</v>
+        <v>0.2451405652143584</v>
       </c>
       <c r="I23" t="n">
-        <v>0.004459836438908744</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.5313504571220375</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.3525255503156972</v>
+        <v>-0.03429743293601418</v>
       </c>
     </row>
     <row r="24">
@@ -2474,34 +2294,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1746166517445758</v>
+        <v>0.1737620117142288</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1689551321831703</v>
+        <v>-0.1572352780113971</v>
       </c>
       <c r="D24" t="n">
-        <v>0.165440079492151</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.1227138122887018</v>
+        <v>-0.1838036555234517</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5361854390884924</v>
+        <v>0.2678262482585571</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2559995387089058</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.3434386239183783</v>
+        <v>0.3193809294418415</v>
       </c>
       <c r="I24" t="n">
-        <v>0.05558348288473275</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-0.240152479470594</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.1615308774518783</v>
+        <v>0.1144057961012094</v>
       </c>
     </row>
     <row r="25">
@@ -2511,34 +2319,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2174599528413227</v>
+        <v>-0.191682529939845</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4895484490648185</v>
+        <v>-0.1572352780113971</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3349159101398287</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.07615044837519268</v>
+        <v>-0.1890202725795695</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4043187166919326</v>
+        <v>0.108163553663221</v>
       </c>
       <c r="G25" t="n">
-        <v>0.23401713252289</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.2219650888433038</v>
+        <v>0.146909233176839</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2491176188055556</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-0.3302468887160628</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.1929701103897334</v>
+        <v>0.0912318739921827</v>
       </c>
     </row>
     <row r="26">
@@ -2548,34 +2344,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6080786973999197</v>
+        <v>0.1351554025021827</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1050299501114109</v>
+        <v>-0.1534471651531071</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1166048222542742</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-0.1166717484564057</v>
+        <v>-0.1469231333008619</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7039687064738611</v>
+        <v>0.04328580800434648</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.143100395213017</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-0.3129978227697603</v>
+        <v>0.09025059423198138</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3582343016149987</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-0.2294558721156396</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-0.151189038215048</v>
+        <v>0.03304144213239659</v>
       </c>
     </row>
     <row r="27">
@@ -2585,34 +2369,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4423259336571464</v>
+        <v>-0.1209921139843045</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4353248586485512</v>
+        <v>-0.1703740878923699</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2685249731333189</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.2148413419415073</v>
+        <v>-0.1380559421715735</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3436430435232949</v>
+        <v>0.2033983014507439</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1449070354205094</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-0.1773986681669004</v>
+        <v>0.3294076345067942</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.03329259528680126</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.358096069274778</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.5471844811204095</v>
+        <v>0.07710902799828705</v>
       </c>
     </row>
     <row r="28">
@@ -2622,34 +2394,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5056816195629766</v>
+        <v>0.1890202725795695</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7024743390539998</v>
+        <v>-0.124818709114169</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6732581973981921</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.6697218710813165</v>
+        <v>0.1999040690647506</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3937036371678808</v>
+        <v>0.1326663358276524</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4227938098890435</v>
+        <v>0.329416600329223</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2942839405048707</v>
+        <v>0.3258084920561324</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7875894711436018</v>
+        <v>0.1084786811267815</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4579938448989604</v>
+        <v>0.02127818383517276</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1773942156492643</v>
+        <v>0.2410006102968298</v>
       </c>
     </row>
     <row r="29">
@@ -2659,34 +2428,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.244550225860293</v>
+        <v>0.1380559421715736</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2147173674963968</v>
+        <v>-0.151094777972053</v>
       </c>
       <c r="D29" t="n">
-        <v>0.307730205088866</v>
+        <v>0.1209921139843045</v>
       </c>
       <c r="E29" t="n">
-        <v>0.458481816928321</v>
+        <v>0.08900190308630285</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.02024210104770281</v>
+        <v>0.2159752041826839</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.1192956860035995</v>
+        <v>0.2170515421168798</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.08282815251184344</v>
+        <v>0.2219526027575536</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0230980249598083</v>
+        <v>0.03766217885773536</v>
       </c>
       <c r="J29" t="n">
-        <v>0.04990538467783304</v>
+        <v>0.2185997990251732</v>
       </c>
       <c r="K29" t="n">
-        <v>0.01345622925019509</v>
+        <v>0.1864305816510212</v>
       </c>
     </row>
     <row r="30">
@@ -2696,34 +2465,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2724354944031757</v>
+        <v>0.1890202725795695</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.09182505279689868</v>
+        <v>-0.1482679679745703</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3627237458667481</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-0.2826049493047948</v>
+        <v>0.1787211968653991</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.07188089677407331</v>
+        <v>0.2542045029375167</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1602153723259242</v>
+        <v>0.2167781506164077</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3249671037091335</v>
+        <v>0.1661654223669532</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3563155753702956</v>
+        <v>-0.07802813450692216</v>
       </c>
       <c r="J30" t="n">
-        <v>0.2754494721044271</v>
+        <v>0.178719603119612</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.1321982437386661</v>
+        <v>0.0911088376239388</v>
       </c>
     </row>
     <row r="31">
@@ -2733,34 +2499,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.02343479609368231</v>
+        <v>0.178721196865399</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1653293088310243</v>
+        <v>-0.1527143493489882</v>
       </c>
       <c r="D31" t="n">
-        <v>0.291328361694137</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.3008111587214843</v>
+        <v>0.1838036555234517</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5940364822879934</v>
+        <v>-0.0218840984886425</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3028476193275611</v>
+        <v>0.1590509441495327</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1549605943048965</v>
+        <v>0.0459220642194096</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3216312486506444</v>
+        <v>-0.1140822876517114</v>
       </c>
       <c r="J31" t="n">
-        <v>0.2031493888418711</v>
+        <v>-0.09588841367903547</v>
       </c>
       <c r="K31" t="n">
-        <v>0.3612543130023611</v>
+        <v>-0.03169823876956402</v>
       </c>
     </row>
     <row r="32">
@@ -2770,34 +2533,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1062048991005758</v>
+        <v>0.1838036555234517</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2839184864366087</v>
+        <v>-0.1331860599689335</v>
       </c>
       <c r="D32" t="n">
-        <v>0.173945682885153</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.08695246136443346</v>
+        <v>-0.1890202725795695</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2914613088569625</v>
+        <v>0.258551362524562</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0006116063059528944</v>
+        <v>0.259150563370419</v>
       </c>
       <c r="H32" t="n">
-        <v>0.04003375726234217</v>
+        <v>0.1667283013474745</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5978386581941435</v>
+        <v>0.2282078535113691</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.1273800667784356</v>
+        <v>0.01988109009130417</v>
       </c>
       <c r="K32" t="n">
-        <v>0.09366547588075338</v>
+        <v>0.07054324725566639</v>
       </c>
     </row>
     <row r="33">
@@ -2807,34 +2567,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.03694513690146339</v>
+        <v>0.1812463559520403</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2580168072056581</v>
+        <v>-0.1504823163572114</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.273977079087146</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.1823049448573328</v>
+        <v>0.1812463559520403</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1218638621998941</v>
+        <v>0.2346879446681253</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2344843807059921</v>
+        <v>0.3831372549019613</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1639808878139933</v>
+        <v>0.1826134841491253</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2716836654999222</v>
+        <v>0.03321055820775363</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0707028395120384</v>
+        <v>0.0354517223751869</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1656314065048431</v>
+        <v>0.08056354613917351</v>
       </c>
     </row>
     <row r="34">
@@ -2844,34 +2601,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.06752310124598576</v>
+        <v>-0.1812463559520403</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3062950530275269</v>
+        <v>-0.1838036555234518</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2459735633298625</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.3198935828226905</v>
+        <v>-0.1155419694359621</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2113517104241359</v>
+        <v>0.08935921591221259</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1128186940697274</v>
+        <v>0.3014103138565244</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.08718284049823379</v>
+        <v>-0.01188816754191122</v>
       </c>
       <c r="I34" t="n">
-        <v>0.017504082279605</v>
+        <v>0.3151302167872919</v>
       </c>
       <c r="J34" t="n">
-        <v>0.06228186043982176</v>
+        <v>0.1589721526516377</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2103323776576123</v>
+        <v>0.04877261811377206</v>
       </c>
     </row>
     <row r="35">
@@ -2881,34 +2635,34 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4114052458273766</v>
+        <v>0.1661155106119584</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3300495591307788</v>
+        <v>-0.04007316022734394</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2516371363483164</v>
+        <v>0.08363465972687385</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1643623265217111</v>
+        <v>0.1703088600627004</v>
       </c>
       <c r="F35" t="n">
-        <v>0.09444012082417555</v>
+        <v>0.1295408117845809</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4577669923074066</v>
+        <v>0.2586578018595246</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4719944886619823</v>
+        <v>0.02750445636984245</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3973480417428889</v>
+        <v>0.1110132589467214</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.00163936182835946</v>
+        <v>0.08693333796001949</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.03348985826784274</v>
+        <v>-0.009033096526298339</v>
       </c>
     </row>
     <row r="36">
@@ -2918,34 +2672,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.2246492681065307</v>
+        <v>0.1374444522110988</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.390568261218791</v>
+        <v>-0.1174440439029408</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4623074122188183</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.1087932622419168</v>
+        <v>0.153735011567023</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2801678949902626</v>
+        <v>0.09295722569028871</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.4790951314144136</v>
+        <v>0.08025905141196826</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05488050976921902</v>
+        <v>0.09184536734866695</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2268310586795189</v>
+        <v>-0.07543087004899</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1532281334347085</v>
+        <v>0.1281254468576351</v>
       </c>
       <c r="K36" t="n">
-        <v>0.002793027452335775</v>
+        <v>-0.04255339588796631</v>
       </c>
     </row>
     <row r="37">
@@ -2955,34 +2706,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1207781284636244</v>
+        <v>0.08839718243279208</v>
       </c>
       <c r="C37" t="n">
-        <v>0.04978456906691039</v>
+        <v>-0.04693865581875915</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4003331108211568</v>
+        <v>0.06739652661281453</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4195894626311329</v>
+        <v>0.06048684647232055</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4434929654459966</v>
+        <v>0.0309661768642666</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.08827169115985527</v>
+        <v>0.1780469737892875</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2457570159361747</v>
+        <v>-0.04216215741155647</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.605545316819212</v>
+        <v>0.07560410711501211</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3086714142571746</v>
+        <v>-0.01624336459342361</v>
       </c>
       <c r="K37" t="n">
-        <v>0.07540840122652499</v>
+        <v>-0.1365782381520591</v>
       </c>
     </row>
     <row r="38">
@@ -2992,34 +2743,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1406054049484531</v>
+        <v>-0.133630620956212</v>
       </c>
       <c r="C38" t="n">
-        <v>0.342538350566911</v>
+        <v>-0.1157275124715688</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.6912046174184495</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.6934699185591796</v>
+        <v>-0.1393864104874338</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5497281605142216</v>
+        <v>0.2886751345948128</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02977516063404131</v>
+        <v>0.1712888475092462</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.07069037237540868</v>
+        <v>0.2932104815960772</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.09451014858089733</v>
+        <v>0.2833967633728306</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3158433536464469</v>
+        <v>0.2773662100794704</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.7935229577181043</v>
+        <v>0.2038732981461446</v>
       </c>
     </row>
     <row r="39">
@@ -3029,34 +2777,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.01277762683021809</v>
+        <v>-0.1413530862085967</v>
       </c>
       <c r="C39" t="n">
-        <v>0.08449290496211166</v>
+        <v>-0.1226826002665548</v>
       </c>
       <c r="D39" t="n">
-        <v>0.8228677022591177</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.08955573482362575</v>
+        <v>-0.1515960634700894</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.2886440982209637</v>
+        <v>0.2425234717545934</v>
       </c>
       <c r="G39" t="n">
-        <v>0.06684300564254983</v>
+        <v>0.0642381511946728</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2605861103911369</v>
+        <v>0.1215130586467259</v>
       </c>
       <c r="I39" t="n">
-        <v>0.04198903145508651</v>
+        <v>0.2123074326507425</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4489098707055079</v>
+        <v>0.09064482702864127</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2846562327352387</v>
+        <v>-0.03339485983682655</v>
       </c>
     </row>
     <row r="40">
@@ -3066,34 +2811,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5446753681733605</v>
+        <v>-0.1393864104874338</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2896953690250594</v>
+        <v>-0.1157275124715689</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1368267253038068</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.101572285385617</v>
+        <v>0.1453648939082349</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.2420652195203972</v>
+        <v>0.2258317958127242</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.08769292374934191</v>
+        <v>0.1333725950203337</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4319819409330257</v>
+        <v>0.09882455334321616</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2932896525491303</v>
+        <v>0.008845748207237993</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2187083642588392</v>
+        <v>0.1746919552985211</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1667009405339025</v>
+        <v>-0.1689522642636974</v>
       </c>
     </row>
     <row r="41">
@@ -3103,34 +2845,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.3622077851698211</v>
+        <v>0.1393864104874338</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1295340694675309</v>
+        <v>-0.1157275124715689</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.131150579377894</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.4104799727892759</v>
+        <v>-0.1453648939082349</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1375950981608243</v>
+        <v>0.1195580095479128</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1453052104792792</v>
+        <v>0.2734040273838261</v>
       </c>
       <c r="H41" t="n">
-        <v>0.06481460880732808</v>
+        <v>0.2912531926230222</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5346395453076335</v>
+        <v>0.1348976601603782</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3444567368833556</v>
+        <v>0.08432538731103996</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.3044982615356005</v>
+        <v>0.2115458114414729</v>
       </c>
     </row>
     <row r="42">
@@ -3140,34 +2879,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.08365053618220504</v>
+        <v>-0.133630620956212</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4017077199138588</v>
+        <v>-0.1226826002665549</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.05832472355690407</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.1571309401772211</v>
+        <v>0.1603567451474549</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1426407710673374</v>
+        <v>0.1478252354712509</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4333009236558562</v>
+        <v>0.3230769230769232</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5977950725655065</v>
+        <v>0.1935229335810309</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2914558785705189</v>
+        <v>0.06224220440894774</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4696351870780855</v>
+        <v>0.119808543700518</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7277982411950313</v>
+        <v>0.3290220704642741</v>
       </c>
     </row>
     <row r="43">
@@ -3177,34 +2913,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0895356744233735</v>
+        <v>0.1413530862085967</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3535533905932738</v>
+        <v>-0.1299038105676661</v>
       </c>
       <c r="D43" t="n">
-        <v>0.02865867797911589</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.3765148822530835</v>
+        <v>-0.1413530862085967</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4130897261428311</v>
+        <v>0.1521814181454137</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2516032548133206</v>
+        <v>0.09224441833137471</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2373368137949158</v>
+        <v>0.0003713086380706885</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2923780366438845</v>
+        <v>-0.06761428293248317</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1096323542489478</v>
+        <v>0.143644939791271</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5057225095720171</v>
+        <v>-0.003310254980065936</v>
       </c>
     </row>
     <row r="44">
@@ -3214,34 +2947,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.05525076065621567</v>
+        <v>0.1413530862085966</v>
       </c>
       <c r="C44" t="n">
-        <v>0.3902985826986551</v>
+        <v>-0.1262567485345741</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1034339776237052</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.04216396796223459</v>
+        <v>0.1433455447702487</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.009712706569709779</v>
+        <v>0.04056407827850718</v>
       </c>
       <c r="G44" t="n">
-        <v>0.008137689034491621</v>
+        <v>0.1742365051333263</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4477579696380408</v>
+        <v>0.006913929951764767</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3452884238395965</v>
+        <v>0.05261376041853497</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1245917585760705</v>
+        <v>0.1025791564336875</v>
       </c>
       <c r="K44" t="n">
-        <v>0.3722189421726209</v>
+        <v>-0.100887966781641</v>
       </c>
     </row>
     <row r="45">
@@ -3251,34 +2981,34 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.3390685152296488</v>
+        <v>-0.07428966838182749</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3110520961974577</v>
+        <v>-0.062836726043882</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.01005869953094736</v>
+        <v>-0.1732347467810421</v>
       </c>
       <c r="E45" t="n">
-        <v>0.308215983419325</v>
+        <v>0.1199229069488544</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.3004115305650787</v>
+        <v>0.0551723714684129</v>
       </c>
       <c r="G45" t="n">
-        <v>0.05196539513677037</v>
+        <v>0.1905511689678471</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.06627601390319819</v>
+        <v>0.1866585351862866</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3864522138070876</v>
+        <v>0.0380985550581057</v>
       </c>
       <c r="J45" t="n">
-        <v>0.14390464057563</v>
+        <v>0.008622863480711614</v>
       </c>
       <c r="K45" t="n">
-        <v>0.2728613373064874</v>
+        <v>-0.1027314109573268</v>
       </c>
     </row>
     <row r="46">
@@ -3288,34 +3018,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4064349435067104</v>
+        <v>-0.1393864104874338</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3838745910619778</v>
+        <v>-0.1209208366638928</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2630010023761389</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.5317517939018086</v>
+        <v>-0.1433455447702487</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.01740781261337389</v>
+        <v>0.3541884654207529</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02498577308327999</v>
+        <v>0.3281098537518824</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3492415458921299</v>
+        <v>0.2606976572232881</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.204999087837749</v>
+        <v>0.01733346320565998</v>
       </c>
       <c r="J46" t="n">
-        <v>0.5050171788827243</v>
+        <v>0.09891997809561481</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.03827213461353984</v>
+        <v>0.2976829221081503</v>
       </c>
     </row>
     <row r="47">
@@ -3325,34 +3052,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.3290853356191158</v>
+        <v>-0.1393864104874338</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2710236126024882</v>
+        <v>-0.1157275124715689</v>
       </c>
       <c r="D47" t="n">
-        <v>0.7377752684451543</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.3318593253961844</v>
+        <v>-0.153735011567023</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09756270543538333</v>
+        <v>0.168266828252618</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.4874208388861863</v>
+        <v>0.1215686274509805</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.9155431142593642</v>
+        <v>-0.05238484015392204</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2815185932360685</v>
+        <v>0.03321055820775356</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.2069576892241895</v>
+        <v>0.2532865850399696</v>
       </c>
       <c r="K47" t="n">
-        <v>0.4251473023874682</v>
+        <v>-0.1104460976568725</v>
       </c>
     </row>
     <row r="48">
@@ -3362,34 +3086,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.01895118583148413</v>
+        <v>-0.1433455447702487</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2047592774491713</v>
+        <v>-0.1244609720467531</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4341550551742728</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.5599658381644137</v>
+        <v>0.1453648939082348</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3004002393390721</v>
+        <v>0.4147024095410597</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.2860232946540188</v>
+        <v>0.1610252427612625</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.2444558308656127</v>
+        <v>0.2528926675632091</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1094111165292119</v>
+        <v>0.07907929734027659</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1773207961505762</v>
+        <v>0.1242439543530815</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2888069611218965</v>
+        <v>0.2317842616842407</v>
       </c>
     </row>
     <row r="49">
@@ -3399,34 +3120,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4739080620568228</v>
+        <v>0.1515960634700892</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2365358311211139</v>
+        <v>-0.02960775348761247</v>
       </c>
       <c r="D49" t="n">
-        <v>0.05149334312608513</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-0.3402906741994698</v>
+        <v>0.1453648939082349</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1527144279290228</v>
+        <v>0.3412439643944813</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3485429621304406</v>
+        <v>0.203170909953546</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1167823013376089</v>
+        <v>0.3386695638070374</v>
       </c>
       <c r="I49" t="n">
-        <v>0.07855243035441058</v>
+        <v>0.1632193833686187</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.1948403221262212</v>
+        <v>0.2267323858247974</v>
       </c>
       <c r="K49" t="n">
-        <v>0.256096358680902</v>
+        <v>0.1536082042967861</v>
       </c>
     </row>
     <row r="50">
@@ -3436,34 +3154,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1925083307245224</v>
+        <v>0.132321068799443</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4261485685378508</v>
+        <v>-0.1056892272937856</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1887837083499434</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.324294354842353</v>
+        <v>-0.1250781983185651</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1601894015772173</v>
+        <v>0.2777341047142731</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7585577615795716</v>
+        <v>0.2374973057024743</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.4085394238643176</v>
+        <v>0.2951856396038918</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05818931278264989</v>
+        <v>0.1962559012456229</v>
       </c>
       <c r="J50" t="n">
-        <v>0.3779007120729178</v>
+        <v>0.1923919490052155</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.05491443548658605</v>
+        <v>0.12394003857844</v>
       </c>
     </row>
     <row r="51">
@@ -3473,34 +3188,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2122609673109542</v>
+        <v>0.1233379585935061</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1182454050265079</v>
+        <v>-0.1056892272937855</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5169079202415419</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.002473742739269535</v>
+        <v>0.1118242635572416</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.05833078847409793</v>
+        <v>0.01695285228044751</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.5070803409543623</v>
+        <v>0.1774859487735229</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3472208324021553</v>
+        <v>-0.3282412338910235</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1228715109818904</v>
+        <v>0.01460737753661614</v>
       </c>
       <c r="J51" t="n">
-        <v>0.6658476397900855</v>
+        <v>0.09238426986883645</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.3275897692773882</v>
+        <v>-0.1365435025644474</v>
       </c>
     </row>
     <row r="52">
@@ -3510,34 +3222,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.07654624599733313</v>
+        <v>0.03764616262105228</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2311518750873345</v>
+        <v>-0.02759710350482505</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2487938224847509</v>
+        <v>-0.1537350115670228</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3659629338069359</v>
+        <v>0.1266061158603291</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.07284355988327423</v>
+        <v>0.1178141002631941</v>
       </c>
       <c r="G52" t="n">
-        <v>0.09024814423567476</v>
+        <v>0.07346308866924531</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2688963297612906</v>
+        <v>0.1378921435969462</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1031461067497801</v>
+        <v>0.05682310548199958</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2939118690504518</v>
+        <v>0.1424261969524876</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.332217201523172</v>
+        <v>0.10978143793521</v>
       </c>
     </row>
     <row r="53">
@@ -3547,34 +3259,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3138405302349203</v>
+        <v>0.1102635692839942</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4255778691820071</v>
+        <v>-0.09415544714433857</v>
       </c>
       <c r="D53" t="n">
-        <v>0.229647317712392</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-0.1836218512120097</v>
+        <v>0.1118242635572416</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.07529953893815881</v>
+        <v>0.03992318480243996</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3490790761471312</v>
+        <v>0.002162375725080849</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1640048442301508</v>
+        <v>-0.3623676606028003</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3977072214742471</v>
+        <v>-0.09306258188811782</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.2318327785241652</v>
+        <v>0.06880735989696617</v>
       </c>
       <c r="K53" t="n">
-        <v>0.2787641162068089</v>
+        <v>0.1375954127818002</v>
       </c>
     </row>
     <row r="54">
@@ -3584,34 +3293,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2666457395746782</v>
+        <v>0.04167926980261508</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.3632414523290475</v>
+        <v>-0.1244609720467533</v>
       </c>
       <c r="D54" t="n">
-        <v>0.5713658708163926</v>
+        <v>-0.1537350115670229</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3627809080826135</v>
+        <v>0.07383551714670031</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6533028764822782</v>
+        <v>0.1002055136808601</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.1774256216738872</v>
+        <v>0.2429411764705884</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.4392447883112519</v>
+        <v>0.3097539770062858</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.07814087382485423</v>
+        <v>0.1285805403271234</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.5225993647522537</v>
+        <v>0.3049116433213472</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.08007209525805002</v>
+        <v>0.154914366760297</v>
       </c>
     </row>
     <row r="55">
@@ -3621,34 +3330,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1873586843847983</v>
+        <v>0.1268454332888114</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1091512050408167</v>
+        <v>-0.1087213455089071</v>
       </c>
       <c r="D55" t="n">
-        <v>0.4245702858498834</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.3330096228617831</v>
+        <v>-0.1216235992670948</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4149394520839548</v>
+        <v>0.2405044014395775</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1050394181629349</v>
+        <v>0.1344836439423284</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.266596954843554</v>
+        <v>0.2507759872010954</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2878320951175537</v>
+        <v>0.05108094442387968</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.01752017377587671</v>
+        <v>0.2399714959776694</v>
       </c>
       <c r="K55" t="n">
-        <v>0.04013757755573681</v>
+        <v>0.07502832441823606</v>
       </c>
     </row>
     <row r="56">
@@ -3658,34 +3364,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.04068146301303018</v>
+        <v>0.1233379585935061</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2078005411647113</v>
+        <v>-0.1056892272937856</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3110647963006511</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.01183667863483522</v>
+        <v>-0.1118242635572417</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2470348514085701</v>
+        <v>0.1860871227063087</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1713350728242826</v>
+        <v>0.299274649534139</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2312551342766662</v>
+        <v>0.03717049228284659</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4839077196299407</v>
+        <v>-0.01460737753661615</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.1511927559385499</v>
+        <v>0.05262139323661692</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.169792709283932</v>
+        <v>0.06750912409524273</v>
       </c>
     </row>
     <row r="57">
@@ -3695,34 +3398,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3735873790511273</v>
+        <v>0.1134042331421657</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.01502914723656337</v>
+        <v>0.009188630773666192</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.2989012700481803</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-0.4334260888928091</v>
+        <v>0.009188630773666178</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.1686942542138273</v>
+        <v>0.2074251915366928</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.08004721873085753</v>
+        <v>0.2355140195572865</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3545536755278364</v>
+        <v>0.06781595105649316</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1234363005347566</v>
+        <v>0.2121212121212122</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.3089896505322169</v>
+        <v>0.1147433812621334</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1957428286628974</v>
+        <v>0.2292316645957932</v>
       </c>
     </row>
     <row r="58">
@@ -3732,34 +3432,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.01775024247289007</v>
+        <v>-0.09323508829909925</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3275880101295097</v>
+        <v>-0.07446995802259677</v>
       </c>
       <c r="D58" t="n">
-        <v>0.6758319772972309</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-0.01116840680670634</v>
+        <v>-0.08217570104462957</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3612810325872179</v>
+        <v>0.1188591033014006</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4399680164264769</v>
+        <v>0.2343137522464546</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4891156720486208</v>
+        <v>-0.02050648155456843</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3498794773686733</v>
+        <v>0.2299562076188008</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.07806901460993662</v>
+        <v>0.1816420489139354</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2891686151665048</v>
+        <v>0.0152123139361088</v>
       </c>
     </row>
     <row r="59">
@@ -3769,34 +3466,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.001329833253294141</v>
+        <v>0.08333333333333325</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2002549770323199</v>
+        <v>-0.07341911803280055</v>
       </c>
       <c r="D59" t="n">
-        <v>0.01217973297009986</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.3961088536014947</v>
+        <v>0.08103348431673224</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1641096494511076</v>
+        <v>0.07855056176627598</v>
       </c>
       <c r="G59" t="n">
-        <v>0.6020757471679291</v>
+        <v>0.04873753042238239</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.2130131301024825</v>
+        <v>-0.206084593262753</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1501358928463456</v>
+        <v>-0.002369749752739528</v>
       </c>
       <c r="J59" t="n">
-        <v>0.06732235019413628</v>
+        <v>-0.04448422977261062</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.3299200849433792</v>
+        <v>0.3208917014082571</v>
       </c>
     </row>
     <row r="60">
@@ -3805,23 +3499,35 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="B60" t="n">
+        <v>-0.0008328753777787323</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.01425965765074887</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.0041668229254563</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.0244635374620877</v>
+      </c>
       <c r="F60" t="n">
-        <v>0.09231757446583171</v>
+        <v>-0.1048095705503215</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.0792703755833403</v>
+        <v>0.1606968372561283</v>
       </c>
       <c r="H60" t="n">
-        <v>0.06986592893503589</v>
+        <v>-0.1386722827267753</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3095173673185369</v>
+        <v>0.01123619279052928</v>
       </c>
       <c r="J60" t="n">
-        <v>0.2113323093181039</v>
+        <v>0.09556797093229463</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.2513154470193898</v>
+        <v>0.0159192080784544</v>
       </c>
     </row>
     <row r="61">
@@ -3831,34 +3537,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5455432967861679</v>
+        <v>-0.08569751680368508</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1750353635194763</v>
+        <v>-0.07134974196115186</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1727174671708138</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.2522287334020101</v>
+        <v>0.08103348431673225</v>
       </c>
       <c r="F61" t="n">
-        <v>0.2339507189139954</v>
+        <v>0.1805898160095151</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.01079042913192608</v>
+        <v>0.03425998696441809</v>
       </c>
       <c r="H61" t="n">
-        <v>0.347670499338211</v>
+        <v>0.1099616682522261</v>
       </c>
       <c r="I61" t="n">
-        <v>0.02141490212813946</v>
+        <v>0.02697017918001057</v>
       </c>
       <c r="J61" t="n">
-        <v>0.1542630774261792</v>
+        <v>0.04846678256791465</v>
       </c>
       <c r="K61" t="n">
-        <v>0.169117468475187</v>
+        <v>-0.2824171813644292</v>
       </c>
     </row>
     <row r="62">
@@ -3868,34 +3571,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4630336560884317</v>
+        <v>0.07990604811790902</v>
       </c>
       <c r="C62" t="n">
-        <v>0.1241636547805274</v>
+        <v>-0.06932028853554484</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5132164579195314</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.7446042670574503</v>
+        <v>-0.07990604811790902</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.03550639450137515</v>
+        <v>0.1021083864276044</v>
       </c>
       <c r="G62" t="n">
-        <v>0.6049385247648027</v>
+        <v>0.458039215686275</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5329162795120779</v>
+        <v>0.3307156750672215</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.02975888053337666</v>
+        <v>-0.04507127994655973</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.2865412993819823</v>
+        <v>-0.04252651903248619</v>
       </c>
       <c r="K62" t="n">
-        <v>0.7295824703405061</v>
+        <v>0.2159498703239424</v>
       </c>
     </row>
     <row r="63">
@@ -3905,34 +3605,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.03229718273426623</v>
+        <v>-0.0008328753777787229</v>
       </c>
       <c r="C63" t="n">
-        <v>0.03713089791552409</v>
+        <v>0.03006433534123327</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4215376161576915</v>
+        <v>-0.1102635692839942</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1595555696026312</v>
+        <v>0.09403533674948798</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3054520579437195</v>
+        <v>0.2542045029375168</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.05885833434225379</v>
+        <v>0.2460281401407436</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5948099048877711</v>
+        <v>0.3717978019044921</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.1414606046318683</v>
+        <v>0.06009623101612525</v>
       </c>
       <c r="J63" t="n">
-        <v>0.5377060541023133</v>
+        <v>0.1602895460227629</v>
       </c>
       <c r="K63" t="n">
-        <v>0.01331145208674765</v>
+        <v>-0.00822798951919637</v>
       </c>
     </row>
     <row r="64">
@@ -3942,34 +3642,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.1176622373013586</v>
+        <v>-0.1102635692839942</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1805673997866258</v>
+        <v>-0.1071968152299286</v>
       </c>
       <c r="D64" t="n">
-        <v>0.284821256495602</v>
+        <v>0.0008328753777787669</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4089869924441235</v>
+        <v>0.0399988756497339</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.299265043431989</v>
+        <v>0.1258635032831601</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.3003101303689066</v>
+        <v>0.1467536274523734</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5885864734460529</v>
+        <v>0.1794068048883942</v>
       </c>
       <c r="I64" t="n">
-        <v>0.083179525009256</v>
+        <v>0.06255012252977551</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.1261733916855509</v>
+        <v>-0.01894479370166062</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.4874927231326549</v>
+        <v>0.1785978438783266</v>
       </c>
     </row>
     <row r="65">
@@ -3979,34 +3679,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.2362382068481566</v>
+        <v>0.07990604811790901</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1580206859824446</v>
+        <v>-0.07446995802259679</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4204186470545902</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0.0344117014391628</v>
+        <v>0.08450704225352117</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4832013029323111</v>
+        <v>0.1398446572694943</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3235437814339232</v>
+        <v>0.2453977409111277</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3100794758868072</v>
+        <v>0.1668815229498265</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2010376570546362</v>
+        <v>-0.03605291618554286</v>
       </c>
       <c r="J65" t="n">
-        <v>-0.04359036189357887</v>
+        <v>0.09696788531634978</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4992043342892382</v>
+        <v>-0.1298707308797332</v>
       </c>
     </row>
     <row r="66">
@@ -4016,34 +3713,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.05914491789698873</v>
+        <v>0.1216235992670947</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.141587767278958</v>
+        <v>-0.09838071519901896</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4682608145231487</v>
+        <v>-0.004166822925456281</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3031024096711738</v>
+        <v>0.0729994845009882</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3776987117477166</v>
+        <v>0.2452585425996257</v>
       </c>
       <c r="G66" t="n">
-        <v>0.08844174607021038</v>
+        <v>0.1897024421058346</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.05045931948179256</v>
+        <v>0.2784558741902757</v>
       </c>
       <c r="I66" t="n">
-        <v>0.06972679912360116</v>
+        <v>0.1706121279836849</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.376959921144647</v>
+        <v>0.1076542177590761</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.1120022476437436</v>
+        <v>0.1346583059980944</v>
       </c>
     </row>
     <row r="67">
@@ -4053,34 +3750,31 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.005637675858660764</v>
+        <v>0.08450704225352117</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6015404564515187</v>
+        <v>-0.07237920675576846</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0954856198665696</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.2999763598009739</v>
+        <v>0.08569751680368511</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2819070469012428</v>
+        <v>0.2464057148024252</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.006416789038238754</v>
+        <v>0.3146155411422963</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1907463810614773</v>
+        <v>0.2187655271270719</v>
       </c>
       <c r="I67" t="n">
-        <v>0.02596983354195163</v>
+        <v>0.1453801274722676</v>
       </c>
       <c r="J67" t="n">
-        <v>0.2619931138049026</v>
+        <v>0.1934986966544018</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.2768520478756172</v>
+        <v>0.05644307784225475</v>
       </c>
     </row>
     <row r="68">
@@ -4090,34 +3784,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.2053426543996386</v>
+        <v>0.08217570104462957</v>
       </c>
       <c r="C68" t="n">
-        <v>0.2106560080171187</v>
+        <v>-0.06932028853554484</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5435529971861168</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0.276489461798409</v>
+        <v>0.0766064266294869</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.326445050932887</v>
+        <v>0.2390822511125512</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.2955465561649014</v>
+        <v>0.2579587693405925</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.3776240893549867</v>
+        <v>-0.0005401940449005025</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3195664024817995</v>
+        <v>0.01040101934984686</v>
       </c>
       <c r="J68" t="n">
-        <v>0.0187747567885813</v>
+        <v>0.09337526539748435</v>
       </c>
       <c r="K68" t="n">
-        <v>0.3064307591067054</v>
+        <v>0.03265998972716215</v>
       </c>
     </row>
     <row r="69">
@@ -4127,34 +3818,34 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3740724777271033</v>
+        <v>-0.0008328753777784195</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.1113596846169161</v>
+        <v>0.01256212678475732</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.3184506805795048</v>
+        <v>0.002499115053433486</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2122456927017567</v>
+        <v>0.07544214663174818</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.5630889408382901</v>
+        <v>0.218728730355693</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.6173290661749115</v>
+        <v>0.3009195909681911</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1424795329820853</v>
+        <v>0.3068798410215121</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3826087424335661</v>
+        <v>0.07515352926796454</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.162438859232946</v>
+        <v>0.06475170965266923</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.1362698205613969</v>
+        <v>0.2294442335976572</v>
       </c>
     </row>
     <row r="70">
@@ -4163,35 +3854,23 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>0.197645251742685</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.5220784666078347</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0.2241822978084657</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0.7528551477471989</v>
-      </c>
       <c r="F70" t="n">
-        <v>0.3409900640538172</v>
+        <v>0.1205704082270613</v>
       </c>
       <c r="G70" t="n">
-        <v>0.02095519892063923</v>
+        <v>0.2451405652143583</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.1479776217432114</v>
+        <v>0.2363159703465706</v>
       </c>
       <c r="I70" t="n">
-        <v>0.09037111700338815</v>
+        <v>0.04629100498862761</v>
       </c>
       <c r="J70" t="n">
-        <v>0.5541865397044689</v>
+        <v>0.2834794795908391</v>
       </c>
       <c r="K70" t="n">
-        <v>0.2637778965735981</v>
+        <v>0.2515966253176367</v>
       </c>
     </row>
     <row r="71">
@@ -4201,34 +3880,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.007533909518559358</v>
+        <v>0.08690547593388662</v>
       </c>
       <c r="C71" t="n">
-        <v>0.315678963459565</v>
+        <v>0.09456502606044032</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2512812985484426</v>
+        <v>0.07990604811790905</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.194675498522456</v>
+        <v>0.06848163867833729</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1682062837638209</v>
+        <v>0.157898077635332</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2451404938759839</v>
+        <v>0.3870273057601314</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.112990171008442</v>
+        <v>0.3556969897488861</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2521280117240508</v>
+        <v>0.02702216931723656</v>
       </c>
       <c r="J71" t="n">
-        <v>0.07997933833603184</v>
+        <v>0.09449817908227102</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.2596086165554797</v>
+        <v>0.3377616691218402</v>
       </c>
     </row>
     <row r="72">
@@ -4237,35 +3916,23 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>0.2022537574904776</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.2280622410671326</v>
-      </c>
-      <c r="D72" t="n">
-        <v>0.3090597015686999</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.1559500542778379</v>
-      </c>
       <c r="F72" t="n">
-        <v>-0.3014770852315651</v>
+        <v>0.334387043130316</v>
       </c>
       <c r="G72" t="n">
-        <v>0.09022219753297255</v>
+        <v>-0.008225616921269052</v>
       </c>
       <c r="H72" t="n">
-        <v>0.204761273402275</v>
+        <v>0.1470872534254294</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.1493097653478746</v>
+        <v>-0.003345838571639537</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.2349926039462911</v>
+        <v>0.1869222733425607</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.1280124872906915</v>
+        <v>0.002239538240265456</v>
       </c>
     </row>
     <row r="73">
@@ -4274,35 +3941,23 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>0.1726577445719092</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0.6382588324662438</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0.0316751743300577</v>
-      </c>
-      <c r="E73" t="n">
-        <v>-0.03574019243912507</v>
-      </c>
       <c r="F73" t="n">
-        <v>0.3619651433146613</v>
+        <v>0.1839739981638681</v>
       </c>
       <c r="G73" t="n">
-        <v>0.09448720615482513</v>
+        <v>0.1855852317360563</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.1354498570934317</v>
+        <v>0.1101570643737091</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2335810902199691</v>
+        <v>0.09929068785024213</v>
       </c>
       <c r="J73" t="n">
-        <v>0.2462822458474995</v>
+        <v>0.0905718579923652</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1141500460071368</v>
+        <v>0.04130109308988684</v>
       </c>
     </row>
     <row r="74">
@@ -4311,35 +3966,23 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>0.4528253495386964</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0.3360143085805596</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.7944940746973576</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0.4492780967615606</v>
-      </c>
       <c r="F74" t="n">
-        <v>0.1352093171798163</v>
+        <v>0.2142761677772856</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3589084095756348</v>
+        <v>0.3702036305697977</v>
       </c>
       <c r="H74" t="n">
-        <v>0.5191846619934327</v>
+        <v>0.2739854410538231</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3868927740666876</v>
+        <v>0.1454221775687018</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.07482964746078041</v>
+        <v>0.2356181280637863</v>
       </c>
       <c r="K74" t="n">
-        <v>0.2507548345239687</v>
+        <v>0.2972383901984174</v>
       </c>
     </row>
     <row r="75">
@@ -4348,35 +3991,23 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>-0.04446944156973466</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.4346800556633272</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0.3950157759680226</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0.001868631661384786</v>
-      </c>
       <c r="F75" t="n">
-        <v>-0.2594248903010605</v>
+        <v>0.1174861721749233</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.5889074924064673</v>
+        <v>0.2444227005870837</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.4222408638958541</v>
+        <v>0.2401530985838919</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5241176526462956</v>
+        <v>0.03320261387552179</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.1325819525903545</v>
+        <v>0.1545715019960448</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.01234068108174933</v>
+        <v>0.2321645201349792</v>
       </c>
     </row>
     <row r="76">
@@ -4386,34 +4017,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.1549682002464392</v>
+        <v>0.08450704225352114</v>
       </c>
       <c r="C76" t="n">
-        <v>0.299077004912542</v>
+        <v>0.09591852517188472</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3004612879714781</v>
+        <v>0.08813167071828207</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.0356511523399099</v>
+        <v>0.08662083924813022</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.04933885783346558</v>
+        <v>0.03434120037018094</v>
       </c>
       <c r="G76" t="n">
-        <v>0.120938107133027</v>
+        <v>0.2587154155974462</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.3132291201869397</v>
+        <v>-0.02504279767913358</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4562997975078554</v>
+        <v>0.09939042388802176</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1016088997197716</v>
+        <v>0.1858432503538201</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2103739224912718</v>
+        <v>0.1286553167498355</v>
       </c>
     </row>
     <row r="77">
@@ -4422,35 +4053,23 @@
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>0.3132009932395022</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.1096115082473384</v>
-      </c>
-      <c r="D77" t="n">
-        <v>-0.01683842960768596</v>
-      </c>
-      <c r="E77" t="n">
-        <v>-0.5759591642956644</v>
-      </c>
       <c r="F77" t="n">
-        <v>0.1556404822493064</v>
+        <v>0.2139072287722145</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.02522981064013339</v>
+        <v>0.35900456919117</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.04977191454475792</v>
+        <v>0.2420588641857856</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5278901674734442</v>
+        <v>0.136042780304048</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.1805633102268057</v>
+        <v>-0.08714501826446729</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.06157301977907179</v>
+        <v>0.0158482086197114</v>
       </c>
     </row>
     <row r="78">
@@ -4459,35 +4078,23 @@
           <t>2025-12-30</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>-0.02915505750245069</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.3761383924712342</v>
-      </c>
-      <c r="D78" t="n">
-        <v>-0.1478831300292048</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-0.2909285601997129</v>
-      </c>
       <c r="F78" t="n">
-        <v>0.2830292092291452</v>
+        <v>-0.005945811830095973</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2003566178831032</v>
+        <v>0.2448064286798311</v>
       </c>
       <c r="H78" t="n">
-        <v>0.2960584569046261</v>
+        <v>-0.1147444762442587</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2364714956095406</v>
+        <v>0.003177321150842809</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.1958576354140294</v>
+        <v>0.153658554251345</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2058165455190323</v>
+        <v>0.1478367334920618</v>
       </c>
     </row>
     <row r="79">
@@ -4496,35 +4103,23 @@
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>0.2968408546141086</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0.2178809024518155</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0.2279996338075116</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.4642417637802715</v>
-      </c>
       <c r="F79" t="n">
-        <v>0.2613090634325655</v>
+        <v>0.2202597395398871</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3977435886689815</v>
+        <v>0.1897024421058349</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6839165509661014</v>
+        <v>0.2523325299964341</v>
       </c>
       <c r="I79" t="n">
-        <v>0.09094231573016649</v>
+        <v>0.1316723964219479</v>
       </c>
       <c r="J79" t="n">
-        <v>0.325596872288909</v>
+        <v>0.2083547085244181</v>
       </c>
       <c r="K79" t="n">
-        <v>0.5495679681198558</v>
+        <v>0.2094015414514154</v>
       </c>
     </row>
     <row r="80">
@@ -4533,35 +4128,23 @@
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>-0.05132651036150812</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0.2137412426528469</v>
-      </c>
-      <c r="D80" t="n">
-        <v>-0.1301381069526711</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-0.1200345901878029</v>
-      </c>
       <c r="F80" t="n">
-        <v>-0.1186162298268817</v>
+        <v>0.2253744679276044</v>
       </c>
       <c r="G80" t="n">
-        <v>0.09574659909864768</v>
+        <v>0.2451405652143584</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.05350996497117667</v>
+        <v>0.3208343950052108</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.273147014186866</v>
+        <v>0.03453026528291139</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.1694122900830539</v>
+        <v>0.1719724517666151</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.3281491193150257</v>
+        <v>0.3501371610561964</v>
       </c>
     </row>
     <row r="81">
@@ -4571,34 +4154,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.3321219540221289</v>
+        <v>0.07990604811790908</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2129789285865736</v>
+        <v>-0.07990604811790911</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.01324970808700121</v>
+        <v>0.0821757010446296</v>
       </c>
       <c r="E81" t="n">
-        <v>0.3033389168699863</v>
+        <v>0.09795621206216791</v>
       </c>
       <c r="F81" t="n">
-        <v>0.01525234719696055</v>
+        <v>0.2337254901960787</v>
       </c>
       <c r="G81" t="n">
-        <v>0.01738736313871471</v>
+        <v>0.1600392540389778</v>
       </c>
       <c r="H81" t="n">
-        <v>0.04095955772841704</v>
+        <v>-0.07342368740673366</v>
       </c>
       <c r="I81" t="n">
-        <v>0.09814375816586467</v>
+        <v>0.09206664553037903</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.4155261154355751</v>
+        <v>0.109264294988267</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.2140070805020489</v>
+        <v>0.1867890371353841</v>
       </c>
     </row>
     <row r="82">
@@ -4607,35 +4190,23 @@
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>0.2020401782835508</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.02470080462267759</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0.1483602663137072</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.07962560755747655</v>
-      </c>
       <c r="F82" t="n">
-        <v>-0.07080368635968975</v>
+        <v>0.1140059406230855</v>
       </c>
       <c r="G82" t="n">
-        <v>0.02607727390402682</v>
+        <v>0.1348226766394786</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.00544283032002753</v>
+        <v>0.16526340921684</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.04904759250972644</v>
+        <v>0.1239923730744369</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.4268074865241485</v>
+        <v>0.2001600440682214</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1925574383276958</v>
+        <v>0.2708742375311791</v>
       </c>
     </row>
     <row r="83">
@@ -4644,35 +4215,23 @@
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>-0.2674343641524937</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.4226365998484868</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0.3759120526906599</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0.131612698892763</v>
-      </c>
       <c r="F83" t="n">
-        <v>-0.4462822877226162</v>
+        <v>0.1736001875854013</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.125622548711887</v>
+        <v>0.2041137120056486</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.02745191285128214</v>
+        <v>0.01838575761681316</v>
       </c>
       <c r="I83" t="n">
-        <v>0.06250740119110003</v>
+        <v>0.1680502792575588</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1276520355800037</v>
+        <v>0.1618608605940533</v>
       </c>
       <c r="K83" t="n">
-        <v>0.657132927174866</v>
+        <v>-0.007096166645578372</v>
       </c>
     </row>
     <row r="84">
@@ -4681,35 +4240,110 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>-0.151706427270369</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.2379065151110886</v>
-      </c>
-      <c r="D84" t="n">
-        <v>-0.01061519401829271</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0.3024393201878091</v>
-      </c>
       <c r="F84" t="n">
-        <v>-0.1290861478242187</v>
+        <v>-0.01788533204874311</v>
       </c>
       <c r="G84" t="n">
-        <v>0.3524579096228487</v>
+        <v>0.04972592393692672</v>
       </c>
       <c r="H84" t="n">
-        <v>0.04520205991488789</v>
+        <v>-0.2106035785629322</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1373390301246171</v>
+        <v>-0.07917546385701349</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.516733349902659</v>
+        <v>0.1160851846373412</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1980980157743456</v>
+        <v>0.08784587757966851</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.08569751680368512</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.07769309688655057</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-0.08937688669175563</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.06896738346400709</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.2439177179619692</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.07841611891680945</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.3450078241199699</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-0.03027326015113104</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.1980751056323429</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-0.06851174308897001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0.3157591325886372</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.1886866639645648</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.3054651696543554</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.177485948773523</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.1123463364336247</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-0.02534389667363553</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0.1877950571919586</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.1753424657534245</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.3326884286982739</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.2050635681981158</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.07119435023714031</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.03625861961670493</v>
       </c>
     </row>
   </sheetData>
@@ -4724,7 +4358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4733,52 +4367,52 @@
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>alpha023 vs alpha043</t>
+          <t>alpha095 vs alpha099</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>alpha023 vs alpha066</t>
+          <t>alpha095 vs alpha027</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>alpha023 vs alpha045</t>
+          <t>alpha095 vs alpha075</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>alpha023 vs alpha031</t>
+          <t>alpha095 vs alpha019</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>alpha043 vs alpha066</t>
+          <t>alpha099 vs alpha027</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>alpha043 vs alpha045</t>
+          <t>alpha099 vs alpha075</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>alpha043 vs alpha031</t>
+          <t>alpha099 vs alpha019</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alpha066 vs alpha045</t>
+          <t>alpha027 vs alpha075</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>alpha066 vs alpha031</t>
+          <t>alpha027 vs alpha019</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>alpha045 vs alpha031</t>
+          <t>alpha075 vs alpha019</t>
         </is>
       </c>
     </row>
@@ -4796,6 +4430,15 @@
           <t>2023-01-18</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>0.2798584181713235</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4283196239717975</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0516305063644384</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4803,8 +4446,23 @@
           <t>2023-02-01</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>-0.207815658533888</v>
+      </c>
       <c r="C5" t="n">
-        <v>-0.5714561291862538</v>
+        <v>-0.1558140140741855</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.210742639639999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5040544470635858</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8549628164600608</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1194201981606416</v>
       </c>
     </row>
     <row r="6">
@@ -4813,23 +4471,23 @@
           <t>2023-02-15</t>
         </is>
       </c>
+      <c r="B6" t="n">
+        <v>0.002926981106110976</v>
+      </c>
       <c r="C6" t="n">
-        <v>-1.079079797315318</v>
+        <v>-0.3092611792272927</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4723304542800635</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1055822156319885</v>
+        <v>-0.002926981106111004</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7438232152774211</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.253632613017182</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7946969570461895</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.3531290376127579</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.4917108237894436</v>
+        <v>0.290273392277087</v>
       </c>
     </row>
     <row r="7">
@@ -4839,34 +4497,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02331650761758647</v>
+        <v>0.21366962074611</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.545510732244594</v>
+        <v>-0.4556907043901371</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5980799878617021</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.375040468573533</v>
+        <v>0.2020017880307724</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1807598435971681</v>
+        <v>0.9422557740332009</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2879676387076954</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.3551465542354422</v>
+        <v>1.526573334343987</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.074855535666136</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.215457194832265</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.7122091299513051</v>
+        <v>0.4989494992387805</v>
       </c>
     </row>
     <row r="8">
@@ -4876,34 +4522,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.398820654182622</v>
+        <v>0.424412260386109</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3281833886668523</v>
+        <v>-0.6211363533922267</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7506918979774182</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.4581537957273363</v>
+        <v>0.4098174465646605</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2058447444218008</v>
+        <v>1.220896842561195</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4486842902279781</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.2606558153536617</v>
+        <v>1.869296339038823</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9903128327224091</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.02741303787724386</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.3287970760397939</v>
+        <v>0.5940412924665881</v>
       </c>
     </row>
     <row r="9">
@@ -4913,34 +4547,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1093364239029047</v>
+        <v>0.6351549000261081</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3439120435135662</v>
+        <v>-0.7745835185453338</v>
       </c>
       <c r="D9" t="n">
-        <v>1.08649044838738</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.6638374846764312</v>
+        <v>0.1961060158933396</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.07734964385291912</v>
+        <v>1.284684769776339</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3600765241284535</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5368393910692514</v>
+        <v>2.030321581800085</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9142598127767394</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.1715107596204242</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.3203889546636421</v>
+        <v>0.6079912211125386</v>
       </c>
     </row>
     <row r="10">
@@ -4950,34 +4572,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1320401737605847</v>
+        <v>0.8636183021231685</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.5973599086861561</v>
+        <v>-0.9308164618229634</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9790196406135849</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.8843772593863183</v>
+        <v>0.3503186791887901</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1332035966262344</v>
+        <v>1.43920884610782</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6670986081853401</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.855575826360109</v>
+        <v>2.429421278712687</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5962442996022392</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.03594364347280657</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.2067859463233486</v>
+        <v>0.6438166107249167</v>
       </c>
     </row>
     <row r="11">
@@ -4987,34 +4597,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1673841045367369</v>
+        <v>1.074360941763167</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.5908850111180477</v>
+        <v>-1.077245986985808</v>
       </c>
       <c r="D11" t="n">
-        <v>1.565503374729724</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.8695242738379092</v>
+        <v>0.564030109860111</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1228108178117153</v>
+        <v>1.6376414048636</v>
       </c>
       <c r="G11" t="n">
-        <v>1.039754379194837</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.039114336118211</v>
+        <v>2.660100210930826</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.365006703070563</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.1550166427780326</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.2812641265449134</v>
+        <v>0.6733894721905461</v>
       </c>
     </row>
     <row r="12">
@@ -5024,34 +4622,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.05224091542540735</v>
+        <v>1.291084766299987</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04284674580455572</v>
+        <v>-1.226001872531359</v>
       </c>
       <c r="D12" t="n">
-        <v>1.159213203790609</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.6767758609026343</v>
+        <v>0.3647613737345454</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1016300480637728</v>
+        <v>1.781052670276538</v>
       </c>
       <c r="G12" t="n">
-        <v>1.038479690077945</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.6637200649562233</v>
+        <v>2.777482163411999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4643049710705595</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.1781416272853429</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-0.5131227060314625</v>
+        <v>0.82683852441019</v>
       </c>
     </row>
     <row r="13">
@@ -5061,34 +4647,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1269158604528799</v>
+        <v>1.094592280527527</v>
       </c>
       <c r="C13" t="n">
-        <v>0.07323604036193045</v>
+        <v>-1.391447521533448</v>
       </c>
       <c r="D13" t="n">
-        <v>1.307395588568302</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.08336602125108927</v>
+        <v>0.1540187340945465</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3678677248369284</v>
+        <v>2.046945761385446</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8878971190903548</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.137385336769911</v>
+        <v>3.12126957406406</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6271356565193391</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-0.251399885895583</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.8094603159838747</v>
+        <v>0.7781869092703815</v>
       </c>
     </row>
     <row r="14">
@@ -5098,34 +4672,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05050522847844599</v>
+        <v>1.28030456093701</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3755196344321783</v>
+        <v>-1.554458636603902</v>
       </c>
       <c r="D14" t="n">
-        <v>1.179655282254871</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.3091592220368196</v>
+        <v>0.3532874702201122</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7013917931230578</v>
+        <v>2.244238943913007</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9460271904017424</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.349252170237381</v>
+        <v>3.291686758663275</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.661472723223959</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.2159862947220437</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-0.5833335315545094</v>
+        <v>0.7400114005686</v>
       </c>
     </row>
     <row r="15">
@@ -5135,34 +4697,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3129197478562744</v>
+        <v>1.491047200577009</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6048347583221648</v>
+        <v>-1.703214522149453</v>
       </c>
       <c r="D15" t="n">
-        <v>0.992952066100585</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.3167136949515822</v>
+        <v>0.5553677930990382</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5231508319086919</v>
+        <v>2.338064329549673</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8631746451323513</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.384794567407257</v>
+        <v>3.382898361783075</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9053150828235144</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-0.3277452406455909</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.7533274844010859</v>
+        <v>0.8336846548556638</v>
       </c>
     </row>
     <row r="16">
@@ -5172,34 +4722,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7114110818995768</v>
+        <v>1.291778464451444</v>
       </c>
       <c r="C16" t="n">
-        <v>1.022578034169378</v>
+        <v>-1.845025078436958</v>
       </c>
       <c r="D16" t="n">
-        <v>1.403360463868428</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.574457866837598</v>
+        <v>0.3588753073265781</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7014823038192084</v>
+        <v>2.476810661617621</v>
       </c>
       <c r="G16" t="n">
-        <v>1.142595279789337</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.221839870542707</v>
+        <v>3.695496574250716</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.413120406648299</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-0.2655569336279666</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-1.00400529185766</v>
+        <v>0.9518593620151785</v>
       </c>
     </row>
     <row r="17">
@@ -5209,34 +4747,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.3456558523023113</v>
+        <v>1.508502288988263</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8386862039502024</v>
+        <v>-2.010470727439047</v>
       </c>
       <c r="D17" t="n">
-        <v>1.621580547596715</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.310729810186356</v>
+        <v>0.5526254124427663</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.143922736458715</v>
+        <v>2.720211620192831</v>
       </c>
       <c r="G17" t="n">
-        <v>1.440728125962953</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.6181674915728103</v>
+        <v>3.831539354554764</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.240502392514392</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.09921812539616803</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-1.320748485613159</v>
+        <v>0.9629491355714118</v>
       </c>
     </row>
     <row r="18">
@@ -5246,34 +4772,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5160052549067287</v>
+        <v>1.710582611867189</v>
       </c>
       <c r="C18" t="n">
-        <v>1.092887058066507</v>
+        <v>-2.178370353465533</v>
       </c>
       <c r="D18" t="n">
-        <v>1.54279134497462</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.634383257217109</v>
+        <v>0.7491178982152263</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.515610101702448</v>
+        <v>2.806825940518911</v>
       </c>
       <c r="G18" t="n">
-        <v>1.59026887084715</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.058142627889227</v>
+        <v>4.214948227319667</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8501516571099372</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.4077988670886817</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-1.322633162771633</v>
+        <v>1.027196030216968</v>
       </c>
     </row>
     <row r="19">
@@ -5283,34 +4797,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5828061300906029</v>
+        <v>1.92429404253851</v>
       </c>
       <c r="C19" t="n">
-        <v>1.712733027879325</v>
+        <v>-2.351240450406814</v>
       </c>
       <c r="D19" t="n">
-        <v>1.203625726017987</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.378058389315396</v>
+        <v>0.5441891290783429</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5068044150502118</v>
+        <v>2.909631308497308</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9293695734532406</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.9601695047897548</v>
+        <v>4.43138658348405</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8884814679258142</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.9018152974414217</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-1.242027648031869</v>
+        <v>1.101510763271119</v>
       </c>
     </row>
     <row r="20">
@@ -5320,34 +4822,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8235905068092633</v>
+        <v>2.069323051241411</v>
       </c>
       <c r="C20" t="n">
-        <v>1.544021486703318</v>
+        <v>-2.522739035549323</v>
       </c>
       <c r="D20" t="n">
-        <v>1.443995962500801</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.823115955459531</v>
+        <v>0.683209304606243</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1590513556118627</v>
+        <v>3.113755453729239</v>
       </c>
       <c r="G20" t="n">
-        <v>1.202387174593217</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.9817264672618757</v>
+        <v>4.782936368516324</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6949890587806454</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.405640975209104</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-1.188803691074672</v>
+        <v>1.138719548132843</v>
       </c>
     </row>
     <row r="21">
@@ -5357,34 +4847,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6314662586033484</v>
+        <v>1.918196534955009</v>
       </c>
       <c r="C21" t="n">
-        <v>1.744118356404031</v>
+        <v>-2.635478044031806</v>
       </c>
       <c r="D21" t="n">
-        <v>1.683653866013907</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.257830089060862</v>
+        <v>0.9181568328034292</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3980773055075666</v>
+        <v>3.253239798201804</v>
       </c>
       <c r="G21" t="n">
-        <v>1.272146722171545</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.152696281382932</v>
+        <v>4.872295584428537</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5930171430633091</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.838583600403239</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-0.6813612028480965</v>
+        <v>1.209527099718359</v>
       </c>
     </row>
     <row r="22">
@@ -5394,34 +4872,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8974290330632602</v>
+        <v>2.114689020727469</v>
       </c>
       <c r="C22" t="n">
-        <v>2.363631917664101</v>
+        <v>-2.723855796003188</v>
       </c>
       <c r="D22" t="n">
-        <v>2.062044228090683</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.086987879634941</v>
+        <v>0.7771739095257446</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7968673246309155</v>
+        <v>3.393448400628709</v>
       </c>
       <c r="G22" t="n">
-        <v>1.378117587238753</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.749039053303233</v>
+        <v>5.089073735044945</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1775153668200799</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.981795239121289</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-1.114450879996805</v>
+        <v>1.276557742138261</v>
       </c>
     </row>
     <row r="23">
@@ -5431,34 +4897,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6706648573667184</v>
+        <v>2.288451032441698</v>
       </c>
       <c r="C23" t="n">
-        <v>2.176219860920606</v>
+        <v>-2.872123763977758</v>
       </c>
       <c r="D23" t="n">
-        <v>1.846101352448665</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1.891729293545638</v>
+        <v>0.9661941821053143</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8000776921524192</v>
+        <v>3.5830665858847</v>
       </c>
       <c r="G23" t="n">
-        <v>1.747104524144965</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.059074885607381</v>
+        <v>5.334214300259303</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1730555303811712</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.450444781999252</v>
-      </c>
-      <c r="K23" t="n">
-        <v>-0.7619253296811075</v>
+        <v>1.242260309202247</v>
       </c>
     </row>
     <row r="24">
@@ -5468,34 +4922,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4960482056221426</v>
+        <v>2.462213044155926</v>
       </c>
       <c r="C24" t="n">
-        <v>2.007264728737436</v>
+        <v>-3.029359041989155</v>
       </c>
       <c r="D24" t="n">
-        <v>2.011541431940816</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.014443105834339</v>
+        <v>0.7823905265818625</v>
       </c>
       <c r="F24" t="n">
-        <v>1.336263131240912</v>
+        <v>3.850892834143257</v>
       </c>
       <c r="G24" t="n">
-        <v>2.003104062853871</v>
-      </c>
-      <c r="H24" t="n">
-        <v>2.40251350952576</v>
+        <v>5.653595229701144</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1174720474964384</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.210292302528658</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-0.6003944522292292</v>
+        <v>1.356666105303457</v>
       </c>
     </row>
     <row r="25">
@@ -5505,34 +4947,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7135081584634653</v>
+        <v>2.270530514216081</v>
       </c>
       <c r="C25" t="n">
-        <v>2.496813177802255</v>
+        <v>-3.186594320000552</v>
       </c>
       <c r="D25" t="n">
-        <v>2.346457342080645</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.090593554209532</v>
+        <v>0.5933702540022929</v>
       </c>
       <c r="F25" t="n">
-        <v>1.740581847932844</v>
+        <v>3.959056387806478</v>
       </c>
       <c r="G25" t="n">
-        <v>2.237121195376761</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.624478598369063</v>
+        <v>5.800504462877983</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.366589666301994</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.880045413812595</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-0.4074243418394958</v>
+        <v>1.447897979295639</v>
       </c>
     </row>
     <row r="26">
@@ -5542,34 +4972,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.321586855863385</v>
+        <v>2.405685916718264</v>
       </c>
       <c r="C26" t="n">
-        <v>2.601843127913666</v>
+        <v>-3.340041485153659</v>
       </c>
       <c r="D26" t="n">
-        <v>2.229852519826371</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1.973921805753126</v>
+        <v>0.446447120701431</v>
       </c>
       <c r="F26" t="n">
-        <v>2.444550554406705</v>
+        <v>4.002342195810824</v>
       </c>
       <c r="G26" t="n">
-        <v>2.094020800163744</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.311480775599303</v>
+        <v>5.890755057109964</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7248239679169928</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.6505895416969555</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-0.5586133800545439</v>
+        <v>1.480939421428036</v>
       </c>
     </row>
     <row r="27">
@@ -5579,34 +4997,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.763912789520531</v>
+        <v>2.28469380273396</v>
       </c>
       <c r="C27" t="n">
-        <v>3.037167986562217</v>
+        <v>-3.510415573046029</v>
       </c>
       <c r="D27" t="n">
-        <v>1.961327546693052</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2.188763147694634</v>
+        <v>0.3083911785298575</v>
       </c>
       <c r="F27" t="n">
-        <v>2.78819359793</v>
+        <v>4.205740497261568</v>
       </c>
       <c r="G27" t="n">
-        <v>1.949113764743235</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.134082107432403</v>
+        <v>6.220162691616759</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7581165632037941</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.008685610971733</v>
-      </c>
-      <c r="K27" t="n">
-        <v>-0.01142889893413435</v>
+        <v>1.558048449426323</v>
       </c>
     </row>
     <row r="28">
@@ -5616,34 +5022,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.269594409083508</v>
+        <v>2.473714075313529</v>
       </c>
       <c r="C28" t="n">
-        <v>3.739642325616217</v>
+        <v>-3.635234282160198</v>
       </c>
       <c r="D28" t="n">
-        <v>2.634585744091244</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2.85848501877595</v>
+        <v>0.5082952475946081</v>
       </c>
       <c r="F28" t="n">
-        <v>3.181897235097881</v>
+        <v>4.338406833089221</v>
       </c>
       <c r="G28" t="n">
-        <v>2.371907574632278</v>
+        <v>6.549579291945982</v>
       </c>
       <c r="H28" t="n">
-        <v>2.428366047937273</v>
+        <v>0.3258084920561324</v>
       </c>
       <c r="I28" t="n">
-        <v>0.02947290793980772</v>
+        <v>1.666527130553105</v>
       </c>
       <c r="J28" t="n">
-        <v>1.466679455870694</v>
+        <v>0.02127818383517276</v>
       </c>
       <c r="K28" t="n">
-        <v>0.16596531671513</v>
+        <v>0.2410006102968298</v>
       </c>
     </row>
     <row r="29">
@@ -5653,34 +5056,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.514144634943801</v>
+        <v>2.611770017485103</v>
       </c>
       <c r="C29" t="n">
-        <v>3.52492495811982</v>
+        <v>-3.786329060132251</v>
       </c>
       <c r="D29" t="n">
-        <v>2.94231594918011</v>
+        <v>0.6292873615789125</v>
       </c>
       <c r="E29" t="n">
-        <v>3.316966835704271</v>
+        <v>0.08900190308630285</v>
       </c>
       <c r="F29" t="n">
-        <v>3.161655134050178</v>
+        <v>4.554382037271905</v>
       </c>
       <c r="G29" t="n">
-        <v>2.252611888628679</v>
+        <v>6.766630834062862</v>
       </c>
       <c r="H29" t="n">
-        <v>2.34553789542543</v>
+        <v>0.547761094813686</v>
       </c>
       <c r="I29" t="n">
-        <v>0.05257093289961603</v>
+        <v>1.70418930941084</v>
       </c>
       <c r="J29" t="n">
-        <v>1.516584840548527</v>
+        <v>0.239877982860346</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1794215459653251</v>
+        <v>0.4274311919478511</v>
       </c>
     </row>
     <row r="30">
@@ -5690,34 +5093,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.786580129346977</v>
+        <v>2.800790290064672</v>
       </c>
       <c r="C30" t="n">
-        <v>3.433099905322921</v>
+        <v>-3.934597028106822</v>
       </c>
       <c r="D30" t="n">
-        <v>3.305039695046859</v>
-      </c>
-      <c r="E30" t="n">
-        <v>3.034361886399476</v>
+        <v>0.8080085584443115</v>
       </c>
       <c r="F30" t="n">
-        <v>3.089774237276105</v>
+        <v>4.808586540209422</v>
       </c>
       <c r="G30" t="n">
-        <v>2.412827260954603</v>
+        <v>6.98340898467927</v>
       </c>
       <c r="H30" t="n">
-        <v>2.670504999134564</v>
+        <v>0.7139265171806392</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4088865082699116</v>
+        <v>1.626161174903918</v>
       </c>
       <c r="J30" t="n">
-        <v>1.792034312652954</v>
+        <v>0.4185975859799579</v>
       </c>
       <c r="K30" t="n">
-        <v>0.04722330222665896</v>
+        <v>0.5185400295717899</v>
       </c>
     </row>
     <row r="31">
@@ -5727,34 +5127,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.763145333253294</v>
+        <v>2.979511486930071</v>
       </c>
       <c r="C31" t="n">
-        <v>3.598429214153945</v>
+        <v>-4.08731137745581</v>
       </c>
       <c r="D31" t="n">
-        <v>3.596368056740995</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3.33517304512096</v>
+        <v>0.9918122139677632</v>
       </c>
       <c r="F31" t="n">
-        <v>3.683810719564098</v>
+        <v>4.78670244172078</v>
       </c>
       <c r="G31" t="n">
-        <v>2.715674880282164</v>
+        <v>7.142459928828802</v>
       </c>
       <c r="H31" t="n">
-        <v>2.82546559343946</v>
+        <v>0.7598485814000487</v>
       </c>
       <c r="I31" t="n">
-        <v>0.730517756920556</v>
+        <v>1.512078887252206</v>
       </c>
       <c r="J31" t="n">
-        <v>1.995183701494825</v>
+        <v>0.3227091723009224</v>
       </c>
       <c r="K31" t="n">
-        <v>0.40847761522902</v>
+        <v>0.4868417908022259</v>
       </c>
     </row>
     <row r="32">
@@ -5764,34 +5161,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.86935023235387</v>
+        <v>3.163315142453523</v>
       </c>
       <c r="C32" t="n">
-        <v>3.882347700590554</v>
+        <v>-4.220497437424743</v>
       </c>
       <c r="D32" t="n">
-        <v>3.770313739626149</v>
-      </c>
-      <c r="E32" t="n">
-        <v>3.422125506485394</v>
+        <v>0.8027919413881937</v>
       </c>
       <c r="F32" t="n">
-        <v>3.975272028421061</v>
+        <v>5.045253804245342</v>
       </c>
       <c r="G32" t="n">
-        <v>2.716286486588117</v>
+        <v>7.401610492199221</v>
       </c>
       <c r="H32" t="n">
-        <v>2.865499350701803</v>
+        <v>0.9265768827475233</v>
       </c>
       <c r="I32" t="n">
-        <v>1.328356415114699</v>
+        <v>1.740286740763576</v>
       </c>
       <c r="J32" t="n">
-        <v>1.86780363471639</v>
+        <v>0.3425902623922266</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5021430911097734</v>
+        <v>0.5573850380578923</v>
       </c>
     </row>
     <row r="33">
@@ -5801,34 +5195,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.832405095452406</v>
+        <v>3.344561498405563</v>
       </c>
       <c r="C33" t="n">
-        <v>4.140364507796212</v>
+        <v>-4.370979753781955</v>
       </c>
       <c r="D33" t="n">
-        <v>3.496336660539002</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3.604430451342727</v>
+        <v>0.984038297340234</v>
       </c>
       <c r="F33" t="n">
-        <v>4.097135890620955</v>
+        <v>5.279941748913467</v>
       </c>
       <c r="G33" t="n">
-        <v>2.950770867294109</v>
+        <v>7.784747747101182</v>
       </c>
       <c r="H33" t="n">
-        <v>3.029480238515796</v>
+        <v>1.109190366896649</v>
       </c>
       <c r="I33" t="n">
-        <v>1.600040080614622</v>
+        <v>1.773497298971329</v>
       </c>
       <c r="J33" t="n">
-        <v>1.938506474228428</v>
+        <v>0.3780419847674135</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6677744976146165</v>
+        <v>0.6379485841970658</v>
       </c>
     </row>
     <row r="34">
@@ -5838,34 +5229,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.764881994206421</v>
+        <v>3.163315142453523</v>
       </c>
       <c r="C34" t="n">
-        <v>3.834069454768685</v>
+        <v>-4.554783409305407</v>
       </c>
       <c r="D34" t="n">
-        <v>3.25036309720914</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3.924324034165417</v>
+        <v>0.8684963279042718</v>
       </c>
       <c r="F34" t="n">
-        <v>4.308487601045091</v>
+        <v>5.36930096482568</v>
       </c>
       <c r="G34" t="n">
-        <v>3.063589561363836</v>
+        <v>8.086158060957706</v>
       </c>
       <c r="H34" t="n">
-        <v>2.942297398017562</v>
+        <v>1.097302199354737</v>
       </c>
       <c r="I34" t="n">
-        <v>1.617544162894227</v>
+        <v>2.088627515758621</v>
       </c>
       <c r="J34" t="n">
-        <v>2.00078833466825</v>
+        <v>0.5370141374190511</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8781068752722287</v>
+        <v>0.6867212023108379</v>
       </c>
     </row>
     <row r="35">
@@ -5875,34 +5263,34 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.176287240033797</v>
+        <v>3.329430653065481</v>
       </c>
       <c r="C35" t="n">
-        <v>4.164119013899464</v>
+        <v>-4.594856569532751</v>
       </c>
       <c r="D35" t="n">
-        <v>2.998725960860824</v>
+        <v>0.9521309876311457</v>
       </c>
       <c r="E35" t="n">
-        <v>4.088686360687128</v>
+        <v>0.2593107631490033</v>
       </c>
       <c r="F35" t="n">
-        <v>4.402927721869267</v>
+        <v>5.498841776610261</v>
       </c>
       <c r="G35" t="n">
-        <v>3.521356553671243</v>
+        <v>8.34481586281723</v>
       </c>
       <c r="H35" t="n">
-        <v>3.414291886679544</v>
+        <v>1.12480665572458</v>
       </c>
       <c r="I35" t="n">
-        <v>1.220196121151338</v>
+        <v>2.199640774705342</v>
       </c>
       <c r="J35" t="n">
-        <v>1.99914897283989</v>
+        <v>0.6239474753790706</v>
       </c>
       <c r="K35" t="n">
-        <v>0.844617017004386</v>
+        <v>0.6776881057845395</v>
       </c>
     </row>
     <row r="36">
@@ -5912,34 +5300,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.951637971927267</v>
+        <v>3.46687510527658</v>
       </c>
       <c r="C36" t="n">
-        <v>3.773550752680673</v>
+        <v>-4.712300613435692</v>
       </c>
       <c r="D36" t="n">
-        <v>3.461033373079642</v>
-      </c>
-      <c r="E36" t="n">
-        <v>4.197479622929045</v>
+        <v>1.105865999198169</v>
       </c>
       <c r="F36" t="n">
-        <v>4.122759826879004</v>
+        <v>5.59179900230055</v>
       </c>
       <c r="G36" t="n">
-        <v>3.042261422256829</v>
+        <v>8.425074914229198</v>
       </c>
       <c r="H36" t="n">
-        <v>3.469172396448764</v>
+        <v>1.216652023073247</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9933650624718188</v>
+        <v>2.124209904656352</v>
       </c>
       <c r="J36" t="n">
-        <v>2.152377106274598</v>
+        <v>0.7520729222367056</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8474100444567217</v>
+        <v>0.6351347098965732</v>
       </c>
     </row>
     <row r="37">
@@ -5949,34 +5334,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.072416100390891</v>
+        <v>3.555272287709372</v>
       </c>
       <c r="C37" t="n">
-        <v>3.823335321747583</v>
+        <v>-4.759239269254451</v>
       </c>
       <c r="D37" t="n">
-        <v>3.861366483900799</v>
+        <v>1.173262525810983</v>
       </c>
       <c r="E37" t="n">
-        <v>4.617069085560177</v>
+        <v>0.3197976096213238</v>
       </c>
       <c r="F37" t="n">
-        <v>4.566252792325001</v>
+        <v>5.622765179164817</v>
       </c>
       <c r="G37" t="n">
-        <v>2.953989731096974</v>
+        <v>8.603121888018485</v>
       </c>
       <c r="H37" t="n">
-        <v>3.714929412384938</v>
+        <v>1.17448986566169</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3878197456526068</v>
+        <v>2.199814011771364</v>
       </c>
       <c r="J37" t="n">
-        <v>2.461048520531773</v>
+        <v>0.7358295576432821</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9228184456832468</v>
+        <v>0.4985564717445141</v>
       </c>
     </row>
     <row r="38">
@@ -5986,34 +5371,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.213021505339344</v>
+        <v>3.42164166675316</v>
       </c>
       <c r="C38" t="n">
-        <v>4.165873672314494</v>
+        <v>-4.87496678172602</v>
       </c>
       <c r="D38" t="n">
-        <v>3.170161866482349</v>
-      </c>
-      <c r="E38" t="n">
-        <v>5.310539004119357</v>
+        <v>1.033876115323549</v>
       </c>
       <c r="F38" t="n">
-        <v>4.016524631810779</v>
+        <v>5.91144031375963</v>
       </c>
       <c r="G38" t="n">
-        <v>2.983764891731016</v>
+        <v>8.774410735527731</v>
       </c>
       <c r="H38" t="n">
-        <v>3.64423904000953</v>
+        <v>1.467700347257768</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2933095970717094</v>
+        <v>2.483210775144195</v>
       </c>
       <c r="J38" t="n">
-        <v>2.77689187417822</v>
+        <v>1.013195767722753</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1292954879651425</v>
+        <v>0.7024297698906588</v>
       </c>
     </row>
     <row r="39">
@@ -6023,34 +5405,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.200243878509126</v>
+        <v>3.280288580544563</v>
       </c>
       <c r="C39" t="n">
-        <v>4.250366577276606</v>
+        <v>-4.997649381992574</v>
       </c>
       <c r="D39" t="n">
-        <v>3.993029568741467</v>
-      </c>
-      <c r="E39" t="n">
-        <v>5.400094738942983</v>
+        <v>0.88228005185346</v>
       </c>
       <c r="F39" t="n">
-        <v>3.727880533589816</v>
+        <v>6.153963785514223</v>
       </c>
       <c r="G39" t="n">
-        <v>3.050607897373566</v>
+        <v>8.838648886722403</v>
       </c>
       <c r="H39" t="n">
-        <v>3.904825150400667</v>
+        <v>1.589213405904494</v>
       </c>
       <c r="I39" t="n">
-        <v>0.335298628526796</v>
+        <v>2.695518207794937</v>
       </c>
       <c r="J39" t="n">
-        <v>3.225801744883728</v>
+        <v>1.103840594751394</v>
       </c>
       <c r="K39" t="n">
-        <v>0.4139517207003812</v>
+        <v>0.6690349100538322</v>
       </c>
     </row>
     <row r="40">
@@ -6060,34 +5439,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.744919246682486</v>
+        <v>3.140902170057129</v>
       </c>
       <c r="C40" t="n">
-        <v>3.960671208251546</v>
+        <v>-5.113376894464143</v>
       </c>
       <c r="D40" t="n">
-        <v>4.129856294045274</v>
-      </c>
-      <c r="E40" t="n">
-        <v>5.5016670243286</v>
+        <v>1.027644945761695</v>
       </c>
       <c r="F40" t="n">
-        <v>3.485815314069419</v>
+        <v>6.379795581326947</v>
       </c>
       <c r="G40" t="n">
-        <v>2.962914973624224</v>
+        <v>8.972021481742736</v>
       </c>
       <c r="H40" t="n">
-        <v>3.472843209467641</v>
+        <v>1.68803795924771</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6285882810759262</v>
+        <v>2.704363956002175</v>
       </c>
       <c r="J40" t="n">
-        <v>3.444510109142567</v>
+        <v>1.278532550049915</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5806526612342837</v>
+        <v>0.5000826457901348</v>
       </c>
     </row>
     <row r="41">
@@ -6097,34 +5473,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4.107127031852308</v>
+        <v>3.280288580544563</v>
       </c>
       <c r="C41" t="n">
-        <v>4.090205277719077</v>
+        <v>-5.229104406935712</v>
       </c>
       <c r="D41" t="n">
-        <v>3.99870571466738</v>
-      </c>
-      <c r="E41" t="n">
-        <v>5.912146997117876</v>
+        <v>0.8822800518534601</v>
       </c>
       <c r="F41" t="n">
-        <v>3.623410412230243</v>
+        <v>6.49935359087486</v>
       </c>
       <c r="G41" t="n">
-        <v>2.817609763144944</v>
+        <v>9.245425509126562</v>
       </c>
       <c r="H41" t="n">
-        <v>3.537657818274969</v>
+        <v>1.979291151870732</v>
       </c>
       <c r="I41" t="n">
-        <v>1.16322782638356</v>
+        <v>2.839261616162553</v>
       </c>
       <c r="J41" t="n">
-        <v>3.788966846025923</v>
+        <v>1.362857937360955</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2761543996986832</v>
+        <v>0.7116284572316077</v>
       </c>
     </row>
     <row r="42">
@@ -6134,34 +5507,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4.190777568034513</v>
+        <v>3.146657959588351</v>
       </c>
       <c r="C42" t="n">
-        <v>4.491912997632936</v>
+        <v>-5.351787007202267</v>
       </c>
       <c r="D42" t="n">
-        <v>3.940380991110476</v>
-      </c>
-      <c r="E42" t="n">
-        <v>6.069277937295097</v>
+        <v>1.042636797000915</v>
       </c>
       <c r="F42" t="n">
-        <v>3.76605118329758</v>
+        <v>6.647178826346111</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2509106868008</v>
+        <v>9.568502432203486</v>
       </c>
       <c r="H42" t="n">
-        <v>4.135452890840476</v>
+        <v>2.172814085451763</v>
       </c>
       <c r="I42" t="n">
-        <v>1.454683704954079</v>
+        <v>2.901503820571501</v>
       </c>
       <c r="J42" t="n">
-        <v>4.258602033104008</v>
+        <v>1.482666481061473</v>
       </c>
       <c r="K42" t="n">
-        <v>1.003952640893714</v>
+        <v>1.040650527695882</v>
       </c>
     </row>
     <row r="43">
@@ -6171,34 +5541,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4.280313242457886</v>
+        <v>3.288011045796948</v>
       </c>
       <c r="C43" t="n">
-        <v>4.84546638822621</v>
+        <v>-5.481690817769933</v>
       </c>
       <c r="D43" t="n">
-        <v>3.969039669089592</v>
-      </c>
-      <c r="E43" t="n">
-        <v>6.44579281954818</v>
+        <v>0.9012837107923185</v>
       </c>
       <c r="F43" t="n">
-        <v>4.179140909440411</v>
+        <v>6.799360244491525</v>
       </c>
       <c r="G43" t="n">
-        <v>3.502513941614121</v>
+        <v>9.66074685053486</v>
       </c>
       <c r="H43" t="n">
-        <v>4.372789704635392</v>
+        <v>2.173185394089833</v>
       </c>
       <c r="I43" t="n">
-        <v>1.747061741597963</v>
+        <v>2.833889537639018</v>
       </c>
       <c r="J43" t="n">
-        <v>4.368234387352956</v>
+        <v>1.626311420852744</v>
       </c>
       <c r="K43" t="n">
-        <v>1.509675150465732</v>
+        <v>1.037340272715816</v>
       </c>
     </row>
     <row r="44">
@@ -6208,34 +5575,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4.335564003114102</v>
+        <v>3.429364132005545</v>
       </c>
       <c r="C44" t="n">
-        <v>5.235764970924865</v>
+        <v>-5.607947566304508</v>
       </c>
       <c r="D44" t="n">
-        <v>3.865605691465886</v>
-      </c>
-      <c r="E44" t="n">
-        <v>6.487956787510415</v>
+        <v>1.044629255562567</v>
       </c>
       <c r="F44" t="n">
-        <v>4.169428202870701</v>
+        <v>6.839924322770032</v>
       </c>
       <c r="G44" t="n">
-        <v>3.510651630648613</v>
+        <v>9.834983355668186</v>
       </c>
       <c r="H44" t="n">
-        <v>4.820547674273433</v>
+        <v>2.180099324041598</v>
       </c>
       <c r="I44" t="n">
-        <v>1.401773317758367</v>
+        <v>2.886503298057553</v>
       </c>
       <c r="J44" t="n">
-        <v>4.492826145929026</v>
+        <v>1.728890577286432</v>
       </c>
       <c r="K44" t="n">
-        <v>1.881894092638353</v>
+        <v>0.9364523059341752</v>
       </c>
     </row>
     <row r="45">
@@ -6245,34 +5609,34 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.996495487884453</v>
+        <v>3.355074463623717</v>
       </c>
       <c r="C45" t="n">
-        <v>5.546817067122324</v>
+        <v>-5.670784292348389</v>
       </c>
       <c r="D45" t="n">
-        <v>3.855546991934939</v>
+        <v>0.871394508781525</v>
       </c>
       <c r="E45" t="n">
-        <v>6.79617277092974</v>
+        <v>0.4397205165701782</v>
       </c>
       <c r="F45" t="n">
-        <v>3.869016672305623</v>
+        <v>6.895096694238445</v>
       </c>
       <c r="G45" t="n">
-        <v>3.562617025785383</v>
+        <v>10.02553452463603</v>
       </c>
       <c r="H45" t="n">
-        <v>4.754271660370235</v>
+        <v>2.366757859227885</v>
       </c>
       <c r="I45" t="n">
-        <v>1.788225531565454</v>
+        <v>2.924601853115659</v>
       </c>
       <c r="J45" t="n">
-        <v>4.636730786504656</v>
+        <v>1.737513440767143</v>
       </c>
       <c r="K45" t="n">
-        <v>2.15475542994484</v>
+        <v>0.8337208949768484</v>
       </c>
     </row>
     <row r="46">
@@ -6282,34 +5646,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4.402930431391163</v>
+        <v>3.215688053136283</v>
       </c>
       <c r="C46" t="n">
-        <v>5.930691658184301</v>
+        <v>-5.791705129012282</v>
       </c>
       <c r="D46" t="n">
-        <v>4.118547994311077</v>
-      </c>
-      <c r="E46" t="n">
-        <v>7.327924564831548</v>
+        <v>0.7280489640112763</v>
       </c>
       <c r="F46" t="n">
-        <v>3.851608859692249</v>
+        <v>7.249285159659198</v>
       </c>
       <c r="G46" t="n">
-        <v>3.587602798868663</v>
+        <v>10.35364437838792</v>
       </c>
       <c r="H46" t="n">
-        <v>5.103513206262365</v>
+        <v>2.627455516451173</v>
       </c>
       <c r="I46" t="n">
-        <v>1.583226443727705</v>
+        <v>2.941935316321318</v>
       </c>
       <c r="J46" t="n">
-        <v>5.14174796538738</v>
+        <v>1.836433418862758</v>
       </c>
       <c r="K46" t="n">
-        <v>2.1164832953313</v>
+        <v>1.131403817084999</v>
       </c>
     </row>
     <row r="47">
@@ -6319,34 +5680,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4.073845095772048</v>
+        <v>3.07630164264885</v>
       </c>
       <c r="C47" t="n">
-        <v>5.659668045581813</v>
+        <v>-5.907432641483851</v>
       </c>
       <c r="D47" t="n">
-        <v>4.856323262756232</v>
-      </c>
-      <c r="E47" t="n">
-        <v>7.659783890227732</v>
+        <v>0.5743139524442532</v>
       </c>
       <c r="F47" t="n">
-        <v>3.949171565127632</v>
+        <v>7.417551987911816</v>
       </c>
       <c r="G47" t="n">
-        <v>3.100181959982477</v>
+        <v>10.4752130058389</v>
       </c>
       <c r="H47" t="n">
-        <v>4.187970092003001</v>
+        <v>2.575070676297251</v>
       </c>
       <c r="I47" t="n">
-        <v>1.301707850491637</v>
+        <v>2.975145874529072</v>
       </c>
       <c r="J47" t="n">
-        <v>4.934790276163191</v>
+        <v>2.089720003902727</v>
       </c>
       <c r="K47" t="n">
-        <v>2.541630597718768</v>
+        <v>1.020957719428126</v>
       </c>
     </row>
     <row r="48">
@@ -6356,34 +5714,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4.092796281603531</v>
+        <v>2.932956097878601</v>
       </c>
       <c r="C48" t="n">
-        <v>5.864427323030984</v>
+        <v>-6.031893613530604</v>
       </c>
       <c r="D48" t="n">
-        <v>5.290478317930504</v>
-      </c>
-      <c r="E48" t="n">
-        <v>8.219749728392147</v>
+        <v>0.719678846352488</v>
       </c>
       <c r="F48" t="n">
-        <v>4.249571804466704</v>
+        <v>7.832254397452876</v>
       </c>
       <c r="G48" t="n">
-        <v>2.814158665328458</v>
+        <v>10.63623824860016</v>
       </c>
       <c r="H48" t="n">
-        <v>3.943514261137388</v>
+        <v>2.827963343860461</v>
       </c>
       <c r="I48" t="n">
-        <v>1.192296733962425</v>
+        <v>3.054225171869349</v>
       </c>
       <c r="J48" t="n">
-        <v>5.112111072313767</v>
+        <v>2.213963958255809</v>
       </c>
       <c r="K48" t="n">
-        <v>2.830437558840665</v>
+        <v>1.252741981112367</v>
       </c>
     </row>
     <row r="49">
@@ -6393,34 +5748,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4.566704343660354</v>
+        <v>3.08455216134869</v>
       </c>
       <c r="C49" t="n">
-        <v>6.100963154152098</v>
+        <v>-6.061501367018217</v>
       </c>
       <c r="D49" t="n">
-        <v>5.34197166105659</v>
-      </c>
-      <c r="E49" t="n">
-        <v>7.879459054192677</v>
+        <v>0.8650437402607229</v>
       </c>
       <c r="F49" t="n">
-        <v>4.402286232395727</v>
+        <v>8.173498361847358</v>
       </c>
       <c r="G49" t="n">
-        <v>3.162701627458898</v>
+        <v>10.8394091585537</v>
       </c>
       <c r="H49" t="n">
-        <v>4.060296562474997</v>
+        <v>3.166632907667498</v>
       </c>
       <c r="I49" t="n">
-        <v>1.270849164316835</v>
+        <v>3.217444555237968</v>
       </c>
       <c r="J49" t="n">
-        <v>4.917270750187546</v>
+        <v>2.440696344080606</v>
       </c>
       <c r="K49" t="n">
-        <v>3.086533917521566</v>
+        <v>1.406350185409153</v>
       </c>
     </row>
     <row r="50">
@@ -6430,34 +5782,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4.374196012935831</v>
+        <v>3.216873230148134</v>
       </c>
       <c r="C50" t="n">
-        <v>6.527111722689949</v>
+        <v>-6.167190594312002</v>
       </c>
       <c r="D50" t="n">
-        <v>5.153187952706647</v>
-      </c>
-      <c r="E50" t="n">
-        <v>8.203753409035031</v>
+        <v>0.7399655419421579</v>
       </c>
       <c r="F50" t="n">
-        <v>4.242096830818509</v>
+        <v>8.451232466561631</v>
       </c>
       <c r="G50" t="n">
-        <v>3.92125938903847</v>
+        <v>11.07690646425618</v>
       </c>
       <c r="H50" t="n">
-        <v>3.65175713861068</v>
+        <v>3.46181854727139</v>
       </c>
       <c r="I50" t="n">
-        <v>1.329038477099485</v>
+        <v>3.41370045648359</v>
       </c>
       <c r="J50" t="n">
-        <v>5.295171462260464</v>
+        <v>2.633088293085822</v>
       </c>
       <c r="K50" t="n">
-        <v>3.03161948203498</v>
+        <v>1.530290223987593</v>
       </c>
     </row>
     <row r="51">
@@ -6467,34 +5816,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4.161935045624877</v>
+        <v>3.34021118874164</v>
       </c>
       <c r="C51" t="n">
-        <v>6.645357127716458</v>
+        <v>-6.272879821605787</v>
       </c>
       <c r="D51" t="n">
-        <v>5.670095872948188</v>
-      </c>
-      <c r="E51" t="n">
-        <v>8.2062271517743</v>
+        <v>0.8517898054993995</v>
       </c>
       <c r="F51" t="n">
-        <v>4.183766042344411</v>
+        <v>8.468185318842078</v>
       </c>
       <c r="G51" t="n">
-        <v>3.414179048084108</v>
+        <v>11.2543924130297</v>
       </c>
       <c r="H51" t="n">
-        <v>3.998977971012835</v>
+        <v>3.133577313380366</v>
       </c>
       <c r="I51" t="n">
-        <v>1.206166966117594</v>
+        <v>3.428307834020206</v>
       </c>
       <c r="J51" t="n">
-        <v>5.961019102050549</v>
+        <v>2.725472562954658</v>
       </c>
       <c r="K51" t="n">
-        <v>2.704029712757592</v>
+        <v>1.393746721423145</v>
       </c>
     </row>
     <row r="52">
@@ -6504,34 +5850,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.085388799627544</v>
+        <v>3.377857351362692</v>
       </c>
       <c r="C52" t="n">
-        <v>6.876509002803792</v>
+        <v>-6.300476925110613</v>
       </c>
       <c r="D52" t="n">
-        <v>5.918889695432939</v>
+        <v>0.6980547939323768</v>
       </c>
       <c r="E52" t="n">
-        <v>8.572190085581235</v>
+        <v>0.5663266324305073</v>
       </c>
       <c r="F52" t="n">
-        <v>4.110922482461136</v>
+        <v>8.585999419105272</v>
       </c>
       <c r="G52" t="n">
-        <v>3.504427192319783</v>
+        <v>11.32785550169895</v>
       </c>
       <c r="H52" t="n">
-        <v>3.730081641251545</v>
+        <v>3.271469456977312</v>
       </c>
       <c r="I52" t="n">
-        <v>1.103020859367814</v>
+        <v>3.485130939502206</v>
       </c>
       <c r="J52" t="n">
-        <v>6.254930971101</v>
+        <v>2.867898759907146</v>
       </c>
       <c r="K52" t="n">
-        <v>2.37181251123442</v>
+        <v>1.503528159358355</v>
       </c>
     </row>
     <row r="53">
@@ -6541,34 +5887,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3.771548269392623</v>
+        <v>3.488120920646686</v>
       </c>
       <c r="C53" t="n">
-        <v>7.302086871985799</v>
+        <v>-6.394632372254951</v>
       </c>
       <c r="D53" t="n">
-        <v>6.148537013145331</v>
-      </c>
-      <c r="E53" t="n">
-        <v>8.388568234369226</v>
+        <v>0.8098790574896184</v>
       </c>
       <c r="F53" t="n">
-        <v>4.035622943522977</v>
+        <v>8.625922603907712</v>
       </c>
       <c r="G53" t="n">
-        <v>3.853506268466914</v>
+        <v>11.33001787742403</v>
       </c>
       <c r="H53" t="n">
-        <v>3.894086485481695</v>
+        <v>2.909101796374512</v>
       </c>
       <c r="I53" t="n">
-        <v>1.500728080842062</v>
+        <v>3.392068357614088</v>
       </c>
       <c r="J53" t="n">
-        <v>6.023098192576835</v>
+        <v>2.936706119804112</v>
       </c>
       <c r="K53" t="n">
-        <v>2.650576627441229</v>
+        <v>1.641123572140156</v>
       </c>
     </row>
     <row r="54">
@@ -6578,34 +5921,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3.504902529817945</v>
+        <v>3.529800190449301</v>
       </c>
       <c r="C54" t="n">
-        <v>6.938845419656752</v>
+        <v>-6.519093344301704</v>
       </c>
       <c r="D54" t="n">
-        <v>6.719902883961724</v>
+        <v>0.6561440459225955</v>
       </c>
       <c r="E54" t="n">
-        <v>8.75134914245184</v>
+        <v>0.6401621495772076</v>
       </c>
       <c r="F54" t="n">
-        <v>4.688925820005255</v>
+        <v>8.726128117588573</v>
       </c>
       <c r="G54" t="n">
-        <v>3.676080646793027</v>
+        <v>11.57295905389461</v>
       </c>
       <c r="H54" t="n">
-        <v>3.454841697170444</v>
+        <v>3.218855773380798</v>
       </c>
       <c r="I54" t="n">
-        <v>1.422587207017207</v>
+        <v>3.520648897941212</v>
       </c>
       <c r="J54" t="n">
-        <v>5.500498827824582</v>
+        <v>3.241617763125459</v>
       </c>
       <c r="K54" t="n">
-        <v>2.570504532183179</v>
+        <v>1.796037938900453</v>
       </c>
     </row>
     <row r="55">
@@ -6615,34 +5958,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.692261214202744</v>
+        <v>3.656645623738113</v>
       </c>
       <c r="C55" t="n">
-        <v>7.047996624697569</v>
+        <v>-6.627814689810611</v>
       </c>
       <c r="D55" t="n">
-        <v>7.144473169811607</v>
-      </c>
-      <c r="E55" t="n">
-        <v>9.084358765313622</v>
+        <v>0.5345204466555006</v>
       </c>
       <c r="F55" t="n">
-        <v>4.2739863679213</v>
+        <v>8.966632519028151</v>
       </c>
       <c r="G55" t="n">
-        <v>3.781120064955962</v>
+        <v>11.70744269783694</v>
       </c>
       <c r="H55" t="n">
-        <v>3.18824474232689</v>
+        <v>3.469631760581893</v>
       </c>
       <c r="I55" t="n">
-        <v>1.710419302134761</v>
+        <v>3.571729842365091</v>
       </c>
       <c r="J55" t="n">
-        <v>5.482978654048705</v>
+        <v>3.481589259103129</v>
       </c>
       <c r="K55" t="n">
-        <v>2.610642109738916</v>
+        <v>1.871066263318689</v>
       </c>
     </row>
     <row r="56">
@@ -6652,34 +5992,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.651579751189713</v>
+        <v>3.779983582331619</v>
       </c>
       <c r="C56" t="n">
-        <v>7.25579716586228</v>
+        <v>-6.733503917104397</v>
       </c>
       <c r="D56" t="n">
-        <v>7.455537966112258</v>
-      </c>
-      <c r="E56" t="n">
-        <v>9.096195443948458</v>
+        <v>0.4226961830982589</v>
       </c>
       <c r="F56" t="n">
-        <v>4.521021219329871</v>
+        <v>9.152719641734459</v>
       </c>
       <c r="G56" t="n">
-        <v>3.952455137780245</v>
+        <v>12.00671734737108</v>
       </c>
       <c r="H56" t="n">
-        <v>2.956989608050224</v>
+        <v>3.50680225286474</v>
       </c>
       <c r="I56" t="n">
-        <v>2.194327021764702</v>
+        <v>3.557122464828475</v>
       </c>
       <c r="J56" t="n">
-        <v>5.331785898110155</v>
+        <v>3.534210652339746</v>
       </c>
       <c r="K56" t="n">
-        <v>2.440849400454984</v>
+        <v>1.938575387413932</v>
       </c>
     </row>
     <row r="57">
@@ -6689,34 +6026,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4.025167130240841</v>
+        <v>3.893387815473785</v>
       </c>
       <c r="C57" t="n">
-        <v>7.240768018625716</v>
+        <v>-6.724315286330731</v>
       </c>
       <c r="D57" t="n">
-        <v>7.156636696064078</v>
-      </c>
-      <c r="E57" t="n">
-        <v>8.66276935505565</v>
+        <v>0.4318848138719251</v>
       </c>
       <c r="F57" t="n">
-        <v>4.352326965116044</v>
+        <v>9.360144833271152</v>
       </c>
       <c r="G57" t="n">
-        <v>3.872407919049387</v>
+        <v>12.24223136692837</v>
       </c>
       <c r="H57" t="n">
-        <v>3.31154328357806</v>
+        <v>3.574618203921233</v>
       </c>
       <c r="I57" t="n">
-        <v>2.317763322299458</v>
+        <v>3.769243676949688</v>
       </c>
       <c r="J57" t="n">
-        <v>5.022796247577938</v>
+        <v>3.648954033601879</v>
       </c>
       <c r="K57" t="n">
-        <v>2.636592229117881</v>
+        <v>2.167807052009725</v>
       </c>
     </row>
     <row r="58">
@@ -6726,34 +6060,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4.007416887767951</v>
+        <v>3.800152727174686</v>
       </c>
       <c r="C58" t="n">
-        <v>7.568356028755225</v>
+        <v>-6.798785244353327</v>
       </c>
       <c r="D58" t="n">
-        <v>7.832468673361309</v>
-      </c>
-      <c r="E58" t="n">
-        <v>8.651600948248943</v>
+        <v>0.3497091128272955</v>
       </c>
       <c r="F58" t="n">
-        <v>4.713607997703262</v>
+        <v>9.479003936572552</v>
       </c>
       <c r="G58" t="n">
-        <v>4.312375935475864</v>
+        <v>12.47654511917482</v>
       </c>
       <c r="H58" t="n">
-        <v>3.800658955626681</v>
+        <v>3.554111722366665</v>
       </c>
       <c r="I58" t="n">
-        <v>2.667642799668132</v>
+        <v>3.999199884568489</v>
       </c>
       <c r="J58" t="n">
-        <v>4.944727232968002</v>
+        <v>3.830596082515814</v>
       </c>
       <c r="K58" t="n">
-        <v>2.925760844284386</v>
+        <v>2.183019365945833</v>
       </c>
     </row>
     <row r="59">
@@ -6763,34 +6094,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4.006087054514657</v>
+        <v>3.883486060508019</v>
       </c>
       <c r="C59" t="n">
-        <v>7.768611005787545</v>
+        <v>-6.872204362386128</v>
       </c>
       <c r="D59" t="n">
-        <v>7.844648406331409</v>
-      </c>
-      <c r="E59" t="n">
-        <v>9.047709801850438</v>
+        <v>0.4307425971440277</v>
       </c>
       <c r="F59" t="n">
-        <v>4.87771764715437</v>
+        <v>9.557554498338828</v>
       </c>
       <c r="G59" t="n">
-        <v>4.914451682643794</v>
+        <v>12.5252826495972</v>
       </c>
       <c r="H59" t="n">
-        <v>3.587645825524199</v>
+        <v>3.348027129103912</v>
       </c>
       <c r="I59" t="n">
-        <v>2.517506906821786</v>
+        <v>3.996830134815749</v>
       </c>
       <c r="J59" t="n">
-        <v>5.012049583162138</v>
+        <v>3.786111852743204</v>
       </c>
       <c r="K59" t="n">
-        <v>2.595840759341007</v>
+        <v>2.503911067354091</v>
       </c>
     </row>
     <row r="60">
@@ -6799,23 +6127,35 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="B60" t="n">
+        <v>3.88265318513024</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-6.857944704735379</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.4265757742185715</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.6156986121151199</v>
+      </c>
       <c r="F60" t="n">
-        <v>4.970035221620202</v>
+        <v>9.452744927788507</v>
       </c>
       <c r="G60" t="n">
-        <v>4.835181307060453</v>
+        <v>12.68597948685333</v>
       </c>
       <c r="H60" t="n">
-        <v>3.657511754459235</v>
+        <v>3.209354846377136</v>
       </c>
       <c r="I60" t="n">
-        <v>2.827024274140323</v>
+        <v>4.008066327606278</v>
       </c>
       <c r="J60" t="n">
-        <v>5.223381892480242</v>
+        <v>3.881679823675498</v>
       </c>
       <c r="K60" t="n">
-        <v>2.344525312321617</v>
+        <v>2.519830275432545</v>
       </c>
     </row>
     <row r="61">
@@ -6825,34 +6165,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4.551630351300824</v>
+        <v>3.796955668326555</v>
       </c>
       <c r="C61" t="n">
-        <v>7.943646369307022</v>
+        <v>-6.929294446696531</v>
       </c>
       <c r="D61" t="n">
-        <v>8.017365873502223</v>
-      </c>
-      <c r="E61" t="n">
-        <v>9.299938535252448</v>
+        <v>0.5076092585353037</v>
       </c>
       <c r="F61" t="n">
-        <v>5.203985940534197</v>
+        <v>9.633334743798022</v>
       </c>
       <c r="G61" t="n">
-        <v>4.824390877928526</v>
+        <v>12.72023947381775</v>
       </c>
       <c r="H61" t="n">
-        <v>4.005182253797446</v>
+        <v>3.319316514629362</v>
       </c>
       <c r="I61" t="n">
-        <v>2.848439176268462</v>
+        <v>4.035036506786289</v>
       </c>
       <c r="J61" t="n">
-        <v>5.377644969906422</v>
+        <v>3.930146606243413</v>
       </c>
       <c r="K61" t="n">
-        <v>2.513642780796804</v>
+        <v>2.237413094068116</v>
       </c>
     </row>
     <row r="62">
@@ -6862,34 +6199,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5.014664007389256</v>
+        <v>3.876861716444464</v>
       </c>
       <c r="C62" t="n">
-        <v>8.067810024087549</v>
+        <v>-6.998614735232076</v>
       </c>
       <c r="D62" t="n">
-        <v>8.530582331421755</v>
-      </c>
-      <c r="E62" t="n">
-        <v>10.0445428023099</v>
+        <v>0.4277032104173947</v>
       </c>
       <c r="F62" t="n">
-        <v>5.168479546032821</v>
+        <v>9.735443130225626</v>
       </c>
       <c r="G62" t="n">
-        <v>5.429329402693329</v>
+        <v>13.17827868950403</v>
       </c>
       <c r="H62" t="n">
-        <v>4.538098533309523</v>
+        <v>3.650032189696584</v>
       </c>
       <c r="I62" t="n">
-        <v>2.818680295735086</v>
+        <v>3.989965226839729</v>
       </c>
       <c r="J62" t="n">
-        <v>5.09110367052444</v>
+        <v>3.887620087210927</v>
       </c>
       <c r="K62" t="n">
-        <v>3.243225251137311</v>
+        <v>2.453362964392058</v>
       </c>
     </row>
     <row r="63">
@@ -6899,34 +6233,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5.046961190123523</v>
+        <v>3.876028841066685</v>
       </c>
       <c r="C63" t="n">
-        <v>8.104940922003074</v>
+        <v>-6.968550399890843</v>
       </c>
       <c r="D63" t="n">
-        <v>8.952119947579446</v>
+        <v>0.3174396411334005</v>
       </c>
       <c r="E63" t="n">
-        <v>10.20409837191253</v>
+        <v>0.7097339488646078</v>
       </c>
       <c r="F63" t="n">
-        <v>4.863027488089101</v>
+        <v>9.989647633163143</v>
       </c>
       <c r="G63" t="n">
-        <v>5.370471068351075</v>
+        <v>13.42430682964477</v>
       </c>
       <c r="H63" t="n">
-        <v>3.943288628421752</v>
+        <v>4.021829991601075</v>
       </c>
       <c r="I63" t="n">
-        <v>2.677219691103217</v>
+        <v>4.050061457855855</v>
       </c>
       <c r="J63" t="n">
-        <v>5.628809724626754</v>
+        <v>4.047909633233689</v>
       </c>
       <c r="K63" t="n">
-        <v>3.256536703224058</v>
+        <v>2.445134974872862</v>
       </c>
     </row>
     <row r="64">
@@ -6936,34 +6270,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5.164623427424881</v>
+        <v>3.765765271782691</v>
       </c>
       <c r="C64" t="n">
-        <v>8.285508321789699</v>
+        <v>-7.075747215120772</v>
       </c>
       <c r="D64" t="n">
-        <v>9.236941204075048</v>
+        <v>0.3182725165111793</v>
       </c>
       <c r="E64" t="n">
-        <v>10.61308536435665</v>
+        <v>0.7497328245143418</v>
       </c>
       <c r="F64" t="n">
-        <v>4.563762444657113</v>
+        <v>10.1155111364463</v>
       </c>
       <c r="G64" t="n">
-        <v>5.070160937982169</v>
+        <v>13.57106045709714</v>
       </c>
       <c r="H64" t="n">
-        <v>4.531875101867805</v>
+        <v>4.20123679648947</v>
       </c>
       <c r="I64" t="n">
-        <v>2.760399216112473</v>
+        <v>4.11261158038563</v>
       </c>
       <c r="J64" t="n">
-        <v>5.502636332941202</v>
+        <v>4.028964839532029</v>
       </c>
       <c r="K64" t="n">
-        <v>2.769043980091404</v>
+        <v>2.623732818751189</v>
       </c>
     </row>
     <row r="65">
@@ -6973,34 +6307,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5.400861634273038</v>
+        <v>3.8456713199006</v>
       </c>
       <c r="C65" t="n">
-        <v>8.443529007772144</v>
+        <v>-7.150217173143369</v>
       </c>
       <c r="D65" t="n">
-        <v>9.657359851129639</v>
-      </c>
-      <c r="E65" t="n">
-        <v>10.64749706579582</v>
+        <v>0.4027795587647005</v>
       </c>
       <c r="F65" t="n">
-        <v>5.046963747589424</v>
+        <v>10.2553557937158</v>
       </c>
       <c r="G65" t="n">
-        <v>5.393704719416092</v>
+        <v>13.81645819800827</v>
       </c>
       <c r="H65" t="n">
-        <v>4.841954577754612</v>
+        <v>4.368118319439296</v>
       </c>
       <c r="I65" t="n">
-        <v>2.96143687316711</v>
+        <v>4.076558664200087</v>
       </c>
       <c r="J65" t="n">
-        <v>5.459045971047623</v>
+        <v>4.125932724848378</v>
       </c>
       <c r="K65" t="n">
-        <v>3.268248314380642</v>
+        <v>2.493862087871455</v>
       </c>
     </row>
     <row r="66">
@@ -7010,34 +6341,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5.341716716376049</v>
+        <v>3.967294919167695</v>
       </c>
       <c r="C66" t="n">
-        <v>8.301941240493186</v>
+        <v>-7.248597888342387</v>
       </c>
       <c r="D66" t="n">
-        <v>10.12562066565279</v>
+        <v>0.3986127358392442</v>
       </c>
       <c r="E66" t="n">
-        <v>10.95059947546699</v>
+        <v>0.82273230901533</v>
       </c>
       <c r="F66" t="n">
-        <v>5.42466245933714</v>
+        <v>10.50061433631542</v>
       </c>
       <c r="G66" t="n">
-        <v>5.482146465486302</v>
+        <v>14.00616064011411</v>
       </c>
       <c r="H66" t="n">
-        <v>4.79149525827282</v>
+        <v>4.646574193629572</v>
       </c>
       <c r="I66" t="n">
-        <v>3.031163672290711</v>
+        <v>4.247170792183772</v>
       </c>
       <c r="J66" t="n">
-        <v>5.082086049902976</v>
+        <v>4.233586942607454</v>
       </c>
       <c r="K66" t="n">
-        <v>3.156246066736898</v>
+        <v>2.62852039386955</v>
       </c>
     </row>
     <row r="67">
@@ -7047,34 +6378,31 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5.336079040517388</v>
+        <v>4.051801961421216</v>
       </c>
       <c r="C67" t="n">
-        <v>8.903481696944704</v>
+        <v>-7.320977095098156</v>
       </c>
       <c r="D67" t="n">
-        <v>10.22110628551936</v>
-      </c>
-      <c r="E67" t="n">
-        <v>11.25057583526796</v>
+        <v>0.4843102526429293</v>
       </c>
       <c r="F67" t="n">
-        <v>5.706569506238383</v>
+        <v>10.74702005111785</v>
       </c>
       <c r="G67" t="n">
-        <v>5.475729676448063</v>
+        <v>14.3207761812564</v>
       </c>
       <c r="H67" t="n">
-        <v>4.982241639334298</v>
+        <v>4.865339720756644</v>
       </c>
       <c r="I67" t="n">
-        <v>3.057133505832663</v>
+        <v>4.39255091965604</v>
       </c>
       <c r="J67" t="n">
-        <v>5.344079163707879</v>
+        <v>4.427085639261856</v>
       </c>
       <c r="K67" t="n">
-        <v>2.879394018861281</v>
+        <v>2.684963471711804</v>
       </c>
     </row>
     <row r="68">
@@ -7084,34 +6412,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>5.13073638611775</v>
+        <v>4.133977662465846</v>
       </c>
       <c r="C68" t="n">
-        <v>9.114137704961824</v>
+        <v>-7.390297383633701</v>
       </c>
       <c r="D68" t="n">
-        <v>10.76465928270547</v>
-      </c>
-      <c r="E68" t="n">
-        <v>11.52706529706637</v>
+        <v>0.5609166792724162</v>
       </c>
       <c r="F68" t="n">
-        <v>5.380124455305496</v>
+        <v>10.9861023022304</v>
       </c>
       <c r="G68" t="n">
-        <v>5.180183120283162</v>
+        <v>14.578734950597</v>
       </c>
       <c r="H68" t="n">
-        <v>4.604617549979311</v>
+        <v>4.864799526711744</v>
       </c>
       <c r="I68" t="n">
-        <v>3.376699908314462</v>
+        <v>4.402951939005887</v>
       </c>
       <c r="J68" t="n">
-        <v>5.362853920496461</v>
+        <v>4.52046090465934</v>
       </c>
       <c r="K68" t="n">
-        <v>3.185824777967986</v>
+        <v>2.717623461438967</v>
       </c>
     </row>
     <row r="69">
@@ -7121,34 +6446,34 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5.504808863844853</v>
+        <v>4.133144787088067</v>
       </c>
       <c r="C69" t="n">
-        <v>9.002778020344907</v>
+        <v>-7.377735256848944</v>
       </c>
       <c r="D69" t="n">
-        <v>10.44620860212597</v>
+        <v>0.5634157943258497</v>
       </c>
       <c r="E69" t="n">
-        <v>11.73931098976813</v>
+        <v>0.8981744556470782</v>
       </c>
       <c r="F69" t="n">
-        <v>4.817035514467205</v>
+        <v>11.20483103258609</v>
       </c>
       <c r="G69" t="n">
-        <v>4.56285405410825</v>
+        <v>14.87965454156519</v>
       </c>
       <c r="H69" t="n">
-        <v>4.747097082961396</v>
+        <v>5.171679367733256</v>
       </c>
       <c r="I69" t="n">
-        <v>3.759308650748028</v>
+        <v>4.478105468273852</v>
       </c>
       <c r="J69" t="n">
-        <v>5.200415061263515</v>
+        <v>4.58521261431201</v>
       </c>
       <c r="K69" t="n">
-        <v>3.049554957406589</v>
+        <v>2.947067695036624</v>
       </c>
     </row>
     <row r="70">
@@ -7157,35 +6482,23 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>5.702454115587538</v>
-      </c>
-      <c r="C70" t="n">
-        <v>9.524856486952743</v>
-      </c>
-      <c r="D70" t="n">
-        <v>10.67039089993443</v>
-      </c>
-      <c r="E70" t="n">
-        <v>12.49216613751533</v>
-      </c>
       <c r="F70" t="n">
-        <v>5.158025578521023</v>
+        <v>11.32540144081315</v>
       </c>
       <c r="G70" t="n">
-        <v>4.583809253028889</v>
+        <v>15.12479510677955</v>
       </c>
       <c r="H70" t="n">
-        <v>4.599119461218184</v>
+        <v>5.407995338079827</v>
       </c>
       <c r="I70" t="n">
-        <v>3.849679767751416</v>
+        <v>4.524396473262479</v>
       </c>
       <c r="J70" t="n">
-        <v>5.754601600967984</v>
+        <v>4.868692093902848</v>
       </c>
       <c r="K70" t="n">
-        <v>3.313332853980187</v>
+        <v>3.19866432035426</v>
       </c>
     </row>
     <row r="71">
@@ -7195,34 +6508,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5.709988025106098</v>
+        <v>4.220050263021954</v>
       </c>
       <c r="C71" t="n">
-        <v>9.840535450412307</v>
+        <v>-7.283170230788504</v>
       </c>
       <c r="D71" t="n">
-        <v>10.41910960138599</v>
+        <v>0.6433218424437587</v>
       </c>
       <c r="E71" t="n">
-        <v>12.29749063899287</v>
+        <v>0.9666560943254154</v>
       </c>
       <c r="F71" t="n">
-        <v>4.989819294757202</v>
+        <v>11.48329951844848</v>
       </c>
       <c r="G71" t="n">
-        <v>4.828949746904873</v>
+        <v>15.51182241253968</v>
       </c>
       <c r="H71" t="n">
-        <v>4.486129290209742</v>
+        <v>5.763692327828713</v>
       </c>
       <c r="I71" t="n">
-        <v>3.597551756027365</v>
+        <v>4.551418642579716</v>
       </c>
       <c r="J71" t="n">
-        <v>5.834580939304016</v>
+        <v>4.96319027298512</v>
       </c>
       <c r="K71" t="n">
-        <v>3.053724237424708</v>
+        <v>3.536425989476101</v>
       </c>
     </row>
     <row r="72">
@@ -7231,35 +6544,23 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>5.912241782596575</v>
-      </c>
-      <c r="C72" t="n">
-        <v>9.612473209345175</v>
-      </c>
-      <c r="D72" t="n">
-        <v>10.72816930295469</v>
-      </c>
-      <c r="E72" t="n">
-        <v>12.45344069327071</v>
-      </c>
       <c r="F72" t="n">
-        <v>4.688342209525636</v>
+        <v>11.8176865615788</v>
       </c>
       <c r="G72" t="n">
-        <v>4.919171944437846</v>
+        <v>15.50359679561841</v>
       </c>
       <c r="H72" t="n">
-        <v>4.690890563612017</v>
+        <v>5.910779581254142</v>
       </c>
       <c r="I72" t="n">
-        <v>3.448241990679491</v>
+        <v>4.548072804008076</v>
       </c>
       <c r="J72" t="n">
-        <v>5.599588335357724</v>
+        <v>5.150112546327681</v>
       </c>
       <c r="K72" t="n">
-        <v>2.925711750134016</v>
+        <v>3.538665527716366</v>
       </c>
     </row>
     <row r="73">
@@ -7268,35 +6569,23 @@
           <t>2025-10-17</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>6.084899527168484</v>
-      </c>
-      <c r="C73" t="n">
-        <v>10.25073204181142</v>
-      </c>
-      <c r="D73" t="n">
-        <v>10.75984447728475</v>
-      </c>
-      <c r="E73" t="n">
-        <v>12.41770050083159</v>
-      </c>
       <c r="F73" t="n">
-        <v>5.050307352840298</v>
+        <v>12.00166055974267</v>
       </c>
       <c r="G73" t="n">
-        <v>5.01365915059267</v>
+        <v>15.68918202735446</v>
       </c>
       <c r="H73" t="n">
-        <v>4.555440706518586</v>
+        <v>6.020936645627851</v>
       </c>
       <c r="I73" t="n">
-        <v>3.68182308089946</v>
+        <v>4.647363491858319</v>
       </c>
       <c r="J73" t="n">
-        <v>5.845870581205224</v>
+        <v>5.240684404320046</v>
       </c>
       <c r="K73" t="n">
-        <v>3.039861796141153</v>
+        <v>3.579966620806253</v>
       </c>
     </row>
     <row r="74">
@@ -7305,35 +6594,23 @@
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>6.53772487670718</v>
-      </c>
-      <c r="C74" t="n">
-        <v>10.58674635039198</v>
-      </c>
-      <c r="D74" t="n">
-        <v>11.55433855198211</v>
-      </c>
-      <c r="E74" t="n">
-        <v>12.86697859759315</v>
-      </c>
       <c r="F74" t="n">
-        <v>5.185516670020114</v>
+        <v>12.21593672751995</v>
       </c>
       <c r="G74" t="n">
-        <v>5.372567560168306</v>
+        <v>16.05938565792426</v>
       </c>
       <c r="H74" t="n">
-        <v>5.074625368512018</v>
+        <v>6.294922086681675</v>
       </c>
       <c r="I74" t="n">
-        <v>4.068715854966147</v>
+        <v>4.792785669427021</v>
       </c>
       <c r="J74" t="n">
-        <v>5.771040933744444</v>
+        <v>5.476302532383832</v>
       </c>
       <c r="K74" t="n">
-        <v>3.290616630665122</v>
+        <v>3.87720501100467</v>
       </c>
     </row>
     <row r="75">
@@ -7342,35 +6619,23 @@
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>6.493255435137446</v>
-      </c>
-      <c r="C75" t="n">
-        <v>11.0214264060553</v>
-      </c>
-      <c r="D75" t="n">
-        <v>11.94935432795013</v>
-      </c>
-      <c r="E75" t="n">
-        <v>12.86884722925453</v>
-      </c>
       <c r="F75" t="n">
-        <v>4.926091779719053</v>
+        <v>12.33342289969488</v>
       </c>
       <c r="G75" t="n">
-        <v>4.783660067761838</v>
+        <v>16.30380835851135</v>
       </c>
       <c r="H75" t="n">
-        <v>4.652384504616164</v>
+        <v>6.535075185265566</v>
       </c>
       <c r="I75" t="n">
-        <v>4.592833507612442</v>
+        <v>4.825988283302543</v>
       </c>
       <c r="J75" t="n">
-        <v>5.638458981154089</v>
+        <v>5.630874034379876</v>
       </c>
       <c r="K75" t="n">
-        <v>3.278275949583373</v>
+        <v>4.10936953113965</v>
       </c>
     </row>
     <row r="76">
@@ -7380,34 +6645,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>6.338287234891006</v>
+        <v>4.304557305275475</v>
       </c>
       <c r="C76" t="n">
-        <v>11.32050341096785</v>
+        <v>-7.187251705616619</v>
       </c>
       <c r="D76" t="n">
-        <v>12.24981561592161</v>
+        <v>0.7314535131620408</v>
       </c>
       <c r="E76" t="n">
-        <v>12.83319607691462</v>
+        <v>1.053276933573546</v>
       </c>
       <c r="F76" t="n">
-        <v>4.876752921885588</v>
+        <v>12.36776410006506</v>
       </c>
       <c r="G76" t="n">
-        <v>4.904598174894865</v>
+        <v>16.56252377410879</v>
       </c>
       <c r="H76" t="n">
-        <v>4.339155384429225</v>
+        <v>6.510032387586433</v>
       </c>
       <c r="I76" t="n">
-        <v>5.049133305120298</v>
+        <v>4.925378707190565</v>
       </c>
       <c r="J76" t="n">
-        <v>5.740067880873861</v>
+        <v>5.816717284733697</v>
       </c>
       <c r="K76" t="n">
-        <v>3.488649872074645</v>
+        <v>4.238024847889485</v>
       </c>
     </row>
     <row r="77">
@@ -7416,35 +6681,23 @@
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>6.651488228130509</v>
-      </c>
-      <c r="C77" t="n">
-        <v>11.43011491921519</v>
-      </c>
-      <c r="D77" t="n">
-        <v>12.23297718631392</v>
-      </c>
-      <c r="E77" t="n">
-        <v>12.25723691261896</v>
-      </c>
       <c r="F77" t="n">
-        <v>5.032393404134894</v>
+        <v>12.58167132883727</v>
       </c>
       <c r="G77" t="n">
-        <v>4.879368364254732</v>
+        <v>16.92152834329996</v>
       </c>
       <c r="H77" t="n">
-        <v>4.289383469884467</v>
+        <v>6.752091251772218</v>
       </c>
       <c r="I77" t="n">
-        <v>5.577023472593742</v>
+        <v>5.061421487494613</v>
       </c>
       <c r="J77" t="n">
-        <v>5.559504570647055</v>
+        <v>5.72957226646923</v>
       </c>
       <c r="K77" t="n">
-        <v>3.427076852295573</v>
+        <v>4.253873056509197</v>
       </c>
     </row>
     <row r="78">
@@ -7453,35 +6706,23 @@
           <t>2025-12-30</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>6.622333170628058</v>
-      </c>
-      <c r="C78" t="n">
-        <v>11.80625331168642</v>
-      </c>
-      <c r="D78" t="n">
-        <v>12.08509405628472</v>
-      </c>
-      <c r="E78" t="n">
-        <v>11.96630835241925</v>
-      </c>
       <c r="F78" t="n">
-        <v>5.315422613364039</v>
+        <v>12.57572551700718</v>
       </c>
       <c r="G78" t="n">
-        <v>5.079724982137835</v>
+        <v>17.16633477197979</v>
       </c>
       <c r="H78" t="n">
-        <v>4.585441926789093</v>
+        <v>6.637346775527959</v>
       </c>
       <c r="I78" t="n">
-        <v>5.813494968203283</v>
+        <v>5.064598808645456</v>
       </c>
       <c r="J78" t="n">
-        <v>5.363646935233026</v>
+        <v>5.883230820720575</v>
       </c>
       <c r="K78" t="n">
-        <v>3.632893397814605</v>
+        <v>4.401709790001259</v>
       </c>
     </row>
     <row r="79">
@@ -7490,35 +6731,23 @@
           <t>2026-01-14</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>6.919174025242167</v>
-      </c>
-      <c r="C79" t="n">
-        <v>12.02413421413823</v>
-      </c>
-      <c r="D79" t="n">
-        <v>12.31309369009223</v>
-      </c>
-      <c r="E79" t="n">
-        <v>12.43055011619952</v>
-      </c>
       <c r="F79" t="n">
-        <v>5.576731676796605</v>
+        <v>12.79598525654706</v>
       </c>
       <c r="G79" t="n">
-        <v>5.477468570806816</v>
+        <v>17.35603721408563</v>
       </c>
       <c r="H79" t="n">
-        <v>5.269358477755194</v>
+        <v>6.889679305524393</v>
       </c>
       <c r="I79" t="n">
-        <v>5.90443728393345</v>
+        <v>5.196271205067403</v>
       </c>
       <c r="J79" t="n">
-        <v>5.689243807521935</v>
+        <v>6.091585529244993</v>
       </c>
       <c r="K79" t="n">
-        <v>4.18246136593446</v>
+        <v>4.611111331452674</v>
       </c>
     </row>
     <row r="80">
@@ -7527,35 +6756,23 @@
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>6.867847514880658</v>
-      </c>
-      <c r="C80" t="n">
-        <v>12.23787545679108</v>
-      </c>
-      <c r="D80" t="n">
-        <v>12.18295558313956</v>
-      </c>
-      <c r="E80" t="n">
-        <v>12.31051552601171</v>
-      </c>
       <c r="F80" t="n">
-        <v>5.458115446969724</v>
+        <v>13.02135972447467</v>
       </c>
       <c r="G80" t="n">
-        <v>5.573215169905463</v>
+        <v>17.60117777929999</v>
       </c>
       <c r="H80" t="n">
-        <v>5.215848512784017</v>
+        <v>7.210513700529605</v>
       </c>
       <c r="I80" t="n">
-        <v>5.631290269746584</v>
+        <v>5.230801470350315</v>
       </c>
       <c r="J80" t="n">
-        <v>5.519831517438881</v>
+        <v>6.263557981011608</v>
       </c>
       <c r="K80" t="n">
-        <v>3.854312246619435</v>
+        <v>4.96124849250887</v>
       </c>
     </row>
     <row r="81">
@@ -7565,34 +6782,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>7.199969468902787</v>
+        <v>4.384463353393384</v>
       </c>
       <c r="C81" t="n">
-        <v>12.45085438537766</v>
+        <v>-7.267157753734528</v>
       </c>
       <c r="D81" t="n">
-        <v>12.16970587505256</v>
+        <v>0.8136292142066703</v>
       </c>
       <c r="E81" t="n">
-        <v>12.6138544428817</v>
+        <v>1.151233145635714</v>
       </c>
       <c r="F81" t="n">
-        <v>5.473367794166684</v>
+        <v>13.25508521467075</v>
       </c>
       <c r="G81" t="n">
-        <v>5.590602533044178</v>
+        <v>17.76121703333897</v>
       </c>
       <c r="H81" t="n">
-        <v>5.256808070512434</v>
+        <v>7.137090013122871</v>
       </c>
       <c r="I81" t="n">
-        <v>5.729434027912449</v>
+        <v>5.322868115880694</v>
       </c>
       <c r="J81" t="n">
-        <v>5.104305402003306</v>
+        <v>6.372822275999876</v>
       </c>
       <c r="K81" t="n">
-        <v>3.640305166117386</v>
+        <v>5.148037529644254</v>
       </c>
     </row>
     <row r="82">
@@ -7601,35 +6818,23 @@
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>7.402009647186338</v>
-      </c>
-      <c r="C82" t="n">
-        <v>12.42615358075498</v>
-      </c>
-      <c r="D82" t="n">
-        <v>12.31806614136626</v>
-      </c>
-      <c r="E82" t="n">
-        <v>12.69348005043918</v>
-      </c>
       <c r="F82" t="n">
-        <v>5.402564107806994</v>
+        <v>13.36909115529383</v>
       </c>
       <c r="G82" t="n">
-        <v>5.616679806948205</v>
+        <v>17.89603970997845</v>
       </c>
       <c r="H82" t="n">
-        <v>5.251365240192407</v>
+        <v>7.302353422339712</v>
       </c>
       <c r="I82" t="n">
-        <v>5.680386435402722</v>
+        <v>5.446860488955131</v>
       </c>
       <c r="J82" t="n">
-        <v>4.677497915479158</v>
+        <v>6.572982320068097</v>
       </c>
       <c r="K82" t="n">
-        <v>3.832862604445082</v>
+        <v>5.418911767175433</v>
       </c>
     </row>
     <row r="83">
@@ -7638,35 +6843,23 @@
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>7.134575283033844</v>
-      </c>
-      <c r="C83" t="n">
-        <v>12.84879018060347</v>
-      </c>
-      <c r="D83" t="n">
-        <v>12.69397819405692</v>
-      </c>
-      <c r="E83" t="n">
-        <v>12.82509274933194</v>
-      </c>
       <c r="F83" t="n">
-        <v>4.956281820084378</v>
+        <v>13.54269134287924</v>
       </c>
       <c r="G83" t="n">
-        <v>5.491057258236317</v>
+        <v>18.10015342198409</v>
       </c>
       <c r="H83" t="n">
-        <v>5.223913327341125</v>
+        <v>7.320739179956525</v>
       </c>
       <c r="I83" t="n">
-        <v>5.742893836593822</v>
+        <v>5.614910768212689</v>
       </c>
       <c r="J83" t="n">
-        <v>4.805149951059162</v>
+        <v>6.734843180662151</v>
       </c>
       <c r="K83" t="n">
-        <v>4.489995531619948</v>
+        <v>5.411815600529855</v>
       </c>
     </row>
     <row r="84">
@@ -7675,35 +6868,110 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>6.982868855763475</v>
-      </c>
-      <c r="C84" t="n">
-        <v>12.61088366549238</v>
-      </c>
-      <c r="D84" t="n">
-        <v>12.68336300003863</v>
-      </c>
-      <c r="E84" t="n">
-        <v>13.12753206951975</v>
-      </c>
       <c r="F84" t="n">
-        <v>4.827195672260159</v>
+        <v>13.52480601083049</v>
       </c>
       <c r="G84" t="n">
-        <v>5.843515167859166</v>
+        <v>18.14987934592102</v>
       </c>
       <c r="H84" t="n">
-        <v>5.269115387256013</v>
+        <v>7.110135601393592</v>
       </c>
       <c r="I84" t="n">
-        <v>5.88023286671844</v>
+        <v>5.535735304355676</v>
       </c>
       <c r="J84" t="n">
-        <v>4.288416601156503</v>
+        <v>6.850928365299492</v>
       </c>
       <c r="K84" t="n">
-        <v>4.688093547394293</v>
+        <v>5.499661478109523</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4.470160870197069</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-7.344850850621079</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.7242523275149148</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.220200529099721</v>
+      </c>
+      <c r="F85" t="n">
+        <v>13.76872372879246</v>
+      </c>
+      <c r="G85" t="n">
+        <v>18.22829546483783</v>
+      </c>
+      <c r="H85" t="n">
+        <v>7.455143425513562</v>
+      </c>
+      <c r="I85" t="n">
+        <v>5.505462044204545</v>
+      </c>
+      <c r="J85" t="n">
+        <v>7.049003470931835</v>
+      </c>
+      <c r="K85" t="n">
+        <v>5.431149735020553</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>14.0844828613811</v>
+      </c>
+      <c r="G86" t="n">
+        <v>18.41698212880239</v>
+      </c>
+      <c r="H86" t="n">
+        <v>7.760608595167917</v>
+      </c>
+      <c r="I86" t="n">
+        <v>5.682947992978067</v>
+      </c>
+      <c r="J86" t="n">
+        <v>7.161349807365459</v>
+      </c>
+      <c r="K86" t="n">
+        <v>5.405805838346918</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>14.27227791857306</v>
+      </c>
+      <c r="G87" t="n">
+        <v>18.59232459455582</v>
+      </c>
+      <c r="H87" t="n">
+        <v>8.093297023866191</v>
+      </c>
+      <c r="I87" t="n">
+        <v>5.888011561176183</v>
+      </c>
+      <c r="J87" t="n">
+        <v>7.232544157602599</v>
+      </c>
+      <c r="K87" t="n">
+        <v>5.442064457963623</v>
       </c>
     </row>
   </sheetData>

--- a/output/multi_factor_reports/factor_collinearity_report_P10.xlsx
+++ b/output/multi_factor_reports/factor_collinearity_report_P10.xlsx
@@ -190,12 +190,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$B$2:$B$86</f>
+              <f>'corr_series'!$B$2:$B$87</f>
             </numRef>
           </val>
         </ser>
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$C$2:$C$86</f>
+              <f>'corr_series'!$C$2:$C$87</f>
             </numRef>
           </val>
         </ser>
@@ -254,12 +254,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$D$2:$D$86</f>
+              <f>'corr_series'!$D$2:$D$87</f>
             </numRef>
           </val>
         </ser>
@@ -286,12 +286,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$E$2:$E$86</f>
+              <f>'corr_series'!$E$2:$E$87</f>
             </numRef>
           </val>
         </ser>
@@ -318,12 +318,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$F$2:$F$86</f>
+              <f>'corr_series'!$F$2:$F$87</f>
             </numRef>
           </val>
         </ser>
@@ -350,12 +350,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$G$2:$G$86</f>
+              <f>'corr_series'!$G$2:$G$87</f>
             </numRef>
           </val>
         </ser>
@@ -382,12 +382,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$H$2:$H$86</f>
+              <f>'corr_series'!$H$2:$H$87</f>
             </numRef>
           </val>
         </ser>
@@ -414,12 +414,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$I$2:$I$86</f>
+              <f>'corr_series'!$I$2:$I$87</f>
             </numRef>
           </val>
         </ser>
@@ -446,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$J$2:$J$86</f>
+              <f>'corr_series'!$J$2:$J$87</f>
             </numRef>
           </val>
         </ser>
@@ -478,12 +478,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'corr_series'!$A$2:$A$86</f>
+              <f>'corr_series'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'corr_series'!$K$2:$K$86</f>
+              <f>'corr_series'!$K$2:$K$87</f>
             </numRef>
           </val>
         </ser>
@@ -520,8 +520,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.523671765789401"/>
-          <min val="-0.4280002107059264"/>
+          <max val="0.6974468395508909"/>
+          <min val="-0.4408724383919627"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -598,12 +598,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$B$2:$B$86</f>
+              <f>'cum_corr'!$B$2:$B$87</f>
             </numRef>
           </val>
         </ser>
@@ -630,12 +630,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$C$2:$C$86</f>
+              <f>'cum_corr'!$C$2:$C$87</f>
             </numRef>
           </val>
         </ser>
@@ -662,12 +662,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$D$2:$D$86</f>
+              <f>'cum_corr'!$D$2:$D$87</f>
             </numRef>
           </val>
         </ser>
@@ -694,12 +694,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$E$2:$E$86</f>
+              <f>'cum_corr'!$E$2:$E$87</f>
             </numRef>
           </val>
         </ser>
@@ -726,12 +726,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$F$2:$F$86</f>
+              <f>'cum_corr'!$F$2:$F$87</f>
             </numRef>
           </val>
         </ser>
@@ -758,12 +758,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$G$2:$G$86</f>
+              <f>'cum_corr'!$G$2:$G$87</f>
             </numRef>
           </val>
         </ser>
@@ -790,12 +790,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$H$2:$H$86</f>
+              <f>'cum_corr'!$H$2:$H$87</f>
             </numRef>
           </val>
         </ser>
@@ -822,12 +822,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$I$2:$I$86</f>
+              <f>'cum_corr'!$I$2:$I$87</f>
             </numRef>
           </val>
         </ser>
@@ -854,12 +854,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$J$2:$J$86</f>
+              <f>'cum_corr'!$J$2:$J$87</f>
             </numRef>
           </val>
         </ser>
@@ -886,12 +886,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'cum_corr'!$A$2:$A$86</f>
+              <f>'cum_corr'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'cum_corr'!$K$2:$K$86</f>
+              <f>'cum_corr'!$K$2:$K$87</f>
             </numRef>
           </val>
         </ser>
@@ -928,8 +928,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="20.67093435281098"/>
-          <min val="-9.468907141888863"/>
+          <max val="21.57888785668759"/>
+          <min val="-9.307073546294426"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>alpha075</t>
+          <t>alpha046</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1355,16 +1355,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.038951</v>
+        <v>0.0272</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.075352</v>
+        <v>0.074313</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-0.001175</v>
+        <v>0.063387</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.335272</v>
+        <v>0.32193</v>
       </c>
     </row>
     <row r="4">
@@ -1374,19 +1374,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.038951</v>
+        <v>0.0272</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.211093</v>
+        <v>0.219104</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.291451</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.264458</v>
+        <v>0.259285</v>
       </c>
     </row>
     <row r="5">
@@ -1396,41 +1396,41 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.075352</v>
+        <v>0.074313</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.211093</v>
+        <v>0.219104</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.182269</v>
+        <v>0.250993</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.260248</v>
+        <v>0.225824</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>alpha075</t>
+          <t>alpha046</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>-0.001175</v>
+        <v>0.063387</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.291451</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.182269</v>
+        <v>0.250993</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.118276</v>
+        <v>0.519636</v>
       </c>
     </row>
     <row r="7">
@@ -1440,16 +1440,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.335272</v>
+        <v>0.32193</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.264458</v>
+        <v>0.259285</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.260248</v>
+        <v>0.225824</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.118276</v>
+        <v>0.519636</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>alpha075</t>
+          <t>alpha046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1499,16 +1499,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.005978</v>
+        <v>0.033106</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.019739</v>
+        <v>-0.001046</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.030635</v>
+        <v>0.084207</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.081347</v>
+        <v>0.077624</v>
       </c>
     </row>
     <row r="13">
@@ -1518,19 +1518,19 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0.005978</v>
+        <v>0.033106</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.172416</v>
+        <v>0.170488</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.206298</v>
+        <v>0.107218</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.134888</v>
+        <v>0.135554</v>
       </c>
     </row>
     <row r="14">
@@ -1540,41 +1540,41 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0.019739</v>
+        <v>-0.001046</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.172416</v>
+        <v>0.170488</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.075514</v>
+        <v>0.100893</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.120542</v>
+        <v>0.121511</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>alpha075</t>
+          <t>alpha046</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>-0.030635</v>
+        <v>0.084207</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.206298</v>
+        <v>0.107218</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.075514</v>
+        <v>0.100893</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.090701</v>
+        <v>0.318833</v>
       </c>
     </row>
     <row r="16">
@@ -1584,16 +1584,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.081347</v>
+        <v>0.077624</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.134888</v>
+        <v>0.135554</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.120542</v>
+        <v>0.121511</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.090701</v>
+        <v>0.318833</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>1</v>
@@ -1730,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha075</t>
+          <t>alpha095 vs alpha046</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>alpha099 vs alpha075</t>
+          <t>alpha099 vs alpha046</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alpha027 vs alpha075</t>
+          <t>alpha027 vs alpha046</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>alpha075 vs alpha019</t>
+          <t>alpha046 vs alpha019</t>
         </is>
       </c>
     </row>
@@ -1803,13 +1803,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.2798584181713235</v>
+        <v>0.2937262937810178</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4283196239717975</v>
+        <v>0.1731024711161231</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0516305063644384</v>
+        <v>0.1949626043686179</v>
       </c>
     </row>
     <row r="5">
@@ -1819,22 +1819,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.207815658533888</v>
+        <v>-0.2078156585338879</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1558140140741855</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.210742639639999</v>
+        <v>-0.1581962983817549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2241960288922624</v>
+        <v>0.2378855548858317</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4266431924882633</v>
+        <v>0.1259216499517458</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06778969179620321</v>
+        <v>0.1046459058283275</v>
       </c>
     </row>
     <row r="6">
@@ -1844,22 +1841,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.210742639639999</v>
+        <v>0.2107426396399989</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1534471651531071</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.207815658533888</v>
+        <v>-0.1418105562875054</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2397687682138353</v>
+        <v>0.140268293000487</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3986697965571209</v>
+        <v>-0.07056421327435494</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1708531941164454</v>
+        <v>-0.02528462721767522</v>
       </c>
     </row>
     <row r="7">
@@ -1869,22 +1863,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.210742639639999</v>
+        <v>0.2107426396399989</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1464295251628444</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2049287691368834</v>
+        <v>-0.1464295251628442</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1984325587557798</v>
+        <v>0.1984325587557795</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2729407213268054</v>
+        <v>0.1316078883507791</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2086761069616935</v>
+        <v>-0.08039075941373966</v>
       </c>
     </row>
     <row r="8">
@@ -1897,19 +1888,16 @@
         <v>0.210742639639999</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1654456490020896</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.207815658533888</v>
+        <v>-0.1630111150704537</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2786410685279945</v>
+        <v>0.3227993688095452</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3427230046948359</v>
+        <v>0.1852992320774793</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09509179322780759</v>
+        <v>0.312714824573174</v>
       </c>
     </row>
     <row r="9">
@@ -1919,22 +1907,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2107426396399991</v>
+        <v>0.2107426396399989</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1534471651531071</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.2137114306713208</v>
+        <v>-0.1510947779720529</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06378792721514344</v>
+        <v>0.07872378625742851</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1610252427612625</v>
+        <v>-0.1618091260945719</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0139499286459505</v>
+        <v>0.04779745690135578</v>
       </c>
     </row>
     <row r="10">
@@ -1944,22 +1929,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2284634020970603</v>
+        <v>0.2284634020970602</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1562329432776296</v>
+        <v>-0.1537350115670228</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1542126632954505</v>
+        <v>0.1195876556350968</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1545240763314812</v>
+        <v>0.2005036260307262</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3990996969126015</v>
+        <v>0.1254847969044124</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03582538961237814</v>
+        <v>0.1338542331600603</v>
       </c>
     </row>
     <row r="11">
@@ -1969,22 +1954,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2107426396399991</v>
+        <v>0.210742639639999</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.1464295251628444</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.213711430671321</v>
+        <v>-0.1441147359394835</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1984325587557798</v>
+        <v>0.2144073904653614</v>
       </c>
       <c r="G11" t="n">
-        <v>0.230678932218139</v>
+        <v>0.0277662161119407</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02957286146562942</v>
+        <v>0.04620469410512932</v>
       </c>
     </row>
     <row r="12">
@@ -1997,19 +1979,16 @@
         <v>0.2167238245368195</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1487558855455509</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-0.1992687361255656</v>
+        <v>-0.1349519921383911</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1434112654129383</v>
+        <v>0.1454664804899016</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1173819524811741</v>
+        <v>-0.1224728222918526</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1534490522196439</v>
+        <v>0.1227503275356007</v>
       </c>
     </row>
     <row r="13">
@@ -2022,19 +2001,16 @@
         <v>-0.19649248577246</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1654456490020896</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-0.2107426396399989</v>
+        <v>-0.1581962983817549</v>
       </c>
       <c r="F13" t="n">
-        <v>0.265893091108908</v>
+        <v>0.3098579537797803</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3437874106520606</v>
+        <v>0.0912864227726668</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04865161513980852</v>
+        <v>0.03031948428729626</v>
       </c>
     </row>
     <row r="14">
@@ -2044,22 +2020,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1857122804094833</v>
+        <v>0.1857122804094832</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1630111150704538</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.1992687361255656</v>
+        <v>-0.151094777972053</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1972931825275606</v>
+        <v>0.2251917641290269</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1704171845992144</v>
+        <v>0.2139104105553632</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.03817550870178144</v>
+        <v>-0.0006884418384246017</v>
       </c>
     </row>
     <row r="15">
@@ -2069,22 +2042,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.210742639639999</v>
+        <v>0.2107426396399989</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1487558855455509</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.2020803228789259</v>
+        <v>-0.1395160212830312</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0938253856366657</v>
+        <v>0.1864847462881532</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09121160311979995</v>
+        <v>-0.02190463252424729</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09367325428706379</v>
+        <v>-0.02991148713754593</v>
       </c>
     </row>
     <row r="16">
@@ -2097,19 +2067,16 @@
         <v>-0.1992687361255656</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1418105562875052</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.19649248577246</v>
+        <v>-0.1372301599078029</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1387463320679484</v>
+        <v>0.1695513244383158</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3125982124676416</v>
+        <v>0.04929265754794831</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1181747071595148</v>
+        <v>-9.781359236828322e-05</v>
       </c>
     </row>
     <row r="17">
@@ -2122,19 +2089,16 @@
         <v>0.2167238245368195</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1654456490020896</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1937501051161881</v>
+        <v>-0.1630111150704537</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2434009585752097</v>
+        <v>0.2581893094760165</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1360427803040479</v>
+        <v>-0.03097846865939105</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01108977355623327</v>
+        <v>0.2638060960395275</v>
       </c>
     </row>
     <row r="18">
@@ -2147,19 +2111,16 @@
         <v>0.2020803228789259</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.1678996260264862</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.19649248577246</v>
+        <v>-0.1654456490020896</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0866143203260797</v>
+        <v>0.0730202875725629</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3834088727649029</v>
+        <v>-0.05586053383248003</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0642468946455559</v>
+        <v>0.0339168374629135</v>
       </c>
     </row>
     <row r="19">
@@ -2169,22 +2130,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2137114306713208</v>
+        <v>0.2137114306713209</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.1728700969412806</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0.2049287691368834</v>
+        <v>-0.1630111150704537</v>
       </c>
       <c r="F19" t="n">
-        <v>0.102805367978397</v>
+        <v>0.1029124323174433</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2164383561643832</v>
+        <v>0.1820937082151202</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07431473305415143</v>
+        <v>-0.119758028477839</v>
       </c>
     </row>
     <row r="20">
@@ -2197,19 +2155,19 @@
         <v>0.1450290087029011</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.1714985851425089</v>
+        <v>-0.1637999176320621</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1390201755279001</v>
+        <v>0.09050212805495189</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2041241452319315</v>
+        <v>0.2250860514065848</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3515497850322746</v>
+        <v>0.120605308635569</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03720878486172419</v>
+        <v>0.2384856805228162</v>
       </c>
     </row>
     <row r="21">
@@ -2222,19 +2180,19 @@
         <v>-0.1511265162864019</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1127390084824832</v>
+        <v>-0.09263101300455008</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2349475281971863</v>
+        <v>-0.03664452576943143</v>
       </c>
       <c r="F21" t="n">
-        <v>0.139484344472565</v>
+        <v>0.0941430671725924</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08935921591221256</v>
+        <v>0.03009778642621423</v>
       </c>
       <c r="I21" t="n">
-        <v>0.07080755158551552</v>
+        <v>0.02699415213671848</v>
       </c>
     </row>
     <row r="22">
@@ -2244,22 +2202,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1964924857724599</v>
+        <v>0.1964924857724598</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0883777519713818</v>
+        <v>-0.06944659376793955</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1409829232776846</v>
+        <v>-0.09475438053284511</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1402086024269046</v>
+        <v>0.1365752512400552</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2167781506164077</v>
+        <v>-0.05048105846852354</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06703064241990256</v>
+        <v>0.07473713297279257</v>
       </c>
     </row>
     <row r="23">
@@ -2272,19 +2230,16 @@
         <v>0.1737620117142288</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1482679679745704</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.1890202725795696</v>
+        <v>-0.1374293752410856</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1896181852559908</v>
+        <v>0.2152124506156314</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2451405652143584</v>
+        <v>0.1985482837925662</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.03429743293601418</v>
+        <v>0.1039320530275207</v>
       </c>
     </row>
     <row r="24">
@@ -2297,19 +2252,16 @@
         <v>0.1737620117142288</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1572352780113971</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-0.1838036555234517</v>
+        <v>-0.1482679679745704</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2678262482585571</v>
+        <v>0.2765265201649867</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3193809294418415</v>
+        <v>0.1451410712969786</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1144057961012094</v>
+        <v>0.1429362529496355</v>
       </c>
     </row>
     <row r="25">
@@ -2319,22 +2271,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.191682529939845</v>
+        <v>-0.1916825299398449</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1572352780113971</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-0.1890202725795695</v>
+        <v>-0.1527143493489882</v>
       </c>
       <c r="F25" t="n">
-        <v>0.108163553663221</v>
+        <v>0.1090058579139103</v>
       </c>
       <c r="G25" t="n">
-        <v>0.146909233176839</v>
+        <v>0.1285318280657484</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0912318739921827</v>
+        <v>0.130135473552985</v>
       </c>
     </row>
     <row r="26">
@@ -2344,22 +2293,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1351554025021827</v>
+        <v>0.1351554025021828</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1534471651531071</v>
+        <v>-0.1395160212830312</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1469231333008619</v>
+        <v>-0.05612996848608811</v>
       </c>
       <c r="F26" t="n">
-        <v>0.04328580800434648</v>
+        <v>0.0769400101789733</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09025059423198138</v>
+        <v>0.1502433760944025</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03304144213239659</v>
+        <v>0.2954970128871199</v>
       </c>
     </row>
     <row r="27">
@@ -2372,19 +2321,19 @@
         <v>-0.1209921139843045</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1703740878923699</v>
+        <v>-0.1558140140741855</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1380559421715735</v>
+        <v>0.1094079877643268</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2033983014507439</v>
+        <v>0.1705848056019203</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3294076345067942</v>
+        <v>0.2981869728912896</v>
       </c>
       <c r="I27" t="n">
-        <v>0.07710902799828705</v>
+        <v>0.163544067423597</v>
       </c>
     </row>
     <row r="28">
@@ -2397,28 +2346,25 @@
         <v>0.1890202725795695</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.124818709114169</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.1999040690647506</v>
+        <v>-0.1104090874835196</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1326663358276524</v>
+        <v>0.1248450141543724</v>
       </c>
       <c r="G28" t="n">
-        <v>0.329416600329223</v>
+        <v>0.3349263087984788</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3258084920561324</v>
+        <v>0.3258084920561323</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1084786811267815</v>
+        <v>-0.1179833088992816</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02127818383517276</v>
+        <v>0.006962507023841867</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2410006102968298</v>
+        <v>0.2722092158804773</v>
       </c>
     </row>
     <row r="29">
@@ -2428,34 +2374,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1380559421715736</v>
+        <v>0.1380559421715735</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.151094777972053</v>
+        <v>-0.1418105562875053</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1209921139843045</v>
+        <v>0.116972318708808</v>
       </c>
       <c r="E29" t="n">
         <v>0.08900190308630285</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2159752041826839</v>
+        <v>0.1910260386658285</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2170515421168798</v>
+        <v>0.1765437899398761</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2219526027575536</v>
+        <v>0.2219526027575535</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03766217885773536</v>
+        <v>0.1014682102012804</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2185997990251732</v>
+        <v>0.1684484031574332</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1864305816510212</v>
+        <v>0.589493496728811</v>
       </c>
     </row>
     <row r="30">
@@ -2468,28 +2414,25 @@
         <v>0.1890202725795695</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1482679679745703</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.1787211968653991</v>
+        <v>-0.1353020182983475</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2542045029375167</v>
+        <v>0.2319744633842508</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2167781506164077</v>
+        <v>0.1411368330666413</v>
       </c>
       <c r="H30" t="n">
         <v>0.1661654223669532</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.07802813450692216</v>
+        <v>0.2939897500795909</v>
       </c>
       <c r="J30" t="n">
-        <v>0.178719603119612</v>
+        <v>0.1164968406703322</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0911088376239388</v>
+        <v>0.1929404772603392</v>
       </c>
     </row>
     <row r="31">
@@ -2499,31 +2442,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.178721196865399</v>
+        <v>0.1787211968653991</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1527143493489882</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.1838036555234517</v>
+        <v>-0.1460703732631967</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0218840984886425</v>
+        <v>0.02414590982460445</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1590509441495327</v>
+        <v>0.02576011247906947</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0459220642194096</v>
+        <v>0.04592206421940961</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1140822876517114</v>
+        <v>0.08106508706735854</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.09588841367903547</v>
+        <v>-0.1232446830476908</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.03169823876956402</v>
+        <v>0.4487461640075358</v>
       </c>
     </row>
     <row r="32">
@@ -2536,28 +2476,25 @@
         <v>0.1838036555234517</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1331860599689335</v>
-      </c>
-      <c r="D32" t="n">
-        <v>-0.1890202725795695</v>
+        <v>-0.1227465847333876</v>
       </c>
       <c r="F32" t="n">
-        <v>0.258551362524562</v>
+        <v>0.2539754504269776</v>
       </c>
       <c r="G32" t="n">
-        <v>0.259150563370419</v>
+        <v>0.3245882557896115</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1667283013474745</v>
+        <v>0.1667283013474746</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2282078535113691</v>
+        <v>0.2481277783200164</v>
       </c>
       <c r="J32" t="n">
-        <v>0.01988109009130417</v>
+        <v>0.0753257869605387</v>
       </c>
       <c r="K32" t="n">
-        <v>0.07054324725566639</v>
+        <v>0.06797270283336361</v>
       </c>
     </row>
     <row r="33">
@@ -2570,28 +2507,25 @@
         <v>0.1812463559520403</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1504823163572114</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.1812463559520403</v>
+        <v>-0.1438886157672385</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2346879446681253</v>
+        <v>0.2249338527106093</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3831372549019613</v>
+        <v>0.1413713788054123</v>
       </c>
       <c r="H33" t="n">
         <v>0.1826134841491253</v>
       </c>
       <c r="I33" t="n">
-        <v>0.03321055820775363</v>
+        <v>0.006017064202970184</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0354517223751869</v>
+        <v>0.02367748268420092</v>
       </c>
       <c r="K33" t="n">
-        <v>0.08056354613917351</v>
+        <v>0.3798745089685405</v>
       </c>
     </row>
     <row r="34">
@@ -2607,25 +2541,25 @@
         <v>-0.1838036555234518</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1155419694359621</v>
+        <v>0.01662806319126938</v>
       </c>
       <c r="F34" t="n">
-        <v>0.08935921591221259</v>
+        <v>0.08935921591221258</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3014103138565244</v>
+        <v>0.1572152267644786</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.01188816754191122</v>
+        <v>-0.01188816754191113</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3151302167872919</v>
+        <v>0.04428260454124002</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1589721526516377</v>
+        <v>0.1582125933229769</v>
       </c>
       <c r="K34" t="n">
-        <v>0.04877261811377206</v>
+        <v>0.3009258917216516</v>
       </c>
     </row>
     <row r="35">
@@ -2635,34 +2569,34 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1661155106119584</v>
+        <v>0.1661155106119585</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.04007316022734394</v>
+        <v>-0.1093922496904076</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08363465972687385</v>
+        <v>0.1511257343193206</v>
       </c>
       <c r="E35" t="n">
         <v>0.1703088600627004</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1295408117845809</v>
+        <v>0.1400399069660162</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2586578018595246</v>
+        <v>-0.01742478831528567</v>
       </c>
       <c r="H35" t="n">
-        <v>0.02750445636984245</v>
+        <v>0.02750445636984244</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1110132589467214</v>
+        <v>0.1487504817342958</v>
       </c>
       <c r="J35" t="n">
-        <v>0.08693333796001949</v>
+        <v>0.1083322485058775</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.009033096526298339</v>
+        <v>0.2979896044796067</v>
       </c>
     </row>
     <row r="36">
@@ -2675,28 +2609,25 @@
         <v>0.1374444522110988</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1174440439029408</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.153735011567023</v>
+        <v>-0.112334534400814</v>
       </c>
       <c r="F36" t="n">
-        <v>0.09295722569028871</v>
+        <v>0.1111929292763296</v>
       </c>
       <c r="G36" t="n">
-        <v>0.08025905141196826</v>
+        <v>0.07046036357583495</v>
       </c>
       <c r="H36" t="n">
         <v>0.09184536734866695</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.07543087004899</v>
+        <v>0.04785073787832662</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1281254468576351</v>
+        <v>0.188732271265144</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.04255339588796631</v>
+        <v>0.2872315659047761</v>
       </c>
     </row>
     <row r="37">
@@ -2706,34 +2637,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.08839718243279208</v>
+        <v>0.0883971824327921</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.04693865581875915</v>
+        <v>-0.04007316022734381</v>
       </c>
       <c r="D37" t="n">
-        <v>0.06739652661281453</v>
+        <v>0.08362938025176651</v>
       </c>
       <c r="E37" t="n">
         <v>0.06048684647232055</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0309661768642666</v>
+        <v>0.07402332101976047</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1780469737892875</v>
+        <v>-0.005122384850001072</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.04216215741155647</v>
+        <v>-0.0421621574115565</v>
       </c>
       <c r="I37" t="n">
-        <v>0.07560410711501211</v>
+        <v>0.08683558853232626</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.01624336459342361</v>
+        <v>-0.05283676870897929</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1365782381520591</v>
+        <v>0.1262896441311337</v>
       </c>
     </row>
     <row r="38">
@@ -2746,28 +2677,25 @@
         <v>-0.133630620956212</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1157275124715688</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-0.1393864104874338</v>
+        <v>-0.1089902839136482</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2886751345948128</v>
+        <v>0.2878618594532406</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1712888475092462</v>
+        <v>0.2070014337072129</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2932104815960772</v>
+        <v>0.2932104815960771</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2833967633728306</v>
+        <v>0.2449010631365287</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2773662100794704</v>
+        <v>0.1869026314447499</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2038732981461446</v>
+        <v>0.5431393711986539</v>
       </c>
     </row>
     <row r="39">
@@ -2780,28 +2708,25 @@
         <v>-0.1413530862085967</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1226826002665548</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.1515960634700894</v>
+        <v>-0.1174440439029409</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2425234717545934</v>
+        <v>0.2574370076358481</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0642381511946728</v>
+        <v>0.0924752346919743</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1215130586467259</v>
+        <v>0.1215130586467258</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2123074326507425</v>
+        <v>0.00112209484449307</v>
       </c>
       <c r="J39" t="n">
-        <v>0.09064482702864127</v>
+        <v>0.0419383183615468</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.03339485983682655</v>
+        <v>0.3147485149246226</v>
       </c>
     </row>
     <row r="40">
@@ -2814,28 +2739,25 @@
         <v>-0.1393864104874338</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1157275124715689</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.1453648939082349</v>
+        <v>-0.107334697685273</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2258317958127242</v>
+        <v>0.2708527385642827</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1333725950203337</v>
+        <v>0.1870568368957714</v>
       </c>
       <c r="H40" t="n">
-        <v>0.09882455334321616</v>
+        <v>0.0988245533432161</v>
       </c>
       <c r="I40" t="n">
-        <v>0.008845748207237993</v>
+        <v>0.1503135100616758</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1746919552985211</v>
+        <v>0.1158560439950347</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.1689522642636974</v>
+        <v>0.185672696136769</v>
       </c>
     </row>
     <row r="41">
@@ -2848,28 +2770,25 @@
         <v>0.1393864104874338</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1157275124715689</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-0.1453648939082349</v>
+        <v>-0.1089902839136482</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1195580095479128</v>
+        <v>0.1827567511441421</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2734040273838261</v>
+        <v>0.07308405038036571</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2912531926230222</v>
+        <v>0.2912531926230223</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1348976601603782</v>
+        <v>0.1151594302641353</v>
       </c>
       <c r="J41" t="n">
-        <v>0.08432538731103996</v>
+        <v>0.1049047569737832</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2115458114414729</v>
+        <v>0.2520408024148225</v>
       </c>
     </row>
     <row r="42">
@@ -2882,28 +2801,25 @@
         <v>-0.133630620956212</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.1226826002665549</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.1603567451474549</v>
+        <v>-0.1174440439029408</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1478252354712509</v>
+        <v>0.102011783343331</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3230769230769232</v>
+        <v>0.08611467193080924</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1935229335810309</v>
+        <v>0.1935229335810308</v>
       </c>
       <c r="I42" t="n">
-        <v>0.06224220440894774</v>
+        <v>0.1933242579380296</v>
       </c>
       <c r="J42" t="n">
-        <v>0.119808543700518</v>
+        <v>0.1463083671172514</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3290220704642741</v>
+        <v>0.3031040405409911</v>
       </c>
     </row>
     <row r="43">
@@ -2913,31 +2829,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1413530862085967</v>
+        <v>0.1413530862085966</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1299038105676661</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-0.1413530862085967</v>
+        <v>-0.128070747644091</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1521814181454137</v>
+        <v>0.1388278396813196</v>
       </c>
       <c r="G43" t="n">
-        <v>0.09224441833137471</v>
+        <v>-0.03827315360460863</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0003713086380706885</v>
+        <v>0.0003713086380707083</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.06761428293248317</v>
+        <v>0.1996139092575999</v>
       </c>
       <c r="J43" t="n">
-        <v>0.143644939791271</v>
+        <v>0.1406073950803977</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.003310254980065936</v>
+        <v>-0.006479391655202822</v>
       </c>
     </row>
     <row r="44">
@@ -2950,28 +2863,25 @@
         <v>0.1413530862085966</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.1262567485345741</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.1433455447702487</v>
+        <v>-0.1174440439029408</v>
       </c>
       <c r="F44" t="n">
-        <v>0.04056407827850718</v>
+        <v>0.0006014883355978183</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1742365051333263</v>
+        <v>0.03688846926095696</v>
       </c>
       <c r="H44" t="n">
-        <v>0.006913929951764767</v>
+        <v>0.006913929951764728</v>
       </c>
       <c r="I44" t="n">
-        <v>0.05261376041853497</v>
+        <v>0.05706579191112363</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1025791564336875</v>
+        <v>0.1371563179016386</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.100887966781641</v>
+        <v>0.3437135603856583</v>
       </c>
     </row>
     <row r="45">
@@ -2981,34 +2891,34 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.07428966838182749</v>
+        <v>-0.07428966838182745</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.062836726043882</v>
+        <v>-0.05602474698879131</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1732347467810421</v>
+        <v>-0.006345099386942003</v>
       </c>
       <c r="E45" t="n">
         <v>0.1199229069488544</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0551723714684129</v>
+        <v>0.09555015392970502</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1905511689678471</v>
+        <v>0.03518411372481545</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1866585351862866</v>
+        <v>0.1866585351862864</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0380985550581057</v>
+        <v>0.06243904342876505</v>
       </c>
       <c r="J45" t="n">
-        <v>0.008622863480711614</v>
+        <v>-0.02684357173721798</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.1027314109573268</v>
+        <v>0.1038119245488622</v>
       </c>
     </row>
     <row r="46">
@@ -3021,28 +2931,25 @@
         <v>-0.1393864104874338</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1209208366638928</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-0.1433455447702487</v>
+        <v>-0.1123345344008139</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3541884654207529</v>
+        <v>0.3420352015349858</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3281098537518824</v>
+        <v>0.2969380550301052</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2606976572232881</v>
+        <v>0.2606976572232882</v>
       </c>
       <c r="I46" t="n">
-        <v>0.01733346320565998</v>
+        <v>0.1453484685112249</v>
       </c>
       <c r="J46" t="n">
-        <v>0.09891997809561481</v>
+        <v>0.1266605256593488</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2976829221081503</v>
+        <v>0.6150017554978287</v>
       </c>
     </row>
     <row r="47">
@@ -3055,28 +2962,25 @@
         <v>-0.1393864104874338</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1157275124715689</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.153735011567023</v>
+        <v>-0.1056892272937854</v>
       </c>
       <c r="F47" t="n">
-        <v>0.168266828252618</v>
+        <v>0.1386507484204357</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1215686274509805</v>
+        <v>-0.06140641032087227</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.05238484015392204</v>
+        <v>-0.05238484015392209</v>
       </c>
       <c r="I47" t="n">
-        <v>0.03321055820775356</v>
+        <v>0.178687217587262</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2532865850399696</v>
+        <v>0.3263985566284278</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.1104460976568725</v>
+        <v>0.2261724751617335</v>
       </c>
     </row>
     <row r="48">
@@ -3086,31 +2990,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1433455447702487</v>
+        <v>-0.1433455447702488</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.1244609720467531</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.1453648939082348</v>
+        <v>-0.1157275124715691</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4147024095410597</v>
+        <v>0.4335264760997324</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1610252427612625</v>
+        <v>0.258012015430246</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2528926675632091</v>
+        <v>0.2528926675632092</v>
       </c>
       <c r="I48" t="n">
-        <v>0.07907929734027659</v>
+        <v>0.1093332739468077</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1242439543530815</v>
+        <v>0.1546489146699552</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2317842616842407</v>
+        <v>0.2789191361468958</v>
       </c>
     </row>
     <row r="49">
@@ -3120,31 +3021,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1515960634700892</v>
+        <v>0.1515960634700893</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.02960775348761247</v>
+        <v>-0.02154336745161308</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1453648939082349</v>
+        <v>-0.001528587720358759</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3412439643944813</v>
+        <v>0.3424201353691254</v>
       </c>
       <c r="G49" t="n">
-        <v>0.203170909953546</v>
+        <v>0.1254813225230633</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3386695638070374</v>
+        <v>0.3386695638070376</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1632193833686187</v>
+        <v>0.06911954340519573</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2267323858247974</v>
+        <v>0.2179283007083183</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1536082042967861</v>
+        <v>0.3099643957761463</v>
       </c>
     </row>
     <row r="50">
@@ -3154,31 +3055,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.132321068799443</v>
+        <v>0.1323210687994431</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1056892272937856</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-0.1250781983185651</v>
+        <v>-0.1012609553666858</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2777341047142731</v>
+        <v>0.3176655454398467</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2374973057024743</v>
+        <v>0.1439519532909493</v>
       </c>
       <c r="H50" t="n">
         <v>0.2951856396038918</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1962559012456229</v>
+        <v>0.1238305081474506</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1923919490052155</v>
+        <v>0.1800078158383991</v>
       </c>
       <c r="K50" t="n">
-        <v>0.12394003857844</v>
+        <v>0.4298625450607859</v>
       </c>
     </row>
     <row r="51">
@@ -3191,28 +3089,25 @@
         <v>0.1233379585935061</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1056892272937855</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.1118242635572416</v>
+        <v>-0.09838071519901918</v>
       </c>
       <c r="F51" t="n">
-        <v>0.01695285228044751</v>
+        <v>-0.02810316594123786</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1774859487735229</v>
+        <v>0.04148683435324871</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3282412338910235</v>
+        <v>-0.3282412338910234</v>
       </c>
       <c r="I51" t="n">
-        <v>0.01460737753661614</v>
+        <v>0.2187059021257881</v>
       </c>
       <c r="J51" t="n">
-        <v>0.09238426986883645</v>
+        <v>0.06527982857321273</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.1365435025644474</v>
+        <v>0.230738944958959</v>
       </c>
     </row>
     <row r="52">
@@ -3222,34 +3117,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.03764616262105228</v>
+        <v>0.03764616262105232</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.02759710350482505</v>
+        <v>-0.02154336745161314</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.1537350115670228</v>
+        <v>0.1176465989600643</v>
       </c>
       <c r="E52" t="n">
-        <v>0.1266061158603291</v>
+        <v>0.1266061158603292</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1178141002631941</v>
+        <v>0.1076832055237</v>
       </c>
       <c r="G52" t="n">
-        <v>0.07346308866924531</v>
+        <v>0.1048535523995</v>
       </c>
       <c r="H52" t="n">
         <v>0.1378921435969462</v>
       </c>
       <c r="I52" t="n">
-        <v>0.05682310548199958</v>
+        <v>0.1074229691046932</v>
       </c>
       <c r="J52" t="n">
-        <v>0.1424261969524876</v>
+        <v>0.1371335740967083</v>
       </c>
       <c r="K52" t="n">
-        <v>0.10978143793521</v>
+        <v>0.4367052579856434</v>
       </c>
     </row>
     <row r="53">
@@ -3262,28 +3157,25 @@
         <v>0.1102635692839942</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.09415544714433857</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.1118242635572416</v>
+        <v>-0.08070466898086182</v>
       </c>
       <c r="F53" t="n">
-        <v>0.03992318480243996</v>
+        <v>-0.006970714806775202</v>
       </c>
       <c r="G53" t="n">
-        <v>0.002162375725080849</v>
+        <v>-0.02109370633453271</v>
       </c>
       <c r="H53" t="n">
         <v>-0.3623676606028003</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.09306258188811782</v>
+        <v>0.008018639028226918</v>
       </c>
       <c r="J53" t="n">
-        <v>0.06880735989696617</v>
+        <v>0.04589690507021008</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1375954127818002</v>
+        <v>0.08087562625755575</v>
       </c>
     </row>
     <row r="54">
@@ -3293,34 +3185,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.04167926980261508</v>
+        <v>0.139386410487434</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1244609720467533</v>
+        <v>-0.1174440439029408</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.1537350115670229</v>
+        <v>0.01524212136561521</v>
       </c>
       <c r="E54" t="n">
-        <v>0.07383551714670031</v>
+        <v>-0.1117570378429426</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1002055136808601</v>
+        <v>0.1041186743495366</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2429411764705884</v>
+        <v>0.1841095113932352</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3097539770062858</v>
+        <v>0.3097539770062859</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1285805403271234</v>
+        <v>-0.02398399858809618</v>
       </c>
       <c r="J54" t="n">
-        <v>0.3049116433213472</v>
+        <v>0.2311980656945798</v>
       </c>
       <c r="K54" t="n">
-        <v>0.154914366760297</v>
+        <v>0.3479989823262859</v>
       </c>
     </row>
     <row r="55">
@@ -3333,28 +3225,25 @@
         <v>0.1268454332888114</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1087213455089071</v>
-      </c>
-      <c r="D55" t="n">
-        <v>-0.1216235992670948</v>
+        <v>-0.1071968152299286</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2405044014395775</v>
+        <v>0.1694925919367845</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1344836439423284</v>
+        <v>0.2565327978457874</v>
       </c>
       <c r="H55" t="n">
         <v>0.2507759872010954</v>
       </c>
       <c r="I55" t="n">
-        <v>0.05108094442387968</v>
+        <v>0.2644515761504541</v>
       </c>
       <c r="J55" t="n">
-        <v>0.2399714959776694</v>
+        <v>0.2001065524683977</v>
       </c>
       <c r="K55" t="n">
-        <v>0.07502832441823606</v>
+        <v>0.5527068693365813</v>
       </c>
     </row>
     <row r="56">
@@ -3367,28 +3256,25 @@
         <v>0.1233379585935061</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1056892272937856</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-0.1118242635572417</v>
+        <v>-0.09981407910902304</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1860871227063087</v>
+        <v>0.1856696087039262</v>
       </c>
       <c r="G56" t="n">
-        <v>0.299274649534139</v>
+        <v>0.1106828011140285</v>
       </c>
       <c r="H56" t="n">
-        <v>0.03717049228284659</v>
+        <v>0.0371704922828467</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.01460737753661615</v>
+        <v>0.06510686512496887</v>
       </c>
       <c r="J56" t="n">
-        <v>0.05262139323661692</v>
+        <v>0.04675788927281604</v>
       </c>
       <c r="K56" t="n">
-        <v>0.06750912409524273</v>
+        <v>0.275724472753315</v>
       </c>
     </row>
     <row r="57">
@@ -3401,28 +3287,28 @@
         <v>0.1134042331421657</v>
       </c>
       <c r="C57" t="n">
-        <v>0.009188630773666192</v>
+        <v>0.01425965765074889</v>
       </c>
       <c r="D57" t="n">
-        <v>0.009188630773666178</v>
+        <v>0.0983897771006277</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2074251915366928</v>
+        <v>0.1962559012456229</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2355140195572865</v>
+        <v>0.1063130984619621</v>
       </c>
       <c r="H57" t="n">
         <v>0.06781595105649316</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2121212121212122</v>
+        <v>0.0156266727437842</v>
       </c>
       <c r="J57" t="n">
-        <v>0.1147433812621334</v>
+        <v>0.1623937727680042</v>
       </c>
       <c r="K57" t="n">
-        <v>0.2292316645957932</v>
+        <v>0.4001303762803127</v>
       </c>
     </row>
     <row r="58">
@@ -3435,28 +3321,25 @@
         <v>-0.09323508829909925</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.07446995802259677</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-0.08217570104462957</v>
+        <v>-0.07237920675576852</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1188591033014006</v>
+        <v>0.1222924763921006</v>
       </c>
       <c r="G58" t="n">
-        <v>0.2343137522464546</v>
+        <v>0.005529388142398848</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.02050648155456843</v>
+        <v>-0.02050648155456842</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2299562076188008</v>
+        <v>-0.03311351913625107</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1816420489139354</v>
+        <v>0.1667667807449416</v>
       </c>
       <c r="K58" t="n">
-        <v>0.0152123139361088</v>
+        <v>-0.02274738645053313</v>
       </c>
     </row>
     <row r="59">
@@ -3466,31 +3349,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.08333333333333325</v>
+        <v>0.08333333333333326</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.07341911803280055</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.08103348431673224</v>
+        <v>-0.07033025476334581</v>
       </c>
       <c r="F59" t="n">
-        <v>0.07855056176627598</v>
+        <v>0.06516475582592497</v>
       </c>
       <c r="G59" t="n">
-        <v>0.04873753042238239</v>
+        <v>-0.1021575146198749</v>
       </c>
       <c r="H59" t="n">
         <v>-0.206084593262753</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.002369749752739528</v>
+        <v>-0.03474285792516433</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.04448422977261062</v>
+        <v>-0.06320984501571503</v>
       </c>
       <c r="K59" t="n">
-        <v>0.3208917014082571</v>
+        <v>0.2063144849284884</v>
       </c>
     </row>
     <row r="60">
@@ -3500,34 +3380,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.0008328753777787323</v>
+        <v>0.08333333333333323</v>
       </c>
       <c r="C60" t="n">
-        <v>0.01425965765074887</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-0.0041668229254563</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-0.0244635374620877</v>
+        <v>-0.07341911803280055</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1048095705503215</v>
+        <v>-0.09078708143840929</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1606968372561283</v>
+        <v>-0.168033149163658</v>
       </c>
       <c r="H60" t="n">
         <v>-0.1386722827267753</v>
       </c>
       <c r="I60" t="n">
-        <v>0.01123619279052928</v>
+        <v>0.09340856472353309</v>
       </c>
       <c r="J60" t="n">
-        <v>0.09556797093229463</v>
+        <v>0.12706172625978</v>
       </c>
       <c r="K60" t="n">
-        <v>0.0159192080784544</v>
+        <v>0.3719652732562254</v>
       </c>
     </row>
     <row r="61">
@@ -3537,31 +3411,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.08569751680368508</v>
+        <v>-0.08569751680368515</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.07134974196115186</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.08103348431673225</v>
+        <v>-0.06932028853554488</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1805898160095151</v>
+        <v>0.1536103463398144</v>
       </c>
       <c r="G61" t="n">
-        <v>0.03425998696441809</v>
+        <v>0.2775867391699406</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1099616682522261</v>
+        <v>0.1099616682522262</v>
       </c>
       <c r="I61" t="n">
-        <v>0.02697017918001057</v>
+        <v>0.06930585444109781</v>
       </c>
       <c r="J61" t="n">
-        <v>0.04846678256791465</v>
+        <v>0.0397620121145748</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.2824171813644292</v>
+        <v>0.3961593366160344</v>
       </c>
     </row>
     <row r="62">
@@ -3571,31 +3442,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.07990604811790902</v>
+        <v>0.07990604811790904</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.06932028853554484</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-0.07990604811790902</v>
+        <v>-0.06536687218393283</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1021083864276044</v>
+        <v>0.1062450665456986</v>
       </c>
       <c r="G62" t="n">
-        <v>0.458039215686275</v>
+        <v>0.2425732089397062</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3307156750672215</v>
+        <v>0.3307156750672212</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.04507127994655973</v>
+        <v>-0.02208838771044699</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.04252651903248619</v>
+        <v>-0.02446257121299245</v>
       </c>
       <c r="K62" t="n">
-        <v>0.2159498703239424</v>
+        <v>0.4741148882059507</v>
       </c>
     </row>
     <row r="63">
@@ -3605,34 +3473,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.0008328753777787229</v>
+        <v>-0.0008328753777787151</v>
       </c>
       <c r="C63" t="n">
-        <v>0.03006433534123327</v>
+        <v>0.03564349655273723</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.1102635692839942</v>
+        <v>0.124729982632624</v>
       </c>
       <c r="E63" t="n">
-        <v>0.09403533674948798</v>
+        <v>0.09403533674948802</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2542045029375168</v>
+        <v>0.2137825521404359</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2460281401407436</v>
+        <v>0.1293091429098599</v>
       </c>
       <c r="H63" t="n">
         <v>0.3717978019044921</v>
       </c>
       <c r="I63" t="n">
-        <v>0.06009623101612525</v>
+        <v>0.04686848743745854</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1602895460227629</v>
+        <v>0.1571007485499741</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.00822798951919637</v>
+        <v>0.4268889382010703</v>
       </c>
     </row>
     <row r="64">
@@ -3642,34 +3510,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.1102635692839942</v>
+        <v>0.009188630773666261</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1071968152299286</v>
+        <v>-0.102721992025739</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0008328753777787669</v>
+        <v>0.08351887167122082</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0399988756497339</v>
+        <v>0.07256183588607053</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1258635032831601</v>
+        <v>0.0807244761062626</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1467536274523734</v>
+        <v>-0.1101371825475505</v>
       </c>
       <c r="H64" t="n">
         <v>0.1794068048883942</v>
       </c>
       <c r="I64" t="n">
-        <v>0.06255012252977551</v>
+        <v>0.08998004978778705</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.01894479370166062</v>
+        <v>-0.006119955913069565</v>
       </c>
       <c r="K64" t="n">
-        <v>0.1785978438783266</v>
+        <v>0.1892662230850101</v>
       </c>
     </row>
     <row r="65">
@@ -3679,31 +3547,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.07990604811790901</v>
+        <v>0.07990604811790904</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.07446995802259679</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0.08450704225352117</v>
+        <v>-0.0703302547633458</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1398446572694943</v>
+        <v>0.1153658463916655</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2453977409111277</v>
+        <v>0.04529263752247166</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1668815229498265</v>
+        <v>0.1668815229498266</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.03605291618554286</v>
+        <v>0.1891084157620655</v>
       </c>
       <c r="J65" t="n">
-        <v>0.09696788531634978</v>
+        <v>0.125985759259241</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.1298707308797332</v>
+        <v>0.473395117638521</v>
       </c>
     </row>
     <row r="66">
@@ -3716,31 +3581,31 @@
         <v>0.1216235992670947</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.09838071519901896</v>
+        <v>-0.09276994905294821</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.004166822925456281</v>
+        <v>0.07691765549685739</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0729994845009882</v>
+        <v>0.07299948450098818</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2452585425996257</v>
+        <v>0.1894799489138807</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1897024421058346</v>
+        <v>0.1966724666795011</v>
       </c>
       <c r="H66" t="n">
         <v>0.2784558741902757</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1706121279836849</v>
+        <v>0.2253757481033278</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1076542177590761</v>
+        <v>0.09676668758444903</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1346583059980944</v>
+        <v>0.3229992120789645</v>
       </c>
     </row>
     <row r="67">
@@ -3750,31 +3615,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.08450704225352117</v>
+        <v>0.08450704225352119</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.07237920675576846</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0.08569751680368511</v>
+        <v>-0.07134974196115187</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2464057148024252</v>
+        <v>0.2893628423980049</v>
       </c>
       <c r="G67" t="n">
-        <v>0.3146155411422963</v>
+        <v>0.1178787218259339</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2187655271270719</v>
+        <v>0.218765527127072</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1453801274722676</v>
+        <v>0.1134397050021612</v>
       </c>
       <c r="J67" t="n">
-        <v>0.1934986966544018</v>
+        <v>0.2409177370652101</v>
       </c>
       <c r="K67" t="n">
-        <v>0.05644307784225475</v>
+        <v>0.4426811637816921</v>
       </c>
     </row>
     <row r="68">
@@ -3784,31 +3646,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.08217570104462957</v>
+        <v>0.08217570104462958</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.06932028853554484</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0.0766064266294869</v>
+        <v>-0.0683193978637673</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2390822511125512</v>
+        <v>0.2257778535676575</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2579587693405925</v>
+        <v>-0.01540120723845582</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.0005401940449005025</v>
+        <v>-0.000540194044900528</v>
       </c>
       <c r="I68" t="n">
-        <v>0.01040101934984686</v>
+        <v>0.1285178656057793</v>
       </c>
       <c r="J68" t="n">
-        <v>0.09337526539748435</v>
+        <v>0.05558020223569553</v>
       </c>
       <c r="K68" t="n">
-        <v>0.03265998972716215</v>
+        <v>0.3723137851846206</v>
       </c>
     </row>
     <row r="69">
@@ -3818,34 +3677,34 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.0008328753777784195</v>
+        <v>-0.0008328753777789333</v>
       </c>
       <c r="C69" t="n">
-        <v>0.01256212678475732</v>
+        <v>0.01940834977861456</v>
       </c>
       <c r="D69" t="n">
-        <v>0.002499115053433486</v>
+        <v>0.1204332478764677</v>
       </c>
       <c r="E69" t="n">
-        <v>0.07544214663174818</v>
+        <v>0.07544214663174817</v>
       </c>
       <c r="F69" t="n">
-        <v>0.218728730355693</v>
+        <v>0.2207878126242311</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3009195909681911</v>
+        <v>0.3166727323290923</v>
       </c>
       <c r="H69" t="n">
         <v>0.3068798410215121</v>
       </c>
       <c r="I69" t="n">
-        <v>0.07515352926796454</v>
+        <v>0.2482592030975533</v>
       </c>
       <c r="J69" t="n">
-        <v>0.06475170965266923</v>
+        <v>0.09670991903407797</v>
       </c>
       <c r="K69" t="n">
-        <v>0.2294442335976572</v>
+        <v>0.488776213104933</v>
       </c>
     </row>
     <row r="70">
@@ -3855,22 +3714,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.1205704082270613</v>
+        <v>0.1212252834461369</v>
       </c>
       <c r="G70" t="n">
-        <v>0.2451405652143583</v>
+        <v>0.07194174481359097</v>
       </c>
       <c r="H70" t="n">
         <v>0.2363159703465706</v>
       </c>
       <c r="I70" t="n">
-        <v>0.04629100498862761</v>
+        <v>0.1621651306439774</v>
       </c>
       <c r="J70" t="n">
-        <v>0.2834794795908391</v>
+        <v>0.3358006555396553</v>
       </c>
       <c r="K70" t="n">
-        <v>0.2515966253176367</v>
+        <v>0.2932343154920674</v>
       </c>
     </row>
     <row r="71">
@@ -3880,34 +3739,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.08690547593388662</v>
+        <v>0.08690547593388663</v>
       </c>
       <c r="C71" t="n">
-        <v>0.09456502606044032</v>
+        <v>-0.07033025476334583</v>
       </c>
       <c r="D71" t="n">
-        <v>0.07990604811790905</v>
+        <v>0.08074467214941052</v>
       </c>
       <c r="E71" t="n">
-        <v>0.06848163867833729</v>
+        <v>0.05492502569403366</v>
       </c>
       <c r="F71" t="n">
-        <v>0.157898077635332</v>
+        <v>0.2140965402292599</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3870273057601314</v>
+        <v>0.1385933188325413</v>
       </c>
       <c r="H71" t="n">
         <v>0.3556969897488861</v>
       </c>
       <c r="I71" t="n">
-        <v>0.02702216931723656</v>
+        <v>0.1418370311222529</v>
       </c>
       <c r="J71" t="n">
-        <v>0.09449817908227102</v>
+        <v>0.1475685384802354</v>
       </c>
       <c r="K71" t="n">
-        <v>0.3377616691218402</v>
+        <v>0.2156912817240277</v>
       </c>
     </row>
     <row r="72">
@@ -3917,22 +3776,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.334387043130316</v>
+        <v>0.3365044648890025</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.008225616921269052</v>
+        <v>0.1046630746805243</v>
       </c>
       <c r="H72" t="n">
         <v>0.1470872534254294</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.003345838571639537</v>
+        <v>0.02135961537364894</v>
       </c>
       <c r="J72" t="n">
-        <v>0.1869222733425607</v>
+        <v>0.1871611599472587</v>
       </c>
       <c r="K72" t="n">
-        <v>0.002239538240265456</v>
+        <v>0.2183832454087829</v>
       </c>
     </row>
     <row r="73">
@@ -3942,22 +3801,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.1839739981638681</v>
+        <v>0.1297852263285619</v>
       </c>
       <c r="G73" t="n">
-        <v>0.1855852317360563</v>
+        <v>0.2650541441707999</v>
       </c>
       <c r="H73" t="n">
         <v>0.1101570643737091</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09929068785024213</v>
+        <v>0.106706764163147</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0905718579923652</v>
+        <v>0.1472667117132984</v>
       </c>
       <c r="K73" t="n">
-        <v>0.04130109308988684</v>
+        <v>0.3037050960192058</v>
       </c>
     </row>
     <row r="74">
@@ -3967,22 +3826,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.2142761677772856</v>
+        <v>0.2282858928472341</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3702036305697977</v>
+        <v>0.1423357252108602</v>
       </c>
       <c r="H74" t="n">
         <v>0.2739854410538231</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1454221775687018</v>
+        <v>0.05961871920840531</v>
       </c>
       <c r="J74" t="n">
-        <v>0.2356181280637863</v>
+        <v>0.2834686638316494</v>
       </c>
       <c r="K74" t="n">
-        <v>0.2972383901984174</v>
+        <v>0.363771600531856</v>
       </c>
     </row>
     <row r="75">
@@ -3992,22 +3851,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.1174861721749233</v>
+        <v>0.08906615753530248</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2444227005870837</v>
+        <v>0.1579858247427836</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2401530985838919</v>
+        <v>0.2401530985838918</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03320261387552179</v>
+        <v>0.09253735579563704</v>
       </c>
       <c r="J75" t="n">
-        <v>0.1545715019960448</v>
+        <v>0.0872187601794483</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2321645201349792</v>
+        <v>0.4756599047921574</v>
       </c>
     </row>
     <row r="76">
@@ -4017,34 +3876,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.08450704225352114</v>
+        <v>0.08450704225352115</v>
       </c>
       <c r="C76" t="n">
-        <v>0.09591852517188472</v>
+        <v>0.09591852517188471</v>
       </c>
       <c r="D76" t="n">
-        <v>0.08813167071828207</v>
+        <v>0.07074941387257684</v>
       </c>
       <c r="E76" t="n">
-        <v>0.08662083924813022</v>
+        <v>0.08662083924813026</v>
       </c>
       <c r="F76" t="n">
-        <v>0.03434120037018094</v>
+        <v>0.03434120037018097</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2587154155974462</v>
+        <v>0.1056381116843522</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.02504279767913358</v>
+        <v>-0.02504279767913357</v>
       </c>
       <c r="I76" t="n">
-        <v>0.09939042388802176</v>
+        <v>0.031872918948741</v>
       </c>
       <c r="J76" t="n">
         <v>0.1858432503538201</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1286553167498355</v>
+        <v>0.3165220049793157</v>
       </c>
     </row>
     <row r="77">
@@ -4054,22 +3913,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.2139072287722145</v>
+        <v>0.2130780139055367</v>
       </c>
       <c r="G77" t="n">
-        <v>0.35900456919117</v>
+        <v>0.1615959558935857</v>
       </c>
       <c r="H77" t="n">
-        <v>0.2420588641857856</v>
+        <v>0.2420588641857857</v>
       </c>
       <c r="I77" t="n">
-        <v>0.136042780304048</v>
+        <v>0.0005281423942024455</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.08714501826446729</v>
+        <v>-0.05773316969938153</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0158482086197114</v>
+        <v>0.3508906619141646</v>
       </c>
     </row>
     <row r="78">
@@ -4079,22 +3938,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>-0.005945811830095973</v>
+        <v>0.06778969179620321</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2448064286798311</v>
+        <v>0.01993380777392787</v>
       </c>
       <c r="H78" t="n">
         <v>-0.1147444762442587</v>
       </c>
       <c r="I78" t="n">
-        <v>0.003177321150842809</v>
+        <v>0.06914400876926441</v>
       </c>
       <c r="J78" t="n">
-        <v>0.153658554251345</v>
+        <v>0.1133708307620115</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1478367334920618</v>
+        <v>0.2217069109244709</v>
       </c>
     </row>
     <row r="79">
@@ -4104,22 +3963,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0.2202597395398871</v>
+        <v>0.2335754309273655</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1897024421058349</v>
+        <v>0.2214877419828668</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2523325299964341</v>
+        <v>0.252332529996434</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1316723964219479</v>
+        <v>0.1251240172033583</v>
       </c>
       <c r="J79" t="n">
-        <v>0.2083547085244181</v>
+        <v>0.2274607975205767</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2094015414514154</v>
+        <v>0.4130086944071192</v>
       </c>
     </row>
     <row r="80">
@@ -4129,22 +3988,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.2253744679276044</v>
+        <v>0.2516297091929393</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2451405652143584</v>
+        <v>0.1190458442489613</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3208343950052108</v>
+        <v>0.3208343950052109</v>
       </c>
       <c r="I80" t="n">
-        <v>0.03453026528291139</v>
+        <v>0.1490264267277116</v>
       </c>
       <c r="J80" t="n">
-        <v>0.1719724517666151</v>
+        <v>0.2111235625440701</v>
       </c>
       <c r="K80" t="n">
-        <v>0.3501371610561964</v>
+        <v>0.6189420617617286</v>
       </c>
     </row>
     <row r="81">
@@ -4157,31 +4016,31 @@
         <v>0.07990604811790908</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.07990604811790911</v>
+        <v>-0.07769309688655061</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0821757010446296</v>
+        <v>0.08173821527657278</v>
       </c>
       <c r="E81" t="n">
-        <v>0.09795621206216791</v>
+        <v>0.09795621206216784</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2337254901960787</v>
+        <v>0.2355140195572866</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1600392540389778</v>
+        <v>0.002286419939286167</v>
       </c>
       <c r="H81" t="n">
         <v>-0.07342368740673366</v>
       </c>
       <c r="I81" t="n">
-        <v>0.09206664553037903</v>
+        <v>0.1664064227086939</v>
       </c>
       <c r="J81" t="n">
-        <v>0.109264294988267</v>
+        <v>0.1679484893896905</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1867890371353841</v>
+        <v>0.4180393717201797</v>
       </c>
     </row>
     <row r="82">
@@ -4191,22 +4050,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.1140059406230855</v>
+        <v>0.1559026728581495</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1348226766394786</v>
+        <v>0.1690260062390218</v>
       </c>
       <c r="H82" t="n">
-        <v>0.16526340921684</v>
+        <v>0.1652634092168399</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1239923730744369</v>
+        <v>0.06082255920116105</v>
       </c>
       <c r="J82" t="n">
-        <v>0.2001600440682214</v>
+        <v>0.2122779830770629</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2708742375311791</v>
+        <v>0.1199421258337414</v>
       </c>
     </row>
     <row r="83">
@@ -4216,22 +4075,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.1736001875854013</v>
+        <v>0.1595006864608777</v>
       </c>
       <c r="G83" t="n">
-        <v>0.2041137120056486</v>
+        <v>0.06571705144052313</v>
       </c>
       <c r="H83" t="n">
-        <v>0.01838575761681316</v>
+        <v>0.01838575761681319</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1680502792575588</v>
+        <v>0.2103773999378265</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1618608605940533</v>
+        <v>0.179399551585347</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.007096166645578372</v>
+        <v>0.4202240346346371</v>
       </c>
     </row>
     <row r="84">
@@ -4241,22 +4100,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>-0.01788533204874311</v>
+        <v>-0.01788533204874322</v>
       </c>
       <c r="G84" t="n">
-        <v>0.04972592393692672</v>
+        <v>-0.03048452402302099</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.2106035785629322</v>
+        <v>-0.2106035785629324</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.07917546385701349</v>
+        <v>0.06153683337760462</v>
       </c>
       <c r="J84" t="n">
-        <v>0.1160851846373412</v>
+        <v>0.1055086949738591</v>
       </c>
       <c r="K84" t="n">
-        <v>0.08784587757966851</v>
+        <v>0.1811826203625848</v>
       </c>
     </row>
     <row r="85">
@@ -4265,35 +4124,23 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>0.08569751680368512</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.07769309688655057</v>
-      </c>
-      <c r="D85" t="n">
-        <v>-0.08937688669175563</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0.06896738346400709</v>
-      </c>
       <c r="F85" t="n">
-        <v>0.2439177179619692</v>
+        <v>0.2298642499074587</v>
       </c>
       <c r="G85" t="n">
-        <v>0.07841611891680945</v>
+        <v>0.2383098069891619</v>
       </c>
       <c r="H85" t="n">
-        <v>0.3450078241199699</v>
+        <v>0.3450078241199694</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.03027326015113104</v>
+        <v>0.1494497387756616</v>
       </c>
       <c r="J85" t="n">
-        <v>0.1980751056323429</v>
+        <v>0.1914110209096992</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.06851174308897001</v>
+        <v>0.3548311290280645</v>
       </c>
     </row>
     <row r="86">
@@ -4303,22 +4150,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.3157591325886372</v>
+        <v>0.3593681567984275</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1886866639645648</v>
+        <v>0.07906700578074256</v>
       </c>
       <c r="H86" t="n">
-        <v>0.3054651696543554</v>
+        <v>0.3054651696543556</v>
       </c>
       <c r="I86" t="n">
-        <v>0.177485948773523</v>
+        <v>0.0712329393455719</v>
       </c>
       <c r="J86" t="n">
-        <v>0.1123463364336247</v>
+        <v>0.1107417531936869</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.02534389667363553</v>
+        <v>0.1438855454832004</v>
       </c>
     </row>
     <row r="87">
@@ -4331,19 +4178,44 @@
         <v>0.1877950571919586</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1753424657534245</v>
+        <v>0.06415094699695939</v>
       </c>
       <c r="H87" t="n">
-        <v>0.3326884286982739</v>
+        <v>0.3326884286982736</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2050635681981158</v>
+        <v>0.08549395362627456</v>
       </c>
       <c r="J87" t="n">
-        <v>0.07119435023714031</v>
+        <v>0.0717362958662717</v>
       </c>
       <c r="K87" t="n">
-        <v>0.03625861961670493</v>
+        <v>0.3092830825930277</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0.1108486128284266</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-0.01820070543379673</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.1755142731084054</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.04633638961121415</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.08041120451552063</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.3795649878389025</v>
       </c>
     </row>
   </sheetData>
@@ -4358,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4377,7 +4249,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>alpha095 vs alpha075</t>
+          <t>alpha095 vs alpha046</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -4392,7 +4264,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>alpha099 vs alpha075</t>
+          <t>alpha099 vs alpha046</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -4402,7 +4274,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alpha027 vs alpha075</t>
+          <t>alpha027 vs alpha046</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -4412,7 +4284,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>alpha075 vs alpha019</t>
+          <t>alpha046 vs alpha019</t>
         </is>
       </c>
     </row>
@@ -4431,13 +4303,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.2798584181713235</v>
+        <v>0.2937262937810178</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4283196239717975</v>
+        <v>0.1731024711161231</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0516305063644384</v>
+        <v>0.1949626043686179</v>
       </c>
     </row>
     <row r="5">
@@ -4447,22 +4319,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.207815658533888</v>
+        <v>-0.2078156585338879</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1558140140741855</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.210742639639999</v>
+        <v>-0.1581962983817549</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5040544470635858</v>
+        <v>0.5316118486668495</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8549628164600608</v>
+        <v>0.299024121067869</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1194201981606416</v>
+        <v>0.2996085101969455</v>
       </c>
     </row>
     <row r="6">
@@ -4472,22 +4341,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002926981106110976</v>
+        <v>0.002926981106110949</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.3092611792272927</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.002926981106111004</v>
+        <v>-0.3000068546692604</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7438232152774211</v>
+        <v>0.6718801416673365</v>
       </c>
       <c r="G6" t="n">
-        <v>1.253632613017182</v>
+        <v>0.228459907793514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.290273392277087</v>
+        <v>0.2743238829792702</v>
       </c>
     </row>
     <row r="7">
@@ -4497,22 +4363,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.21366962074611</v>
+        <v>0.2136696207461098</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.4556907043901371</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2020017880307724</v>
+        <v>-0.4464363798321046</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9422557740332009</v>
+        <v>0.8703127004231159</v>
       </c>
       <c r="G7" t="n">
-        <v>1.526573334343987</v>
+        <v>0.3600677961442931</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4989494992387805</v>
+        <v>0.1939331235655306</v>
       </c>
     </row>
     <row r="8">
@@ -4522,22 +4385,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.424412260386109</v>
+        <v>0.4244122603861088</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.6211363533922267</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4098174465646605</v>
+        <v>-0.6094474949025583</v>
       </c>
       <c r="F8" t="n">
-        <v>1.220896842561195</v>
+        <v>1.193112069232661</v>
       </c>
       <c r="G8" t="n">
-        <v>1.869296339038823</v>
+        <v>0.5453670282217724</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5940412924665881</v>
+        <v>0.5066479481387045</v>
       </c>
     </row>
     <row r="9">
@@ -4547,22 +4407,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6351549000261081</v>
+        <v>0.6351549000261076</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.7745835185453338</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.1961060158933396</v>
+        <v>-0.7605422728746113</v>
       </c>
       <c r="F9" t="n">
-        <v>1.284684769776339</v>
+        <v>1.27183585549009</v>
       </c>
       <c r="G9" t="n">
-        <v>2.030321581800085</v>
+        <v>0.3835579021272005</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6079912211125386</v>
+        <v>0.5544454050400602</v>
       </c>
     </row>
     <row r="10">
@@ -4572,22 +4429,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8636183021231685</v>
+        <v>0.8636183021231678</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.9308164618229634</v>
+        <v>-0.9142772844416341</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3503186791887901</v>
+        <v>0.1195876556350968</v>
       </c>
       <c r="F10" t="n">
-        <v>1.43920884610782</v>
+        <v>1.472339481520816</v>
       </c>
       <c r="G10" t="n">
-        <v>2.429421278712687</v>
+        <v>0.5090426990316129</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6438166107249167</v>
+        <v>0.6882996382001205</v>
       </c>
     </row>
     <row r="11">
@@ -4600,19 +4457,16 @@
         <v>1.074360941763167</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.077245986985808</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.564030109860111</v>
+        <v>-1.058392020381118</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6376414048636</v>
+        <v>1.686746871986177</v>
       </c>
       <c r="G11" t="n">
-        <v>2.660100210930826</v>
+        <v>0.5368089151435537</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6733894721905461</v>
+        <v>0.7345043323052498</v>
       </c>
     </row>
     <row r="12">
@@ -4622,22 +4476,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.291084766299987</v>
+        <v>1.291084766299986</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.226001872531359</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.3647613737345454</v>
+        <v>-1.193344012519509</v>
       </c>
       <c r="F12" t="n">
-        <v>1.781052670276538</v>
+        <v>1.832213352476079</v>
       </c>
       <c r="G12" t="n">
-        <v>2.777482163411999</v>
+        <v>0.414336092851701</v>
       </c>
       <c r="I12" t="n">
-        <v>0.82683852441019</v>
+        <v>0.8572546598408506</v>
       </c>
     </row>
     <row r="13">
@@ -4647,22 +4498,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.094592280527527</v>
+        <v>1.094592280527526</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.391447521533448</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.1540187340945465</v>
+        <v>-1.351540310901264</v>
       </c>
       <c r="F13" t="n">
-        <v>2.046945761385446</v>
+        <v>2.142071306255859</v>
       </c>
       <c r="G13" t="n">
-        <v>3.12126957406406</v>
+        <v>0.5056225156243679</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7781869092703815</v>
+        <v>0.8875741441281468</v>
       </c>
     </row>
     <row r="14">
@@ -4675,19 +4523,16 @@
         <v>1.28030456093701</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.554458636603902</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.3532874702201122</v>
+        <v>-1.502635088873316</v>
       </c>
       <c r="F14" t="n">
-        <v>2.244238943913007</v>
+        <v>2.367263070384886</v>
       </c>
       <c r="G14" t="n">
-        <v>3.291686758663275</v>
+        <v>0.7195329261797311</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7400114005686</v>
+        <v>0.8868857022897222</v>
       </c>
     </row>
     <row r="15">
@@ -4700,19 +4545,16 @@
         <v>1.491047200577009</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.703214522149453</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.5553677930990382</v>
+        <v>-1.642151110156348</v>
       </c>
       <c r="F15" t="n">
-        <v>2.338064329549673</v>
+        <v>2.553747816673039</v>
       </c>
       <c r="G15" t="n">
-        <v>3.382898361783075</v>
+        <v>0.6976282936554838</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8336846548556638</v>
+        <v>0.8569742151521763</v>
       </c>
     </row>
     <row r="16">
@@ -4722,22 +4564,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.291778464451444</v>
+        <v>1.291778464451443</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.845025078436958</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.3588753073265781</v>
+        <v>-1.779381270064151</v>
       </c>
       <c r="F16" t="n">
-        <v>2.476810661617621</v>
+        <v>2.723299141111355</v>
       </c>
       <c r="G16" t="n">
-        <v>3.695496574250716</v>
+        <v>0.7469209512034322</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9518593620151785</v>
+        <v>0.856876401559808</v>
       </c>
     </row>
     <row r="17">
@@ -4747,22 +4586,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.508502288988263</v>
+        <v>1.508502288988262</v>
       </c>
       <c r="C17" t="n">
-        <v>-2.010470727439047</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.5526254124427663</v>
+        <v>-1.942392385134604</v>
       </c>
       <c r="F17" t="n">
-        <v>2.720211620192831</v>
+        <v>2.981488450587371</v>
       </c>
       <c r="G17" t="n">
-        <v>3.831539354554764</v>
+        <v>0.7159424825440411</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9629491355714118</v>
+        <v>1.120682497599335</v>
       </c>
     </row>
     <row r="18">
@@ -4772,22 +4608,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.710582611867189</v>
+        <v>1.710582611867188</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.178370353465533</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.7491178982152263</v>
+        <v>-2.107838034136694</v>
       </c>
       <c r="F18" t="n">
-        <v>2.806825940518911</v>
+        <v>3.054508738159934</v>
       </c>
       <c r="G18" t="n">
-        <v>4.214948227319667</v>
+        <v>0.6600819487115611</v>
       </c>
       <c r="I18" t="n">
-        <v>1.027196030216968</v>
+        <v>1.154599335062249</v>
       </c>
     </row>
     <row r="19">
@@ -4797,22 +4630,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.92429404253851</v>
+        <v>1.924294042538509</v>
       </c>
       <c r="C19" t="n">
-        <v>-2.351240450406814</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.5441891290783429</v>
+        <v>-2.270849149207148</v>
       </c>
       <c r="F19" t="n">
-        <v>2.909631308497308</v>
+        <v>3.157421170477377</v>
       </c>
       <c r="G19" t="n">
-        <v>4.43138658348405</v>
+        <v>0.8421756569266813</v>
       </c>
       <c r="I19" t="n">
-        <v>1.101510763271119</v>
+        <v>1.03484130658441</v>
       </c>
     </row>
     <row r="20">
@@ -4822,22 +4652,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.069323051241411</v>
+        <v>2.06932305124141</v>
       </c>
       <c r="C20" t="n">
-        <v>-2.522739035549323</v>
+        <v>-2.43464906683921</v>
       </c>
       <c r="D20" t="n">
-        <v>0.683209304606243</v>
+        <v>0.2100897836900487</v>
       </c>
       <c r="F20" t="n">
-        <v>3.113755453729239</v>
+        <v>3.382507221883962</v>
       </c>
       <c r="G20" t="n">
-        <v>4.782936368516324</v>
+        <v>0.9627809655622502</v>
       </c>
       <c r="I20" t="n">
-        <v>1.138719548132843</v>
+        <v>1.273326987107226</v>
       </c>
     </row>
     <row r="21">
@@ -4847,22 +4677,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.918196534955009</v>
+        <v>1.918196534955008</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.635478044031806</v>
+        <v>-2.52728007984376</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9181568328034292</v>
+        <v>0.1734452579206173</v>
       </c>
       <c r="F21" t="n">
-        <v>3.253239798201804</v>
+        <v>3.476650289056554</v>
       </c>
       <c r="G21" t="n">
-        <v>4.872295584428537</v>
+        <v>0.9928787519884644</v>
       </c>
       <c r="I21" t="n">
-        <v>1.209527099718359</v>
+        <v>1.300321139243945</v>
       </c>
     </row>
     <row r="22">
@@ -4872,22 +4702,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.114689020727469</v>
+        <v>2.114689020727468</v>
       </c>
       <c r="C22" t="n">
-        <v>-2.723855796003188</v>
+        <v>-2.596726673611699</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7771739095257446</v>
+        <v>0.07869087738777215</v>
       </c>
       <c r="F22" t="n">
-        <v>3.393448400628709</v>
+        <v>3.61322554029661</v>
       </c>
       <c r="G22" t="n">
-        <v>5.089073735044945</v>
+        <v>0.9423976935199408</v>
       </c>
       <c r="I22" t="n">
-        <v>1.276557742138261</v>
+        <v>1.375058272216737</v>
       </c>
     </row>
     <row r="23">
@@ -4897,22 +4727,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.288451032441698</v>
+        <v>2.288451032441697</v>
       </c>
       <c r="C23" t="n">
-        <v>-2.872123763977758</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.9661941821053143</v>
+        <v>-2.734156048852785</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5830665858847</v>
+        <v>3.828437990912241</v>
       </c>
       <c r="G23" t="n">
-        <v>5.334214300259303</v>
+        <v>1.140945977312507</v>
       </c>
       <c r="I23" t="n">
-        <v>1.242260309202247</v>
+        <v>1.478990325244258</v>
       </c>
     </row>
     <row r="24">
@@ -4922,22 +4749,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.462213044155926</v>
+        <v>2.462213044155925</v>
       </c>
       <c r="C24" t="n">
-        <v>-3.029359041989155</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.7823905265818625</v>
+        <v>-2.882424016827355</v>
       </c>
       <c r="F24" t="n">
-        <v>3.850892834143257</v>
+        <v>4.104964511077227</v>
       </c>
       <c r="G24" t="n">
-        <v>5.653595229701144</v>
+        <v>1.286087048609486</v>
       </c>
       <c r="I24" t="n">
-        <v>1.356666105303457</v>
+        <v>1.621926578193893</v>
       </c>
     </row>
     <row r="25">
@@ -4947,22 +4771,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.270530514216081</v>
+        <v>2.27053051421608</v>
       </c>
       <c r="C25" t="n">
-        <v>-3.186594320000552</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.5933702540022929</v>
+        <v>-3.035138366176343</v>
       </c>
       <c r="F25" t="n">
-        <v>3.959056387806478</v>
+        <v>4.213970368991138</v>
       </c>
       <c r="G25" t="n">
-        <v>5.800504462877983</v>
+        <v>1.414618876675234</v>
       </c>
       <c r="I25" t="n">
-        <v>1.447897979295639</v>
+        <v>1.752062051746878</v>
       </c>
     </row>
     <row r="26">
@@ -4972,22 +4793,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.405685916718264</v>
+        <v>2.405685916718263</v>
       </c>
       <c r="C26" t="n">
-        <v>-3.340041485153659</v>
+        <v>-3.174654387459375</v>
       </c>
       <c r="D26" t="n">
-        <v>0.446447120701431</v>
+        <v>0.02256090890168404</v>
       </c>
       <c r="F26" t="n">
-        <v>4.002342195810824</v>
+        <v>4.290910379170112</v>
       </c>
       <c r="G26" t="n">
-        <v>5.890755057109964</v>
+        <v>1.564862252769636</v>
       </c>
       <c r="I26" t="n">
-        <v>1.480939421428036</v>
+        <v>2.047559064633998</v>
       </c>
     </row>
     <row r="27">
@@ -4997,22 +4818,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.28469380273396</v>
+        <v>2.284693802733959</v>
       </c>
       <c r="C27" t="n">
-        <v>-3.510415573046029</v>
+        <v>-3.33046840153356</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3083911785298575</v>
+        <v>0.1319688966660108</v>
       </c>
       <c r="F27" t="n">
-        <v>4.205740497261568</v>
+        <v>4.461495184772032</v>
       </c>
       <c r="G27" t="n">
-        <v>6.220162691616759</v>
+        <v>1.863049225660926</v>
       </c>
       <c r="I27" t="n">
-        <v>1.558048449426323</v>
+        <v>2.211103132057595</v>
       </c>
     </row>
     <row r="28">
@@ -5022,31 +4843,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.473714075313529</v>
+        <v>2.473714075313528</v>
       </c>
       <c r="C28" t="n">
-        <v>-3.635234282160198</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.5082952475946081</v>
+        <v>-3.44087748901708</v>
       </c>
       <c r="F28" t="n">
-        <v>4.338406833089221</v>
+        <v>4.586340198926404</v>
       </c>
       <c r="G28" t="n">
-        <v>6.549579291945982</v>
+        <v>2.197975534459405</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3258084920561324</v>
+        <v>0.3258084920561323</v>
       </c>
       <c r="I28" t="n">
-        <v>1.666527130553105</v>
+        <v>2.093119823158314</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02127818383517276</v>
+        <v>0.006962507023841867</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2410006102968298</v>
+        <v>0.2722092158804773</v>
       </c>
     </row>
     <row r="29">
@@ -5056,34 +4874,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.611770017485103</v>
+        <v>2.611770017485102</v>
       </c>
       <c r="C29" t="n">
-        <v>-3.786329060132251</v>
+        <v>-3.582688045304586</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6292873615789125</v>
+        <v>0.2489412153748188</v>
       </c>
       <c r="E29" t="n">
         <v>0.08900190308630285</v>
       </c>
       <c r="F29" t="n">
-        <v>4.554382037271905</v>
+        <v>4.777366237592233</v>
       </c>
       <c r="G29" t="n">
-        <v>6.766630834062862</v>
+        <v>2.374519324399281</v>
       </c>
       <c r="H29" t="n">
-        <v>0.547761094813686</v>
+        <v>0.5477610948136857</v>
       </c>
       <c r="I29" t="n">
-        <v>1.70418930941084</v>
+        <v>2.194588033359594</v>
       </c>
       <c r="J29" t="n">
-        <v>0.239877982860346</v>
+        <v>0.1754109101812751</v>
       </c>
       <c r="K29" t="n">
-        <v>0.4274311919478511</v>
+        <v>0.8617027126092882</v>
       </c>
     </row>
     <row r="30">
@@ -5093,31 +4911,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.800790290064672</v>
+        <v>2.800790290064671</v>
       </c>
       <c r="C30" t="n">
-        <v>-3.934597028106822</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.8080085584443115</v>
+        <v>-3.717990063602933</v>
       </c>
       <c r="F30" t="n">
-        <v>4.808586540209422</v>
+        <v>5.009340700976484</v>
       </c>
       <c r="G30" t="n">
-        <v>6.98340898467927</v>
+        <v>2.515656157465922</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7139265171806392</v>
+        <v>0.7139265171806389</v>
       </c>
       <c r="I30" t="n">
-        <v>1.626161174903918</v>
+        <v>2.488577783439185</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4185975859799579</v>
+        <v>0.2919077508516073</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5185400295717899</v>
+        <v>1.054643189869627</v>
       </c>
     </row>
     <row r="31">
@@ -5127,31 +4942,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.979511486930071</v>
+        <v>2.97951148693007</v>
       </c>
       <c r="C31" t="n">
-        <v>-4.08731137745581</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.9918122139677632</v>
+        <v>-3.86406043686613</v>
       </c>
       <c r="F31" t="n">
-        <v>4.78670244172078</v>
+        <v>5.033486610801089</v>
       </c>
       <c r="G31" t="n">
-        <v>7.142459928828802</v>
+        <v>2.541416269944992</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7598485814000487</v>
+        <v>0.7598485814000485</v>
       </c>
       <c r="I31" t="n">
-        <v>1.512078887252206</v>
+        <v>2.569642870506543</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3227091723009224</v>
+        <v>0.1686630678039164</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4868417908022259</v>
+        <v>1.503389353877163</v>
       </c>
     </row>
     <row r="32">
@@ -5161,31 +4973,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.163315142453523</v>
+        <v>3.163315142453522</v>
       </c>
       <c r="C32" t="n">
-        <v>-4.220497437424743</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.8027919413881937</v>
+        <v>-3.986807021599517</v>
       </c>
       <c r="F32" t="n">
-        <v>5.045253804245342</v>
+        <v>5.287462061228067</v>
       </c>
       <c r="G32" t="n">
-        <v>7.401610492199221</v>
+        <v>2.866004525734604</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9265768827475233</v>
+        <v>0.9265768827475231</v>
       </c>
       <c r="I32" t="n">
-        <v>1.740286740763576</v>
+        <v>2.817770648826559</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3425902623922266</v>
+        <v>0.2439888547644551</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5573850380578923</v>
+        <v>1.571362056710527</v>
       </c>
     </row>
     <row r="33">
@@ -5195,31 +5004,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.344561498405563</v>
+        <v>3.344561498405562</v>
       </c>
       <c r="C33" t="n">
-        <v>-4.370979753781955</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.984038297340234</v>
+        <v>-4.130695637366756</v>
       </c>
       <c r="F33" t="n">
-        <v>5.279941748913467</v>
+        <v>5.512395913938676</v>
       </c>
       <c r="G33" t="n">
-        <v>7.784747747101182</v>
+        <v>3.007375904540016</v>
       </c>
       <c r="H33" t="n">
         <v>1.109190366896649</v>
       </c>
       <c r="I33" t="n">
-        <v>1.773497298971329</v>
+        <v>2.823787713029529</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3780419847674135</v>
+        <v>0.2676663374486561</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6379485841970658</v>
+        <v>1.951236565679067</v>
       </c>
     </row>
     <row r="34">
@@ -5229,31 +5035,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.163315142453523</v>
+        <v>3.163315142453522</v>
       </c>
       <c r="C34" t="n">
-        <v>-4.554783409305407</v>
+        <v>-4.314499292890208</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8684963279042718</v>
+        <v>0.2655692785660882</v>
       </c>
       <c r="F34" t="n">
-        <v>5.36930096482568</v>
+        <v>5.601755129850888</v>
       </c>
       <c r="G34" t="n">
-        <v>8.086158060957706</v>
+        <v>3.164591131304495</v>
       </c>
       <c r="H34" t="n">
         <v>1.097302199354737</v>
       </c>
       <c r="I34" t="n">
-        <v>2.088627515758621</v>
+        <v>2.86807031757077</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5370141374190511</v>
+        <v>0.425878930771633</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6867212023108379</v>
+        <v>2.252162457400719</v>
       </c>
     </row>
     <row r="35">
@@ -5263,34 +5069,34 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.329430653065481</v>
+        <v>3.32943065306548</v>
       </c>
       <c r="C35" t="n">
-        <v>-4.594856569532751</v>
+        <v>-4.423891542580615</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9521309876311457</v>
+        <v>0.4166950128854088</v>
       </c>
       <c r="E35" t="n">
         <v>0.2593107631490033</v>
       </c>
       <c r="F35" t="n">
-        <v>5.498841776610261</v>
+        <v>5.741795036816904</v>
       </c>
       <c r="G35" t="n">
-        <v>8.34481586281723</v>
+        <v>3.147166342989209</v>
       </c>
       <c r="H35" t="n">
         <v>1.12480665572458</v>
       </c>
       <c r="I35" t="n">
-        <v>2.199640774705342</v>
+        <v>3.016820799305065</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6239474753790706</v>
+        <v>0.5342111792775104</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6776881057845395</v>
+        <v>2.550152061880326</v>
       </c>
     </row>
     <row r="36">
@@ -5300,31 +5106,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.46687510527658</v>
+        <v>3.466875105276579</v>
       </c>
       <c r="C36" t="n">
-        <v>-4.712300613435692</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1.105865999198169</v>
+        <v>-4.536226076981429</v>
       </c>
       <c r="F36" t="n">
-        <v>5.59179900230055</v>
+        <v>5.852987966093234</v>
       </c>
       <c r="G36" t="n">
-        <v>8.425074914229198</v>
+        <v>3.217626706565044</v>
       </c>
       <c r="H36" t="n">
         <v>1.216652023073247</v>
       </c>
       <c r="I36" t="n">
-        <v>2.124209904656352</v>
+        <v>3.064671537183392</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7520729222367056</v>
+        <v>0.7229434505426544</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6351347098965732</v>
+        <v>2.837383627785102</v>
       </c>
     </row>
     <row r="37">
@@ -5334,34 +5137,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.555272287709372</v>
+        <v>3.555272287709371</v>
       </c>
       <c r="C37" t="n">
-        <v>-4.759239269254451</v>
+        <v>-4.576299237208773</v>
       </c>
       <c r="D37" t="n">
-        <v>1.173262525810983</v>
+        <v>0.5003243931371752</v>
       </c>
       <c r="E37" t="n">
         <v>0.3197976096213238</v>
       </c>
       <c r="F37" t="n">
-        <v>5.622765179164817</v>
+        <v>5.927011287112994</v>
       </c>
       <c r="G37" t="n">
-        <v>8.603121888018485</v>
+        <v>3.212504321715043</v>
       </c>
       <c r="H37" t="n">
         <v>1.17448986566169</v>
       </c>
       <c r="I37" t="n">
-        <v>2.199814011771364</v>
+        <v>3.151507125715718</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7358295576432821</v>
+        <v>0.6701066818336752</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4985564717445141</v>
+        <v>2.963673271916235</v>
       </c>
     </row>
     <row r="38">
@@ -5371,31 +5174,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.42164166675316</v>
+        <v>3.421641666753159</v>
       </c>
       <c r="C38" t="n">
-        <v>-4.87496678172602</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.033876115323549</v>
+        <v>-4.685289521122422</v>
       </c>
       <c r="F38" t="n">
-        <v>5.91144031375963</v>
+        <v>6.214873146566235</v>
       </c>
       <c r="G38" t="n">
-        <v>8.774410735527731</v>
+        <v>3.419505755422255</v>
       </c>
       <c r="H38" t="n">
-        <v>1.467700347257768</v>
+        <v>1.467700347257767</v>
       </c>
       <c r="I38" t="n">
-        <v>2.483210775144195</v>
+        <v>3.396408188852247</v>
       </c>
       <c r="J38" t="n">
-        <v>1.013195767722753</v>
+        <v>0.8570093132784251</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7024297698906588</v>
+        <v>3.506812643114889</v>
       </c>
     </row>
     <row r="39">
@@ -5405,31 +5205,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.280288580544563</v>
+        <v>3.280288580544562</v>
       </c>
       <c r="C39" t="n">
-        <v>-4.997649381992574</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.88228005185346</v>
+        <v>-4.802733565025362</v>
       </c>
       <c r="F39" t="n">
-        <v>6.153963785514223</v>
+        <v>6.472310154202082</v>
       </c>
       <c r="G39" t="n">
-        <v>8.838648886722403</v>
+        <v>3.51198099011423</v>
       </c>
       <c r="H39" t="n">
-        <v>1.589213405904494</v>
+        <v>1.589213405904493</v>
       </c>
       <c r="I39" t="n">
-        <v>2.695518207794937</v>
+        <v>3.39753028369674</v>
       </c>
       <c r="J39" t="n">
-        <v>1.103840594751394</v>
+        <v>0.8989476316399719</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6690349100538322</v>
+        <v>3.821561158039512</v>
       </c>
     </row>
     <row r="40">
@@ -5439,31 +5236,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3.140902170057129</v>
+        <v>3.140902170057128</v>
       </c>
       <c r="C40" t="n">
-        <v>-5.113376894464143</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1.027644945761695</v>
+        <v>-4.910068262710635</v>
       </c>
       <c r="F40" t="n">
-        <v>6.379795581326947</v>
+        <v>6.743162892766365</v>
       </c>
       <c r="G40" t="n">
-        <v>8.972021481742736</v>
+        <v>3.699037827010001</v>
       </c>
       <c r="H40" t="n">
-        <v>1.68803795924771</v>
+        <v>1.688037959247709</v>
       </c>
       <c r="I40" t="n">
-        <v>2.704363956002175</v>
+        <v>3.547843793758416</v>
       </c>
       <c r="J40" t="n">
-        <v>1.278532550049915</v>
+        <v>1.014803675635007</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5000826457901348</v>
+        <v>4.007233854176281</v>
       </c>
     </row>
     <row r="41">
@@ -5473,31 +5267,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.280288580544563</v>
+        <v>3.280288580544562</v>
       </c>
       <c r="C41" t="n">
-        <v>-5.229104406935712</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.8822800518534601</v>
+        <v>-5.019058546624284</v>
       </c>
       <c r="F41" t="n">
-        <v>6.49935359087486</v>
+        <v>6.925919643910507</v>
       </c>
       <c r="G41" t="n">
-        <v>9.245425509126562</v>
+        <v>3.772121877390367</v>
       </c>
       <c r="H41" t="n">
-        <v>1.979291151870732</v>
+        <v>1.979291151870731</v>
       </c>
       <c r="I41" t="n">
-        <v>2.839261616162553</v>
+        <v>3.663003224022551</v>
       </c>
       <c r="J41" t="n">
-        <v>1.362857937360955</v>
+        <v>1.11970843260879</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7116284572316077</v>
+        <v>4.259274656591104</v>
       </c>
     </row>
     <row r="42">
@@ -5507,31 +5298,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.146657959588351</v>
+        <v>3.14665795958835</v>
       </c>
       <c r="C42" t="n">
-        <v>-5.351787007202267</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1.042636797000915</v>
+        <v>-5.136502590527225</v>
       </c>
       <c r="F42" t="n">
-        <v>6.647178826346111</v>
+        <v>7.027931427253837</v>
       </c>
       <c r="G42" t="n">
-        <v>9.568502432203486</v>
+        <v>3.858236549321176</v>
       </c>
       <c r="H42" t="n">
-        <v>2.172814085451763</v>
+        <v>2.172814085451762</v>
       </c>
       <c r="I42" t="n">
-        <v>2.901503820571501</v>
+        <v>3.856327481960581</v>
       </c>
       <c r="J42" t="n">
-        <v>1.482666481061473</v>
+        <v>1.266016799726041</v>
       </c>
       <c r="K42" t="n">
-        <v>1.040650527695882</v>
+        <v>4.562378697132095</v>
       </c>
     </row>
     <row r="43">
@@ -5541,31 +5329,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.288011045796948</v>
+        <v>3.288011045796947</v>
       </c>
       <c r="C43" t="n">
-        <v>-5.481690817769933</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.9012837107923185</v>
+        <v>-5.264573338171315</v>
       </c>
       <c r="F43" t="n">
-        <v>6.799360244491525</v>
+        <v>7.166759266935157</v>
       </c>
       <c r="G43" t="n">
-        <v>9.66074685053486</v>
+        <v>3.819963395716567</v>
       </c>
       <c r="H43" t="n">
         <v>2.173185394089833</v>
       </c>
       <c r="I43" t="n">
-        <v>2.833889537639018</v>
+        <v>4.055941391218181</v>
       </c>
       <c r="J43" t="n">
-        <v>1.626311420852744</v>
+        <v>1.406624194806439</v>
       </c>
       <c r="K43" t="n">
-        <v>1.037340272715816</v>
+        <v>4.555899305476892</v>
       </c>
     </row>
     <row r="44">
@@ -5575,31 +5360,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3.429364132005545</v>
+        <v>3.429364132005544</v>
       </c>
       <c r="C44" t="n">
-        <v>-5.607947566304508</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1.044629255562567</v>
+        <v>-5.382017382074256</v>
       </c>
       <c r="F44" t="n">
-        <v>6.839924322770032</v>
+        <v>7.167360755270756</v>
       </c>
       <c r="G44" t="n">
-        <v>9.834983355668186</v>
+        <v>3.856851864977524</v>
       </c>
       <c r="H44" t="n">
         <v>2.180099324041598</v>
       </c>
       <c r="I44" t="n">
-        <v>2.886503298057553</v>
+        <v>4.113007183129305</v>
       </c>
       <c r="J44" t="n">
-        <v>1.728890577286432</v>
+        <v>1.543780512708077</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9364523059341752</v>
+        <v>4.89961286586255</v>
       </c>
     </row>
     <row r="45">
@@ -5609,34 +5391,34 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.355074463623717</v>
+        <v>3.355074463623716</v>
       </c>
       <c r="C45" t="n">
-        <v>-5.670784292348389</v>
+        <v>-5.438042129063048</v>
       </c>
       <c r="D45" t="n">
-        <v>0.871394508781525</v>
+        <v>0.4939792937502333</v>
       </c>
       <c r="E45" t="n">
         <v>0.4397205165701782</v>
       </c>
       <c r="F45" t="n">
-        <v>6.895096694238445</v>
+        <v>7.26291090920046</v>
       </c>
       <c r="G45" t="n">
-        <v>10.02553452463603</v>
+        <v>3.89203597870234</v>
       </c>
       <c r="H45" t="n">
-        <v>2.366757859227885</v>
+        <v>2.366757859227884</v>
       </c>
       <c r="I45" t="n">
-        <v>2.924601853115659</v>
+        <v>4.17544622655807</v>
       </c>
       <c r="J45" t="n">
-        <v>1.737513440767143</v>
+        <v>1.51693694097086</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8337208949768484</v>
+        <v>5.003424790411412</v>
       </c>
     </row>
     <row r="46">
@@ -5649,28 +5431,25 @@
         <v>3.215688053136283</v>
       </c>
       <c r="C46" t="n">
-        <v>-5.791705129012282</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.7280489640112763</v>
+        <v>-5.550376663463862</v>
       </c>
       <c r="F46" t="n">
-        <v>7.249285159659198</v>
+        <v>7.604946110735447</v>
       </c>
       <c r="G46" t="n">
-        <v>10.35364437838792</v>
+        <v>4.188974033732444</v>
       </c>
       <c r="H46" t="n">
-        <v>2.627455516451173</v>
+        <v>2.627455516451172</v>
       </c>
       <c r="I46" t="n">
-        <v>2.941935316321318</v>
+        <v>4.320794695069295</v>
       </c>
       <c r="J46" t="n">
-        <v>1.836433418862758</v>
+        <v>1.643597466630208</v>
       </c>
       <c r="K46" t="n">
-        <v>1.131403817084999</v>
+        <v>5.618426545909241</v>
       </c>
     </row>
     <row r="47">
@@ -5680,31 +5459,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.07630164264885</v>
+        <v>3.076301642648849</v>
       </c>
       <c r="C47" t="n">
-        <v>-5.907432641483851</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.5743139524442532</v>
+        <v>-5.656065890757647</v>
       </c>
       <c r="F47" t="n">
-        <v>7.417551987911816</v>
+        <v>7.743596859155883</v>
       </c>
       <c r="G47" t="n">
-        <v>10.4752130058389</v>
+        <v>4.127567623411572</v>
       </c>
       <c r="H47" t="n">
-        <v>2.575070676297251</v>
+        <v>2.57507067629725</v>
       </c>
       <c r="I47" t="n">
-        <v>2.975145874529072</v>
+        <v>4.499481912656557</v>
       </c>
       <c r="J47" t="n">
-        <v>2.089720003902727</v>
+        <v>1.969996023258636</v>
       </c>
       <c r="K47" t="n">
-        <v>1.020957719428126</v>
+        <v>5.844599021070974</v>
       </c>
     </row>
     <row r="48">
@@ -5714,31 +5490,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.932956097878601</v>
+        <v>2.9329560978786</v>
       </c>
       <c r="C48" t="n">
-        <v>-6.031893613530604</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.719678846352488</v>
+        <v>-5.771793403229216</v>
       </c>
       <c r="F48" t="n">
-        <v>7.832254397452876</v>
+        <v>8.177123335255615</v>
       </c>
       <c r="G48" t="n">
-        <v>10.63623824860016</v>
+        <v>4.385579638841818</v>
       </c>
       <c r="H48" t="n">
-        <v>2.827963343860461</v>
+        <v>2.82796334386046</v>
       </c>
       <c r="I48" t="n">
-        <v>3.054225171869349</v>
+        <v>4.608815186603365</v>
       </c>
       <c r="J48" t="n">
-        <v>2.213963958255809</v>
+        <v>2.124644937928592</v>
       </c>
       <c r="K48" t="n">
-        <v>1.252741981112367</v>
+        <v>6.12351815721787</v>
       </c>
     </row>
     <row r="49">
@@ -5748,31 +5521,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3.08455216134869</v>
+        <v>3.084552161348689</v>
       </c>
       <c r="C49" t="n">
-        <v>-6.061501367018217</v>
+        <v>-5.793336770680829</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8650437402607229</v>
+        <v>0.4924507060298745</v>
       </c>
       <c r="F49" t="n">
-        <v>8.173498361847358</v>
+        <v>8.51954347062474</v>
       </c>
       <c r="G49" t="n">
-        <v>10.8394091585537</v>
+        <v>4.511060961364882</v>
       </c>
       <c r="H49" t="n">
-        <v>3.166632907667498</v>
+        <v>3.166632907667497</v>
       </c>
       <c r="I49" t="n">
-        <v>3.217444555237968</v>
+        <v>4.677934730008561</v>
       </c>
       <c r="J49" t="n">
-        <v>2.440696344080606</v>
+        <v>2.34257323863691</v>
       </c>
       <c r="K49" t="n">
-        <v>1.406350185409153</v>
+        <v>6.433482552994016</v>
       </c>
     </row>
     <row r="50">
@@ -5782,31 +5555,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3.216873230148134</v>
+        <v>3.216873230148132</v>
       </c>
       <c r="C50" t="n">
-        <v>-6.167190594312002</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.7399655419421579</v>
+        <v>-5.894597726047516</v>
       </c>
       <c r="F50" t="n">
-        <v>8.451232466561631</v>
+        <v>8.837209016064586</v>
       </c>
       <c r="G50" t="n">
-        <v>11.07690646425618</v>
+        <v>4.655012914655831</v>
       </c>
       <c r="H50" t="n">
-        <v>3.46181854727139</v>
+        <v>3.461818547271389</v>
       </c>
       <c r="I50" t="n">
-        <v>3.41370045648359</v>
+        <v>4.801765238156011</v>
       </c>
       <c r="J50" t="n">
-        <v>2.633088293085822</v>
+        <v>2.522581054475309</v>
       </c>
       <c r="K50" t="n">
-        <v>1.530290223987593</v>
+        <v>6.863345098054801</v>
       </c>
     </row>
     <row r="51">
@@ -5816,31 +5586,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3.34021118874164</v>
+        <v>3.340211188741638</v>
       </c>
       <c r="C51" t="n">
-        <v>-6.272879821605787</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.8517898054993995</v>
+        <v>-5.992978441246534</v>
       </c>
       <c r="F51" t="n">
-        <v>8.468185318842078</v>
+        <v>8.809105850123348</v>
       </c>
       <c r="G51" t="n">
-        <v>11.2543924130297</v>
+        <v>4.69649974900908</v>
       </c>
       <c r="H51" t="n">
-        <v>3.133577313380366</v>
+        <v>3.133577313380365</v>
       </c>
       <c r="I51" t="n">
-        <v>3.428307834020206</v>
+        <v>5.020471140281799</v>
       </c>
       <c r="J51" t="n">
-        <v>2.725472562954658</v>
+        <v>2.587860883048522</v>
       </c>
       <c r="K51" t="n">
-        <v>1.393746721423145</v>
+        <v>7.09408404301376</v>
       </c>
     </row>
     <row r="52">
@@ -5850,34 +5617,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3.377857351362692</v>
+        <v>3.377857351362691</v>
       </c>
       <c r="C52" t="n">
-        <v>-6.300476925110613</v>
+        <v>-6.014521808698148</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6980547939323768</v>
+        <v>0.6100973049899387</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5663266324305073</v>
+        <v>0.5663266324305074</v>
       </c>
       <c r="F52" t="n">
-        <v>8.585999419105272</v>
+        <v>8.916789055647047</v>
       </c>
       <c r="G52" t="n">
-        <v>11.32785550169895</v>
+        <v>4.80135330140858</v>
       </c>
       <c r="H52" t="n">
-        <v>3.271469456977312</v>
+        <v>3.271469456977311</v>
       </c>
       <c r="I52" t="n">
-        <v>3.485130939502206</v>
+        <v>5.127894109386492</v>
       </c>
       <c r="J52" t="n">
-        <v>2.867898759907146</v>
+        <v>2.72499445714523</v>
       </c>
       <c r="K52" t="n">
-        <v>1.503528159358355</v>
+        <v>7.530789300999404</v>
       </c>
     </row>
     <row r="53">
@@ -5887,31 +5654,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3.488120920646686</v>
+        <v>3.488120920646685</v>
       </c>
       <c r="C53" t="n">
-        <v>-6.394632372254951</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.8098790574896184</v>
+        <v>-6.095226477679009</v>
       </c>
       <c r="F53" t="n">
-        <v>8.625922603907712</v>
+        <v>8.909818340840273</v>
       </c>
       <c r="G53" t="n">
-        <v>11.33001787742403</v>
+        <v>4.780259595074047</v>
       </c>
       <c r="H53" t="n">
-        <v>2.909101796374512</v>
+        <v>2.909101796374511</v>
       </c>
       <c r="I53" t="n">
-        <v>3.392068357614088</v>
+        <v>5.135912748414719</v>
       </c>
       <c r="J53" t="n">
-        <v>2.936706119804112</v>
+        <v>2.770891362215441</v>
       </c>
       <c r="K53" t="n">
-        <v>1.641123572140156</v>
+        <v>7.611664927256959</v>
       </c>
     </row>
     <row r="54">
@@ -5921,34 +5685,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3.529800190449301</v>
+        <v>3.627507331134119</v>
       </c>
       <c r="C54" t="n">
-        <v>-6.519093344301704</v>
+        <v>-6.21267052158195</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6561440459225955</v>
+        <v>0.625339426355554</v>
       </c>
       <c r="E54" t="n">
-        <v>0.6401621495772076</v>
+        <v>0.4545695945875649</v>
       </c>
       <c r="F54" t="n">
-        <v>8.726128117588573</v>
+        <v>9.013937015189809</v>
       </c>
       <c r="G54" t="n">
-        <v>11.57295905389461</v>
+        <v>4.964369106467283</v>
       </c>
       <c r="H54" t="n">
-        <v>3.218855773380798</v>
+        <v>3.218855773380797</v>
       </c>
       <c r="I54" t="n">
-        <v>3.520648897941212</v>
+        <v>5.111928749826623</v>
       </c>
       <c r="J54" t="n">
-        <v>3.241617763125459</v>
+        <v>3.002089427910021</v>
       </c>
       <c r="K54" t="n">
-        <v>1.796037938900453</v>
+        <v>7.959663909583245</v>
       </c>
     </row>
     <row r="55">
@@ -5958,31 +5722,28 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3.656645623738113</v>
+        <v>3.75435276442293</v>
       </c>
       <c r="C55" t="n">
-        <v>-6.627814689810611</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.5345204466555006</v>
+        <v>-6.319867336811879</v>
       </c>
       <c r="F55" t="n">
-        <v>8.966632519028151</v>
+        <v>9.183429607126593</v>
       </c>
       <c r="G55" t="n">
-        <v>11.70744269783694</v>
+        <v>5.22090190431307</v>
       </c>
       <c r="H55" t="n">
-        <v>3.469631760581893</v>
+        <v>3.469631760581892</v>
       </c>
       <c r="I55" t="n">
-        <v>3.571729842365091</v>
+        <v>5.376380325977077</v>
       </c>
       <c r="J55" t="n">
-        <v>3.481589259103129</v>
+        <v>3.202195980378418</v>
       </c>
       <c r="K55" t="n">
-        <v>1.871066263318689</v>
+        <v>8.512370778919827</v>
       </c>
     </row>
     <row r="56">
@@ -5992,31 +5753,28 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3.779983582331619</v>
+        <v>3.877690723016436</v>
       </c>
       <c r="C56" t="n">
-        <v>-6.733503917104397</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.4226961830982589</v>
+        <v>-6.419681415920902</v>
       </c>
       <c r="F56" t="n">
-        <v>9.152719641734459</v>
+        <v>9.369099215830518</v>
       </c>
       <c r="G56" t="n">
-        <v>12.00671734737108</v>
+        <v>5.331584705427098</v>
       </c>
       <c r="H56" t="n">
-        <v>3.50680225286474</v>
+        <v>3.506802252864739</v>
       </c>
       <c r="I56" t="n">
-        <v>3.557122464828475</v>
+        <v>5.441487191102046</v>
       </c>
       <c r="J56" t="n">
-        <v>3.534210652339746</v>
+        <v>3.248953869651234</v>
       </c>
       <c r="K56" t="n">
-        <v>1.938575387413932</v>
+        <v>8.788095251673141</v>
       </c>
     </row>
     <row r="57">
@@ -6026,31 +5784,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.893387815473785</v>
+        <v>3.991094956158602</v>
       </c>
       <c r="C57" t="n">
-        <v>-6.724315286330731</v>
+        <v>-6.405421758270153</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4318848138719251</v>
+        <v>0.7237292034561816</v>
       </c>
       <c r="F57" t="n">
-        <v>9.360144833271152</v>
+        <v>9.565355117076141</v>
       </c>
       <c r="G57" t="n">
-        <v>12.24223136692837</v>
+        <v>5.437897803889061</v>
       </c>
       <c r="H57" t="n">
-        <v>3.574618203921233</v>
+        <v>3.574618203921232</v>
       </c>
       <c r="I57" t="n">
-        <v>3.769243676949688</v>
+        <v>5.45711386384583</v>
       </c>
       <c r="J57" t="n">
-        <v>3.648954033601879</v>
+        <v>3.411347642419238</v>
       </c>
       <c r="K57" t="n">
-        <v>2.167807052009725</v>
+        <v>9.188225627953454</v>
       </c>
     </row>
     <row r="58">
@@ -6060,31 +5818,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3.800152727174686</v>
+        <v>3.897859867859503</v>
       </c>
       <c r="C58" t="n">
-        <v>-6.798785244353327</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0.3497091128272955</v>
+        <v>-6.477800965025922</v>
       </c>
       <c r="F58" t="n">
-        <v>9.479003936572552</v>
+        <v>9.687647593468242</v>
       </c>
       <c r="G58" t="n">
-        <v>12.47654511917482</v>
+        <v>5.44342719203146</v>
       </c>
       <c r="H58" t="n">
-        <v>3.554111722366665</v>
+        <v>3.554111722366664</v>
       </c>
       <c r="I58" t="n">
-        <v>3.999199884568489</v>
+        <v>5.424000344709579</v>
       </c>
       <c r="J58" t="n">
-        <v>3.830596082515814</v>
+        <v>3.57811442316418</v>
       </c>
       <c r="K58" t="n">
-        <v>2.183019365945833</v>
+        <v>9.165478241502921</v>
       </c>
     </row>
     <row r="59">
@@ -6094,31 +5849,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3.883486060508019</v>
+        <v>3.981193201192836</v>
       </c>
       <c r="C59" t="n">
-        <v>-6.872204362386128</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.4307425971440277</v>
+        <v>-6.548131219789267</v>
       </c>
       <c r="F59" t="n">
-        <v>9.557554498338828</v>
+        <v>9.752812349294167</v>
       </c>
       <c r="G59" t="n">
-        <v>12.5252826495972</v>
+        <v>5.341269677411585</v>
       </c>
       <c r="H59" t="n">
-        <v>3.348027129103912</v>
+        <v>3.348027129103911</v>
       </c>
       <c r="I59" t="n">
-        <v>3.996830134815749</v>
+        <v>5.389257486784414</v>
       </c>
       <c r="J59" t="n">
-        <v>3.786111852743204</v>
+        <v>3.514904578148465</v>
       </c>
       <c r="K59" t="n">
-        <v>2.503911067354091</v>
+        <v>9.37179272643141</v>
       </c>
     </row>
     <row r="60">
@@ -6128,34 +5880,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3.88265318513024</v>
+        <v>4.064526534526169</v>
       </c>
       <c r="C60" t="n">
-        <v>-6.857944704735379</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.4265757742185715</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.6156986121151199</v>
+        <v>-6.621550337822068</v>
       </c>
       <c r="F60" t="n">
-        <v>9.452744927788507</v>
+        <v>9.662025267855759</v>
       </c>
       <c r="G60" t="n">
-        <v>12.68597948685333</v>
+        <v>5.173236528247927</v>
       </c>
       <c r="H60" t="n">
-        <v>3.209354846377136</v>
+        <v>3.209354846377135</v>
       </c>
       <c r="I60" t="n">
-        <v>4.008066327606278</v>
+        <v>5.482666051507947</v>
       </c>
       <c r="J60" t="n">
-        <v>3.881679823675498</v>
+        <v>3.641966304408245</v>
       </c>
       <c r="K60" t="n">
-        <v>2.519830275432545</v>
+        <v>9.743757999687636</v>
       </c>
     </row>
     <row r="61">
@@ -6165,31 +5911,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3.796955668326555</v>
+        <v>3.978829017722484</v>
       </c>
       <c r="C61" t="n">
-        <v>-6.929294446696531</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.5076092585353037</v>
+        <v>-6.690870626357613</v>
       </c>
       <c r="F61" t="n">
-        <v>9.633334743798022</v>
+        <v>9.815635614195573</v>
       </c>
       <c r="G61" t="n">
-        <v>12.72023947381775</v>
+        <v>5.450823267417868</v>
       </c>
       <c r="H61" t="n">
         <v>3.319316514629362</v>
       </c>
       <c r="I61" t="n">
-        <v>4.035036506786289</v>
+        <v>5.551971905949045</v>
       </c>
       <c r="J61" t="n">
-        <v>3.930146606243413</v>
+        <v>3.68172831652282</v>
       </c>
       <c r="K61" t="n">
-        <v>2.237413094068116</v>
+        <v>10.13991733630367</v>
       </c>
     </row>
     <row r="62">
@@ -6199,31 +5942,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3.876861716444464</v>
+        <v>4.058735065840393</v>
       </c>
       <c r="C62" t="n">
-        <v>-6.998614735232076</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0.4277032104173947</v>
+        <v>-6.756237498541546</v>
       </c>
       <c r="F62" t="n">
-        <v>9.735443130225626</v>
+        <v>9.921880680741271</v>
       </c>
       <c r="G62" t="n">
-        <v>13.17827868950403</v>
+        <v>5.693396476357575</v>
       </c>
       <c r="H62" t="n">
-        <v>3.650032189696584</v>
+        <v>3.650032189696583</v>
       </c>
       <c r="I62" t="n">
-        <v>3.989965226839729</v>
+        <v>5.529883518238598</v>
       </c>
       <c r="J62" t="n">
-        <v>3.887620087210927</v>
+        <v>3.657265745309827</v>
       </c>
       <c r="K62" t="n">
-        <v>2.453362964392058</v>
+        <v>10.61403222450962</v>
       </c>
     </row>
     <row r="63">
@@ -6233,34 +5973,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3.876028841066685</v>
+        <v>4.057902190462614</v>
       </c>
       <c r="C63" t="n">
-        <v>-6.968550399890843</v>
+        <v>-6.720594001988809</v>
       </c>
       <c r="D63" t="n">
-        <v>0.3174396411334005</v>
+        <v>0.8484591860888057</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7097339488646078</v>
+        <v>0.5486049313370529</v>
       </c>
       <c r="F63" t="n">
-        <v>9.989647633163143</v>
+        <v>10.13566323288171</v>
       </c>
       <c r="G63" t="n">
-        <v>13.42430682964477</v>
+        <v>5.822705619267435</v>
       </c>
       <c r="H63" t="n">
         <v>4.021829991601075</v>
       </c>
       <c r="I63" t="n">
-        <v>4.050061457855855</v>
+        <v>5.576752005676056</v>
       </c>
       <c r="J63" t="n">
-        <v>4.047909633233689</v>
+        <v>3.814366493859801</v>
       </c>
       <c r="K63" t="n">
-        <v>2.445134974872862</v>
+        <v>11.04092116271069</v>
       </c>
     </row>
     <row r="64">
@@ -6270,34 +6010,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3.765765271782691</v>
+        <v>4.06709082123628</v>
       </c>
       <c r="C64" t="n">
-        <v>-7.075747215120772</v>
+        <v>-6.823315994014548</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3182725165111793</v>
+        <v>0.9319780577600265</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7497328245143418</v>
+        <v>0.6211667672231235</v>
       </c>
       <c r="F64" t="n">
-        <v>10.1155111364463</v>
+        <v>10.21638770898797</v>
       </c>
       <c r="G64" t="n">
-        <v>13.57106045709714</v>
+        <v>5.712568436719884</v>
       </c>
       <c r="H64" t="n">
         <v>4.20123679648947</v>
       </c>
       <c r="I64" t="n">
-        <v>4.11261158038563</v>
+        <v>5.666732055463843</v>
       </c>
       <c r="J64" t="n">
-        <v>4.028964839532029</v>
+        <v>3.808246537946732</v>
       </c>
       <c r="K64" t="n">
-        <v>2.623732818751189</v>
+        <v>11.2301873857957</v>
       </c>
     </row>
     <row r="65">
@@ -6307,31 +6047,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3.8456713199006</v>
+        <v>4.146996869354189</v>
       </c>
       <c r="C65" t="n">
-        <v>-7.150217173143369</v>
-      </c>
-      <c r="D65" t="n">
-        <v>0.4027795587647005</v>
+        <v>-6.893646248777894</v>
       </c>
       <c r="F65" t="n">
-        <v>10.2553557937158</v>
+        <v>10.33175355537963</v>
       </c>
       <c r="G65" t="n">
-        <v>13.81645819800827</v>
+        <v>5.757861074242356</v>
       </c>
       <c r="H65" t="n">
         <v>4.368118319439296</v>
       </c>
       <c r="I65" t="n">
-        <v>4.076558664200087</v>
+        <v>5.855840471225909</v>
       </c>
       <c r="J65" t="n">
-        <v>4.125932724848378</v>
+        <v>3.934232297205972</v>
       </c>
       <c r="K65" t="n">
-        <v>2.493862087871455</v>
+        <v>11.70358250343422</v>
       </c>
     </row>
     <row r="66">
@@ -6341,34 +6078,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3.967294919167695</v>
+        <v>4.268620468621284</v>
       </c>
       <c r="C66" t="n">
-        <v>-7.248597888342387</v>
+        <v>-6.986416197830842</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3986127358392442</v>
+        <v>1.008895713256884</v>
       </c>
       <c r="E66" t="n">
-        <v>0.82273230901533</v>
+        <v>0.6941662517241116</v>
       </c>
       <c r="F66" t="n">
-        <v>10.50061433631542</v>
+        <v>10.52123350429352</v>
       </c>
       <c r="G66" t="n">
-        <v>14.00616064011411</v>
+        <v>5.954533540921857</v>
       </c>
       <c r="H66" t="n">
         <v>4.646574193629572</v>
       </c>
       <c r="I66" t="n">
-        <v>4.247170792183772</v>
+        <v>6.081216219329236</v>
       </c>
       <c r="J66" t="n">
-        <v>4.233586942607454</v>
+        <v>4.030998984790421</v>
       </c>
       <c r="K66" t="n">
-        <v>2.62852039386955</v>
+        <v>12.02658171551319</v>
       </c>
     </row>
     <row r="67">
@@ -6378,31 +6115,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4.051801961421216</v>
+        <v>4.353127510874805</v>
       </c>
       <c r="C67" t="n">
-        <v>-7.320977095098156</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0.4843102526429293</v>
+        <v>-7.057765939791993</v>
       </c>
       <c r="F67" t="n">
-        <v>10.74702005111785</v>
+        <v>10.81059634669152</v>
       </c>
       <c r="G67" t="n">
-        <v>14.3207761812564</v>
+        <v>6.072412262747791</v>
       </c>
       <c r="H67" t="n">
         <v>4.865339720756644</v>
       </c>
       <c r="I67" t="n">
-        <v>4.39255091965604</v>
+        <v>6.194655924331397</v>
       </c>
       <c r="J67" t="n">
-        <v>4.427085639261856</v>
+        <v>4.271916721855631</v>
       </c>
       <c r="K67" t="n">
-        <v>2.684963471711804</v>
+        <v>12.46926287929488</v>
       </c>
     </row>
     <row r="68">
@@ -6412,31 +6146,28 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4.133977662465846</v>
+        <v>4.435303211919435</v>
       </c>
       <c r="C68" t="n">
-        <v>-7.390297383633701</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0.5609166792724162</v>
+        <v>-7.126085337655761</v>
       </c>
       <c r="F68" t="n">
-        <v>10.9861023022304</v>
+        <v>11.03637420025918</v>
       </c>
       <c r="G68" t="n">
-        <v>14.578734950597</v>
+        <v>6.057011055509336</v>
       </c>
       <c r="H68" t="n">
         <v>4.864799526711744</v>
       </c>
       <c r="I68" t="n">
-        <v>4.402951939005887</v>
+        <v>6.323173789937177</v>
       </c>
       <c r="J68" t="n">
-        <v>4.52046090465934</v>
+        <v>4.327496924091327</v>
       </c>
       <c r="K68" t="n">
-        <v>2.717623461438967</v>
+        <v>12.8415766644795</v>
       </c>
     </row>
     <row r="69">
@@ -6446,34 +6177,34 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4.133144787088067</v>
+        <v>4.434470336541656</v>
       </c>
       <c r="C69" t="n">
-        <v>-7.377735256848944</v>
+        <v>-7.106676987877147</v>
       </c>
       <c r="D69" t="n">
-        <v>0.5634157943258497</v>
+        <v>1.129328961133352</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8981744556470782</v>
+        <v>0.7696083983558598</v>
       </c>
       <c r="F69" t="n">
-        <v>11.20483103258609</v>
+        <v>11.25716201288341</v>
       </c>
       <c r="G69" t="n">
-        <v>14.87965454156519</v>
+        <v>6.373683787838428</v>
       </c>
       <c r="H69" t="n">
         <v>5.171679367733256</v>
       </c>
       <c r="I69" t="n">
-        <v>4.478105468273852</v>
+        <v>6.57143299303473</v>
       </c>
       <c r="J69" t="n">
-        <v>4.58521261431201</v>
+        <v>4.424206843125405</v>
       </c>
       <c r="K69" t="n">
-        <v>2.947067695036624</v>
+        <v>13.33035287758443</v>
       </c>
     </row>
     <row r="70">
@@ -6483,22 +6214,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>11.32540144081315</v>
+        <v>11.37838729632955</v>
       </c>
       <c r="G70" t="n">
-        <v>15.12479510677955</v>
+        <v>6.445625532652019</v>
       </c>
       <c r="H70" t="n">
         <v>5.407995338079827</v>
       </c>
       <c r="I70" t="n">
-        <v>4.524396473262479</v>
+        <v>6.733598123678707</v>
       </c>
       <c r="J70" t="n">
-        <v>4.868692093902848</v>
+        <v>4.76000749866506</v>
       </c>
       <c r="K70" t="n">
-        <v>3.19866432035426</v>
+        <v>13.6235871930765</v>
       </c>
     </row>
     <row r="71">
@@ -6508,34 +6239,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4.220050263021954</v>
+        <v>4.521375812475543</v>
       </c>
       <c r="C71" t="n">
-        <v>-7.283170230788504</v>
+        <v>-7.177007242640492</v>
       </c>
       <c r="D71" t="n">
-        <v>0.6433218424437587</v>
+        <v>1.210073633282762</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9666560943254154</v>
+        <v>0.8245334240498935</v>
       </c>
       <c r="F71" t="n">
-        <v>11.48329951844848</v>
+        <v>11.59248383655881</v>
       </c>
       <c r="G71" t="n">
-        <v>15.51182241253968</v>
+        <v>6.58421885148456</v>
       </c>
       <c r="H71" t="n">
         <v>5.763692327828713</v>
       </c>
       <c r="I71" t="n">
-        <v>4.551418642579716</v>
+        <v>6.87543515480096</v>
       </c>
       <c r="J71" t="n">
-        <v>4.96319027298512</v>
+        <v>4.907576037145295</v>
       </c>
       <c r="K71" t="n">
-        <v>3.536425989476101</v>
+        <v>13.83927847480053</v>
       </c>
     </row>
     <row r="72">
@@ -6545,22 +6276,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>11.8176865615788</v>
+        <v>11.92898830144781</v>
       </c>
       <c r="G72" t="n">
-        <v>15.50359679561841</v>
+        <v>6.688881926165084</v>
       </c>
       <c r="H72" t="n">
         <v>5.910779581254142</v>
       </c>
       <c r="I72" t="n">
-        <v>4.548072804008076</v>
+        <v>6.896794770174609</v>
       </c>
       <c r="J72" t="n">
-        <v>5.150112546327681</v>
+        <v>5.094737197092554</v>
       </c>
       <c r="K72" t="n">
-        <v>3.538665527716366</v>
+        <v>14.05766172020931</v>
       </c>
     </row>
     <row r="73">
@@ -6570,22 +6301,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>12.00166055974267</v>
+        <v>12.05877352777637</v>
       </c>
       <c r="G73" t="n">
-        <v>15.68918202735446</v>
+        <v>6.953936070335884</v>
       </c>
       <c r="H73" t="n">
         <v>6.020936645627851</v>
       </c>
       <c r="I73" t="n">
-        <v>4.647363491858319</v>
+        <v>7.003501534337756</v>
       </c>
       <c r="J73" t="n">
-        <v>5.240684404320046</v>
+        <v>5.242003908805852</v>
       </c>
       <c r="K73" t="n">
-        <v>3.579966620806253</v>
+        <v>14.36136681622852</v>
       </c>
     </row>
     <row r="74">
@@ -6595,22 +6326,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>12.21593672751995</v>
+        <v>12.2870594206236</v>
       </c>
       <c r="G74" t="n">
-        <v>16.05938565792426</v>
+        <v>7.096271795546745</v>
       </c>
       <c r="H74" t="n">
         <v>6.294922086681675</v>
       </c>
       <c r="I74" t="n">
-        <v>4.792785669427021</v>
+        <v>7.063120253546161</v>
       </c>
       <c r="J74" t="n">
-        <v>5.476302532383832</v>
+        <v>5.525472572637502</v>
       </c>
       <c r="K74" t="n">
-        <v>3.87720501100467</v>
+        <v>14.72513841676037</v>
       </c>
     </row>
     <row r="75">
@@ -6620,22 +6351,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>12.33342289969488</v>
+        <v>12.37612557815891</v>
       </c>
       <c r="G75" t="n">
-        <v>16.30380835851135</v>
+        <v>7.254257620289528</v>
       </c>
       <c r="H75" t="n">
         <v>6.535075185265566</v>
       </c>
       <c r="I75" t="n">
-        <v>4.825988283302543</v>
+        <v>7.155657609341798</v>
       </c>
       <c r="J75" t="n">
-        <v>5.630874034379876</v>
+        <v>5.61269133281695</v>
       </c>
       <c r="K75" t="n">
-        <v>4.10936953113965</v>
+        <v>15.20079832155253</v>
       </c>
     </row>
     <row r="76">
@@ -6645,34 +6376,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4.304557305275475</v>
+        <v>4.605882854729064</v>
       </c>
       <c r="C76" t="n">
-        <v>-7.187251705616619</v>
+        <v>-7.081088717468607</v>
       </c>
       <c r="D76" t="n">
-        <v>0.7314535131620408</v>
+        <v>1.280823047155339</v>
       </c>
       <c r="E76" t="n">
-        <v>1.053276933573546</v>
+        <v>0.9111542632980237</v>
       </c>
       <c r="F76" t="n">
-        <v>12.36776410006506</v>
+        <v>12.41046677852909</v>
       </c>
       <c r="G76" t="n">
-        <v>16.56252377410879</v>
+        <v>7.35989573197388</v>
       </c>
       <c r="H76" t="n">
         <v>6.510032387586433</v>
       </c>
       <c r="I76" t="n">
-        <v>4.925378707190565</v>
+        <v>7.187530528290539</v>
       </c>
       <c r="J76" t="n">
-        <v>5.816717284733697</v>
+        <v>5.79853458317077</v>
       </c>
       <c r="K76" t="n">
-        <v>4.238024847889485</v>
+        <v>15.51732032653185</v>
       </c>
     </row>
     <row r="77">
@@ -6682,22 +6413,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>12.58167132883727</v>
+        <v>12.62354479243463</v>
       </c>
       <c r="G77" t="n">
-        <v>16.92152834329996</v>
+        <v>7.521491687867466</v>
       </c>
       <c r="H77" t="n">
         <v>6.752091251772218</v>
       </c>
       <c r="I77" t="n">
-        <v>5.061421487494613</v>
+        <v>7.188058670684741</v>
       </c>
       <c r="J77" t="n">
-        <v>5.72957226646923</v>
+        <v>5.740801413471389</v>
       </c>
       <c r="K77" t="n">
-        <v>4.253873056509197</v>
+        <v>15.86821098844601</v>
       </c>
     </row>
     <row r="78">
@@ -6707,22 +6438,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>12.57572551700718</v>
+        <v>12.69133448423083</v>
       </c>
       <c r="G78" t="n">
-        <v>17.16633477197979</v>
+        <v>7.541425495641394</v>
       </c>
       <c r="H78" t="n">
         <v>6.637346775527959</v>
       </c>
       <c r="I78" t="n">
-        <v>5.064598808645456</v>
+        <v>7.257202679454005</v>
       </c>
       <c r="J78" t="n">
-        <v>5.883230820720575</v>
+        <v>5.854172244233401</v>
       </c>
       <c r="K78" t="n">
-        <v>4.401709790001259</v>
+        <v>16.08991789937048</v>
       </c>
     </row>
     <row r="79">
@@ -6732,22 +6463,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>12.79598525654706</v>
+        <v>12.92490991515819</v>
       </c>
       <c r="G79" t="n">
-        <v>17.35603721408563</v>
+        <v>7.762913237624261</v>
       </c>
       <c r="H79" t="n">
         <v>6.889679305524393</v>
       </c>
       <c r="I79" t="n">
-        <v>5.196271205067403</v>
+        <v>7.382326696657364</v>
       </c>
       <c r="J79" t="n">
-        <v>6.091585529244993</v>
+        <v>6.081633041753977</v>
       </c>
       <c r="K79" t="n">
-        <v>4.611111331452674</v>
+        <v>16.5029265937776</v>
       </c>
     </row>
     <row r="80">
@@ -6757,22 +6488,22 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>13.02135972447467</v>
+        <v>13.17653962435113</v>
       </c>
       <c r="G80" t="n">
-        <v>17.60117777929999</v>
+        <v>7.881959081873222</v>
       </c>
       <c r="H80" t="n">
         <v>7.210513700529605</v>
       </c>
       <c r="I80" t="n">
-        <v>5.230801470350315</v>
+        <v>7.531353123385076</v>
       </c>
       <c r="J80" t="n">
-        <v>6.263557981011608</v>
+        <v>6.292756604298047</v>
       </c>
       <c r="K80" t="n">
-        <v>4.96124849250887</v>
+        <v>17.12186865553933</v>
       </c>
     </row>
     <row r="81">
@@ -6782,34 +6513,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4.384463353393384</v>
+        <v>4.685788902846973</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.267157753734528</v>
+        <v>-7.158781814355158</v>
       </c>
       <c r="D81" t="n">
-        <v>0.8136292142066703</v>
+        <v>1.362561262431912</v>
       </c>
       <c r="E81" t="n">
-        <v>1.151233145635714</v>
+        <v>1.009110475360192</v>
       </c>
       <c r="F81" t="n">
-        <v>13.25508521467075</v>
+        <v>13.41205364390842</v>
       </c>
       <c r="G81" t="n">
-        <v>17.76121703333897</v>
+        <v>7.884245501812508</v>
       </c>
       <c r="H81" t="n">
         <v>7.137090013122871</v>
       </c>
       <c r="I81" t="n">
-        <v>5.322868115880694</v>
+        <v>7.69775954609377</v>
       </c>
       <c r="J81" t="n">
-        <v>6.372822275999876</v>
+        <v>6.460705093687737</v>
       </c>
       <c r="K81" t="n">
-        <v>5.148037529644254</v>
+        <v>17.53990802725951</v>
       </c>
     </row>
     <row r="82">
@@ -6819,22 +6550,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>13.36909115529383</v>
+        <v>13.56795631676657</v>
       </c>
       <c r="G82" t="n">
-        <v>17.89603970997845</v>
+        <v>8.05327150805153</v>
       </c>
       <c r="H82" t="n">
-        <v>7.302353422339712</v>
+        <v>7.302353422339711</v>
       </c>
       <c r="I82" t="n">
-        <v>5.446860488955131</v>
+        <v>7.758582105294931</v>
       </c>
       <c r="J82" t="n">
-        <v>6.572982320068097</v>
+        <v>6.6729830767648</v>
       </c>
       <c r="K82" t="n">
-        <v>5.418911767175433</v>
+        <v>17.65985015309325</v>
       </c>
     </row>
     <row r="83">
@@ -6844,22 +6575,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>13.54269134287924</v>
+        <v>13.72745700322744</v>
       </c>
       <c r="G83" t="n">
-        <v>18.10015342198409</v>
+        <v>8.118988559492053</v>
       </c>
       <c r="H83" t="n">
-        <v>7.320739179956525</v>
+        <v>7.320739179956524</v>
       </c>
       <c r="I83" t="n">
-        <v>5.614910768212689</v>
+        <v>7.968959505232757</v>
       </c>
       <c r="J83" t="n">
-        <v>6.734843180662151</v>
+        <v>6.852382628350147</v>
       </c>
       <c r="K83" t="n">
-        <v>5.411815600529855</v>
+        <v>18.08007418772788</v>
       </c>
     </row>
     <row r="84">
@@ -6869,22 +6600,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>13.52480601083049</v>
+        <v>13.7095716711787</v>
       </c>
       <c r="G84" t="n">
-        <v>18.14987934592102</v>
+        <v>8.088504035469031</v>
       </c>
       <c r="H84" t="n">
-        <v>7.110135601393592</v>
+        <v>7.110135601393591</v>
       </c>
       <c r="I84" t="n">
-        <v>5.535735304355676</v>
+        <v>8.030496338610362</v>
       </c>
       <c r="J84" t="n">
-        <v>6.850928365299492</v>
+        <v>6.957891323324007</v>
       </c>
       <c r="K84" t="n">
-        <v>5.499661478109523</v>
+        <v>18.26125680809047</v>
       </c>
     </row>
     <row r="85">
@@ -6893,35 +6624,23 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>4.470160870197069</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-7.344850850621079</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0.7242523275149148</v>
-      </c>
-      <c r="E85" t="n">
-        <v>1.220200529099721</v>
-      </c>
       <c r="F85" t="n">
-        <v>13.76872372879246</v>
+        <v>13.93943592108616</v>
       </c>
       <c r="G85" t="n">
-        <v>18.22829546483783</v>
+        <v>8.326813842458193</v>
       </c>
       <c r="H85" t="n">
-        <v>7.455143425513562</v>
+        <v>7.455143425513561</v>
       </c>
       <c r="I85" t="n">
-        <v>5.505462044204545</v>
+        <v>8.179946077386024</v>
       </c>
       <c r="J85" t="n">
-        <v>7.049003470931835</v>
+        <v>7.149302344233706</v>
       </c>
       <c r="K85" t="n">
-        <v>5.431149735020553</v>
+        <v>18.61608793711853</v>
       </c>
     </row>
     <row r="86">
@@ -6931,22 +6650,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>14.0844828613811</v>
+        <v>14.29880407788459</v>
       </c>
       <c r="G86" t="n">
-        <v>18.41698212880239</v>
+        <v>8.405880848238937</v>
       </c>
       <c r="H86" t="n">
-        <v>7.760608595167917</v>
+        <v>7.760608595167916</v>
       </c>
       <c r="I86" t="n">
-        <v>5.682947992978067</v>
+        <v>8.251179016731596</v>
       </c>
       <c r="J86" t="n">
-        <v>7.161349807365459</v>
+        <v>7.260044097427393</v>
       </c>
       <c r="K86" t="n">
-        <v>5.405805838346918</v>
+        <v>18.75997348260173</v>
       </c>
     </row>
     <row r="87">
@@ -6956,22 +6675,47 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>14.27227791857306</v>
+        <v>14.48659913507655</v>
       </c>
       <c r="G87" t="n">
-        <v>18.59232459455582</v>
+        <v>8.470031795235895</v>
       </c>
       <c r="H87" t="n">
         <v>8.093297023866191</v>
       </c>
       <c r="I87" t="n">
-        <v>5.888011561176183</v>
+        <v>8.336672970357871</v>
       </c>
       <c r="J87" t="n">
-        <v>7.232544157602599</v>
+        <v>7.331780393293664</v>
       </c>
       <c r="K87" t="n">
-        <v>5.442064457963623</v>
+        <v>19.06925656519476</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>14.59744774790497</v>
+      </c>
+      <c r="G88" t="n">
+        <v>8.451831089802099</v>
+      </c>
+      <c r="H88" t="n">
+        <v>8.268811296974595</v>
+      </c>
+      <c r="I88" t="n">
+        <v>8.383009359969085</v>
+      </c>
+      <c r="J88" t="n">
+        <v>7.412191597809185</v>
+      </c>
+      <c r="K88" t="n">
+        <v>19.44882155303366</v>
       </c>
     </row>
   </sheetData>
